--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="182">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -419,6 +419,9 @@
   </si>
   <si>
     <t>['39', '86']</t>
+  </si>
+  <si>
+    <t>['58', '64', '70']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -918,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP93"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1174,7 +1177,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1380,7 +1383,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1998,7 +2001,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2204,7 +2207,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2282,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ7">
         <v>1.6</v>
@@ -2410,7 +2413,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2822,7 +2825,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3028,7 +3031,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3440,7 +3443,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3646,7 +3649,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3727,7 +3730,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3852,7 +3855,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4058,7 +4061,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4882,7 +4885,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5088,7 +5091,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5166,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ21">
         <v>1.8</v>
@@ -5706,7 +5709,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5912,7 +5915,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6942,7 +6945,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7148,7 +7151,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7972,7 +7975,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8384,7 +8387,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8465,7 +8468,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ37">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR37">
         <v>2.48</v>
@@ -9002,7 +9005,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9208,7 +9211,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9620,7 +9623,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10032,7 +10035,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10444,7 +10447,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10525,7 +10528,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ47">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR47">
         <v>1.24</v>
@@ -10856,7 +10859,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11140,7 +11143,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11268,7 +11271,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11474,7 +11477,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11680,7 +11683,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12504,7 +12507,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12916,7 +12919,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13328,7 +13331,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14358,7 +14361,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14770,7 +14773,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15260,7 +15263,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ70">
         <v>1.75</v>
@@ -15594,7 +15597,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16006,7 +16009,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16212,7 +16215,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16418,7 +16421,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16830,7 +16833,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17036,7 +17039,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17242,7 +17245,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17735,7 +17738,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR82">
         <v>1.26</v>
@@ -18272,7 +18275,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18478,7 +18481,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18684,7 +18687,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19096,7 +19099,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19302,7 +19305,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19508,7 +19511,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19714,7 +19717,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19920,7 +19923,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20077,6 +20080,212 @@
       </c>
       <c r="BP93">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7729626</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45688.58333333334</v>
+      </c>
+      <c r="F94">
+        <v>11</v>
+      </c>
+      <c r="G94" t="s">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s">
+        <v>76</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>3</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>3</v>
+      </c>
+      <c r="O94" t="s">
+        <v>135</v>
+      </c>
+      <c r="P94" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q94">
+        <v>2.88</v>
+      </c>
+      <c r="R94">
+        <v>2.1</v>
+      </c>
+      <c r="S94">
+        <v>3.6</v>
+      </c>
+      <c r="T94">
+        <v>1.44</v>
+      </c>
+      <c r="U94">
+        <v>2.55</v>
+      </c>
+      <c r="V94">
+        <v>3</v>
+      </c>
+      <c r="W94">
+        <v>1.34</v>
+      </c>
+      <c r="X94">
+        <v>8</v>
+      </c>
+      <c r="Y94">
+        <v>1.07</v>
+      </c>
+      <c r="Z94">
+        <v>2.19</v>
+      </c>
+      <c r="AA94">
+        <v>3.32</v>
+      </c>
+      <c r="AB94">
+        <v>3.09</v>
+      </c>
+      <c r="AC94">
+        <v>1.06</v>
+      </c>
+      <c r="AD94">
+        <v>8.5</v>
+      </c>
+      <c r="AE94">
+        <v>1.33</v>
+      </c>
+      <c r="AF94">
+        <v>3.25</v>
+      </c>
+      <c r="AG94">
+        <v>1.95</v>
+      </c>
+      <c r="AH94">
+        <v>1.77</v>
+      </c>
+      <c r="AI94">
+        <v>1.8</v>
+      </c>
+      <c r="AJ94">
+        <v>1.91</v>
+      </c>
+      <c r="AK94">
+        <v>1.35</v>
+      </c>
+      <c r="AL94">
+        <v>1.34</v>
+      </c>
+      <c r="AM94">
+        <v>1.57</v>
+      </c>
+      <c r="AN94">
+        <v>2.5</v>
+      </c>
+      <c r="AO94">
+        <v>1.75</v>
+      </c>
+      <c r="AP94">
+        <v>2.6</v>
+      </c>
+      <c r="AQ94">
+        <v>1.4</v>
+      </c>
+      <c r="AR94">
+        <v>1.88</v>
+      </c>
+      <c r="AS94">
+        <v>1.51</v>
+      </c>
+      <c r="AT94">
+        <v>3.39</v>
+      </c>
+      <c r="AU94">
+        <v>5</v>
+      </c>
+      <c r="AV94">
+        <v>4</v>
+      </c>
+      <c r="AW94">
+        <v>4</v>
+      </c>
+      <c r="AX94">
+        <v>2</v>
+      </c>
+      <c r="AY94">
+        <v>9</v>
+      </c>
+      <c r="AZ94">
+        <v>6</v>
+      </c>
+      <c r="BA94">
+        <v>2</v>
+      </c>
+      <c r="BB94">
+        <v>6</v>
+      </c>
+      <c r="BC94">
+        <v>8</v>
+      </c>
+      <c r="BD94">
+        <v>1.67</v>
+      </c>
+      <c r="BE94">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF94">
+        <v>2.52</v>
+      </c>
+      <c r="BG94">
+        <v>1.25</v>
+      </c>
+      <c r="BH94">
+        <v>3.28</v>
+      </c>
+      <c r="BI94">
+        <v>1.54</v>
+      </c>
+      <c r="BJ94">
+        <v>2.41</v>
+      </c>
+      <c r="BK94">
+        <v>2.38</v>
+      </c>
+      <c r="BL94">
+        <v>1.88</v>
+      </c>
+      <c r="BM94">
+        <v>2.43</v>
+      </c>
+      <c r="BN94">
+        <v>1.54</v>
+      </c>
+      <c r="BO94">
+        <v>3.2</v>
+      </c>
+      <c r="BP94">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="185">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -424,6 +424,12 @@
     <t>['58', '64', '70']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['14', '83', '90+3']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -560,6 +566,9 @@
   </si>
   <si>
     <t>['45+4']</t>
+  </si>
+  <si>
+    <t>['34', '89']</t>
   </si>
 </sst>
 </file>
@@ -921,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1177,7 +1186,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1258,7 +1267,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ2">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1383,7 +1392,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1464,7 +1473,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2001,7 +2010,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2079,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2207,7 +2216,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2413,7 +2422,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2494,7 +2503,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2700,7 +2709,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2825,7 +2834,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3031,7 +3040,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3443,7 +3452,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3649,7 +3658,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3855,7 +3864,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3933,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
         <v>0.4</v>
@@ -4061,7 +4070,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4139,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ16">
         <v>1.83</v>
@@ -4757,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ19">
         <v>0.2</v>
@@ -4885,7 +4894,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -4963,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5091,7 +5100,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5172,7 +5181,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ21">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>1.79</v>
@@ -5378,7 +5387,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5584,7 +5593,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ23">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5709,7 +5718,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5790,7 +5799,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR24">
         <v>1.3</v>
@@ -5915,7 +5924,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -5996,7 +6005,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ25">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>1.36</v>
@@ -6945,7 +6954,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7023,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>0.4</v>
@@ -7151,7 +7160,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7847,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34">
         <v>0.2</v>
@@ -7975,7 +7984,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8053,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8387,7 +8396,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8674,7 +8683,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ38">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>0.8100000000000001</v>
@@ -9005,7 +9014,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9211,7 +9220,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9292,7 +9301,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>1.57</v>
@@ -9623,7 +9632,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9701,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ43">
         <v>1.6</v>
@@ -9910,7 +9919,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -10035,7 +10044,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10447,7 +10456,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10859,7 +10868,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11271,7 +11280,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11477,7 +11486,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11558,7 +11567,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ52">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11683,7 +11692,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11967,7 +11976,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>0.4</v>
@@ -12382,7 +12391,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12507,7 +12516,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12791,7 +12800,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ58">
         <v>1.8</v>
@@ -12919,7 +12928,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -12997,10 +13006,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -13331,7 +13340,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13409,10 +13418,10 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ61">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR61">
         <v>1.52</v>
@@ -13824,7 +13833,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ63">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.51</v>
@@ -14030,7 +14039,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14233,7 +14242,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14361,7 +14370,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14773,7 +14782,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15266,7 +15275,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ70">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR70">
         <v>1.68</v>
@@ -15597,7 +15606,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16009,7 +16018,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16090,7 +16099,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ74">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.35</v>
@@ -16215,7 +16224,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16421,7 +16430,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16499,7 +16508,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ76">
         <v>2.4</v>
@@ -16708,7 +16717,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR77">
         <v>1.1</v>
@@ -16833,7 +16842,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -16911,7 +16920,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
         <v>1.8</v>
@@ -17039,7 +17048,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17117,10 +17126,10 @@
         <v>1.25</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17245,7 +17254,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17529,10 +17538,10 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.81</v>
@@ -18275,7 +18284,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18481,7 +18490,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18687,7 +18696,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19099,7 +19108,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19305,7 +19314,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19511,7 +19520,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19717,7 +19726,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19923,7 +19932,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20286,6 +20295,1036 @@
       </c>
       <c r="BP94">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7729628</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95" t="s">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s">
+        <v>86</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>2</v>
+      </c>
+      <c r="O95" t="s">
+        <v>136</v>
+      </c>
+      <c r="P95" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q95">
+        <v>3.6</v>
+      </c>
+      <c r="R95">
+        <v>1.83</v>
+      </c>
+      <c r="S95">
+        <v>3.5</v>
+      </c>
+      <c r="T95">
+        <v>1.58</v>
+      </c>
+      <c r="U95">
+        <v>2.2</v>
+      </c>
+      <c r="V95">
+        <v>3.7</v>
+      </c>
+      <c r="W95">
+        <v>1.24</v>
+      </c>
+      <c r="X95">
+        <v>11</v>
+      </c>
+      <c r="Y95">
+        <v>1.03</v>
+      </c>
+      <c r="Z95">
+        <v>2.88</v>
+      </c>
+      <c r="AA95">
+        <v>2.75</v>
+      </c>
+      <c r="AB95">
+        <v>2.75</v>
+      </c>
+      <c r="AC95">
+        <v>1.1</v>
+      </c>
+      <c r="AD95">
+        <v>6.5</v>
+      </c>
+      <c r="AE95">
+        <v>1.5</v>
+      </c>
+      <c r="AF95">
+        <v>2.55</v>
+      </c>
+      <c r="AG95">
+        <v>2.7</v>
+      </c>
+      <c r="AH95">
+        <v>1.44</v>
+      </c>
+      <c r="AI95">
+        <v>2.15</v>
+      </c>
+      <c r="AJ95">
+        <v>1.67</v>
+      </c>
+      <c r="AK95">
+        <v>1.44</v>
+      </c>
+      <c r="AL95">
+        <v>1.4</v>
+      </c>
+      <c r="AM95">
+        <v>1.39</v>
+      </c>
+      <c r="AN95">
+        <v>1</v>
+      </c>
+      <c r="AO95">
+        <v>1.6</v>
+      </c>
+      <c r="AP95">
+        <v>1</v>
+      </c>
+      <c r="AQ95">
+        <v>1.5</v>
+      </c>
+      <c r="AR95">
+        <v>1.28</v>
+      </c>
+      <c r="AS95">
+        <v>1.51</v>
+      </c>
+      <c r="AT95">
+        <v>2.79</v>
+      </c>
+      <c r="AU95">
+        <v>3</v>
+      </c>
+      <c r="AV95">
+        <v>6</v>
+      </c>
+      <c r="AW95">
+        <v>0</v>
+      </c>
+      <c r="AX95">
+        <v>6</v>
+      </c>
+      <c r="AY95">
+        <v>3</v>
+      </c>
+      <c r="AZ95">
+        <v>12</v>
+      </c>
+      <c r="BA95">
+        <v>5</v>
+      </c>
+      <c r="BB95">
+        <v>5</v>
+      </c>
+      <c r="BC95">
+        <v>10</v>
+      </c>
+      <c r="BD95">
+        <v>2.03</v>
+      </c>
+      <c r="BE95">
+        <v>6.1</v>
+      </c>
+      <c r="BF95">
+        <v>2.17</v>
+      </c>
+      <c r="BG95">
+        <v>1.31</v>
+      </c>
+      <c r="BH95">
+        <v>2.92</v>
+      </c>
+      <c r="BI95">
+        <v>1.59</v>
+      </c>
+      <c r="BJ95">
+        <v>2.1</v>
+      </c>
+      <c r="BK95">
+        <v>2.03</v>
+      </c>
+      <c r="BL95">
+        <v>1.67</v>
+      </c>
+      <c r="BM95">
+        <v>2.66</v>
+      </c>
+      <c r="BN95">
+        <v>1.37</v>
+      </c>
+      <c r="BO95">
+        <v>3.72</v>
+      </c>
+      <c r="BP95">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7729627</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F96">
+        <v>11</v>
+      </c>
+      <c r="G96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H96" t="s">
+        <v>85</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
+        <v>89</v>
+      </c>
+      <c r="P96" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q96">
+        <v>4</v>
+      </c>
+      <c r="R96">
+        <v>1.8</v>
+      </c>
+      <c r="S96">
+        <v>3.25</v>
+      </c>
+      <c r="T96">
+        <v>1.67</v>
+      </c>
+      <c r="U96">
+        <v>2.1</v>
+      </c>
+      <c r="V96">
+        <v>4.33</v>
+      </c>
+      <c r="W96">
+        <v>1.2</v>
+      </c>
+      <c r="X96">
+        <v>10</v>
+      </c>
+      <c r="Y96">
+        <v>1.03</v>
+      </c>
+      <c r="Z96">
+        <v>2.7</v>
+      </c>
+      <c r="AA96">
+        <v>3.25</v>
+      </c>
+      <c r="AB96">
+        <v>2.3</v>
+      </c>
+      <c r="AC96">
+        <v>1.15</v>
+      </c>
+      <c r="AD96">
+        <v>5</v>
+      </c>
+      <c r="AE96">
+        <v>1.61</v>
+      </c>
+      <c r="AF96">
+        <v>2.15</v>
+      </c>
+      <c r="AG96">
+        <v>2.75</v>
+      </c>
+      <c r="AH96">
+        <v>1.4</v>
+      </c>
+      <c r="AI96">
+        <v>2.63</v>
+      </c>
+      <c r="AJ96">
+        <v>1.44</v>
+      </c>
+      <c r="AK96">
+        <v>1.49</v>
+      </c>
+      <c r="AL96">
+        <v>1.43</v>
+      </c>
+      <c r="AM96">
+        <v>1.32</v>
+      </c>
+      <c r="AN96">
+        <v>1</v>
+      </c>
+      <c r="AO96">
+        <v>1.8</v>
+      </c>
+      <c r="AP96">
+        <v>0.8</v>
+      </c>
+      <c r="AQ96">
+        <v>2</v>
+      </c>
+      <c r="AR96">
+        <v>0.8</v>
+      </c>
+      <c r="AS96">
+        <v>1.05</v>
+      </c>
+      <c r="AT96">
+        <v>1.85</v>
+      </c>
+      <c r="AU96">
+        <v>2</v>
+      </c>
+      <c r="AV96">
+        <v>3</v>
+      </c>
+      <c r="AW96">
+        <v>3</v>
+      </c>
+      <c r="AX96">
+        <v>5</v>
+      </c>
+      <c r="AY96">
+        <v>5</v>
+      </c>
+      <c r="AZ96">
+        <v>8</v>
+      </c>
+      <c r="BA96">
+        <v>5</v>
+      </c>
+      <c r="BB96">
+        <v>10</v>
+      </c>
+      <c r="BC96">
+        <v>15</v>
+      </c>
+      <c r="BD96">
+        <v>2.2</v>
+      </c>
+      <c r="BE96">
+        <v>6.1</v>
+      </c>
+      <c r="BF96">
+        <v>2</v>
+      </c>
+      <c r="BG96">
+        <v>1.31</v>
+      </c>
+      <c r="BH96">
+        <v>2.92</v>
+      </c>
+      <c r="BI96">
+        <v>1.59</v>
+      </c>
+      <c r="BJ96">
+        <v>2.1</v>
+      </c>
+      <c r="BK96">
+        <v>2.03</v>
+      </c>
+      <c r="BL96">
+        <v>1.67</v>
+      </c>
+      <c r="BM96">
+        <v>2.66</v>
+      </c>
+      <c r="BN96">
+        <v>1.37</v>
+      </c>
+      <c r="BO96">
+        <v>3.72</v>
+      </c>
+      <c r="BP96">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7729629</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F97">
+        <v>11</v>
+      </c>
+      <c r="G97" t="s">
+        <v>74</v>
+      </c>
+      <c r="H97" t="s">
+        <v>79</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+      <c r="L97">
+        <v>3</v>
+      </c>
+      <c r="M97">
+        <v>2</v>
+      </c>
+      <c r="N97">
+        <v>5</v>
+      </c>
+      <c r="O97" t="s">
+        <v>137</v>
+      </c>
+      <c r="P97" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q97">
+        <v>3.2</v>
+      </c>
+      <c r="R97">
+        <v>1.8</v>
+      </c>
+      <c r="S97">
+        <v>4</v>
+      </c>
+      <c r="T97">
+        <v>1.64</v>
+      </c>
+      <c r="U97">
+        <v>2.21</v>
+      </c>
+      <c r="V97">
+        <v>4</v>
+      </c>
+      <c r="W97">
+        <v>1.22</v>
+      </c>
+      <c r="X97">
+        <v>13</v>
+      </c>
+      <c r="Y97">
+        <v>1.01</v>
+      </c>
+      <c r="Z97">
+        <v>2.46</v>
+      </c>
+      <c r="AA97">
+        <v>2.45</v>
+      </c>
+      <c r="AB97">
+        <v>3.92</v>
+      </c>
+      <c r="AC97">
+        <v>1.13</v>
+      </c>
+      <c r="AD97">
+        <v>6</v>
+      </c>
+      <c r="AE97">
+        <v>1.6</v>
+      </c>
+      <c r="AF97">
+        <v>2.2</v>
+      </c>
+      <c r="AG97">
+        <v>2.77</v>
+      </c>
+      <c r="AH97">
+        <v>1.39</v>
+      </c>
+      <c r="AI97">
+        <v>2.25</v>
+      </c>
+      <c r="AJ97">
+        <v>1.57</v>
+      </c>
+      <c r="AK97">
+        <v>1.21</v>
+      </c>
+      <c r="AL97">
+        <v>1.49</v>
+      </c>
+      <c r="AM97">
+        <v>1.49</v>
+      </c>
+      <c r="AN97">
+        <v>1.4</v>
+      </c>
+      <c r="AO97">
+        <v>1.75</v>
+      </c>
+      <c r="AP97">
+        <v>1.67</v>
+      </c>
+      <c r="AQ97">
+        <v>1.4</v>
+      </c>
+      <c r="AR97">
+        <v>1.43</v>
+      </c>
+      <c r="AS97">
+        <v>0.99</v>
+      </c>
+      <c r="AT97">
+        <v>2.42</v>
+      </c>
+      <c r="AU97">
+        <v>5</v>
+      </c>
+      <c r="AV97">
+        <v>4</v>
+      </c>
+      <c r="AW97">
+        <v>6</v>
+      </c>
+      <c r="AX97">
+        <v>1</v>
+      </c>
+      <c r="AY97">
+        <v>11</v>
+      </c>
+      <c r="AZ97">
+        <v>5</v>
+      </c>
+      <c r="BA97">
+        <v>5</v>
+      </c>
+      <c r="BB97">
+        <v>8</v>
+      </c>
+      <c r="BC97">
+        <v>13</v>
+      </c>
+      <c r="BD97">
+        <v>1.98</v>
+      </c>
+      <c r="BE97">
+        <v>6</v>
+      </c>
+      <c r="BF97">
+        <v>2.24</v>
+      </c>
+      <c r="BG97">
+        <v>1.5</v>
+      </c>
+      <c r="BH97">
+        <v>2.48</v>
+      </c>
+      <c r="BI97">
+        <v>1.85</v>
+      </c>
+      <c r="BJ97">
+        <v>1.89</v>
+      </c>
+      <c r="BK97">
+        <v>2.39</v>
+      </c>
+      <c r="BL97">
+        <v>1.54</v>
+      </c>
+      <c r="BM97">
+        <v>3.25</v>
+      </c>
+      <c r="BN97">
+        <v>1.31</v>
+      </c>
+      <c r="BO97">
+        <v>4.55</v>
+      </c>
+      <c r="BP97">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7729630</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F98">
+        <v>11</v>
+      </c>
+      <c r="G98" t="s">
+        <v>83</v>
+      </c>
+      <c r="H98" t="s">
+        <v>80</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>89</v>
+      </c>
+      <c r="P98" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q98">
+        <v>3.25</v>
+      </c>
+      <c r="R98">
+        <v>1.73</v>
+      </c>
+      <c r="S98">
+        <v>4.33</v>
+      </c>
+      <c r="T98">
+        <v>1.62</v>
+      </c>
+      <c r="U98">
+        <v>2.2</v>
+      </c>
+      <c r="V98">
+        <v>4</v>
+      </c>
+      <c r="W98">
+        <v>1.2</v>
+      </c>
+      <c r="X98">
+        <v>10</v>
+      </c>
+      <c r="Y98">
+        <v>1.03</v>
+      </c>
+      <c r="Z98">
+        <v>2.5</v>
+      </c>
+      <c r="AA98">
+        <v>2.49</v>
+      </c>
+      <c r="AB98">
+        <v>3.72</v>
+      </c>
+      <c r="AC98">
+        <v>1.17</v>
+      </c>
+      <c r="AD98">
+        <v>5</v>
+      </c>
+      <c r="AE98">
+        <v>1.65</v>
+      </c>
+      <c r="AF98">
+        <v>2.05</v>
+      </c>
+      <c r="AG98">
+        <v>3.04</v>
+      </c>
+      <c r="AH98">
+        <v>1.33</v>
+      </c>
+      <c r="AI98">
+        <v>2.5</v>
+      </c>
+      <c r="AJ98">
+        <v>1.5</v>
+      </c>
+      <c r="AK98">
+        <v>1.25</v>
+      </c>
+      <c r="AL98">
+        <v>1.51</v>
+      </c>
+      <c r="AM98">
+        <v>1.49</v>
+      </c>
+      <c r="AN98">
+        <v>1.6</v>
+      </c>
+      <c r="AO98">
+        <v>1.2</v>
+      </c>
+      <c r="AP98">
+        <v>1.5</v>
+      </c>
+      <c r="AQ98">
+        <v>1.17</v>
+      </c>
+      <c r="AR98">
+        <v>1.73</v>
+      </c>
+      <c r="AS98">
+        <v>0.86</v>
+      </c>
+      <c r="AT98">
+        <v>2.59</v>
+      </c>
+      <c r="AU98">
+        <v>3</v>
+      </c>
+      <c r="AV98">
+        <v>4</v>
+      </c>
+      <c r="AW98">
+        <v>3</v>
+      </c>
+      <c r="AX98">
+        <v>15</v>
+      </c>
+      <c r="AY98">
+        <v>6</v>
+      </c>
+      <c r="AZ98">
+        <v>19</v>
+      </c>
+      <c r="BA98">
+        <v>5</v>
+      </c>
+      <c r="BB98">
+        <v>6</v>
+      </c>
+      <c r="BC98">
+        <v>11</v>
+      </c>
+      <c r="BD98">
+        <v>1.61</v>
+      </c>
+      <c r="BE98">
+        <v>6.25</v>
+      </c>
+      <c r="BF98">
+        <v>2.97</v>
+      </c>
+      <c r="BG98">
+        <v>1.49</v>
+      </c>
+      <c r="BH98">
+        <v>2.44</v>
+      </c>
+      <c r="BI98">
+        <v>1.84</v>
+      </c>
+      <c r="BJ98">
+        <v>1.86</v>
+      </c>
+      <c r="BK98">
+        <v>2.35</v>
+      </c>
+      <c r="BL98">
+        <v>1.53</v>
+      </c>
+      <c r="BM98">
+        <v>3.1</v>
+      </c>
+      <c r="BN98">
+        <v>1.32</v>
+      </c>
+      <c r="BO98">
+        <v>4.3</v>
+      </c>
+      <c r="BP98">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7729631</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F99">
+        <v>11</v>
+      </c>
+      <c r="G99" t="s">
+        <v>87</v>
+      </c>
+      <c r="H99" t="s">
+        <v>82</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>89</v>
+      </c>
+      <c r="P99" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q99">
+        <v>2.65</v>
+      </c>
+      <c r="R99">
+        <v>2.04</v>
+      </c>
+      <c r="S99">
+        <v>4.2</v>
+      </c>
+      <c r="T99">
+        <v>1.48</v>
+      </c>
+      <c r="U99">
+        <v>2.45</v>
+      </c>
+      <c r="V99">
+        <v>3.1</v>
+      </c>
+      <c r="W99">
+        <v>1.33</v>
+      </c>
+      <c r="X99">
+        <v>9</v>
+      </c>
+      <c r="Y99">
+        <v>1.07</v>
+      </c>
+      <c r="Z99">
+        <v>1.95</v>
+      </c>
+      <c r="AA99">
+        <v>3.25</v>
+      </c>
+      <c r="AB99">
+        <v>3.3</v>
+      </c>
+      <c r="AC99">
+        <v>1.06</v>
+      </c>
+      <c r="AD99">
+        <v>8</v>
+      </c>
+      <c r="AE99">
+        <v>1.37</v>
+      </c>
+      <c r="AF99">
+        <v>2.9</v>
+      </c>
+      <c r="AG99">
+        <v>2.1</v>
+      </c>
+      <c r="AH99">
+        <v>1.6</v>
+      </c>
+      <c r="AI99">
+        <v>1.92</v>
+      </c>
+      <c r="AJ99">
+        <v>1.79</v>
+      </c>
+      <c r="AK99">
+        <v>1.28</v>
+      </c>
+      <c r="AL99">
+        <v>1.28</v>
+      </c>
+      <c r="AM99">
+        <v>1.72</v>
+      </c>
+      <c r="AN99">
+        <v>2</v>
+      </c>
+      <c r="AO99">
+        <v>0.8</v>
+      </c>
+      <c r="AP99">
+        <v>1.6</v>
+      </c>
+      <c r="AQ99">
+        <v>1.17</v>
+      </c>
+      <c r="AR99">
+        <v>1.55</v>
+      </c>
+      <c r="AS99">
+        <v>1.38</v>
+      </c>
+      <c r="AT99">
+        <v>2.93</v>
+      </c>
+      <c r="AU99">
+        <v>5</v>
+      </c>
+      <c r="AV99">
+        <v>3</v>
+      </c>
+      <c r="AW99">
+        <v>5</v>
+      </c>
+      <c r="AX99">
+        <v>4</v>
+      </c>
+      <c r="AY99">
+        <v>10</v>
+      </c>
+      <c r="AZ99">
+        <v>7</v>
+      </c>
+      <c r="BA99">
+        <v>3</v>
+      </c>
+      <c r="BB99">
+        <v>1</v>
+      </c>
+      <c r="BC99">
+        <v>4</v>
+      </c>
+      <c r="BD99">
+        <v>1.62</v>
+      </c>
+      <c r="BE99">
+        <v>7.7</v>
+      </c>
+      <c r="BF99">
+        <v>2.91</v>
+      </c>
+      <c r="BG99">
+        <v>1.29</v>
+      </c>
+      <c r="BH99">
+        <v>3.42</v>
+      </c>
+      <c r="BI99">
+        <v>1.55</v>
+      </c>
+      <c r="BJ99">
+        <v>2.39</v>
+      </c>
+      <c r="BK99">
+        <v>1.9</v>
+      </c>
+      <c r="BL99">
+        <v>1.9</v>
+      </c>
+      <c r="BM99">
+        <v>2.39</v>
+      </c>
+      <c r="BN99">
+        <v>1.55</v>
+      </c>
+      <c r="BO99">
+        <v>3.15</v>
+      </c>
+      <c r="BP99">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="187">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -430,6 +430,9 @@
     <t>['14', '83', '90+3']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -569,6 +572,9 @@
   </si>
   <si>
     <t>['34', '89']</t>
+  </si>
+  <si>
+    <t>['13', '29', '39']</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP99"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1186,7 +1192,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1392,7 +1398,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1882,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -2010,7 +2016,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2216,7 +2222,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2422,7 +2428,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2834,7 +2840,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3040,7 +3046,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3452,7 +3458,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3533,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3658,7 +3664,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3864,7 +3870,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4070,7 +4076,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4894,7 +4900,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5100,7 +5106,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5718,7 +5724,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5924,7 +5930,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6414,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.6</v>
@@ -6954,7 +6960,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7160,7 +7166,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7447,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -7984,7 +7990,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8396,7 +8402,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9014,7 +9020,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9220,7 +9226,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9298,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9632,7 +9638,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10044,7 +10050,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10456,7 +10462,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10868,7 +10874,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11280,7 +11286,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11486,7 +11492,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11692,7 +11698,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11773,7 +11779,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>0.97</v>
@@ -12516,7 +12522,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12803,7 +12809,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ58">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR58">
         <v>0.89</v>
@@ -12928,7 +12934,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13340,7 +13346,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13624,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>0.2</v>
@@ -14370,7 +14376,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14782,7 +14788,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15606,7 +15612,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16018,7 +16024,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16224,7 +16230,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16430,7 +16436,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16842,7 +16848,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -16923,7 +16929,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17048,7 +17054,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17254,7 +17260,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17744,7 +17750,7 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
         <v>1.4</v>
@@ -18284,7 +18290,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18490,7 +18496,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18696,7 +18702,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19108,7 +19114,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19314,7 +19320,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19520,7 +19526,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19726,7 +19732,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19932,7 +19938,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20756,7 +20762,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21168,7 +21174,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21325,6 +21331,212 @@
       </c>
       <c r="BP99">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7729632</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45690.58333333334</v>
+      </c>
+      <c r="F100">
+        <v>11</v>
+      </c>
+      <c r="G100" t="s">
+        <v>73</v>
+      </c>
+      <c r="H100" t="s">
+        <v>78</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3</v>
+      </c>
+      <c r="K100">
+        <v>3</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>3</v>
+      </c>
+      <c r="N100">
+        <v>4</v>
+      </c>
+      <c r="O100" t="s">
+        <v>138</v>
+      </c>
+      <c r="P100" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q100">
+        <v>6.5</v>
+      </c>
+      <c r="R100">
+        <v>1.95</v>
+      </c>
+      <c r="S100">
+        <v>2.25</v>
+      </c>
+      <c r="T100">
+        <v>1.56</v>
+      </c>
+      <c r="U100">
+        <v>2.29</v>
+      </c>
+      <c r="V100">
+        <v>3.54</v>
+      </c>
+      <c r="W100">
+        <v>1.27</v>
+      </c>
+      <c r="X100">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y100">
+        <v>1.03</v>
+      </c>
+      <c r="Z100">
+        <v>6</v>
+      </c>
+      <c r="AA100">
+        <v>3.4</v>
+      </c>
+      <c r="AB100">
+        <v>1.57</v>
+      </c>
+      <c r="AC100">
+        <v>1.07</v>
+      </c>
+      <c r="AD100">
+        <v>7</v>
+      </c>
+      <c r="AE100">
+        <v>1.44</v>
+      </c>
+      <c r="AF100">
+        <v>2.6</v>
+      </c>
+      <c r="AG100">
+        <v>2.38</v>
+      </c>
+      <c r="AH100">
+        <v>1.53</v>
+      </c>
+      <c r="AI100">
+        <v>2.5</v>
+      </c>
+      <c r="AJ100">
+        <v>1.5</v>
+      </c>
+      <c r="AK100">
+        <v>2.04</v>
+      </c>
+      <c r="AL100">
+        <v>1.24</v>
+      </c>
+      <c r="AM100">
+        <v>1.12</v>
+      </c>
+      <c r="AN100">
+        <v>1.2</v>
+      </c>
+      <c r="AO100">
+        <v>1.8</v>
+      </c>
+      <c r="AP100">
+        <v>1</v>
+      </c>
+      <c r="AQ100">
+        <v>2</v>
+      </c>
+      <c r="AR100">
+        <v>1.18</v>
+      </c>
+      <c r="AS100">
+        <v>1.49</v>
+      </c>
+      <c r="AT100">
+        <v>2.67</v>
+      </c>
+      <c r="AU100">
+        <v>4</v>
+      </c>
+      <c r="AV100">
+        <v>8</v>
+      </c>
+      <c r="AW100">
+        <v>3</v>
+      </c>
+      <c r="AX100">
+        <v>7</v>
+      </c>
+      <c r="AY100">
+        <v>7</v>
+      </c>
+      <c r="AZ100">
+        <v>15</v>
+      </c>
+      <c r="BA100">
+        <v>9</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>13</v>
+      </c>
+      <c r="BD100">
+        <v>3.56</v>
+      </c>
+      <c r="BE100">
+        <v>6.9</v>
+      </c>
+      <c r="BF100">
+        <v>1.44</v>
+      </c>
+      <c r="BG100">
+        <v>1.26</v>
+      </c>
+      <c r="BH100">
+        <v>3.22</v>
+      </c>
+      <c r="BI100">
+        <v>1.58</v>
+      </c>
+      <c r="BJ100">
+        <v>2.34</v>
+      </c>
+      <c r="BK100">
+        <v>1.94</v>
+      </c>
+      <c r="BL100">
+        <v>1.85</v>
+      </c>
+      <c r="BM100">
+        <v>2.46</v>
+      </c>
+      <c r="BN100">
+        <v>1.53</v>
+      </c>
+      <c r="BO100">
+        <v>3.28</v>
+      </c>
+      <c r="BP100">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="192">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -433,6 +433,15 @@
     <t>['75']</t>
   </si>
   <si>
+    <t>['11', '81']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['15', '67']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -575,6 +584,12 @@
   </si>
   <si>
     <t>['13', '29', '39']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['23', '51']</t>
   </si>
 </sst>
 </file>
@@ -936,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1192,7 +1207,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1398,7 +1413,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2016,7 +2031,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2222,7 +2237,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2303,7 +2318,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ7">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2428,7 +2443,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2840,7 +2855,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2918,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
         <v>1.83</v>
@@ -3046,7 +3061,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3124,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ11">
         <v>2.4</v>
@@ -3458,7 +3473,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3664,7 +3679,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3870,7 +3885,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3951,7 +3966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4076,7 +4091,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4363,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4772,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19">
         <v>0.2</v>
@@ -4900,7 +4915,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5106,7 +5121,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5390,7 +5405,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -5724,7 +5739,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5930,7 +5945,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6217,7 +6232,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6960,7 +6975,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7038,10 +7053,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -7166,7 +7181,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7990,7 +8005,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8071,7 +8086,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>2.03</v>
@@ -8402,7 +8417,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8480,7 +8495,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ37">
         <v>1.4</v>
@@ -8895,7 +8910,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
         <v>1.3</v>
@@ -9020,7 +9035,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9226,7 +9241,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9638,7 +9653,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9922,7 +9937,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ44">
         <v>1.17</v>
@@ -10050,7 +10065,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10462,7 +10477,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10749,7 +10764,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ48">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR48">
         <v>0.85</v>
@@ -10874,7 +10889,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11161,7 +11176,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>1.6</v>
@@ -11286,7 +11301,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11492,7 +11507,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11698,7 +11713,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12522,7 +12537,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12934,7 +12949,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13221,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.01</v>
@@ -13346,7 +13361,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13424,7 +13439,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
         <v>1.5</v>
@@ -13836,7 +13851,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -14042,7 +14057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ64">
         <v>1.17</v>
@@ -14376,7 +14391,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14788,7 +14803,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15075,7 +15090,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ69">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR69">
         <v>1.78</v>
@@ -15484,7 +15499,7 @@
         <v>0.67</v>
       </c>
       <c r="AP71">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ71">
         <v>0.4</v>
@@ -15612,7 +15627,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15899,7 +15914,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
         <v>1.04</v>
@@ -16024,7 +16039,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16230,7 +16245,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16308,7 +16323,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ75">
         <v>1.17</v>
@@ -16436,7 +16451,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16848,7 +16863,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17054,7 +17069,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17132,7 +17147,7 @@
         <v>1.25</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ79">
         <v>1.17</v>
@@ -17260,7 +17275,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17959,7 +17974,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.22</v>
@@ -18290,7 +18305,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18368,7 +18383,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AQ85">
         <v>1.83</v>
@@ -18496,7 +18511,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18574,7 +18589,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ86">
         <v>1.83</v>
@@ -18702,7 +18717,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18989,7 +19004,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ88">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19114,7 +19129,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19320,7 +19335,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19401,7 +19416,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.09</v>
@@ -19526,7 +19541,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19732,7 +19747,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19938,7 +19953,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20762,7 +20777,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21174,7 +21189,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21252,7 +21267,7 @@
         <v>0.8</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99">
         <v>1.17</v>
@@ -21380,7 +21395,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21537,6 +21552,624 @@
       </c>
       <c r="BP100">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7729633</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45694.45833333334</v>
+      </c>
+      <c r="F101">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>139</v>
+      </c>
+      <c r="P101" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q101">
+        <v>4</v>
+      </c>
+      <c r="R101">
+        <v>1.75</v>
+      </c>
+      <c r="S101">
+        <v>3.3</v>
+      </c>
+      <c r="T101">
+        <v>1.71</v>
+      </c>
+      <c r="U101">
+        <v>2</v>
+      </c>
+      <c r="V101">
+        <v>4.5</v>
+      </c>
+      <c r="W101">
+        <v>1.17</v>
+      </c>
+      <c r="X101">
+        <v>14.5</v>
+      </c>
+      <c r="Y101">
+        <v>1.02</v>
+      </c>
+      <c r="Z101">
+        <v>3.29</v>
+      </c>
+      <c r="AA101">
+        <v>2.64</v>
+      </c>
+      <c r="AB101">
+        <v>2.59</v>
+      </c>
+      <c r="AC101">
+        <v>1.17</v>
+      </c>
+      <c r="AD101">
+        <v>4.75</v>
+      </c>
+      <c r="AE101">
+        <v>1.83</v>
+      </c>
+      <c r="AF101">
+        <v>1.91</v>
+      </c>
+      <c r="AG101">
+        <v>3.21</v>
+      </c>
+      <c r="AH101">
+        <v>1.3</v>
+      </c>
+      <c r="AI101">
+        <v>2.55</v>
+      </c>
+      <c r="AJ101">
+        <v>1.44</v>
+      </c>
+      <c r="AK101">
+        <v>1.5</v>
+      </c>
+      <c r="AL101">
+        <v>1.41</v>
+      </c>
+      <c r="AM101">
+        <v>1.33</v>
+      </c>
+      <c r="AN101">
+        <v>0.17</v>
+      </c>
+      <c r="AO101">
+        <v>0.4</v>
+      </c>
+      <c r="AP101">
+        <v>0.57</v>
+      </c>
+      <c r="AQ101">
+        <v>0.33</v>
+      </c>
+      <c r="AR101">
+        <v>1.45</v>
+      </c>
+      <c r="AS101">
+        <v>1.13</v>
+      </c>
+      <c r="AT101">
+        <v>2.58</v>
+      </c>
+      <c r="AU101">
+        <v>5</v>
+      </c>
+      <c r="AV101">
+        <v>2</v>
+      </c>
+      <c r="AW101">
+        <v>8</v>
+      </c>
+      <c r="AX101">
+        <v>0</v>
+      </c>
+      <c r="AY101">
+        <v>13</v>
+      </c>
+      <c r="AZ101">
+        <v>2</v>
+      </c>
+      <c r="BA101">
+        <v>9</v>
+      </c>
+      <c r="BB101">
+        <v>3</v>
+      </c>
+      <c r="BC101">
+        <v>12</v>
+      </c>
+      <c r="BD101">
+        <v>2.15</v>
+      </c>
+      <c r="BE101">
+        <v>6.7</v>
+      </c>
+      <c r="BF101">
+        <v>1.92</v>
+      </c>
+      <c r="BG101">
+        <v>1.26</v>
+      </c>
+      <c r="BH101">
+        <v>3.4</v>
+      </c>
+      <c r="BI101">
+        <v>1.52</v>
+      </c>
+      <c r="BJ101">
+        <v>2.32</v>
+      </c>
+      <c r="BK101">
+        <v>1.92</v>
+      </c>
+      <c r="BL101">
+        <v>1.75</v>
+      </c>
+      <c r="BM101">
+        <v>2.6</v>
+      </c>
+      <c r="BN101">
+        <v>1.43</v>
+      </c>
+      <c r="BO101">
+        <v>3.55</v>
+      </c>
+      <c r="BP101">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7729634</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45694.45833333334</v>
+      </c>
+      <c r="F102">
+        <v>12</v>
+      </c>
+      <c r="G102" t="s">
+        <v>87</v>
+      </c>
+      <c r="H102" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>2</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>140</v>
+      </c>
+      <c r="P102" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q102">
+        <v>2.35</v>
+      </c>
+      <c r="R102">
+        <v>2.05</v>
+      </c>
+      <c r="S102">
+        <v>5</v>
+      </c>
+      <c r="T102">
+        <v>1.44</v>
+      </c>
+      <c r="U102">
+        <v>2.55</v>
+      </c>
+      <c r="V102">
+        <v>3</v>
+      </c>
+      <c r="W102">
+        <v>1.33</v>
+      </c>
+      <c r="X102">
+        <v>8.25</v>
+      </c>
+      <c r="Y102">
+        <v>1.06</v>
+      </c>
+      <c r="Z102">
+        <v>1.72</v>
+      </c>
+      <c r="AA102">
+        <v>3.41</v>
+      </c>
+      <c r="AB102">
+        <v>5.1</v>
+      </c>
+      <c r="AC102">
+        <v>1.07</v>
+      </c>
+      <c r="AD102">
+        <v>7.5</v>
+      </c>
+      <c r="AE102">
+        <v>1.38</v>
+      </c>
+      <c r="AF102">
+        <v>2.8</v>
+      </c>
+      <c r="AG102">
+        <v>2.1</v>
+      </c>
+      <c r="AH102">
+        <v>1.61</v>
+      </c>
+      <c r="AI102">
+        <v>2.05</v>
+      </c>
+      <c r="AJ102">
+        <v>1.66</v>
+      </c>
+      <c r="AK102">
+        <v>1.18</v>
+      </c>
+      <c r="AL102">
+        <v>1.29</v>
+      </c>
+      <c r="AM102">
+        <v>2.05</v>
+      </c>
+      <c r="AN102">
+        <v>1.6</v>
+      </c>
+      <c r="AO102">
+        <v>1</v>
+      </c>
+      <c r="AP102">
+        <v>1.33</v>
+      </c>
+      <c r="AQ102">
+        <v>1.33</v>
+      </c>
+      <c r="AR102">
+        <v>1.53</v>
+      </c>
+      <c r="AS102">
+        <v>0.85</v>
+      </c>
+      <c r="AT102">
+        <v>2.38</v>
+      </c>
+      <c r="AU102">
+        <v>4</v>
+      </c>
+      <c r="AV102">
+        <v>5</v>
+      </c>
+      <c r="AW102">
+        <v>11</v>
+      </c>
+      <c r="AX102">
+        <v>3</v>
+      </c>
+      <c r="AY102">
+        <v>15</v>
+      </c>
+      <c r="AZ102">
+        <v>8</v>
+      </c>
+      <c r="BA102">
+        <v>7</v>
+      </c>
+      <c r="BB102">
+        <v>1</v>
+      </c>
+      <c r="BC102">
+        <v>8</v>
+      </c>
+      <c r="BD102">
+        <v>1.33</v>
+      </c>
+      <c r="BE102">
+        <v>9</v>
+      </c>
+      <c r="BF102">
+        <v>3.92</v>
+      </c>
+      <c r="BG102">
+        <v>1.31</v>
+      </c>
+      <c r="BH102">
+        <v>2.92</v>
+      </c>
+      <c r="BI102">
+        <v>1.57</v>
+      </c>
+      <c r="BJ102">
+        <v>2.14</v>
+      </c>
+      <c r="BK102">
+        <v>2</v>
+      </c>
+      <c r="BL102">
+        <v>1.69</v>
+      </c>
+      <c r="BM102">
+        <v>2.59</v>
+      </c>
+      <c r="BN102">
+        <v>1.39</v>
+      </c>
+      <c r="BO102">
+        <v>3.58</v>
+      </c>
+      <c r="BP102">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7729635</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45694.58333333334</v>
+      </c>
+      <c r="F103">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>78</v>
+      </c>
+      <c r="H103" t="s">
+        <v>83</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>3</v>
+      </c>
+      <c r="O103" t="s">
+        <v>141</v>
+      </c>
+      <c r="P103" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q103">
+        <v>2.05</v>
+      </c>
+      <c r="R103">
+        <v>2.1</v>
+      </c>
+      <c r="S103">
+        <v>6.5</v>
+      </c>
+      <c r="T103">
+        <v>1.44</v>
+      </c>
+      <c r="U103">
+        <v>2.55</v>
+      </c>
+      <c r="V103">
+        <v>3.1</v>
+      </c>
+      <c r="W103">
+        <v>1.32</v>
+      </c>
+      <c r="X103">
+        <v>8.5</v>
+      </c>
+      <c r="Y103">
+        <v>1.06</v>
+      </c>
+      <c r="Z103">
+        <v>1.46</v>
+      </c>
+      <c r="AA103">
+        <v>3.97</v>
+      </c>
+      <c r="AB103">
+        <v>7.5</v>
+      </c>
+      <c r="AC103">
+        <v>1.07</v>
+      </c>
+      <c r="AD103">
+        <v>7.5</v>
+      </c>
+      <c r="AE103">
+        <v>1.4</v>
+      </c>
+      <c r="AF103">
+        <v>2.85</v>
+      </c>
+      <c r="AG103">
+        <v>2.05</v>
+      </c>
+      <c r="AH103">
+        <v>1.65</v>
+      </c>
+      <c r="AI103">
+        <v>2.4</v>
+      </c>
+      <c r="AJ103">
+        <v>1.5</v>
+      </c>
+      <c r="AK103">
+        <v>1.1</v>
+      </c>
+      <c r="AL103">
+        <v>1.23</v>
+      </c>
+      <c r="AM103">
+        <v>2.55</v>
+      </c>
+      <c r="AN103">
+        <v>2.2</v>
+      </c>
+      <c r="AO103">
+        <v>1.6</v>
+      </c>
+      <c r="AP103">
+        <v>2.33</v>
+      </c>
+      <c r="AQ103">
+        <v>1.33</v>
+      </c>
+      <c r="AR103">
+        <v>2.01</v>
+      </c>
+      <c r="AS103">
+        <v>1.29</v>
+      </c>
+      <c r="AT103">
+        <v>3.3</v>
+      </c>
+      <c r="AU103">
+        <v>8</v>
+      </c>
+      <c r="AV103">
+        <v>4</v>
+      </c>
+      <c r="AW103">
+        <v>4</v>
+      </c>
+      <c r="AX103">
+        <v>2</v>
+      </c>
+      <c r="AY103">
+        <v>12</v>
+      </c>
+      <c r="AZ103">
+        <v>6</v>
+      </c>
+      <c r="BA103">
+        <v>2</v>
+      </c>
+      <c r="BB103">
+        <v>7</v>
+      </c>
+      <c r="BC103">
+        <v>9</v>
+      </c>
+      <c r="BD103">
+        <v>1.21</v>
+      </c>
+      <c r="BE103">
+        <v>8.5</v>
+      </c>
+      <c r="BF103">
+        <v>5.75</v>
+      </c>
+      <c r="BG103">
+        <v>1.25</v>
+      </c>
+      <c r="BH103">
+        <v>3.28</v>
+      </c>
+      <c r="BI103">
+        <v>1.48</v>
+      </c>
+      <c r="BJ103">
+        <v>2.33</v>
+      </c>
+      <c r="BK103">
+        <v>1.84</v>
+      </c>
+      <c r="BL103">
+        <v>1.82</v>
+      </c>
+      <c r="BM103">
+        <v>2.38</v>
+      </c>
+      <c r="BN103">
+        <v>1.46</v>
+      </c>
+      <c r="BO103">
+        <v>3.2</v>
+      </c>
+      <c r="BP103">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="194">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -442,6 +442,9 @@
     <t>['15', '67']</t>
   </si>
   <si>
+    <t>['18', '90+9']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -590,6 +593,9 @@
   </si>
   <si>
     <t>['23', '51']</t>
+  </si>
+  <si>
+    <t>['90+12']</t>
   </si>
 </sst>
 </file>
@@ -951,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1207,7 +1213,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1285,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ2">
         <v>1.17</v>
@@ -1413,7 +1419,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1491,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ3">
         <v>1.5</v>
@@ -1906,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2031,7 +2037,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2237,7 +2243,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2443,7 +2449,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2521,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ8">
         <v>2</v>
@@ -2855,7 +2861,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3061,7 +3067,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3473,7 +3479,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3679,7 +3685,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3757,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14">
         <v>1.4</v>
@@ -3885,7 +3891,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4091,7 +4097,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4172,7 +4178,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ16">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4584,7 +4590,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4790,7 +4796,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4915,7 +4921,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -4996,7 +5002,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5121,7 +5127,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5611,7 +5617,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -5739,7 +5745,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5945,7 +5951,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6023,7 +6029,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ25">
         <v>1.5</v>
@@ -6641,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ28">
         <v>1.83</v>
@@ -6975,7 +6981,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7181,7 +7187,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7671,10 +7677,10 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>1.75</v>
@@ -7880,7 +7886,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ34">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR34">
         <v>0.6899999999999999</v>
@@ -8005,7 +8011,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8292,7 +8298,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.03</v>
@@ -8417,7 +8423,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8701,7 +8707,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ38">
         <v>1.5</v>
@@ -8907,7 +8913,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
@@ -9035,7 +9041,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9113,7 +9119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ40">
         <v>1.83</v>
@@ -9241,7 +9247,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9528,7 +9534,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR42">
         <v>1.45</v>
@@ -9653,7 +9659,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10065,7 +10071,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10146,7 +10152,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.27</v>
@@ -10352,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR46">
         <v>0.9399999999999999</v>
@@ -10477,7 +10483,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10555,7 +10561,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ47">
         <v>1.4</v>
@@ -10889,7 +10895,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11301,7 +11307,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11507,7 +11513,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11585,7 +11591,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ52">
         <v>1.4</v>
@@ -11713,7 +11719,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12000,7 +12006,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR54">
         <v>1.9</v>
@@ -12203,7 +12209,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ55">
         <v>2.4</v>
@@ -12409,7 +12415,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ56">
         <v>1.17</v>
@@ -12537,7 +12543,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12618,7 +12624,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ57">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -12949,7 +12955,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13361,7 +13367,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13648,7 +13654,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -14266,7 +14272,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR65">
         <v>2.1</v>
@@ -14391,7 +14397,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14469,7 +14475,7 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ66">
         <v>1.83</v>
@@ -14678,7 +14684,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR67">
         <v>1.03</v>
@@ -14803,7 +14809,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15087,7 +15093,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
         <v>0.33</v>
@@ -15502,7 +15508,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ71">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -15627,7 +15633,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15705,7 +15711,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ72">
         <v>1.17</v>
@@ -16039,7 +16045,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16245,7 +16251,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16451,7 +16457,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16863,7 +16869,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17069,7 +17075,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17275,7 +17281,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17356,7 +17362,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -17971,7 +17977,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ83">
         <v>1.33</v>
@@ -18180,7 +18186,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR84">
         <v>0.83</v>
@@ -18305,7 +18311,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18511,7 +18517,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18592,7 +18598,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ86">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR86">
         <v>1.96</v>
@@ -18717,7 +18723,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18795,10 +18801,10 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ87">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
         <v>1.76</v>
@@ -19001,7 +19007,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ88">
         <v>0.33</v>
@@ -19129,7 +19135,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19210,7 +19216,7 @@
         <v>2</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR89">
         <v>1.05</v>
@@ -19335,7 +19341,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19541,7 +19547,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19619,7 +19625,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ91">
         <v>1.6</v>
@@ -19747,7 +19753,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19953,7 +19959,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20777,7 +20783,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21189,7 +21195,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21395,7 +21401,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21601,7 +21607,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21807,7 +21813,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22170,6 +22176,830 @@
       </c>
       <c r="BP103">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7729637</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45695.45833333334</v>
+      </c>
+      <c r="F104">
+        <v>12</v>
+      </c>
+      <c r="G104" t="s">
+        <v>70</v>
+      </c>
+      <c r="H104" t="s">
+        <v>84</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>130</v>
+      </c>
+      <c r="P104" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q104">
+        <v>3.78</v>
+      </c>
+      <c r="R104">
+        <v>1.81</v>
+      </c>
+      <c r="S104">
+        <v>3.34</v>
+      </c>
+      <c r="T104">
+        <v>1.63</v>
+      </c>
+      <c r="U104">
+        <v>2.19</v>
+      </c>
+      <c r="V104">
+        <v>4</v>
+      </c>
+      <c r="W104">
+        <v>1.22</v>
+      </c>
+      <c r="X104">
+        <v>11.5</v>
+      </c>
+      <c r="Y104">
+        <v>1.02</v>
+      </c>
+      <c r="Z104">
+        <v>3</v>
+      </c>
+      <c r="AA104">
+        <v>2.82</v>
+      </c>
+      <c r="AB104">
+        <v>2.61</v>
+      </c>
+      <c r="AC104">
+        <v>1.08</v>
+      </c>
+      <c r="AD104">
+        <v>5.5</v>
+      </c>
+      <c r="AE104">
+        <v>1.57</v>
+      </c>
+      <c r="AF104">
+        <v>2.15</v>
+      </c>
+      <c r="AG104">
+        <v>2.89</v>
+      </c>
+      <c r="AH104">
+        <v>1.36</v>
+      </c>
+      <c r="AI104">
+        <v>2.21</v>
+      </c>
+      <c r="AJ104">
+        <v>1.56</v>
+      </c>
+      <c r="AK104">
+        <v>1.44</v>
+      </c>
+      <c r="AL104">
+        <v>1.35</v>
+      </c>
+      <c r="AM104">
+        <v>1.35</v>
+      </c>
+      <c r="AN104">
+        <v>1.6</v>
+      </c>
+      <c r="AO104">
+        <v>0.5</v>
+      </c>
+      <c r="AP104">
+        <v>1.83</v>
+      </c>
+      <c r="AQ104">
+        <v>0.43</v>
+      </c>
+      <c r="AR104">
+        <v>0.91</v>
+      </c>
+      <c r="AS104">
+        <v>1.12</v>
+      </c>
+      <c r="AT104">
+        <v>2.03</v>
+      </c>
+      <c r="AU104">
+        <v>5</v>
+      </c>
+      <c r="AV104">
+        <v>3</v>
+      </c>
+      <c r="AW104">
+        <v>2</v>
+      </c>
+      <c r="AX104">
+        <v>5</v>
+      </c>
+      <c r="AY104">
+        <v>7</v>
+      </c>
+      <c r="AZ104">
+        <v>8</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>5</v>
+      </c>
+      <c r="BC104">
+        <v>9</v>
+      </c>
+      <c r="BD104">
+        <v>2.17</v>
+      </c>
+      <c r="BE104">
+        <v>6.1</v>
+      </c>
+      <c r="BF104">
+        <v>2.03</v>
+      </c>
+      <c r="BG104">
+        <v>1.34</v>
+      </c>
+      <c r="BH104">
+        <v>2.78</v>
+      </c>
+      <c r="BI104">
+        <v>1.71</v>
+      </c>
+      <c r="BJ104">
+        <v>2.11</v>
+      </c>
+      <c r="BK104">
+        <v>2.16</v>
+      </c>
+      <c r="BL104">
+        <v>1.68</v>
+      </c>
+      <c r="BM104">
+        <v>2.78</v>
+      </c>
+      <c r="BN104">
+        <v>1.34</v>
+      </c>
+      <c r="BO104">
+        <v>3.88</v>
+      </c>
+      <c r="BP104">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7729636</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45695.45833333334</v>
+      </c>
+      <c r="F105">
+        <v>12</v>
+      </c>
+      <c r="G105" t="s">
+        <v>82</v>
+      </c>
+      <c r="H105" t="s">
+        <v>75</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>89</v>
+      </c>
+      <c r="P105" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q105">
+        <v>4.75</v>
+      </c>
+      <c r="R105">
+        <v>2.05</v>
+      </c>
+      <c r="S105">
+        <v>2.4</v>
+      </c>
+      <c r="T105">
+        <v>1.44</v>
+      </c>
+      <c r="U105">
+        <v>2.63</v>
+      </c>
+      <c r="V105">
+        <v>3.25</v>
+      </c>
+      <c r="W105">
+        <v>1.33</v>
+      </c>
+      <c r="X105">
+        <v>7.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.07</v>
+      </c>
+      <c r="Z105">
+        <v>3.57</v>
+      </c>
+      <c r="AA105">
+        <v>3.25</v>
+      </c>
+      <c r="AB105">
+        <v>2.07</v>
+      </c>
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
+        <v>9</v>
+      </c>
+      <c r="AE105">
+        <v>1.27</v>
+      </c>
+      <c r="AF105">
+        <v>3.14</v>
+      </c>
+      <c r="AG105">
+        <v>1.98</v>
+      </c>
+      <c r="AH105">
+        <v>1.77</v>
+      </c>
+      <c r="AI105">
+        <v>2</v>
+      </c>
+      <c r="AJ105">
+        <v>1.73</v>
+      </c>
+      <c r="AK105">
+        <v>2.35</v>
+      </c>
+      <c r="AL105">
+        <v>1.25</v>
+      </c>
+      <c r="AM105">
+        <v>1.12</v>
+      </c>
+      <c r="AN105">
+        <v>1.4</v>
+      </c>
+      <c r="AO105">
+        <v>1.83</v>
+      </c>
+      <c r="AP105">
+        <v>1.17</v>
+      </c>
+      <c r="AQ105">
+        <v>2</v>
+      </c>
+      <c r="AR105">
+        <v>1.55</v>
+      </c>
+      <c r="AS105">
+        <v>1.33</v>
+      </c>
+      <c r="AT105">
+        <v>2.88</v>
+      </c>
+      <c r="AU105">
+        <v>8</v>
+      </c>
+      <c r="AV105">
+        <v>6</v>
+      </c>
+      <c r="AW105">
+        <v>5</v>
+      </c>
+      <c r="AX105">
+        <v>9</v>
+      </c>
+      <c r="AY105">
+        <v>13</v>
+      </c>
+      <c r="AZ105">
+        <v>15</v>
+      </c>
+      <c r="BA105">
+        <v>4</v>
+      </c>
+      <c r="BB105">
+        <v>9</v>
+      </c>
+      <c r="BC105">
+        <v>13</v>
+      </c>
+      <c r="BD105">
+        <v>3.04</v>
+      </c>
+      <c r="BE105">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF105">
+        <v>1.5</v>
+      </c>
+      <c r="BG105">
+        <v>1.34</v>
+      </c>
+      <c r="BH105">
+        <v>2.78</v>
+      </c>
+      <c r="BI105">
+        <v>1.71</v>
+      </c>
+      <c r="BJ105">
+        <v>2.1</v>
+      </c>
+      <c r="BK105">
+        <v>2.14</v>
+      </c>
+      <c r="BL105">
+        <v>1.68</v>
+      </c>
+      <c r="BM105">
+        <v>2.78</v>
+      </c>
+      <c r="BN105">
+        <v>1.34</v>
+      </c>
+      <c r="BO105">
+        <v>3.88</v>
+      </c>
+      <c r="BP105">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7729638</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45695.58333333334</v>
+      </c>
+      <c r="F106">
+        <v>12</v>
+      </c>
+      <c r="G106" t="s">
+        <v>71</v>
+      </c>
+      <c r="H106" t="s">
+        <v>72</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" t="s">
+        <v>89</v>
+      </c>
+      <c r="P106" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q106">
+        <v>2.8</v>
+      </c>
+      <c r="R106">
+        <v>1.83</v>
+      </c>
+      <c r="S106">
+        <v>5</v>
+      </c>
+      <c r="T106">
+        <v>1.7</v>
+      </c>
+      <c r="U106">
+        <v>2.06</v>
+      </c>
+      <c r="V106">
+        <v>4.3</v>
+      </c>
+      <c r="W106">
+        <v>1.2</v>
+      </c>
+      <c r="X106">
+        <v>13</v>
+      </c>
+      <c r="Y106">
+        <v>1.01</v>
+      </c>
+      <c r="Z106">
+        <v>2.05</v>
+      </c>
+      <c r="AA106">
+        <v>2.82</v>
+      </c>
+      <c r="AB106">
+        <v>4.4</v>
+      </c>
+      <c r="AC106">
+        <v>1.11</v>
+      </c>
+      <c r="AD106">
+        <v>5.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.63</v>
+      </c>
+      <c r="AF106">
+        <v>2.15</v>
+      </c>
+      <c r="AG106">
+        <v>2.9</v>
+      </c>
+      <c r="AH106">
+        <v>1.36</v>
+      </c>
+      <c r="AI106">
+        <v>2.45</v>
+      </c>
+      <c r="AJ106">
+        <v>1.53</v>
+      </c>
+      <c r="AK106">
+        <v>1.21</v>
+      </c>
+      <c r="AL106">
+        <v>1.36</v>
+      </c>
+      <c r="AM106">
+        <v>1.69</v>
+      </c>
+      <c r="AN106">
+        <v>0.5</v>
+      </c>
+      <c r="AO106">
+        <v>0.4</v>
+      </c>
+      <c r="AP106">
+        <v>0.57</v>
+      </c>
+      <c r="AQ106">
+        <v>0.5</v>
+      </c>
+      <c r="AR106">
+        <v>1.49</v>
+      </c>
+      <c r="AS106">
+        <v>1.18</v>
+      </c>
+      <c r="AT106">
+        <v>2.67</v>
+      </c>
+      <c r="AU106">
+        <v>2</v>
+      </c>
+      <c r="AV106">
+        <v>4</v>
+      </c>
+      <c r="AW106">
+        <v>11</v>
+      </c>
+      <c r="AX106">
+        <v>10</v>
+      </c>
+      <c r="AY106">
+        <v>13</v>
+      </c>
+      <c r="AZ106">
+        <v>14</v>
+      </c>
+      <c r="BA106">
+        <v>3</v>
+      </c>
+      <c r="BB106">
+        <v>3</v>
+      </c>
+      <c r="BC106">
+        <v>6</v>
+      </c>
+      <c r="BD106">
+        <v>1.51</v>
+      </c>
+      <c r="BE106">
+        <v>6.7</v>
+      </c>
+      <c r="BF106">
+        <v>3.26</v>
+      </c>
+      <c r="BG106">
+        <v>1.27</v>
+      </c>
+      <c r="BH106">
+        <v>3.14</v>
+      </c>
+      <c r="BI106">
+        <v>1.52</v>
+      </c>
+      <c r="BJ106">
+        <v>2.24</v>
+      </c>
+      <c r="BK106">
+        <v>1.91</v>
+      </c>
+      <c r="BL106">
+        <v>1.76</v>
+      </c>
+      <c r="BM106">
+        <v>2.46</v>
+      </c>
+      <c r="BN106">
+        <v>1.43</v>
+      </c>
+      <c r="BO106">
+        <v>3.42</v>
+      </c>
+      <c r="BP106">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7729639</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45695.58333333334</v>
+      </c>
+      <c r="F107">
+        <v>12</v>
+      </c>
+      <c r="G107" t="s">
+        <v>76</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>142</v>
+      </c>
+      <c r="P107" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q107">
+        <v>2.05</v>
+      </c>
+      <c r="R107">
+        <v>2.1</v>
+      </c>
+      <c r="S107">
+        <v>6.5</v>
+      </c>
+      <c r="T107">
+        <v>1.44</v>
+      </c>
+      <c r="U107">
+        <v>2.63</v>
+      </c>
+      <c r="V107">
+        <v>3.25</v>
+      </c>
+      <c r="W107">
+        <v>1.33</v>
+      </c>
+      <c r="X107">
+        <v>7.5</v>
+      </c>
+      <c r="Y107">
+        <v>1.07</v>
+      </c>
+      <c r="Z107">
+        <v>1.62</v>
+      </c>
+      <c r="AA107">
+        <v>3.8</v>
+      </c>
+      <c r="AB107">
+        <v>5.3</v>
+      </c>
+      <c r="AC107">
+        <v>1.05</v>
+      </c>
+      <c r="AD107">
+        <v>8.5</v>
+      </c>
+      <c r="AE107">
+        <v>1.34</v>
+      </c>
+      <c r="AF107">
+        <v>3.1</v>
+      </c>
+      <c r="AG107">
+        <v>1.95</v>
+      </c>
+      <c r="AH107">
+        <v>1.7</v>
+      </c>
+      <c r="AI107">
+        <v>2.25</v>
+      </c>
+      <c r="AJ107">
+        <v>1.57</v>
+      </c>
+      <c r="AK107">
+        <v>1.09</v>
+      </c>
+      <c r="AL107">
+        <v>1.21</v>
+      </c>
+      <c r="AM107">
+        <v>2.7</v>
+      </c>
+      <c r="AN107">
+        <v>2.17</v>
+      </c>
+      <c r="AO107">
+        <v>0.2</v>
+      </c>
+      <c r="AP107">
+        <v>2.29</v>
+      </c>
+      <c r="AQ107">
+        <v>0.17</v>
+      </c>
+      <c r="AR107">
+        <v>1.73</v>
+      </c>
+      <c r="AS107">
+        <v>1.05</v>
+      </c>
+      <c r="AT107">
+        <v>2.78</v>
+      </c>
+      <c r="AU107">
+        <v>5</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>3</v>
+      </c>
+      <c r="AX107">
+        <v>7</v>
+      </c>
+      <c r="AY107">
+        <v>8</v>
+      </c>
+      <c r="AZ107">
+        <v>9</v>
+      </c>
+      <c r="BA107">
+        <v>3</v>
+      </c>
+      <c r="BB107">
+        <v>5</v>
+      </c>
+      <c r="BC107">
+        <v>8</v>
+      </c>
+      <c r="BD107">
+        <v>1.35</v>
+      </c>
+      <c r="BE107">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF107">
+        <v>3.72</v>
+      </c>
+      <c r="BG107">
+        <v>1.2</v>
+      </c>
+      <c r="BH107">
+        <v>3.7</v>
+      </c>
+      <c r="BI107">
+        <v>1.39</v>
+      </c>
+      <c r="BJ107">
+        <v>2.59</v>
+      </c>
+      <c r="BK107">
+        <v>1.71</v>
+      </c>
+      <c r="BL107">
+        <v>1.97</v>
+      </c>
+      <c r="BM107">
+        <v>2.15</v>
+      </c>
+      <c r="BN107">
+        <v>1.56</v>
+      </c>
+      <c r="BO107">
+        <v>2.83</v>
+      </c>
+      <c r="BP107">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="196">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -445,6 +445,9 @@
     <t>['18', '90+9']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -491,9 +494,6 @@
   </si>
   <si>
     <t>['62']</t>
-  </si>
-  <si>
-    <t>['90+4']</t>
   </si>
   <si>
     <t>['23', '41']</t>
@@ -596,6 +596,12 @@
   </si>
   <si>
     <t>['90+12']</t>
+  </si>
+  <si>
+    <t>['20', '71']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -957,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1213,7 +1219,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1419,7 +1425,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1500,7 +1506,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ3">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1706,7 +1712,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2037,7 +2043,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2243,7 +2249,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2449,7 +2455,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2861,7 +2867,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3067,7 +3073,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3351,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12">
         <v>1.17</v>
@@ -3479,7 +3485,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3685,7 +3691,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3891,7 +3897,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4097,7 +4103,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4921,7 +4927,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5127,7 +5133,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5745,7 +5751,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5951,7 +5957,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6032,7 +6038,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ25">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR25">
         <v>1.36</v>
@@ -6444,7 +6450,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>2</v>
@@ -6981,7 +6987,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7187,7 +7193,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7265,7 +7271,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ31">
         <v>2.4</v>
@@ -8710,7 +8716,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR38">
         <v>0.8100000000000001</v>
@@ -9740,7 +9746,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ43">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -10071,7 +10077,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10767,7 +10773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ48">
         <v>0.33</v>
@@ -13448,7 +13454,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR61">
         <v>1.52</v>
@@ -14397,7 +14403,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14887,10 +14893,10 @@
         <v>1.67</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>0.92</v>
@@ -17568,7 +17574,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR81">
         <v>1.81</v>
@@ -18183,7 +18189,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ84">
         <v>0.17</v>
@@ -19628,7 +19634,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ91">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.61</v>
@@ -20452,7 +20458,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR95">
         <v>1.28</v>
@@ -21195,7 +21201,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -23000,6 +23006,418 @@
       </c>
       <c r="BP107">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7729640</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F108">
+        <v>12</v>
+      </c>
+      <c r="G108" t="s">
+        <v>80</v>
+      </c>
+      <c r="H108" t="s">
+        <v>86</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>2</v>
+      </c>
+      <c r="N108">
+        <v>3</v>
+      </c>
+      <c r="O108" t="s">
+        <v>120</v>
+      </c>
+      <c r="P108" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q108">
+        <v>4.33</v>
+      </c>
+      <c r="R108">
+        <v>1.83</v>
+      </c>
+      <c r="S108">
+        <v>3</v>
+      </c>
+      <c r="T108">
+        <v>1.62</v>
+      </c>
+      <c r="U108">
+        <v>2.2</v>
+      </c>
+      <c r="V108">
+        <v>4</v>
+      </c>
+      <c r="W108">
+        <v>1.22</v>
+      </c>
+      <c r="X108">
+        <v>9</v>
+      </c>
+      <c r="Y108">
+        <v>1.04</v>
+      </c>
+      <c r="Z108">
+        <v>4</v>
+      </c>
+      <c r="AA108">
+        <v>2.81</v>
+      </c>
+      <c r="AB108">
+        <v>2.15</v>
+      </c>
+      <c r="AC108">
+        <v>1.13</v>
+      </c>
+      <c r="AD108">
+        <v>5.4</v>
+      </c>
+      <c r="AE108">
+        <v>1.53</v>
+      </c>
+      <c r="AF108">
+        <v>2.2</v>
+      </c>
+      <c r="AG108">
+        <v>2.85</v>
+      </c>
+      <c r="AH108">
+        <v>1.37</v>
+      </c>
+      <c r="AI108">
+        <v>2.25</v>
+      </c>
+      <c r="AJ108">
+        <v>1.57</v>
+      </c>
+      <c r="AK108">
+        <v>1.66</v>
+      </c>
+      <c r="AL108">
+        <v>1.39</v>
+      </c>
+      <c r="AM108">
+        <v>1.24</v>
+      </c>
+      <c r="AN108">
+        <v>1.4</v>
+      </c>
+      <c r="AO108">
+        <v>1.5</v>
+      </c>
+      <c r="AP108">
+        <v>1.17</v>
+      </c>
+      <c r="AQ108">
+        <v>1.71</v>
+      </c>
+      <c r="AR108">
+        <v>0.86</v>
+      </c>
+      <c r="AS108">
+        <v>1.51</v>
+      </c>
+      <c r="AT108">
+        <v>2.37</v>
+      </c>
+      <c r="AU108">
+        <v>5</v>
+      </c>
+      <c r="AV108">
+        <v>3</v>
+      </c>
+      <c r="AW108">
+        <v>8</v>
+      </c>
+      <c r="AX108">
+        <v>1</v>
+      </c>
+      <c r="AY108">
+        <v>13</v>
+      </c>
+      <c r="AZ108">
+        <v>4</v>
+      </c>
+      <c r="BA108">
+        <v>10</v>
+      </c>
+      <c r="BB108">
+        <v>3</v>
+      </c>
+      <c r="BC108">
+        <v>13</v>
+      </c>
+      <c r="BD108">
+        <v>2.52</v>
+      </c>
+      <c r="BE108">
+        <v>8</v>
+      </c>
+      <c r="BF108">
+        <v>1.68</v>
+      </c>
+      <c r="BG108">
+        <v>1.36</v>
+      </c>
+      <c r="BH108">
+        <v>2.88</v>
+      </c>
+      <c r="BI108">
+        <v>1.67</v>
+      </c>
+      <c r="BJ108">
+        <v>2.19</v>
+      </c>
+      <c r="BK108">
+        <v>2.07</v>
+      </c>
+      <c r="BL108">
+        <v>1.74</v>
+      </c>
+      <c r="BM108">
+        <v>2.5</v>
+      </c>
+      <c r="BN108">
+        <v>1.48</v>
+      </c>
+      <c r="BO108">
+        <v>3.3</v>
+      </c>
+      <c r="BP108">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7729641</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F109">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>85</v>
+      </c>
+      <c r="H109" t="s">
+        <v>81</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>143</v>
+      </c>
+      <c r="P109" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q109">
+        <v>3.25</v>
+      </c>
+      <c r="R109">
+        <v>1.8</v>
+      </c>
+      <c r="S109">
+        <v>4.33</v>
+      </c>
+      <c r="T109">
+        <v>1.67</v>
+      </c>
+      <c r="U109">
+        <v>2.1</v>
+      </c>
+      <c r="V109">
+        <v>4.33</v>
+      </c>
+      <c r="W109">
+        <v>1.2</v>
+      </c>
+      <c r="X109">
+        <v>10</v>
+      </c>
+      <c r="Y109">
+        <v>1.03</v>
+      </c>
+      <c r="Z109">
+        <v>2.3</v>
+      </c>
+      <c r="AA109">
+        <v>2.75</v>
+      </c>
+      <c r="AB109">
+        <v>3.2</v>
+      </c>
+      <c r="AC109">
+        <v>0</v>
+      </c>
+      <c r="AD109">
+        <v>0</v>
+      </c>
+      <c r="AE109">
+        <v>1.61</v>
+      </c>
+      <c r="AF109">
+        <v>2.15</v>
+      </c>
+      <c r="AG109">
+        <v>3</v>
+      </c>
+      <c r="AH109">
+        <v>1.36</v>
+      </c>
+      <c r="AI109">
+        <v>2.5</v>
+      </c>
+      <c r="AJ109">
+        <v>1.5</v>
+      </c>
+      <c r="AK109">
+        <v>0</v>
+      </c>
+      <c r="AL109">
+        <v>0</v>
+      </c>
+      <c r="AM109">
+        <v>0</v>
+      </c>
+      <c r="AN109">
+        <v>1</v>
+      </c>
+      <c r="AO109">
+        <v>1.6</v>
+      </c>
+      <c r="AP109">
+        <v>1</v>
+      </c>
+      <c r="AQ109">
+        <v>1.5</v>
+      </c>
+      <c r="AR109">
+        <v>1.08</v>
+      </c>
+      <c r="AS109">
+        <v>1.23</v>
+      </c>
+      <c r="AT109">
+        <v>2.31</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>7</v>
+      </c>
+      <c r="AW109">
+        <v>12</v>
+      </c>
+      <c r="AX109">
+        <v>6</v>
+      </c>
+      <c r="AY109">
+        <v>16</v>
+      </c>
+      <c r="AZ109">
+        <v>13</v>
+      </c>
+      <c r="BA109">
+        <v>7</v>
+      </c>
+      <c r="BB109">
+        <v>6</v>
+      </c>
+      <c r="BC109">
+        <v>13</v>
+      </c>
+      <c r="BD109">
+        <v>0</v>
+      </c>
+      <c r="BE109">
+        <v>0</v>
+      </c>
+      <c r="BF109">
+        <v>0</v>
+      </c>
+      <c r="BG109">
+        <v>0</v>
+      </c>
+      <c r="BH109">
+        <v>0</v>
+      </c>
+      <c r="BI109">
+        <v>0</v>
+      </c>
+      <c r="BJ109">
+        <v>0</v>
+      </c>
+      <c r="BK109">
+        <v>0</v>
+      </c>
+      <c r="BL109">
+        <v>0</v>
+      </c>
+      <c r="BM109">
+        <v>0</v>
+      </c>
+      <c r="BN109">
+        <v>0</v>
+      </c>
+      <c r="BO109">
+        <v>0</v>
+      </c>
+      <c r="BP109">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="197">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -603,6 +603,9 @@
   <si>
     <t>['72']</t>
   </si>
+  <si>
+    <t>['4']</t>
+  </si>
 </sst>
 </file>
 
@@ -963,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1300,7 +1303,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ2">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2121,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6">
         <v>1.17</v>
@@ -2742,7 +2745,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2945,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ10">
         <v>1.83</v>
@@ -3772,7 +3775,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ14">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3975,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ15">
         <v>0.33</v>
@@ -5005,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
         <v>0.43</v>
@@ -5417,7 +5420,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -5626,7 +5629,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5832,7 +5835,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR24">
         <v>1.3</v>
@@ -8095,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -8510,7 +8513,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
         <v>2.48</v>
@@ -9743,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -10570,7 +10573,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ47">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR47">
         <v>1.24</v>
@@ -11600,7 +11603,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -12009,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -13039,10 +13042,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -14069,10 +14072,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ64">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14275,7 +14278,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ65">
         <v>0.43</v>
@@ -15308,7 +15311,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ70">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
         <v>1.68</v>
@@ -15511,7 +15514,7 @@
         <v>0.67</v>
       </c>
       <c r="AP71">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ71">
         <v>0.5</v>
@@ -16750,7 +16753,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ77">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
         <v>1.1</v>
@@ -16953,7 +16956,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ78">
         <v>2</v>
@@ -17571,7 +17574,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ81">
         <v>1.71</v>
@@ -17780,7 +17783,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR82">
         <v>1.26</v>
@@ -18601,7 +18604,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ86">
         <v>2</v>
@@ -20252,7 +20255,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ94">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20867,10 +20870,10 @@
         <v>1.75</v>
       </c>
       <c r="AP97">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ97">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.43</v>
@@ -21073,7 +21076,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98">
         <v>1.17</v>
@@ -21282,7 +21285,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -22103,7 +22106,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -23418,6 +23421,624 @@
       </c>
       <c r="BP109">
         <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7729642</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45699.45833333334</v>
+      </c>
+      <c r="F110">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>74</v>
+      </c>
+      <c r="H110" t="s">
+        <v>76</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>89</v>
+      </c>
+      <c r="P110" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q110">
+        <v>5</v>
+      </c>
+      <c r="R110">
+        <v>2.05</v>
+      </c>
+      <c r="S110">
+        <v>2.35</v>
+      </c>
+      <c r="T110">
+        <v>1.46</v>
+      </c>
+      <c r="U110">
+        <v>2.55</v>
+      </c>
+      <c r="V110">
+        <v>3.1</v>
+      </c>
+      <c r="W110">
+        <v>1.33</v>
+      </c>
+      <c r="X110">
+        <v>8.25</v>
+      </c>
+      <c r="Y110">
+        <v>1.06</v>
+      </c>
+      <c r="Z110">
+        <v>5.1</v>
+      </c>
+      <c r="AA110">
+        <v>3.4</v>
+      </c>
+      <c r="AB110">
+        <v>1.72</v>
+      </c>
+      <c r="AC110">
+        <v>1.07</v>
+      </c>
+      <c r="AD110">
+        <v>7.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.37</v>
+      </c>
+      <c r="AF110">
+        <v>2.9</v>
+      </c>
+      <c r="AG110">
+        <v>2.1</v>
+      </c>
+      <c r="AH110">
+        <v>1.61</v>
+      </c>
+      <c r="AI110">
+        <v>2.05</v>
+      </c>
+      <c r="AJ110">
+        <v>1.66</v>
+      </c>
+      <c r="AK110">
+        <v>2</v>
+      </c>
+      <c r="AL110">
+        <v>1.29</v>
+      </c>
+      <c r="AM110">
+        <v>1.18</v>
+      </c>
+      <c r="AN110">
+        <v>1.67</v>
+      </c>
+      <c r="AO110">
+        <v>1.4</v>
+      </c>
+      <c r="AP110">
+        <v>1.43</v>
+      </c>
+      <c r="AQ110">
+        <v>1.67</v>
+      </c>
+      <c r="AR110">
+        <v>1.41</v>
+      </c>
+      <c r="AS110">
+        <v>1.39</v>
+      </c>
+      <c r="AT110">
+        <v>2.8</v>
+      </c>
+      <c r="AU110">
+        <v>3</v>
+      </c>
+      <c r="AV110">
+        <v>3</v>
+      </c>
+      <c r="AW110">
+        <v>6</v>
+      </c>
+      <c r="AX110">
+        <v>4</v>
+      </c>
+      <c r="AY110">
+        <v>9</v>
+      </c>
+      <c r="AZ110">
+        <v>7</v>
+      </c>
+      <c r="BA110">
+        <v>2</v>
+      </c>
+      <c r="BB110">
+        <v>3</v>
+      </c>
+      <c r="BC110">
+        <v>5</v>
+      </c>
+      <c r="BD110">
+        <v>3.28</v>
+      </c>
+      <c r="BE110">
+        <v>8.4</v>
+      </c>
+      <c r="BF110">
+        <v>1.44</v>
+      </c>
+      <c r="BG110">
+        <v>1.31</v>
+      </c>
+      <c r="BH110">
+        <v>2.92</v>
+      </c>
+      <c r="BI110">
+        <v>1.58</v>
+      </c>
+      <c r="BJ110">
+        <v>2.12</v>
+      </c>
+      <c r="BK110">
+        <v>2.01</v>
+      </c>
+      <c r="BL110">
+        <v>1.68</v>
+      </c>
+      <c r="BM110">
+        <v>2.62</v>
+      </c>
+      <c r="BN110">
+        <v>1.38</v>
+      </c>
+      <c r="BO110">
+        <v>3.68</v>
+      </c>
+      <c r="BP110">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7729643</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45699.45833333334</v>
+      </c>
+      <c r="F111">
+        <v>13</v>
+      </c>
+      <c r="G111" t="s">
+        <v>83</v>
+      </c>
+      <c r="H111" t="s">
+        <v>82</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>89</v>
+      </c>
+      <c r="P111" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q111">
+        <v>3.6</v>
+      </c>
+      <c r="R111">
+        <v>1.83</v>
+      </c>
+      <c r="S111">
+        <v>3.5</v>
+      </c>
+      <c r="T111">
+        <v>1.62</v>
+      </c>
+      <c r="U111">
+        <v>2.2</v>
+      </c>
+      <c r="V111">
+        <v>4</v>
+      </c>
+      <c r="W111">
+        <v>1.22</v>
+      </c>
+      <c r="X111">
+        <v>9</v>
+      </c>
+      <c r="Y111">
+        <v>1.04</v>
+      </c>
+      <c r="Z111">
+        <v>2.82</v>
+      </c>
+      <c r="AA111">
+        <v>2.99</v>
+      </c>
+      <c r="AB111">
+        <v>2.62</v>
+      </c>
+      <c r="AC111">
+        <v>1.12</v>
+      </c>
+      <c r="AD111">
+        <v>5.88</v>
+      </c>
+      <c r="AE111">
+        <v>1.57</v>
+      </c>
+      <c r="AF111">
+        <v>2.15</v>
+      </c>
+      <c r="AG111">
+        <v>2.77</v>
+      </c>
+      <c r="AH111">
+        <v>1.43</v>
+      </c>
+      <c r="AI111">
+        <v>2.25</v>
+      </c>
+      <c r="AJ111">
+        <v>1.57</v>
+      </c>
+      <c r="AK111">
+        <v>1.44</v>
+      </c>
+      <c r="AL111">
+        <v>1.41</v>
+      </c>
+      <c r="AM111">
+        <v>1.38</v>
+      </c>
+      <c r="AN111">
+        <v>1.5</v>
+      </c>
+      <c r="AO111">
+        <v>1.17</v>
+      </c>
+      <c r="AP111">
+        <v>1.29</v>
+      </c>
+      <c r="AQ111">
+        <v>1.43</v>
+      </c>
+      <c r="AR111">
+        <v>1.6</v>
+      </c>
+      <c r="AS111">
+        <v>1.31</v>
+      </c>
+      <c r="AT111">
+        <v>2.91</v>
+      </c>
+      <c r="AU111">
+        <v>4</v>
+      </c>
+      <c r="AV111">
+        <v>3</v>
+      </c>
+      <c r="AW111">
+        <v>11</v>
+      </c>
+      <c r="AX111">
+        <v>2</v>
+      </c>
+      <c r="AY111">
+        <v>15</v>
+      </c>
+      <c r="AZ111">
+        <v>5</v>
+      </c>
+      <c r="BA111">
+        <v>10</v>
+      </c>
+      <c r="BB111">
+        <v>3</v>
+      </c>
+      <c r="BC111">
+        <v>13</v>
+      </c>
+      <c r="BD111">
+        <v>2.06</v>
+      </c>
+      <c r="BE111">
+        <v>6.05</v>
+      </c>
+      <c r="BF111">
+        <v>2.14</v>
+      </c>
+      <c r="BG111">
+        <v>1.36</v>
+      </c>
+      <c r="BH111">
+        <v>2.7</v>
+      </c>
+      <c r="BI111">
+        <v>1.68</v>
+      </c>
+      <c r="BJ111">
+        <v>2.01</v>
+      </c>
+      <c r="BK111">
+        <v>2.14</v>
+      </c>
+      <c r="BL111">
+        <v>1.57</v>
+      </c>
+      <c r="BM111">
+        <v>2.88</v>
+      </c>
+      <c r="BN111">
+        <v>1.32</v>
+      </c>
+      <c r="BO111">
+        <v>3.85</v>
+      </c>
+      <c r="BP111">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7729644</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45699.58333333334</v>
+      </c>
+      <c r="F112">
+        <v>13</v>
+      </c>
+      <c r="G112" t="s">
+        <v>78</v>
+      </c>
+      <c r="H112" t="s">
+        <v>79</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>136</v>
+      </c>
+      <c r="P112" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q112">
+        <v>1.69</v>
+      </c>
+      <c r="R112">
+        <v>2.44</v>
+      </c>
+      <c r="S112">
+        <v>10</v>
+      </c>
+      <c r="T112">
+        <v>1.36</v>
+      </c>
+      <c r="U112">
+        <v>2.9</v>
+      </c>
+      <c r="V112">
+        <v>2.7</v>
+      </c>
+      <c r="W112">
+        <v>1.41</v>
+      </c>
+      <c r="X112">
+        <v>7.3</v>
+      </c>
+      <c r="Y112">
+        <v>1.07</v>
+      </c>
+      <c r="Z112">
+        <v>1.27</v>
+      </c>
+      <c r="AA112">
+        <v>5</v>
+      </c>
+      <c r="AB112">
+        <v>12</v>
+      </c>
+      <c r="AC112">
+        <v>1.05</v>
+      </c>
+      <c r="AD112">
+        <v>8.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.31</v>
+      </c>
+      <c r="AF112">
+        <v>3.25</v>
+      </c>
+      <c r="AG112">
+        <v>1.95</v>
+      </c>
+      <c r="AH112">
+        <v>1.79</v>
+      </c>
+      <c r="AI112">
+        <v>2.6</v>
+      </c>
+      <c r="AJ112">
+        <v>1.43</v>
+      </c>
+      <c r="AK112">
+        <v>1.04</v>
+      </c>
+      <c r="AL112">
+        <v>1.13</v>
+      </c>
+      <c r="AM112">
+        <v>3.35</v>
+      </c>
+      <c r="AN112">
+        <v>2.33</v>
+      </c>
+      <c r="AO112">
+        <v>1.4</v>
+      </c>
+      <c r="AP112">
+        <v>2.43</v>
+      </c>
+      <c r="AQ112">
+        <v>1.17</v>
+      </c>
+      <c r="AR112">
+        <v>1.95</v>
+      </c>
+      <c r="AS112">
+        <v>0.97</v>
+      </c>
+      <c r="AT112">
+        <v>2.92</v>
+      </c>
+      <c r="AU112">
+        <v>3</v>
+      </c>
+      <c r="AV112">
+        <v>6</v>
+      </c>
+      <c r="AW112">
+        <v>4</v>
+      </c>
+      <c r="AX112">
+        <v>4</v>
+      </c>
+      <c r="AY112">
+        <v>7</v>
+      </c>
+      <c r="AZ112">
+        <v>10</v>
+      </c>
+      <c r="BA112">
+        <v>5</v>
+      </c>
+      <c r="BB112">
+        <v>6</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>1.27</v>
+      </c>
+      <c r="BE112">
+        <v>12</v>
+      </c>
+      <c r="BF112">
+        <v>4.05</v>
+      </c>
+      <c r="BG112">
+        <v>1.24</v>
+      </c>
+      <c r="BH112">
+        <v>3.34</v>
+      </c>
+      <c r="BI112">
+        <v>1.45</v>
+      </c>
+      <c r="BJ112">
+        <v>2.41</v>
+      </c>
+      <c r="BK112">
+        <v>1.81</v>
+      </c>
+      <c r="BL112">
+        <v>1.85</v>
+      </c>
+      <c r="BM112">
+        <v>2.28</v>
+      </c>
+      <c r="BN112">
+        <v>1.5</v>
+      </c>
+      <c r="BO112">
+        <v>3.08</v>
+      </c>
+      <c r="BP112">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="200">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['47', '87']</t>
+  </si>
+  <si>
+    <t>['8', '83', '90+8']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -966,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1222,7 +1231,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1428,7 +1437,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1712,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>1.5</v>
@@ -2046,7 +2055,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2252,7 +2261,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2330,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2458,7 +2467,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2539,7 +2548,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2870,7 +2879,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2951,7 +2960,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ10">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3076,7 +3085,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3363,7 +3372,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ12">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3488,7 +3497,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3694,7 +3703,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3900,7 +3909,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4106,7 +4115,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4596,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18">
         <v>0.5</v>
@@ -4805,7 +4814,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4930,7 +4939,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5136,7 +5145,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5214,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR21">
         <v>1.79</v>
@@ -5754,7 +5763,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5832,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.17</v>
@@ -5960,7 +5969,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6659,7 +6668,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ28">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR28">
         <v>0.89</v>
@@ -6865,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>0.83</v>
@@ -6990,7 +6999,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7895,7 +7904,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ34">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR34">
         <v>0.6899999999999999</v>
@@ -8020,7 +8029,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8304,7 +8313,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8432,7 +8441,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9050,7 +9059,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9131,7 +9140,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ40">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR40">
         <v>1.52</v>
@@ -9256,7 +9265,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9337,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR41">
         <v>1.57</v>
@@ -9540,7 +9549,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>0.43</v>
@@ -9668,7 +9677,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10080,7 +10089,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10492,7 +10501,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10904,7 +10913,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -10985,7 +10994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.04</v>
@@ -11188,7 +11197,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11316,7 +11325,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11397,7 +11406,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR51">
         <v>1.11</v>
@@ -11522,7 +11531,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11728,7 +11737,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11806,7 +11815,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -12552,7 +12561,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12630,7 +12639,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ57">
         <v>2</v>
@@ -12964,7 +12973,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13376,7 +13385,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13663,7 +13672,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -13869,7 +13878,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR63">
         <v>1.51</v>
@@ -14406,7 +14415,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14487,7 +14496,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ66">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR66">
         <v>1.26</v>
@@ -14693,7 +14702,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR67">
         <v>1.03</v>
@@ -14818,7 +14827,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15308,7 +15317,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ70">
         <v>1.17</v>
@@ -15642,7 +15651,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15723,7 +15732,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>1.61</v>
@@ -15926,7 +15935,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16054,7 +16063,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16132,10 +16141,10 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR74">
         <v>1.35</v>
@@ -16260,7 +16269,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16341,7 +16350,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ75">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.53</v>
@@ -16466,7 +16475,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16878,7 +16887,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17084,7 +17093,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17290,7 +17299,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -18195,7 +18204,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ84">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR84">
         <v>0.83</v>
@@ -18320,7 +18329,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18401,7 +18410,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ85">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR85">
         <v>1.49</v>
@@ -18526,7 +18535,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18732,7 +18741,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19144,7 +19153,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19222,7 +19231,7 @@
         <v>0.6</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89">
         <v>0.43</v>
@@ -19350,7 +19359,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19556,7 +19565,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19762,7 +19771,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19968,7 +19977,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20046,10 +20055,10 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.2</v>
@@ -20252,7 +20261,7 @@
         <v>1.75</v>
       </c>
       <c r="AP94">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ94">
         <v>1.67</v>
@@ -20667,7 +20676,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ96">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR96">
         <v>0.8</v>
@@ -20792,7 +20801,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21204,7 +21213,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21410,7 +21419,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21616,7 +21625,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21822,7 +21831,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22440,7 +22449,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22933,7 +22942,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ107">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23058,7 +23067,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23264,7 +23273,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23470,7 +23479,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23676,7 +23685,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24038,6 +24047,830 @@
         <v>3.08</v>
       </c>
       <c r="BP112">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7729645</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45700.45833333334</v>
+      </c>
+      <c r="F113">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>87</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>144</v>
+      </c>
+      <c r="P113" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q113">
+        <v>3.4</v>
+      </c>
+      <c r="R113">
+        <v>1.93</v>
+      </c>
+      <c r="S113">
+        <v>3.2</v>
+      </c>
+      <c r="T113">
+        <v>1.49</v>
+      </c>
+      <c r="U113">
+        <v>2.4</v>
+      </c>
+      <c r="V113">
+        <v>3.2</v>
+      </c>
+      <c r="W113">
+        <v>1.3</v>
+      </c>
+      <c r="X113">
+        <v>9</v>
+      </c>
+      <c r="Y113">
+        <v>1.06</v>
+      </c>
+      <c r="Z113">
+        <v>2.93</v>
+      </c>
+      <c r="AA113">
+        <v>2.88</v>
+      </c>
+      <c r="AB113">
+        <v>2.69</v>
+      </c>
+      <c r="AC113">
+        <v>1.09</v>
+      </c>
+      <c r="AD113">
+        <v>6.5</v>
+      </c>
+      <c r="AE113">
+        <v>1.42</v>
+      </c>
+      <c r="AF113">
+        <v>2.75</v>
+      </c>
+      <c r="AG113">
+        <v>2.35</v>
+      </c>
+      <c r="AH113">
+        <v>1.53</v>
+      </c>
+      <c r="AI113">
+        <v>1.95</v>
+      </c>
+      <c r="AJ113">
+        <v>1.75</v>
+      </c>
+      <c r="AK113">
+        <v>1.47</v>
+      </c>
+      <c r="AL113">
+        <v>1.36</v>
+      </c>
+      <c r="AM113">
+        <v>1.4</v>
+      </c>
+      <c r="AN113">
+        <v>1</v>
+      </c>
+      <c r="AO113">
+        <v>1.83</v>
+      </c>
+      <c r="AP113">
+        <v>1</v>
+      </c>
+      <c r="AQ113">
+        <v>1.71</v>
+      </c>
+      <c r="AR113">
+        <v>1.17</v>
+      </c>
+      <c r="AS113">
+        <v>1.32</v>
+      </c>
+      <c r="AT113">
+        <v>2.49</v>
+      </c>
+      <c r="AU113">
+        <v>6</v>
+      </c>
+      <c r="AV113">
+        <v>8</v>
+      </c>
+      <c r="AW113">
+        <v>3</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>9</v>
+      </c>
+      <c r="AZ113">
+        <v>11</v>
+      </c>
+      <c r="BA113">
+        <v>3</v>
+      </c>
+      <c r="BB113">
+        <v>5</v>
+      </c>
+      <c r="BC113">
+        <v>8</v>
+      </c>
+      <c r="BD113">
+        <v>2.11</v>
+      </c>
+      <c r="BE113">
+        <v>6.15</v>
+      </c>
+      <c r="BF113">
+        <v>2.08</v>
+      </c>
+      <c r="BG113">
+        <v>1.33</v>
+      </c>
+      <c r="BH113">
+        <v>2.83</v>
+      </c>
+      <c r="BI113">
+        <v>1.62</v>
+      </c>
+      <c r="BJ113">
+        <v>2.06</v>
+      </c>
+      <c r="BK113">
+        <v>2.09</v>
+      </c>
+      <c r="BL113">
+        <v>1.63</v>
+      </c>
+      <c r="BM113">
+        <v>2.74</v>
+      </c>
+      <c r="BN113">
+        <v>1.35</v>
+      </c>
+      <c r="BO113">
+        <v>3.85</v>
+      </c>
+      <c r="BP113">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7729646</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45700.45833333334</v>
+      </c>
+      <c r="F114">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>72</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>145</v>
+      </c>
+      <c r="P114" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q114">
+        <v>3.6</v>
+      </c>
+      <c r="R114">
+        <v>1.8</v>
+      </c>
+      <c r="S114">
+        <v>3.6</v>
+      </c>
+      <c r="T114">
+        <v>1.67</v>
+      </c>
+      <c r="U114">
+        <v>2.1</v>
+      </c>
+      <c r="V114">
+        <v>4.33</v>
+      </c>
+      <c r="W114">
+        <v>1.2</v>
+      </c>
+      <c r="X114">
+        <v>10</v>
+      </c>
+      <c r="Y114">
+        <v>1.03</v>
+      </c>
+      <c r="Z114">
+        <v>2.84</v>
+      </c>
+      <c r="AA114">
+        <v>2.79</v>
+      </c>
+      <c r="AB114">
+        <v>2.79</v>
+      </c>
+      <c r="AC114">
+        <v>1.14</v>
+      </c>
+      <c r="AD114">
+        <v>5.2</v>
+      </c>
+      <c r="AE114">
+        <v>1.57</v>
+      </c>
+      <c r="AF114">
+        <v>2.15</v>
+      </c>
+      <c r="AG114">
+        <v>2.99</v>
+      </c>
+      <c r="AH114">
+        <v>1.34</v>
+      </c>
+      <c r="AI114">
+        <v>2.38</v>
+      </c>
+      <c r="AJ114">
+        <v>1.53</v>
+      </c>
+      <c r="AK114">
+        <v>1.42</v>
+      </c>
+      <c r="AL114">
+        <v>1.41</v>
+      </c>
+      <c r="AM114">
+        <v>1.4</v>
+      </c>
+      <c r="AN114">
+        <v>0.67</v>
+      </c>
+      <c r="AO114">
+        <v>0.17</v>
+      </c>
+      <c r="AP114">
+        <v>1</v>
+      </c>
+      <c r="AQ114">
+        <v>0.14</v>
+      </c>
+      <c r="AR114">
+        <v>1.29</v>
+      </c>
+      <c r="AS114">
+        <v>1.06</v>
+      </c>
+      <c r="AT114">
+        <v>2.35</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>2</v>
+      </c>
+      <c r="AW114">
+        <v>3</v>
+      </c>
+      <c r="AX114">
+        <v>3</v>
+      </c>
+      <c r="AY114">
+        <v>8</v>
+      </c>
+      <c r="AZ114">
+        <v>5</v>
+      </c>
+      <c r="BA114">
+        <v>0</v>
+      </c>
+      <c r="BB114">
+        <v>2</v>
+      </c>
+      <c r="BC114">
+        <v>2</v>
+      </c>
+      <c r="BD114">
+        <v>0</v>
+      </c>
+      <c r="BE114">
+        <v>0</v>
+      </c>
+      <c r="BF114">
+        <v>0</v>
+      </c>
+      <c r="BG114">
+        <v>1.3</v>
+      </c>
+      <c r="BH114">
+        <v>3.2</v>
+      </c>
+      <c r="BI114">
+        <v>1.53</v>
+      </c>
+      <c r="BJ114">
+        <v>2.38</v>
+      </c>
+      <c r="BK114">
+        <v>1.9</v>
+      </c>
+      <c r="BL114">
+        <v>1.9</v>
+      </c>
+      <c r="BM114">
+        <v>2.3</v>
+      </c>
+      <c r="BN114">
+        <v>1.55</v>
+      </c>
+      <c r="BO114">
+        <v>3</v>
+      </c>
+      <c r="BP114">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7729648</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45700.58333333334</v>
+      </c>
+      <c r="F115">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>75</v>
+      </c>
+      <c r="H115" t="s">
+        <v>70</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>3</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>146</v>
+      </c>
+      <c r="P115" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q115">
+        <v>1.73</v>
+      </c>
+      <c r="R115">
+        <v>2.35</v>
+      </c>
+      <c r="S115">
+        <v>8.5</v>
+      </c>
+      <c r="T115">
+        <v>1.37</v>
+      </c>
+      <c r="U115">
+        <v>2.85</v>
+      </c>
+      <c r="V115">
+        <v>2.75</v>
+      </c>
+      <c r="W115">
+        <v>1.39</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>1.08</v>
+      </c>
+      <c r="Z115">
+        <v>1.29</v>
+      </c>
+      <c r="AA115">
+        <v>4.8</v>
+      </c>
+      <c r="AB115">
+        <v>11</v>
+      </c>
+      <c r="AC115">
+        <v>1.04</v>
+      </c>
+      <c r="AD115">
+        <v>9</v>
+      </c>
+      <c r="AE115">
+        <v>1.3</v>
+      </c>
+      <c r="AF115">
+        <v>3.35</v>
+      </c>
+      <c r="AG115">
+        <v>1.87</v>
+      </c>
+      <c r="AH115">
+        <v>1.87</v>
+      </c>
+      <c r="AI115">
+        <v>2.6</v>
+      </c>
+      <c r="AJ115">
+        <v>1.43</v>
+      </c>
+      <c r="AK115">
+        <v>1.05</v>
+      </c>
+      <c r="AL115">
+        <v>1.15</v>
+      </c>
+      <c r="AM115">
+        <v>3.6</v>
+      </c>
+      <c r="AN115">
+        <v>2.6</v>
+      </c>
+      <c r="AO115">
+        <v>1.17</v>
+      </c>
+      <c r="AP115">
+        <v>2.67</v>
+      </c>
+      <c r="AQ115">
+        <v>1</v>
+      </c>
+      <c r="AR115">
+        <v>1.73</v>
+      </c>
+      <c r="AS115">
+        <v>1.01</v>
+      </c>
+      <c r="AT115">
+        <v>2.74</v>
+      </c>
+      <c r="AU115">
+        <v>5</v>
+      </c>
+      <c r="AV115">
+        <v>2</v>
+      </c>
+      <c r="AW115">
+        <v>8</v>
+      </c>
+      <c r="AX115">
+        <v>4</v>
+      </c>
+      <c r="AY115">
+        <v>13</v>
+      </c>
+      <c r="AZ115">
+        <v>6</v>
+      </c>
+      <c r="BA115">
+        <v>7</v>
+      </c>
+      <c r="BB115">
+        <v>8</v>
+      </c>
+      <c r="BC115">
+        <v>15</v>
+      </c>
+      <c r="BD115">
+        <v>1.23</v>
+      </c>
+      <c r="BE115">
+        <v>12.25</v>
+      </c>
+      <c r="BF115">
+        <v>4.5</v>
+      </c>
+      <c r="BG115">
+        <v>1.27</v>
+      </c>
+      <c r="BH115">
+        <v>3.14</v>
+      </c>
+      <c r="BI115">
+        <v>1.51</v>
+      </c>
+      <c r="BJ115">
+        <v>2.26</v>
+      </c>
+      <c r="BK115">
+        <v>1.88</v>
+      </c>
+      <c r="BL115">
+        <v>1.78</v>
+      </c>
+      <c r="BM115">
+        <v>2.43</v>
+      </c>
+      <c r="BN115">
+        <v>1.44</v>
+      </c>
+      <c r="BO115">
+        <v>3.28</v>
+      </c>
+      <c r="BP115">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7729647</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45700.58333333334</v>
+      </c>
+      <c r="F116">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>86</v>
+      </c>
+      <c r="H116" t="s">
+        <v>85</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" t="s">
+        <v>89</v>
+      </c>
+      <c r="P116" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q116">
+        <v>2.88</v>
+      </c>
+      <c r="R116">
+        <v>1.83</v>
+      </c>
+      <c r="S116">
+        <v>4.5</v>
+      </c>
+      <c r="T116">
+        <v>1.62</v>
+      </c>
+      <c r="U116">
+        <v>2.2</v>
+      </c>
+      <c r="V116">
+        <v>4</v>
+      </c>
+      <c r="W116">
+        <v>1.22</v>
+      </c>
+      <c r="X116">
+        <v>9</v>
+      </c>
+      <c r="Y116">
+        <v>1.04</v>
+      </c>
+      <c r="Z116">
+        <v>2.28</v>
+      </c>
+      <c r="AA116">
+        <v>2.86</v>
+      </c>
+      <c r="AB116">
+        <v>3.55</v>
+      </c>
+      <c r="AC116">
+        <v>1.13</v>
+      </c>
+      <c r="AD116">
+        <v>5.4</v>
+      </c>
+      <c r="AE116">
+        <v>1.57</v>
+      </c>
+      <c r="AF116">
+        <v>2.15</v>
+      </c>
+      <c r="AG116">
+        <v>2.89</v>
+      </c>
+      <c r="AH116">
+        <v>1.36</v>
+      </c>
+      <c r="AI116">
+        <v>2.38</v>
+      </c>
+      <c r="AJ116">
+        <v>1.53</v>
+      </c>
+      <c r="AK116">
+        <v>1.27</v>
+      </c>
+      <c r="AL116">
+        <v>1.39</v>
+      </c>
+      <c r="AM116">
+        <v>1.62</v>
+      </c>
+      <c r="AN116">
+        <v>2</v>
+      </c>
+      <c r="AO116">
+        <v>2</v>
+      </c>
+      <c r="AP116">
+        <v>1.83</v>
+      </c>
+      <c r="AQ116">
+        <v>1.86</v>
+      </c>
+      <c r="AR116">
+        <v>1.12</v>
+      </c>
+      <c r="AS116">
+        <v>1.05</v>
+      </c>
+      <c r="AT116">
+        <v>2.17</v>
+      </c>
+      <c r="AU116">
+        <v>3</v>
+      </c>
+      <c r="AV116">
+        <v>2</v>
+      </c>
+      <c r="AW116">
+        <v>3</v>
+      </c>
+      <c r="AX116">
+        <v>7</v>
+      </c>
+      <c r="AY116">
+        <v>6</v>
+      </c>
+      <c r="AZ116">
+        <v>9</v>
+      </c>
+      <c r="BA116">
+        <v>5</v>
+      </c>
+      <c r="BB116">
+        <v>8</v>
+      </c>
+      <c r="BC116">
+        <v>13</v>
+      </c>
+      <c r="BD116">
+        <v>1.6</v>
+      </c>
+      <c r="BE116">
+        <v>6.6</v>
+      </c>
+      <c r="BF116">
+        <v>2.93</v>
+      </c>
+      <c r="BG116">
+        <v>1.23</v>
+      </c>
+      <c r="BH116">
+        <v>3.42</v>
+      </c>
+      <c r="BI116">
+        <v>1.44</v>
+      </c>
+      <c r="BJ116">
+        <v>2.43</v>
+      </c>
+      <c r="BK116">
+        <v>1.79</v>
+      </c>
+      <c r="BL116">
+        <v>1.87</v>
+      </c>
+      <c r="BM116">
+        <v>2.28</v>
+      </c>
+      <c r="BN116">
+        <v>1.5</v>
+      </c>
+      <c r="BO116">
+        <v>3.08</v>
+      </c>
+      <c r="BP116">
         <v>1.28</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,9 @@
     <t>['8', '83', '90+8']</t>
   </si>
   <si>
+    <t>['90+13']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -614,6 +617,9 @@
   </si>
   <si>
     <t>['4']</t>
+  </si>
+  <si>
+    <t>['52']</t>
   </si>
 </sst>
 </file>
@@ -975,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1231,7 +1237,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1437,7 +1443,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2055,7 +2061,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2136,7 +2142,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2261,7 +2267,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2467,7 +2473,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2879,7 +2885,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3085,7 +3091,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3166,7 +3172,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ11">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3497,7 +3503,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3703,7 +3709,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3909,7 +3915,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4115,7 +4121,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4193,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ16">
         <v>2</v>
@@ -4939,7 +4945,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5145,7 +5151,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5432,7 +5438,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5763,7 +5769,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5969,7 +5975,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6999,7 +7005,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7286,7 +7292,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ31">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AR31">
         <v>1.06</v>
@@ -7901,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ34">
         <v>0.14</v>
@@ -8029,7 +8035,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8441,7 +8447,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9059,7 +9065,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9265,7 +9271,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9677,7 +9683,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9964,7 +9970,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -10089,7 +10095,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10501,7 +10507,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10913,7 +10919,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11325,7 +11331,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11531,7 +11537,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11737,7 +11743,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12230,7 +12236,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ55">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AR55">
         <v>0.74</v>
@@ -12436,7 +12442,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ56">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12561,7 +12567,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12845,7 +12851,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -12973,7 +12979,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13385,7 +13391,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14415,7 +14421,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14827,7 +14833,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15651,7 +15657,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16063,7 +16069,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16269,7 +16275,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16475,7 +16481,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16553,10 +16559,10 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ76">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AR76">
         <v>0.77</v>
@@ -16887,7 +16893,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17093,7 +17099,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17174,7 +17180,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17299,7 +17305,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -18329,7 +18335,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18535,7 +18541,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18741,7 +18747,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19153,7 +19159,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19359,7 +19365,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19565,7 +19571,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19771,7 +19777,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19852,7 +19858,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AR92">
         <v>1.04</v>
@@ -19977,7 +19983,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20673,7 +20679,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ96">
         <v>1.86</v>
@@ -20801,7 +20807,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21088,7 +21094,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ98">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR98">
         <v>1.73</v>
@@ -21213,7 +21219,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21419,7 +21425,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21625,7 +21631,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21831,7 +21837,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22449,7 +22455,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23067,7 +23073,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23273,7 +23279,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23479,7 +23485,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23685,7 +23691,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24872,6 +24878,418 @@
       </c>
       <c r="BP116">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7729649</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45701.45833333334</v>
+      </c>
+      <c r="F117">
+        <v>13</v>
+      </c>
+      <c r="G117" t="s">
+        <v>73</v>
+      </c>
+      <c r="H117" t="s">
+        <v>71</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117" t="s">
+        <v>89</v>
+      </c>
+      <c r="P117" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q117">
+        <v>3.35</v>
+      </c>
+      <c r="R117">
+        <v>1.74</v>
+      </c>
+      <c r="S117">
+        <v>4.3</v>
+      </c>
+      <c r="T117">
+        <v>1.76</v>
+      </c>
+      <c r="U117">
+        <v>1.97</v>
+      </c>
+      <c r="V117">
+        <v>4.33</v>
+      </c>
+      <c r="W117">
+        <v>1.18</v>
+      </c>
+      <c r="X117">
+        <v>13.5</v>
+      </c>
+      <c r="Y117">
+        <v>1</v>
+      </c>
+      <c r="Z117">
+        <v>2.47</v>
+      </c>
+      <c r="AA117">
+        <v>2.61</v>
+      </c>
+      <c r="AB117">
+        <v>3.55</v>
+      </c>
+      <c r="AC117">
+        <v>1.17</v>
+      </c>
+      <c r="AD117">
+        <v>4.6</v>
+      </c>
+      <c r="AE117">
+        <v>1.77</v>
+      </c>
+      <c r="AF117">
+        <v>1.98</v>
+      </c>
+      <c r="AG117">
+        <v>3.09</v>
+      </c>
+      <c r="AH117">
+        <v>1.32</v>
+      </c>
+      <c r="AI117">
+        <v>2.48</v>
+      </c>
+      <c r="AJ117">
+        <v>1.49</v>
+      </c>
+      <c r="AK117">
+        <v>1.3</v>
+      </c>
+      <c r="AL117">
+        <v>1.41</v>
+      </c>
+      <c r="AM117">
+        <v>1.48</v>
+      </c>
+      <c r="AN117">
+        <v>1</v>
+      </c>
+      <c r="AO117">
+        <v>2.4</v>
+      </c>
+      <c r="AP117">
+        <v>1</v>
+      </c>
+      <c r="AQ117">
+        <v>2.17</v>
+      </c>
+      <c r="AR117">
+        <v>1.15</v>
+      </c>
+      <c r="AS117">
+        <v>1.2</v>
+      </c>
+      <c r="AT117">
+        <v>2.35</v>
+      </c>
+      <c r="AU117">
+        <v>2</v>
+      </c>
+      <c r="AV117">
+        <v>4</v>
+      </c>
+      <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>6</v>
+      </c>
+      <c r="AY117">
+        <v>6</v>
+      </c>
+      <c r="AZ117">
+        <v>10</v>
+      </c>
+      <c r="BA117">
+        <v>3</v>
+      </c>
+      <c r="BB117">
+        <v>1</v>
+      </c>
+      <c r="BC117">
+        <v>4</v>
+      </c>
+      <c r="BD117">
+        <v>1.71</v>
+      </c>
+      <c r="BE117">
+        <v>6.2</v>
+      </c>
+      <c r="BF117">
+        <v>2.69</v>
+      </c>
+      <c r="BG117">
+        <v>1.37</v>
+      </c>
+      <c r="BH117">
+        <v>2.66</v>
+      </c>
+      <c r="BI117">
+        <v>1.7</v>
+      </c>
+      <c r="BJ117">
+        <v>1.98</v>
+      </c>
+      <c r="BK117">
+        <v>2.17</v>
+      </c>
+      <c r="BL117">
+        <v>1.55</v>
+      </c>
+      <c r="BM117">
+        <v>2.92</v>
+      </c>
+      <c r="BN117">
+        <v>1.31</v>
+      </c>
+      <c r="BO117">
+        <v>3.95</v>
+      </c>
+      <c r="BP117">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7729650</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45701.58333333334</v>
+      </c>
+      <c r="F118">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>84</v>
+      </c>
+      <c r="H118" t="s">
+        <v>80</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>147</v>
+      </c>
+      <c r="P118" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q118">
+        <v>3.6</v>
+      </c>
+      <c r="R118">
+        <v>1.73</v>
+      </c>
+      <c r="S118">
+        <v>4</v>
+      </c>
+      <c r="T118">
+        <v>1.78</v>
+      </c>
+      <c r="U118">
+        <v>1.95</v>
+      </c>
+      <c r="V118">
+        <v>4.33</v>
+      </c>
+      <c r="W118">
+        <v>1.18</v>
+      </c>
+      <c r="X118">
+        <v>13.25</v>
+      </c>
+      <c r="Y118">
+        <v>1.01</v>
+      </c>
+      <c r="Z118">
+        <v>2.6</v>
+      </c>
+      <c r="AA118">
+        <v>2.63</v>
+      </c>
+      <c r="AB118">
+        <v>3.28</v>
+      </c>
+      <c r="AC118">
+        <v>1.17</v>
+      </c>
+      <c r="AD118">
+        <v>4.6</v>
+      </c>
+      <c r="AE118">
+        <v>1.75</v>
+      </c>
+      <c r="AF118">
+        <v>2</v>
+      </c>
+      <c r="AG118">
+        <v>3.41</v>
+      </c>
+      <c r="AH118">
+        <v>1.27</v>
+      </c>
+      <c r="AI118">
+        <v>2.5</v>
+      </c>
+      <c r="AJ118">
+        <v>1.48</v>
+      </c>
+      <c r="AK118">
+        <v>1.35</v>
+      </c>
+      <c r="AL118">
+        <v>1.4</v>
+      </c>
+      <c r="AM118">
+        <v>1.42</v>
+      </c>
+      <c r="AN118">
+        <v>0.8</v>
+      </c>
+      <c r="AO118">
+        <v>1.17</v>
+      </c>
+      <c r="AP118">
+        <v>0.83</v>
+      </c>
+      <c r="AQ118">
+        <v>1.14</v>
+      </c>
+      <c r="AR118">
+        <v>0.78</v>
+      </c>
+      <c r="AS118">
+        <v>1.03</v>
+      </c>
+      <c r="AT118">
+        <v>1.81</v>
+      </c>
+      <c r="AU118">
+        <v>8</v>
+      </c>
+      <c r="AV118">
+        <v>2</v>
+      </c>
+      <c r="AW118">
+        <v>5</v>
+      </c>
+      <c r="AX118">
+        <v>3</v>
+      </c>
+      <c r="AY118">
+        <v>13</v>
+      </c>
+      <c r="AZ118">
+        <v>5</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>1</v>
+      </c>
+      <c r="BC118">
+        <v>4</v>
+      </c>
+      <c r="BD118">
+        <v>1.82</v>
+      </c>
+      <c r="BE118">
+        <v>7.8</v>
+      </c>
+      <c r="BF118">
+        <v>2.27</v>
+      </c>
+      <c r="BG118">
+        <v>1.33</v>
+      </c>
+      <c r="BH118">
+        <v>2.83</v>
+      </c>
+      <c r="BI118">
+        <v>1.68</v>
+      </c>
+      <c r="BJ118">
+        <v>2.14</v>
+      </c>
+      <c r="BK118">
+        <v>2.12</v>
+      </c>
+      <c r="BL118">
+        <v>1.7</v>
+      </c>
+      <c r="BM118">
+        <v>2.7</v>
+      </c>
+      <c r="BN118">
+        <v>1.36</v>
+      </c>
+      <c r="BO118">
+        <v>3.82</v>
+      </c>
+      <c r="BP118">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,12 @@
     <t>['90+13']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['23', '74']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -620,6 +626,12 @@
   </si>
   <si>
     <t>['52']</t>
+  </si>
+  <si>
+    <t>['21', '61', '75', '87']</t>
+  </si>
+  <si>
+    <t>['9', '51', '83', '87']</t>
   </si>
 </sst>
 </file>
@@ -981,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1237,7 +1249,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1315,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.43</v>
@@ -1443,7 +1455,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2061,7 +2073,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2267,7 +2279,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2348,7 +2360,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2473,7 +2485,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2551,10 +2563,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ8">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2757,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ9">
         <v>1.17</v>
@@ -2885,7 +2897,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3091,7 +3103,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3503,7 +3515,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3584,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3709,7 +3721,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3787,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>1.67</v>
@@ -3915,7 +3927,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4121,7 +4133,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4408,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4945,7 +4957,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5151,7 +5163,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5232,7 +5244,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ21">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>1.79</v>
@@ -5769,7 +5781,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5975,7 +5987,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6053,7 +6065,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ25">
         <v>1.71</v>
@@ -6259,10 +6271,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6671,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1.71</v>
@@ -7005,7 +7017,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7498,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -7701,7 +7713,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0.5</v>
@@ -8035,7 +8047,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8116,7 +8128,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR35">
         <v>2.03</v>
@@ -8447,7 +8459,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8731,7 +8743,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>1.71</v>
@@ -8940,7 +8952,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR39">
         <v>1.3</v>
@@ -9065,7 +9077,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9143,7 +9155,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ40">
         <v>1.71</v>
@@ -9271,7 +9283,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9352,7 +9364,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>1.57</v>
@@ -9683,7 +9695,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10095,7 +10107,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10173,7 +10185,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10507,7 +10519,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10919,7 +10931,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -10997,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11206,7 +11218,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR50">
         <v>1.6</v>
@@ -11331,7 +11343,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11537,7 +11549,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11615,7 +11627,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ52">
         <v>1.17</v>
@@ -11743,7 +11755,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11824,7 +11836,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR53">
         <v>0.97</v>
@@ -12233,7 +12245,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>2.17</v>
@@ -12439,7 +12451,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ56">
         <v>1.14</v>
@@ -12567,7 +12579,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12854,7 +12866,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR58">
         <v>0.89</v>
@@ -12979,7 +12991,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13266,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR60">
         <v>1.01</v>
@@ -13391,7 +13403,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13884,7 +13896,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ63">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.51</v>
@@ -14421,7 +14433,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14833,7 +14845,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15117,7 +15129,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
         <v>0.33</v>
@@ -15657,7 +15669,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15735,7 +15747,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -15944,7 +15956,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR73">
         <v>1.04</v>
@@ -16069,7 +16081,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16150,7 +16162,7 @@
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.35</v>
@@ -16275,7 +16287,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16481,7 +16493,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16765,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -16893,7 +16905,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -16974,7 +16986,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17099,7 +17111,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17305,7 +17317,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -18004,7 +18016,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR83">
         <v>1.22</v>
@@ -18335,7 +18347,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18541,7 +18553,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18747,7 +18759,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18825,7 +18837,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ87">
         <v>0.5</v>
@@ -19031,7 +19043,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>0.33</v>
@@ -19159,7 +19171,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19365,7 +19377,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19446,7 +19458,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>1.09</v>
@@ -19571,7 +19583,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19649,7 +19661,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
         <v>1.5</v>
@@ -19777,7 +19789,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19855,7 +19867,7 @@
         <v>2.25</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ92">
         <v>2.17</v>
@@ -19983,7 +19995,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20682,7 +20694,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ96">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR96">
         <v>0.8</v>
@@ -20807,7 +20819,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21219,7 +21231,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21425,7 +21437,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21506,7 +21518,7 @@
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -21631,7 +21643,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21837,7 +21849,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -21918,7 +21930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR102">
         <v>1.53</v>
@@ -22124,7 +22136,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR103">
         <v>2.01</v>
@@ -22327,7 +22339,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
         <v>0.43</v>
@@ -22455,7 +22467,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22533,7 +22545,7 @@
         <v>1.83</v>
       </c>
       <c r="AP105">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>2</v>
@@ -22945,7 +22957,7 @@
         <v>0.2</v>
       </c>
       <c r="AP107">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ107">
         <v>0.14</v>
@@ -23073,7 +23085,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23279,7 +23291,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23485,7 +23497,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23691,7 +23703,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24802,7 +24814,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ116">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR116">
         <v>1.12</v>
@@ -25133,7 +25145,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25290,6 +25302,830 @@
       </c>
       <c r="BP118">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7729651</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F119">
+        <v>14</v>
+      </c>
+      <c r="G119" t="s">
+        <v>76</v>
+      </c>
+      <c r="H119" t="s">
+        <v>83</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>2</v>
+      </c>
+      <c r="O119" t="s">
+        <v>116</v>
+      </c>
+      <c r="P119" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q119">
+        <v>2.15</v>
+      </c>
+      <c r="R119">
+        <v>2.2</v>
+      </c>
+      <c r="S119">
+        <v>5.25</v>
+      </c>
+      <c r="T119">
+        <v>1.37</v>
+      </c>
+      <c r="U119">
+        <v>2.8</v>
+      </c>
+      <c r="V119">
+        <v>2.7</v>
+      </c>
+      <c r="W119">
+        <v>1.41</v>
+      </c>
+      <c r="X119">
+        <v>6.75</v>
+      </c>
+      <c r="Y119">
+        <v>1.09</v>
+      </c>
+      <c r="Z119">
+        <v>1.73</v>
+      </c>
+      <c r="AA119">
+        <v>3.38</v>
+      </c>
+      <c r="AB119">
+        <v>5.1</v>
+      </c>
+      <c r="AC119">
+        <v>1.05</v>
+      </c>
+      <c r="AD119">
+        <v>8.5</v>
+      </c>
+      <c r="AE119">
+        <v>1.3</v>
+      </c>
+      <c r="AF119">
+        <v>3.35</v>
+      </c>
+      <c r="AG119">
+        <v>1.92</v>
+      </c>
+      <c r="AH119">
+        <v>1.82</v>
+      </c>
+      <c r="AI119">
+        <v>1.9</v>
+      </c>
+      <c r="AJ119">
+        <v>1.78</v>
+      </c>
+      <c r="AK119">
+        <v>1.15</v>
+      </c>
+      <c r="AL119">
+        <v>1.24</v>
+      </c>
+      <c r="AM119">
+        <v>2.25</v>
+      </c>
+      <c r="AN119">
+        <v>2.29</v>
+      </c>
+      <c r="AO119">
+        <v>1.33</v>
+      </c>
+      <c r="AP119">
+        <v>2.13</v>
+      </c>
+      <c r="AQ119">
+        <v>1.29</v>
+      </c>
+      <c r="AR119">
+        <v>1.64</v>
+      </c>
+      <c r="AS119">
+        <v>1.24</v>
+      </c>
+      <c r="AT119">
+        <v>2.88</v>
+      </c>
+      <c r="AU119">
+        <v>4</v>
+      </c>
+      <c r="AV119">
+        <v>4</v>
+      </c>
+      <c r="AW119">
+        <v>8</v>
+      </c>
+      <c r="AX119">
+        <v>9</v>
+      </c>
+      <c r="AY119">
+        <v>12</v>
+      </c>
+      <c r="AZ119">
+        <v>13</v>
+      </c>
+      <c r="BA119">
+        <v>6</v>
+      </c>
+      <c r="BB119">
+        <v>6</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>1.4</v>
+      </c>
+      <c r="BE119">
+        <v>8.9</v>
+      </c>
+      <c r="BF119">
+        <v>3.44</v>
+      </c>
+      <c r="BG119">
+        <v>1.24</v>
+      </c>
+      <c r="BH119">
+        <v>3.34</v>
+      </c>
+      <c r="BI119">
+        <v>1.47</v>
+      </c>
+      <c r="BJ119">
+        <v>2.35</v>
+      </c>
+      <c r="BK119">
+        <v>1.83</v>
+      </c>
+      <c r="BL119">
+        <v>1.83</v>
+      </c>
+      <c r="BM119">
+        <v>2.33</v>
+      </c>
+      <c r="BN119">
+        <v>1.48</v>
+      </c>
+      <c r="BO119">
+        <v>3.14</v>
+      </c>
+      <c r="BP119">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7729652</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F120">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>82</v>
+      </c>
+      <c r="H120" t="s">
+        <v>85</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>4</v>
+      </c>
+      <c r="N120">
+        <v>5</v>
+      </c>
+      <c r="O120" t="s">
+        <v>148</v>
+      </c>
+      <c r="P120" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q120">
+        <v>2.95</v>
+      </c>
+      <c r="R120">
+        <v>1.88</v>
+      </c>
+      <c r="S120">
+        <v>4</v>
+      </c>
+      <c r="T120">
+        <v>1.55</v>
+      </c>
+      <c r="U120">
+        <v>2.25</v>
+      </c>
+      <c r="V120">
+        <v>3.6</v>
+      </c>
+      <c r="W120">
+        <v>1.25</v>
+      </c>
+      <c r="X120">
+        <v>10.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.04</v>
+      </c>
+      <c r="Z120">
+        <v>2.3</v>
+      </c>
+      <c r="AA120">
+        <v>2.65</v>
+      </c>
+      <c r="AB120">
+        <v>3.88</v>
+      </c>
+      <c r="AC120">
+        <v>1.12</v>
+      </c>
+      <c r="AD120">
+        <v>5.8</v>
+      </c>
+      <c r="AE120">
+        <v>1.48</v>
+      </c>
+      <c r="AF120">
+        <v>2.37</v>
+      </c>
+      <c r="AG120">
+        <v>2.69</v>
+      </c>
+      <c r="AH120">
+        <v>1.41</v>
+      </c>
+      <c r="AI120">
+        <v>2.15</v>
+      </c>
+      <c r="AJ120">
+        <v>1.61</v>
+      </c>
+      <c r="AK120">
+        <v>1.3</v>
+      </c>
+      <c r="AL120">
+        <v>1.36</v>
+      </c>
+      <c r="AM120">
+        <v>1.6</v>
+      </c>
+      <c r="AN120">
+        <v>1.17</v>
+      </c>
+      <c r="AO120">
+        <v>1.86</v>
+      </c>
+      <c r="AP120">
+        <v>1</v>
+      </c>
+      <c r="AQ120">
+        <v>2</v>
+      </c>
+      <c r="AR120">
+        <v>1.58</v>
+      </c>
+      <c r="AS120">
+        <v>1.06</v>
+      </c>
+      <c r="AT120">
+        <v>2.64</v>
+      </c>
+      <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
+        <v>6</v>
+      </c>
+      <c r="AW120">
+        <v>3</v>
+      </c>
+      <c r="AX120">
+        <v>4</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>10</v>
+      </c>
+      <c r="BA120">
+        <v>6</v>
+      </c>
+      <c r="BB120">
+        <v>3</v>
+      </c>
+      <c r="BC120">
+        <v>9</v>
+      </c>
+      <c r="BD120">
+        <v>1.88</v>
+      </c>
+      <c r="BE120">
+        <v>6.25</v>
+      </c>
+      <c r="BF120">
+        <v>2.35</v>
+      </c>
+      <c r="BG120">
+        <v>1.28</v>
+      </c>
+      <c r="BH120">
+        <v>3.08</v>
+      </c>
+      <c r="BI120">
+        <v>1.52</v>
+      </c>
+      <c r="BJ120">
+        <v>2.24</v>
+      </c>
+      <c r="BK120">
+        <v>1.92</v>
+      </c>
+      <c r="BL120">
+        <v>1.75</v>
+      </c>
+      <c r="BM120">
+        <v>2.49</v>
+      </c>
+      <c r="BN120">
+        <v>1.42</v>
+      </c>
+      <c r="BO120">
+        <v>3.42</v>
+      </c>
+      <c r="BP120">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7729653</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45704.5625</v>
+      </c>
+      <c r="F121">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>70</v>
+      </c>
+      <c r="H121" t="s">
+        <v>74</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>149</v>
+      </c>
+      <c r="P121" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q121">
+        <v>3.5</v>
+      </c>
+      <c r="R121">
+        <v>1.78</v>
+      </c>
+      <c r="S121">
+        <v>3.6</v>
+      </c>
+      <c r="T121">
+        <v>1.63</v>
+      </c>
+      <c r="U121">
+        <v>2.1</v>
+      </c>
+      <c r="V121">
+        <v>3.9</v>
+      </c>
+      <c r="W121">
+        <v>1.21</v>
+      </c>
+      <c r="X121">
+        <v>12</v>
+      </c>
+      <c r="Y121">
+        <v>1.03</v>
+      </c>
+      <c r="Z121">
+        <v>2.91</v>
+      </c>
+      <c r="AA121">
+        <v>2.47</v>
+      </c>
+      <c r="AB121">
+        <v>3.11</v>
+      </c>
+      <c r="AC121">
+        <v>1.15</v>
+      </c>
+      <c r="AD121">
+        <v>5</v>
+      </c>
+      <c r="AE121">
+        <v>1.6</v>
+      </c>
+      <c r="AF121">
+        <v>2.1</v>
+      </c>
+      <c r="AG121">
+        <v>2.99</v>
+      </c>
+      <c r="AH121">
+        <v>1.34</v>
+      </c>
+      <c r="AI121">
+        <v>2.25</v>
+      </c>
+      <c r="AJ121">
+        <v>1.55</v>
+      </c>
+      <c r="AK121">
+        <v>1.39</v>
+      </c>
+      <c r="AL121">
+        <v>1.41</v>
+      </c>
+      <c r="AM121">
+        <v>1.43</v>
+      </c>
+      <c r="AN121">
+        <v>1.83</v>
+      </c>
+      <c r="AO121">
+        <v>1.33</v>
+      </c>
+      <c r="AP121">
+        <v>2</v>
+      </c>
+      <c r="AQ121">
+        <v>1.14</v>
+      </c>
+      <c r="AR121">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS121">
+        <v>0.88</v>
+      </c>
+      <c r="AT121">
+        <v>1.82</v>
+      </c>
+      <c r="AU121">
+        <v>7</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>2</v>
+      </c>
+      <c r="AX121">
+        <v>8</v>
+      </c>
+      <c r="AY121">
+        <v>9</v>
+      </c>
+      <c r="AZ121">
+        <v>12</v>
+      </c>
+      <c r="BA121">
+        <v>10</v>
+      </c>
+      <c r="BB121">
+        <v>3</v>
+      </c>
+      <c r="BC121">
+        <v>13</v>
+      </c>
+      <c r="BD121">
+        <v>1.99</v>
+      </c>
+      <c r="BE121">
+        <v>6</v>
+      </c>
+      <c r="BF121">
+        <v>2.23</v>
+      </c>
+      <c r="BG121">
+        <v>1.42</v>
+      </c>
+      <c r="BH121">
+        <v>2.49</v>
+      </c>
+      <c r="BI121">
+        <v>1.79</v>
+      </c>
+      <c r="BJ121">
+        <v>1.87</v>
+      </c>
+      <c r="BK121">
+        <v>2.3</v>
+      </c>
+      <c r="BL121">
+        <v>1.49</v>
+      </c>
+      <c r="BM121">
+        <v>3.14</v>
+      </c>
+      <c r="BN121">
+        <v>1.27</v>
+      </c>
+      <c r="BO121">
+        <v>3.8</v>
+      </c>
+      <c r="BP121">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7729654</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45704.58333333334</v>
+      </c>
+      <c r="F122">
+        <v>14</v>
+      </c>
+      <c r="G122" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" t="s">
+        <v>78</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>4</v>
+      </c>
+      <c r="N122">
+        <v>4</v>
+      </c>
+      <c r="O122" t="s">
+        <v>89</v>
+      </c>
+      <c r="P122" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q122">
+        <v>6.25</v>
+      </c>
+      <c r="R122">
+        <v>2.2</v>
+      </c>
+      <c r="S122">
+        <v>2</v>
+      </c>
+      <c r="T122">
+        <v>1.4</v>
+      </c>
+      <c r="U122">
+        <v>2.7</v>
+      </c>
+      <c r="V122">
+        <v>2.9</v>
+      </c>
+      <c r="W122">
+        <v>1.36</v>
+      </c>
+      <c r="X122">
+        <v>7.5</v>
+      </c>
+      <c r="Y122">
+        <v>1.07</v>
+      </c>
+      <c r="Z122">
+        <v>7.4</v>
+      </c>
+      <c r="AA122">
+        <v>4.1</v>
+      </c>
+      <c r="AB122">
+        <v>1.45</v>
+      </c>
+      <c r="AC122">
+        <v>1.05</v>
+      </c>
+      <c r="AD122">
+        <v>8.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.33</v>
+      </c>
+      <c r="AF122">
+        <v>3.15</v>
+      </c>
+      <c r="AG122">
+        <v>1.98</v>
+      </c>
+      <c r="AH122">
+        <v>1.77</v>
+      </c>
+      <c r="AI122">
+        <v>2.2</v>
+      </c>
+      <c r="AJ122">
+        <v>1.58</v>
+      </c>
+      <c r="AK122">
+        <v>2.6</v>
+      </c>
+      <c r="AL122">
+        <v>1.22</v>
+      </c>
+      <c r="AM122">
+        <v>1.1</v>
+      </c>
+      <c r="AN122">
+        <v>1.5</v>
+      </c>
+      <c r="AO122">
+        <v>2</v>
+      </c>
+      <c r="AP122">
+        <v>1.29</v>
+      </c>
+      <c r="AQ122">
+        <v>2.14</v>
+      </c>
+      <c r="AR122">
+        <v>1.04</v>
+      </c>
+      <c r="AS122">
+        <v>1.55</v>
+      </c>
+      <c r="AT122">
+        <v>2.59</v>
+      </c>
+      <c r="AU122">
+        <v>2</v>
+      </c>
+      <c r="AV122">
+        <v>9</v>
+      </c>
+      <c r="AW122">
+        <v>1</v>
+      </c>
+      <c r="AX122">
+        <v>3</v>
+      </c>
+      <c r="AY122">
+        <v>3</v>
+      </c>
+      <c r="AZ122">
+        <v>12</v>
+      </c>
+      <c r="BA122">
+        <v>3</v>
+      </c>
+      <c r="BB122">
+        <v>4</v>
+      </c>
+      <c r="BC122">
+        <v>7</v>
+      </c>
+      <c r="BD122">
+        <v>3.78</v>
+      </c>
+      <c r="BE122">
+        <v>8.9</v>
+      </c>
+      <c r="BF122">
+        <v>1.35</v>
+      </c>
+      <c r="BG122">
+        <v>1.35</v>
+      </c>
+      <c r="BH122">
+        <v>2.74</v>
+      </c>
+      <c r="BI122">
+        <v>1.64</v>
+      </c>
+      <c r="BJ122">
+        <v>2.02</v>
+      </c>
+      <c r="BK122">
+        <v>2.12</v>
+      </c>
+      <c r="BL122">
+        <v>1.61</v>
+      </c>
+      <c r="BM122">
+        <v>2.81</v>
+      </c>
+      <c r="BN122">
+        <v>1.33</v>
+      </c>
+      <c r="BO122">
+        <v>3.95</v>
+      </c>
+      <c r="BP122">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -466,6 +466,9 @@
     <t>['23', '74']</t>
   </si>
   <si>
+    <t>['22', '28']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -632,6 +635,9 @@
   </si>
   <si>
     <t>['9', '51', '83', '87']</t>
+  </si>
+  <si>
+    <t>['33', '60']</t>
   </si>
 </sst>
 </file>
@@ -993,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1249,7 +1255,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1455,7 +1461,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1945,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ5">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2073,7 +2079,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2279,7 +2285,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2485,7 +2491,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2897,7 +2903,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3103,7 +3109,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3387,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3515,7 +3521,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3721,7 +3727,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3927,7 +3933,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4133,7 +4139,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4214,7 +4220,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4626,7 +4632,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4829,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ19">
         <v>0.14</v>
@@ -4957,7 +4963,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5038,7 +5044,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ20">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5163,7 +5169,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5781,7 +5787,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5987,7 +5993,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6477,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -7017,7 +7023,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7095,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
         <v>0.33</v>
@@ -7301,7 +7307,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ31">
         <v>2.17</v>
@@ -7716,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR33">
         <v>1.75</v>
@@ -8047,7 +8053,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8334,7 +8340,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR36">
         <v>1.03</v>
@@ -8459,7 +8465,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9077,7 +9083,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9283,7 +9289,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9361,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9570,7 +9576,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.45</v>
@@ -9695,7 +9701,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10107,7 +10113,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10188,7 +10194,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR45">
         <v>1.27</v>
@@ -10394,7 +10400,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
         <v>0.9399999999999999</v>
@@ -10519,7 +10525,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10803,7 +10809,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ48">
         <v>0.33</v>
@@ -10931,7 +10937,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11343,7 +11349,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11549,7 +11555,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11755,7 +11761,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12042,7 +12048,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ54">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR54">
         <v>1.9</v>
@@ -12579,7 +12585,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12660,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -12991,7 +12997,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13403,7 +13409,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13481,7 +13487,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ61">
         <v>1.71</v>
@@ -13687,7 +13693,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ62">
         <v>0.14</v>
@@ -14308,7 +14314,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>2.1</v>
@@ -14433,7 +14439,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14845,7 +14851,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14923,7 +14929,7 @@
         <v>1.67</v>
       </c>
       <c r="AP68">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68">
         <v>1.5</v>
@@ -15544,7 +15550,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ71">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -15669,7 +15675,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16081,7 +16087,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16287,7 +16293,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16493,7 +16499,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16905,7 +16911,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17111,7 +17117,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17189,7 +17195,7 @@
         <v>1.25</v>
       </c>
       <c r="AP79">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ79">
         <v>1.14</v>
@@ -17317,7 +17323,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17398,7 +17404,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -17807,7 +17813,7 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ82">
         <v>1.67</v>
@@ -18219,7 +18225,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ84">
         <v>0.14</v>
@@ -18347,7 +18353,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18553,7 +18559,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18634,7 +18640,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ86">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR86">
         <v>1.96</v>
@@ -18759,7 +18765,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18840,7 +18846,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR87">
         <v>1.76</v>
@@ -19171,7 +19177,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19252,7 +19258,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
         <v>1.05</v>
@@ -19377,7 +19383,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19583,7 +19589,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19789,7 +19795,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19995,7 +20001,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20819,7 +20825,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21231,7 +21237,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21309,7 +21315,7 @@
         <v>0.8</v>
       </c>
       <c r="AP99">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ99">
         <v>1.43</v>
@@ -21437,7 +21443,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21515,7 +21521,7 @@
         <v>1.8</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ100">
         <v>2.14</v>
@@ -21643,7 +21649,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21849,7 +21855,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -21927,7 +21933,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>1.14</v>
@@ -22342,7 +22348,7 @@
         <v>2</v>
       </c>
       <c r="AQ104">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR104">
         <v>0.91</v>
@@ -22467,7 +22473,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22548,7 +22554,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR105">
         <v>1.55</v>
@@ -22754,7 +22760,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR106">
         <v>1.49</v>
@@ -23085,7 +23091,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23163,7 +23169,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ108">
         <v>1.71</v>
@@ -23291,7 +23297,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23497,7 +23503,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23703,7 +23709,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -25017,7 +25023,7 @@
         <v>2.4</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ117">
         <v>2.17</v>
@@ -25145,7 +25151,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25557,7 +25563,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25969,7 +25975,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26126,6 +26132,624 @@
       </c>
       <c r="BP122">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7729655</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45705.45833333334</v>
+      </c>
+      <c r="F123">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>87</v>
+      </c>
+      <c r="H123" t="s">
+        <v>84</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>3</v>
+      </c>
+      <c r="L123">
+        <v>2</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>4</v>
+      </c>
+      <c r="O123" t="s">
+        <v>150</v>
+      </c>
+      <c r="P123" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q123">
+        <v>2.15</v>
+      </c>
+      <c r="R123">
+        <v>2</v>
+      </c>
+      <c r="S123">
+        <v>6.25</v>
+      </c>
+      <c r="T123">
+        <v>1.49</v>
+      </c>
+      <c r="U123">
+        <v>2.4</v>
+      </c>
+      <c r="V123">
+        <v>3.2</v>
+      </c>
+      <c r="W123">
+        <v>1.3</v>
+      </c>
+      <c r="X123">
+        <v>9</v>
+      </c>
+      <c r="Y123">
+        <v>1.06</v>
+      </c>
+      <c r="Z123">
+        <v>1.54</v>
+      </c>
+      <c r="AA123">
+        <v>3.59</v>
+      </c>
+      <c r="AB123">
+        <v>6.9</v>
+      </c>
+      <c r="AC123">
+        <v>1.1</v>
+      </c>
+      <c r="AD123">
+        <v>6.21</v>
+      </c>
+      <c r="AE123">
+        <v>1.44</v>
+      </c>
+      <c r="AF123">
+        <v>2.66</v>
+      </c>
+      <c r="AG123">
+        <v>2.3</v>
+      </c>
+      <c r="AH123">
+        <v>1.5</v>
+      </c>
+      <c r="AI123">
+        <v>2.37</v>
+      </c>
+      <c r="AJ123">
+        <v>1.51</v>
+      </c>
+      <c r="AK123">
+        <v>1.11</v>
+      </c>
+      <c r="AL123">
+        <v>1.27</v>
+      </c>
+      <c r="AM123">
+        <v>2.35</v>
+      </c>
+      <c r="AN123">
+        <v>1.33</v>
+      </c>
+      <c r="AO123">
+        <v>0.43</v>
+      </c>
+      <c r="AP123">
+        <v>1.29</v>
+      </c>
+      <c r="AQ123">
+        <v>0.5</v>
+      </c>
+      <c r="AR123">
+        <v>1.55</v>
+      </c>
+      <c r="AS123">
+        <v>1.1</v>
+      </c>
+      <c r="AT123">
+        <v>2.65</v>
+      </c>
+      <c r="AU123">
+        <v>7</v>
+      </c>
+      <c r="AV123">
+        <v>6</v>
+      </c>
+      <c r="AW123">
+        <v>14</v>
+      </c>
+      <c r="AX123">
+        <v>7</v>
+      </c>
+      <c r="AY123">
+        <v>21</v>
+      </c>
+      <c r="AZ123">
+        <v>13</v>
+      </c>
+      <c r="BA123">
+        <v>5</v>
+      </c>
+      <c r="BB123">
+        <v>1</v>
+      </c>
+      <c r="BC123">
+        <v>6</v>
+      </c>
+      <c r="BD123">
+        <v>1.42</v>
+      </c>
+      <c r="BE123">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF123">
+        <v>3.34</v>
+      </c>
+      <c r="BG123">
+        <v>1.26</v>
+      </c>
+      <c r="BH123">
+        <v>3.22</v>
+      </c>
+      <c r="BI123">
+        <v>1.49</v>
+      </c>
+      <c r="BJ123">
+        <v>2.3</v>
+      </c>
+      <c r="BK123">
+        <v>1.87</v>
+      </c>
+      <c r="BL123">
+        <v>1.79</v>
+      </c>
+      <c r="BM123">
+        <v>2.41</v>
+      </c>
+      <c r="BN123">
+        <v>1.45</v>
+      </c>
+      <c r="BO123">
+        <v>3.28</v>
+      </c>
+      <c r="BP123">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7729661</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45705.58333333334</v>
+      </c>
+      <c r="F124">
+        <v>14</v>
+      </c>
+      <c r="G124" t="s">
+        <v>73</v>
+      </c>
+      <c r="H124" t="s">
+        <v>75</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>89</v>
+      </c>
+      <c r="P124" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q124">
+        <v>5.25</v>
+      </c>
+      <c r="R124">
+        <v>1.98</v>
+      </c>
+      <c r="S124">
+        <v>2.3</v>
+      </c>
+      <c r="T124">
+        <v>1.5</v>
+      </c>
+      <c r="U124">
+        <v>2.4</v>
+      </c>
+      <c r="V124">
+        <v>3.4</v>
+      </c>
+      <c r="W124">
+        <v>1.28</v>
+      </c>
+      <c r="X124">
+        <v>9.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.05</v>
+      </c>
+      <c r="Z124">
+        <v>5.1</v>
+      </c>
+      <c r="AA124">
+        <v>3.41</v>
+      </c>
+      <c r="AB124">
+        <v>1.72</v>
+      </c>
+      <c r="AC124">
+        <v>1.04</v>
+      </c>
+      <c r="AD124">
+        <v>6.95</v>
+      </c>
+      <c r="AE124">
+        <v>1.46</v>
+      </c>
+      <c r="AF124">
+        <v>2.6</v>
+      </c>
+      <c r="AG124">
+        <v>2.3</v>
+      </c>
+      <c r="AH124">
+        <v>1.5</v>
+      </c>
+      <c r="AI124">
+        <v>2.3</v>
+      </c>
+      <c r="AJ124">
+        <v>1.55</v>
+      </c>
+      <c r="AK124">
+        <v>2.1</v>
+      </c>
+      <c r="AL124">
+        <v>1.29</v>
+      </c>
+      <c r="AM124">
+        <v>1.16</v>
+      </c>
+      <c r="AN124">
+        <v>1</v>
+      </c>
+      <c r="AO124">
+        <v>2</v>
+      </c>
+      <c r="AP124">
+        <v>0.88</v>
+      </c>
+      <c r="AQ124">
+        <v>2.13</v>
+      </c>
+      <c r="AR124">
+        <v>1.13</v>
+      </c>
+      <c r="AS124">
+        <v>1.4</v>
+      </c>
+      <c r="AT124">
+        <v>2.53</v>
+      </c>
+      <c r="AU124">
+        <v>0</v>
+      </c>
+      <c r="AV124">
+        <v>5</v>
+      </c>
+      <c r="AW124">
+        <v>2</v>
+      </c>
+      <c r="AX124">
+        <v>7</v>
+      </c>
+      <c r="AY124">
+        <v>2</v>
+      </c>
+      <c r="AZ124">
+        <v>12</v>
+      </c>
+      <c r="BA124">
+        <v>2</v>
+      </c>
+      <c r="BB124">
+        <v>6</v>
+      </c>
+      <c r="BC124">
+        <v>8</v>
+      </c>
+      <c r="BD124">
+        <v>3.42</v>
+      </c>
+      <c r="BE124">
+        <v>8.6</v>
+      </c>
+      <c r="BF124">
+        <v>1.41</v>
+      </c>
+      <c r="BG124">
+        <v>1.28</v>
+      </c>
+      <c r="BH124">
+        <v>3.08</v>
+      </c>
+      <c r="BI124">
+        <v>1.53</v>
+      </c>
+      <c r="BJ124">
+        <v>2.21</v>
+      </c>
+      <c r="BK124">
+        <v>1.92</v>
+      </c>
+      <c r="BL124">
+        <v>1.75</v>
+      </c>
+      <c r="BM124">
+        <v>2.49</v>
+      </c>
+      <c r="BN124">
+        <v>1.42</v>
+      </c>
+      <c r="BO124">
+        <v>3.42</v>
+      </c>
+      <c r="BP124">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7729660</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45705.58333333334</v>
+      </c>
+      <c r="F125">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s">
+        <v>72</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>130</v>
+      </c>
+      <c r="P125" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q125">
+        <v>3.1</v>
+      </c>
+      <c r="R125">
+        <v>1.75</v>
+      </c>
+      <c r="S125">
+        <v>4.33</v>
+      </c>
+      <c r="T125">
+        <v>1.68</v>
+      </c>
+      <c r="U125">
+        <v>2.05</v>
+      </c>
+      <c r="V125">
+        <v>4.2</v>
+      </c>
+      <c r="W125">
+        <v>1.2</v>
+      </c>
+      <c r="X125">
+        <v>13</v>
+      </c>
+      <c r="Y125">
+        <v>1.02</v>
+      </c>
+      <c r="Z125">
+        <v>2.37</v>
+      </c>
+      <c r="AA125">
+        <v>2.62</v>
+      </c>
+      <c r="AB125">
+        <v>3.75</v>
+      </c>
+      <c r="AC125">
+        <v>1.16</v>
+      </c>
+      <c r="AD125">
+        <v>4.76</v>
+      </c>
+      <c r="AE125">
+        <v>1.67</v>
+      </c>
+      <c r="AF125">
+        <v>2</v>
+      </c>
+      <c r="AG125">
+        <v>3.15</v>
+      </c>
+      <c r="AH125">
+        <v>1.31</v>
+      </c>
+      <c r="AI125">
+        <v>2.5</v>
+      </c>
+      <c r="AJ125">
+        <v>1.46</v>
+      </c>
+      <c r="AK125">
+        <v>1.28</v>
+      </c>
+      <c r="AL125">
+        <v>1.43</v>
+      </c>
+      <c r="AM125">
+        <v>1.55</v>
+      </c>
+      <c r="AN125">
+        <v>1.17</v>
+      </c>
+      <c r="AO125">
+        <v>0.5</v>
+      </c>
+      <c r="AP125">
+        <v>1.43</v>
+      </c>
+      <c r="AQ125">
+        <v>0.43</v>
+      </c>
+      <c r="AR125">
+        <v>0.96</v>
+      </c>
+      <c r="AS125">
+        <v>1.21</v>
+      </c>
+      <c r="AT125">
+        <v>2.17</v>
+      </c>
+      <c r="AU125">
+        <v>6</v>
+      </c>
+      <c r="AV125">
+        <v>2</v>
+      </c>
+      <c r="AW125">
+        <v>7</v>
+      </c>
+      <c r="AX125">
+        <v>5</v>
+      </c>
+      <c r="AY125">
+        <v>13</v>
+      </c>
+      <c r="AZ125">
+        <v>7</v>
+      </c>
+      <c r="BA125">
+        <v>1</v>
+      </c>
+      <c r="BB125">
+        <v>2</v>
+      </c>
+      <c r="BC125">
+        <v>3</v>
+      </c>
+      <c r="BD125">
+        <v>1.73</v>
+      </c>
+      <c r="BE125">
+        <v>8</v>
+      </c>
+      <c r="BF125">
+        <v>2.42</v>
+      </c>
+      <c r="BG125">
+        <v>1.32</v>
+      </c>
+      <c r="BH125">
+        <v>2.88</v>
+      </c>
+      <c r="BI125">
+        <v>1.6</v>
+      </c>
+      <c r="BJ125">
+        <v>2.08</v>
+      </c>
+      <c r="BK125">
+        <v>2.05</v>
+      </c>
+      <c r="BL125">
+        <v>1.65</v>
+      </c>
+      <c r="BM125">
+        <v>2.7</v>
+      </c>
+      <c r="BN125">
+        <v>1.36</v>
+      </c>
+      <c r="BO125">
+        <v>3.78</v>
+      </c>
+      <c r="BP125">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -467,6 +467,9 @@
   </si>
   <si>
     <t>['22', '28']</t>
+  </si>
+  <si>
+    <t>['63']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -999,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1255,7 +1258,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1461,7 +1464,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1539,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ3">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1748,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2079,7 +2082,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2285,7 +2288,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2491,7 +2494,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2903,7 +2906,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3109,7 +3112,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3187,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ11">
         <v>2.17</v>
@@ -3521,7 +3524,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3727,7 +3730,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3933,7 +3936,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4139,7 +4142,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4963,7 +4966,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5169,7 +5172,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5659,7 +5662,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ23">
         <v>1.43</v>
@@ -5787,7 +5790,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5993,7 +5996,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6074,7 +6077,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ25">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>1.36</v>
@@ -6486,7 +6489,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR27">
         <v>2</v>
@@ -7023,7 +7026,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -8053,7 +8056,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8465,7 +8468,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8543,7 +8546,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ37">
         <v>1.67</v>
@@ -8752,7 +8755,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>0.8100000000000001</v>
@@ -8955,7 +8958,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ39">
         <v>1.29</v>
@@ -9083,7 +9086,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9289,7 +9292,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9701,7 +9704,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9782,7 +9785,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -9985,7 +9988,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ44">
         <v>1.14</v>
@@ -10113,7 +10116,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10525,7 +10528,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10603,7 +10606,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ47">
         <v>1.67</v>
@@ -10937,7 +10940,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11349,7 +11352,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11555,7 +11558,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11761,7 +11764,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12585,7 +12588,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12997,7 +13000,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13409,7 +13412,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13490,7 +13493,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ61">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR61">
         <v>1.52</v>
@@ -13899,7 +13902,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -14439,7 +14442,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14517,7 +14520,7 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ66">
         <v>1.71</v>
@@ -14851,7 +14854,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14932,7 +14935,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ68">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR68">
         <v>0.92</v>
@@ -15675,7 +15678,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16087,7 +16090,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16293,7 +16296,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16371,7 +16374,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16499,7 +16502,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16911,7 +16914,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17117,7 +17120,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17323,7 +17326,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17610,7 +17613,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ81">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.81</v>
@@ -18019,7 +18022,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ83">
         <v>1.14</v>
@@ -18353,7 +18356,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18431,7 +18434,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ85">
         <v>1.71</v>
@@ -18559,7 +18562,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18765,7 +18768,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19177,7 +19180,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19383,7 +19386,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19589,7 +19592,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19670,7 +19673,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.61</v>
@@ -19795,7 +19798,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20001,7 +20004,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20494,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR95">
         <v>1.28</v>
@@ -20825,7 +20828,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21237,7 +21240,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21443,7 +21446,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21649,7 +21652,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21727,7 +21730,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ101">
         <v>0.33</v>
@@ -21855,7 +21858,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22473,7 +22476,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22757,7 +22760,7 @@
         <v>0.4</v>
       </c>
       <c r="AP106">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ106">
         <v>0.43</v>
@@ -23091,7 +23094,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23172,7 +23175,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ108">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR108">
         <v>0.86</v>
@@ -23297,7 +23300,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23378,7 +23381,7 @@
         <v>1</v>
       </c>
       <c r="AQ109">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR109">
         <v>1.08</v>
@@ -23503,7 +23506,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23709,7 +23712,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -25151,7 +25154,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25563,7 +25566,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25975,7 +25978,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26181,7 +26184,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26692,10 +26695,10 @@
         <v>2</v>
       </c>
       <c r="AW125">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY125">
         <v>13</v>
@@ -26750,6 +26753,418 @@
       </c>
       <c r="BP125">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7729662</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45706.45833333334</v>
+      </c>
+      <c r="F126">
+        <v>14</v>
+      </c>
+      <c r="G126" t="s">
+        <v>71</v>
+      </c>
+      <c r="H126" t="s">
+        <v>81</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>151</v>
+      </c>
+      <c r="P126" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q126">
+        <v>3.55</v>
+      </c>
+      <c r="R126">
+        <v>1.77</v>
+      </c>
+      <c r="S126">
+        <v>3.85</v>
+      </c>
+      <c r="T126">
+        <v>1.72</v>
+      </c>
+      <c r="U126">
+        <v>2.02</v>
+      </c>
+      <c r="V126">
+        <v>4.2</v>
+      </c>
+      <c r="W126">
+        <v>1.18</v>
+      </c>
+      <c r="X126">
+        <v>15</v>
+      </c>
+      <c r="Y126">
+        <v>1.03</v>
+      </c>
+      <c r="Z126">
+        <v>2.75</v>
+      </c>
+      <c r="AA126">
+        <v>2.41</v>
+      </c>
+      <c r="AB126">
+        <v>2.95</v>
+      </c>
+      <c r="AC126">
+        <v>1.17</v>
+      </c>
+      <c r="AD126">
+        <v>4.6</v>
+      </c>
+      <c r="AE126">
+        <v>1.68</v>
+      </c>
+      <c r="AF126">
+        <v>2.11</v>
+      </c>
+      <c r="AG126">
+        <v>3.15</v>
+      </c>
+      <c r="AH126">
+        <v>1.33</v>
+      </c>
+      <c r="AI126">
+        <v>2.34</v>
+      </c>
+      <c r="AJ126">
+        <v>1.54</v>
+      </c>
+      <c r="AK126">
+        <v>1.35</v>
+      </c>
+      <c r="AL126">
+        <v>1.44</v>
+      </c>
+      <c r="AM126">
+        <v>1.39</v>
+      </c>
+      <c r="AN126">
+        <v>0.57</v>
+      </c>
+      <c r="AO126">
+        <v>1.5</v>
+      </c>
+      <c r="AP126">
+        <v>0.88</v>
+      </c>
+      <c r="AQ126">
+        <v>1.29</v>
+      </c>
+      <c r="AR126">
+        <v>1.44</v>
+      </c>
+      <c r="AS126">
+        <v>1.3</v>
+      </c>
+      <c r="AT126">
+        <v>2.74</v>
+      </c>
+      <c r="AU126">
+        <v>3</v>
+      </c>
+      <c r="AV126">
+        <v>4</v>
+      </c>
+      <c r="AW126">
+        <v>12</v>
+      </c>
+      <c r="AX126">
+        <v>14</v>
+      </c>
+      <c r="AY126">
+        <v>15</v>
+      </c>
+      <c r="AZ126">
+        <v>18</v>
+      </c>
+      <c r="BA126">
+        <v>2</v>
+      </c>
+      <c r="BB126">
+        <v>5</v>
+      </c>
+      <c r="BC126">
+        <v>7</v>
+      </c>
+      <c r="BD126">
+        <v>2.13</v>
+      </c>
+      <c r="BE126">
+        <v>6.05</v>
+      </c>
+      <c r="BF126">
+        <v>2.07</v>
+      </c>
+      <c r="BG126">
+        <v>1.39</v>
+      </c>
+      <c r="BH126">
+        <v>2.59</v>
+      </c>
+      <c r="BI126">
+        <v>1.73</v>
+      </c>
+      <c r="BJ126">
+        <v>1.95</v>
+      </c>
+      <c r="BK126">
+        <v>2.21</v>
+      </c>
+      <c r="BL126">
+        <v>1.53</v>
+      </c>
+      <c r="BM126">
+        <v>2.97</v>
+      </c>
+      <c r="BN126">
+        <v>1.3</v>
+      </c>
+      <c r="BO126">
+        <v>3.8</v>
+      </c>
+      <c r="BP126">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7729663</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45706.58333333334</v>
+      </c>
+      <c r="F127">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s">
+        <v>86</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>106</v>
+      </c>
+      <c r="P127" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q127">
+        <v>4.5</v>
+      </c>
+      <c r="R127">
+        <v>1.93</v>
+      </c>
+      <c r="S127">
+        <v>2.75</v>
+      </c>
+      <c r="T127">
+        <v>1.57</v>
+      </c>
+      <c r="U127">
+        <v>2.28</v>
+      </c>
+      <c r="V127">
+        <v>3.4</v>
+      </c>
+      <c r="W127">
+        <v>1.29</v>
+      </c>
+      <c r="X127">
+        <v>10</v>
+      </c>
+      <c r="Y127">
+        <v>1.05</v>
+      </c>
+      <c r="Z127">
+        <v>3.89</v>
+      </c>
+      <c r="AA127">
+        <v>2.86</v>
+      </c>
+      <c r="AB127">
+        <v>2.16</v>
+      </c>
+      <c r="AC127">
+        <v>1.11</v>
+      </c>
+      <c r="AD127">
+        <v>6</v>
+      </c>
+      <c r="AE127">
+        <v>1.48</v>
+      </c>
+      <c r="AF127">
+        <v>2.37</v>
+      </c>
+      <c r="AG127">
+        <v>2.62</v>
+      </c>
+      <c r="AH127">
+        <v>1.43</v>
+      </c>
+      <c r="AI127">
+        <v>2.09</v>
+      </c>
+      <c r="AJ127">
+        <v>1.67</v>
+      </c>
+      <c r="AK127">
+        <v>1.63</v>
+      </c>
+      <c r="AL127">
+        <v>1.36</v>
+      </c>
+      <c r="AM127">
+        <v>1.24</v>
+      </c>
+      <c r="AN127">
+        <v>0.57</v>
+      </c>
+      <c r="AO127">
+        <v>1.71</v>
+      </c>
+      <c r="AP127">
+        <v>0.88</v>
+      </c>
+      <c r="AQ127">
+        <v>1.5</v>
+      </c>
+      <c r="AR127">
+        <v>1.47</v>
+      </c>
+      <c r="AS127">
+        <v>1.37</v>
+      </c>
+      <c r="AT127">
+        <v>2.84</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>5</v>
+      </c>
+      <c r="AW127">
+        <v>1</v>
+      </c>
+      <c r="AX127">
+        <v>6</v>
+      </c>
+      <c r="AY127">
+        <v>5</v>
+      </c>
+      <c r="AZ127">
+        <v>11</v>
+      </c>
+      <c r="BA127">
+        <v>3</v>
+      </c>
+      <c r="BB127">
+        <v>10</v>
+      </c>
+      <c r="BC127">
+        <v>13</v>
+      </c>
+      <c r="BD127">
+        <v>2.25</v>
+      </c>
+      <c r="BE127">
+        <v>6.2</v>
+      </c>
+      <c r="BF127">
+        <v>1.95</v>
+      </c>
+      <c r="BG127">
+        <v>1.26</v>
+      </c>
+      <c r="BH127">
+        <v>3.22</v>
+      </c>
+      <c r="BI127">
+        <v>1.49</v>
+      </c>
+      <c r="BJ127">
+        <v>2.3</v>
+      </c>
+      <c r="BK127">
+        <v>1.86</v>
+      </c>
+      <c r="BL127">
+        <v>1.8</v>
+      </c>
+      <c r="BM127">
+        <v>2.41</v>
+      </c>
+      <c r="BN127">
+        <v>1.45</v>
+      </c>
+      <c r="BO127">
+        <v>3.28</v>
+      </c>
+      <c r="BP127">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,12 @@
     <t>['63']</t>
   </si>
   <si>
+    <t>['9', '87']</t>
+  </si>
+  <si>
+    <t>['3', '5', '59']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -641,6 +647,12 @@
   </si>
   <si>
     <t>['33', '60']</t>
+  </si>
+  <si>
+    <t>['45', '90+1']</t>
+  </si>
+  <si>
+    <t>['33', '51']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1258,7 +1270,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1339,7 +1351,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1464,7 +1476,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2082,7 +2094,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2160,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2288,7 +2300,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2494,7 +2506,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2906,7 +2918,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3112,7 +3124,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3524,7 +3536,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3730,7 +3742,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3936,7 +3948,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4014,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4142,7 +4154,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4220,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16">
         <v>2.13</v>
@@ -4426,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17">
         <v>1.14</v>
@@ -4966,7 +4978,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5044,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5172,7 +5184,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5459,7 +5471,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5665,7 +5677,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5790,7 +5802,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5996,7 +6008,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -7026,7 +7038,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7107,7 +7119,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -7516,7 +7528,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32">
         <v>2.14</v>
@@ -7928,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ34">
         <v>0.14</v>
@@ -8056,7 +8068,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8134,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ35">
         <v>1.14</v>
@@ -8468,7 +8480,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9086,7 +9098,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9292,7 +9304,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9704,7 +9716,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9782,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
         <v>1.29</v>
@@ -9991,7 +10003,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ44">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -10116,7 +10128,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10528,7 +10540,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10815,7 +10827,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ48">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR48">
         <v>0.85</v>
@@ -10940,7 +10952,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11352,7 +11364,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11430,7 +11442,7 @@
         <v>0.67</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>1.71</v>
@@ -11558,7 +11570,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11764,7 +11776,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12048,7 +12060,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54">
         <v>0.43</v>
@@ -12463,7 +12475,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ56">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12588,7 +12600,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12872,7 +12884,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ58">
         <v>2.14</v>
@@ -13000,7 +13012,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13078,10 +13090,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ59">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -13412,7 +13424,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14111,7 +14123,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ64">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14314,7 +14326,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14442,7 +14454,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14726,7 +14738,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ67">
         <v>0.14</v>
@@ -14854,7 +14866,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15141,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR69">
         <v>1.78</v>
@@ -15678,7 +15690,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16090,7 +16102,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16296,7 +16308,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16502,7 +16514,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16580,7 +16592,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ76">
         <v>2.17</v>
@@ -16789,7 +16801,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
         <v>1.1</v>
@@ -16914,7 +16926,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -16992,7 +17004,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ78">
         <v>2.14</v>
@@ -17120,7 +17132,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17201,7 +17213,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17326,7 +17338,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17610,7 +17622,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -18356,7 +18368,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18562,7 +18574,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18768,7 +18780,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19055,7 +19067,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19180,7 +19192,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19386,7 +19398,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19464,7 +19476,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
         <v>1.29</v>
@@ -19592,7 +19604,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19798,7 +19810,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20004,7 +20016,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20700,7 +20712,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ96">
         <v>2</v>
@@ -20828,7 +20840,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -20906,7 +20918,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -21112,10 +21124,10 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.73</v>
@@ -21240,7 +21252,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21321,7 +21333,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ99">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21446,7 +21458,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21652,7 +21664,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21733,7 +21745,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ101">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR101">
         <v>1.45</v>
@@ -21858,7 +21870,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22476,7 +22488,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23094,7 +23106,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23300,7 +23312,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23378,7 +23390,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ109">
         <v>1.29</v>
@@ -23506,7 +23518,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23584,7 +23596,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ110">
         <v>1.67</v>
@@ -23712,7 +23724,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -23790,10 +23802,10 @@
         <v>1.17</v>
       </c>
       <c r="AP111">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR111">
         <v>1.6</v>
@@ -25154,7 +25166,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25232,10 +25244,10 @@
         <v>1.17</v>
       </c>
       <c r="AP118">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ118">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>0.78</v>
@@ -25566,7 +25578,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25978,7 +25990,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26184,7 +26196,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -27165,6 +27177,830 @@
       </c>
       <c r="BP127">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7729664</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45709.45833333334</v>
+      </c>
+      <c r="F128">
+        <v>15</v>
+      </c>
+      <c r="G128" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" t="s">
+        <v>82</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>136</v>
+      </c>
+      <c r="P128" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q128">
+        <v>3.6</v>
+      </c>
+      <c r="R128">
+        <v>1.82</v>
+      </c>
+      <c r="S128">
+        <v>3.4</v>
+      </c>
+      <c r="T128">
+        <v>1.6</v>
+      </c>
+      <c r="U128">
+        <v>2.15</v>
+      </c>
+      <c r="V128">
+        <v>3.8</v>
+      </c>
+      <c r="W128">
+        <v>1.22</v>
+      </c>
+      <c r="X128">
+        <v>11.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.03</v>
+      </c>
+      <c r="Z128">
+        <v>3.52</v>
+      </c>
+      <c r="AA128">
+        <v>2.88</v>
+      </c>
+      <c r="AB128">
+        <v>2.28</v>
+      </c>
+      <c r="AC128">
+        <v>1.08</v>
+      </c>
+      <c r="AD128">
+        <v>5.55</v>
+      </c>
+      <c r="AE128">
+        <v>1.57</v>
+      </c>
+      <c r="AF128">
+        <v>2.15</v>
+      </c>
+      <c r="AG128">
+        <v>2.89</v>
+      </c>
+      <c r="AH128">
+        <v>1.36</v>
+      </c>
+      <c r="AI128">
+        <v>2.3</v>
+      </c>
+      <c r="AJ128">
+        <v>1.53</v>
+      </c>
+      <c r="AK128">
+        <v>1.46</v>
+      </c>
+      <c r="AL128">
+        <v>1.39</v>
+      </c>
+      <c r="AM128">
+        <v>1.39</v>
+      </c>
+      <c r="AN128">
+        <v>0.83</v>
+      </c>
+      <c r="AO128">
+        <v>1.43</v>
+      </c>
+      <c r="AP128">
+        <v>1.14</v>
+      </c>
+      <c r="AQ128">
+        <v>1.25</v>
+      </c>
+      <c r="AR128">
+        <v>0.96</v>
+      </c>
+      <c r="AS128">
+        <v>1.22</v>
+      </c>
+      <c r="AT128">
+        <v>2.18</v>
+      </c>
+      <c r="AU128">
+        <v>2</v>
+      </c>
+      <c r="AV128">
+        <v>2</v>
+      </c>
+      <c r="AW128">
+        <v>3</v>
+      </c>
+      <c r="AX128">
+        <v>10</v>
+      </c>
+      <c r="AY128">
+        <v>5</v>
+      </c>
+      <c r="AZ128">
+        <v>12</v>
+      </c>
+      <c r="BA128">
+        <v>2</v>
+      </c>
+      <c r="BB128">
+        <v>6</v>
+      </c>
+      <c r="BC128">
+        <v>8</v>
+      </c>
+      <c r="BD128">
+        <v>0</v>
+      </c>
+      <c r="BE128">
+        <v>0</v>
+      </c>
+      <c r="BF128">
+        <v>0</v>
+      </c>
+      <c r="BG128">
+        <v>0</v>
+      </c>
+      <c r="BH128">
+        <v>0</v>
+      </c>
+      <c r="BI128">
+        <v>0</v>
+      </c>
+      <c r="BJ128">
+        <v>0</v>
+      </c>
+      <c r="BK128">
+        <v>0</v>
+      </c>
+      <c r="BL128">
+        <v>0</v>
+      </c>
+      <c r="BM128">
+        <v>0</v>
+      </c>
+      <c r="BN128">
+        <v>0</v>
+      </c>
+      <c r="BO128">
+        <v>0</v>
+      </c>
+      <c r="BP128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7729665</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45709.45833333334</v>
+      </c>
+      <c r="F129">
+        <v>15</v>
+      </c>
+      <c r="G129" t="s">
+        <v>74</v>
+      </c>
+      <c r="H129" t="s">
+        <v>73</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129" t="s">
+        <v>89</v>
+      </c>
+      <c r="P129" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q129">
+        <v>3.8</v>
+      </c>
+      <c r="R129">
+        <v>1.82</v>
+      </c>
+      <c r="S129">
+        <v>3.25</v>
+      </c>
+      <c r="T129">
+        <v>1.6</v>
+      </c>
+      <c r="U129">
+        <v>2.15</v>
+      </c>
+      <c r="V129">
+        <v>3.8</v>
+      </c>
+      <c r="W129">
+        <v>1.23</v>
+      </c>
+      <c r="X129">
+        <v>11.5</v>
+      </c>
+      <c r="Y129">
+        <v>1.03</v>
+      </c>
+      <c r="Z129">
+        <v>2.94</v>
+      </c>
+      <c r="AA129">
+        <v>2.72</v>
+      </c>
+      <c r="AB129">
+        <v>2.76</v>
+      </c>
+      <c r="AC129">
+        <v>1.13</v>
+      </c>
+      <c r="AD129">
+        <v>5.4</v>
+      </c>
+      <c r="AE129">
+        <v>1.57</v>
+      </c>
+      <c r="AF129">
+        <v>2.15</v>
+      </c>
+      <c r="AG129">
+        <v>2.89</v>
+      </c>
+      <c r="AH129">
+        <v>1.36</v>
+      </c>
+      <c r="AI129">
+        <v>2.25</v>
+      </c>
+      <c r="AJ129">
+        <v>1.55</v>
+      </c>
+      <c r="AK129">
+        <v>1.5</v>
+      </c>
+      <c r="AL129">
+        <v>1.4</v>
+      </c>
+      <c r="AM129">
+        <v>1.34</v>
+      </c>
+      <c r="AN129">
+        <v>1.43</v>
+      </c>
+      <c r="AO129">
+        <v>0.33</v>
+      </c>
+      <c r="AP129">
+        <v>1.38</v>
+      </c>
+      <c r="AQ129">
+        <v>0.43</v>
+      </c>
+      <c r="AR129">
+        <v>1.36</v>
+      </c>
+      <c r="AS129">
+        <v>1.02</v>
+      </c>
+      <c r="AT129">
+        <v>2.38</v>
+      </c>
+      <c r="AU129">
+        <v>3</v>
+      </c>
+      <c r="AV129">
+        <v>2</v>
+      </c>
+      <c r="AW129">
+        <v>5</v>
+      </c>
+      <c r="AX129">
+        <v>6</v>
+      </c>
+      <c r="AY129">
+        <v>8</v>
+      </c>
+      <c r="AZ129">
+        <v>8</v>
+      </c>
+      <c r="BA129">
+        <v>2</v>
+      </c>
+      <c r="BB129">
+        <v>7</v>
+      </c>
+      <c r="BC129">
+        <v>9</v>
+      </c>
+      <c r="BD129">
+        <v>2.13</v>
+      </c>
+      <c r="BE129">
+        <v>6.05</v>
+      </c>
+      <c r="BF129">
+        <v>2.07</v>
+      </c>
+      <c r="BG129">
+        <v>1.34</v>
+      </c>
+      <c r="BH129">
+        <v>2.78</v>
+      </c>
+      <c r="BI129">
+        <v>1.65</v>
+      </c>
+      <c r="BJ129">
+        <v>2.05</v>
+      </c>
+      <c r="BK129">
+        <v>2.08</v>
+      </c>
+      <c r="BL129">
+        <v>1.6</v>
+      </c>
+      <c r="BM129">
+        <v>2.78</v>
+      </c>
+      <c r="BN129">
+        <v>1.34</v>
+      </c>
+      <c r="BO129">
+        <v>3.6</v>
+      </c>
+      <c r="BP129">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7729666</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F130">
+        <v>15</v>
+      </c>
+      <c r="G130" t="s">
+        <v>83</v>
+      </c>
+      <c r="H130" t="s">
+        <v>70</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>2</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>152</v>
+      </c>
+      <c r="P130" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q130">
+        <v>2.88</v>
+      </c>
+      <c r="R130">
+        <v>1.8</v>
+      </c>
+      <c r="S130">
+        <v>4.5</v>
+      </c>
+      <c r="T130">
+        <v>1.62</v>
+      </c>
+      <c r="U130">
+        <v>2.15</v>
+      </c>
+      <c r="V130">
+        <v>3.9</v>
+      </c>
+      <c r="W130">
+        <v>1.22</v>
+      </c>
+      <c r="X130">
+        <v>10</v>
+      </c>
+      <c r="Y130">
+        <v>1.03</v>
+      </c>
+      <c r="Z130">
+        <v>2.08</v>
+      </c>
+      <c r="AA130">
+        <v>2.83</v>
+      </c>
+      <c r="AB130">
+        <v>4.2</v>
+      </c>
+      <c r="AC130">
+        <v>1.14</v>
+      </c>
+      <c r="AD130">
+        <v>5.25</v>
+      </c>
+      <c r="AE130">
+        <v>1.65</v>
+      </c>
+      <c r="AF130">
+        <v>2.05</v>
+      </c>
+      <c r="AG130">
+        <v>2.94</v>
+      </c>
+      <c r="AH130">
+        <v>1.35</v>
+      </c>
+      <c r="AI130">
+        <v>2.25</v>
+      </c>
+      <c r="AJ130">
+        <v>1.53</v>
+      </c>
+      <c r="AK130">
+        <v>1.22</v>
+      </c>
+      <c r="AL130">
+        <v>1.38</v>
+      </c>
+      <c r="AM130">
+        <v>1.65</v>
+      </c>
+      <c r="AN130">
+        <v>1.29</v>
+      </c>
+      <c r="AO130">
+        <v>1</v>
+      </c>
+      <c r="AP130">
+        <v>1.25</v>
+      </c>
+      <c r="AQ130">
+        <v>1</v>
+      </c>
+      <c r="AR130">
+        <v>1.63</v>
+      </c>
+      <c r="AS130">
+        <v>0.98</v>
+      </c>
+      <c r="AT130">
+        <v>2.61</v>
+      </c>
+      <c r="AU130">
+        <v>5</v>
+      </c>
+      <c r="AV130">
+        <v>3</v>
+      </c>
+      <c r="AW130">
+        <v>2</v>
+      </c>
+      <c r="AX130">
+        <v>1</v>
+      </c>
+      <c r="AY130">
+        <v>7</v>
+      </c>
+      <c r="AZ130">
+        <v>4</v>
+      </c>
+      <c r="BA130">
+        <v>7</v>
+      </c>
+      <c r="BB130">
+        <v>4</v>
+      </c>
+      <c r="BC130">
+        <v>11</v>
+      </c>
+      <c r="BD130">
+        <v>1.57</v>
+      </c>
+      <c r="BE130">
+        <v>6.55</v>
+      </c>
+      <c r="BF130">
+        <v>3.05</v>
+      </c>
+      <c r="BG130">
+        <v>1.3</v>
+      </c>
+      <c r="BH130">
+        <v>2.97</v>
+      </c>
+      <c r="BI130">
+        <v>1.56</v>
+      </c>
+      <c r="BJ130">
+        <v>2.16</v>
+      </c>
+      <c r="BK130">
+        <v>1.98</v>
+      </c>
+      <c r="BL130">
+        <v>1.7</v>
+      </c>
+      <c r="BM130">
+        <v>2.59</v>
+      </c>
+      <c r="BN130">
+        <v>1.39</v>
+      </c>
+      <c r="BO130">
+        <v>3.58</v>
+      </c>
+      <c r="BP130">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7729667</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F131">
+        <v>15</v>
+      </c>
+      <c r="G131" t="s">
+        <v>85</v>
+      </c>
+      <c r="H131" t="s">
+        <v>80</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>3</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>5</v>
+      </c>
+      <c r="O131" t="s">
+        <v>153</v>
+      </c>
+      <c r="P131" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q131">
+        <v>2.85</v>
+      </c>
+      <c r="R131">
+        <v>1.8</v>
+      </c>
+      <c r="S131">
+        <v>4.75</v>
+      </c>
+      <c r="T131">
+        <v>1.63</v>
+      </c>
+      <c r="U131">
+        <v>2.1</v>
+      </c>
+      <c r="V131">
+        <v>3.9</v>
+      </c>
+      <c r="W131">
+        <v>1.22</v>
+      </c>
+      <c r="X131">
+        <v>12</v>
+      </c>
+      <c r="Y131">
+        <v>1.03</v>
+      </c>
+      <c r="Z131">
+        <v>2.06</v>
+      </c>
+      <c r="AA131">
+        <v>2.83</v>
+      </c>
+      <c r="AB131">
+        <v>4.3</v>
+      </c>
+      <c r="AC131">
+        <v>1.16</v>
+      </c>
+      <c r="AD131">
+        <v>4.8</v>
+      </c>
+      <c r="AE131">
+        <v>1.6</v>
+      </c>
+      <c r="AF131">
+        <v>2.1</v>
+      </c>
+      <c r="AG131">
+        <v>3.04</v>
+      </c>
+      <c r="AH131">
+        <v>1.33</v>
+      </c>
+      <c r="AI131">
+        <v>2.45</v>
+      </c>
+      <c r="AJ131">
+        <v>1.47</v>
+      </c>
+      <c r="AK131">
+        <v>1.22</v>
+      </c>
+      <c r="AL131">
+        <v>1.41</v>
+      </c>
+      <c r="AM131">
+        <v>1.68</v>
+      </c>
+      <c r="AN131">
+        <v>1</v>
+      </c>
+      <c r="AO131">
+        <v>1.14</v>
+      </c>
+      <c r="AP131">
+        <v>1.29</v>
+      </c>
+      <c r="AQ131">
+        <v>1</v>
+      </c>
+      <c r="AR131">
+        <v>1.17</v>
+      </c>
+      <c r="AS131">
+        <v>0.98</v>
+      </c>
+      <c r="AT131">
+        <v>2.15</v>
+      </c>
+      <c r="AU131">
+        <v>6</v>
+      </c>
+      <c r="AV131">
+        <v>5</v>
+      </c>
+      <c r="AW131">
+        <v>2</v>
+      </c>
+      <c r="AX131">
+        <v>7</v>
+      </c>
+      <c r="AY131">
+        <v>8</v>
+      </c>
+      <c r="AZ131">
+        <v>12</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>6</v>
+      </c>
+      <c r="BC131">
+        <v>9</v>
+      </c>
+      <c r="BD131">
+        <v>0</v>
+      </c>
+      <c r="BE131">
+        <v>0</v>
+      </c>
+      <c r="BF131">
+        <v>0</v>
+      </c>
+      <c r="BG131">
+        <v>0</v>
+      </c>
+      <c r="BH131">
+        <v>0</v>
+      </c>
+      <c r="BI131">
+        <v>0</v>
+      </c>
+      <c r="BJ131">
+        <v>0</v>
+      </c>
+      <c r="BK131">
+        <v>0</v>
+      </c>
+      <c r="BL131">
+        <v>0</v>
+      </c>
+      <c r="BM131">
+        <v>0</v>
+      </c>
+      <c r="BN131">
+        <v>0</v>
+      </c>
+      <c r="BO131">
+        <v>0</v>
+      </c>
+      <c r="BP131">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="215">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -478,6 +478,12 @@
     <t>['3', '5', '59']</t>
   </si>
   <si>
+    <t>['27', '86']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -631,9 +637,6 @@
     <t>['20', '71']</t>
   </si>
   <si>
-    <t>['72']</t>
-  </si>
-  <si>
     <t>['4']</t>
   </si>
   <si>
@@ -653,6 +656,9 @@
   </si>
   <si>
     <t>['33', '51']</t>
+  </si>
+  <si>
+    <t>['84']</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1270,7 +1276,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1476,7 +1482,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1760,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4">
         <v>1.29</v>
@@ -2094,7 +2100,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2300,7 +2306,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2506,7 +2512,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2918,7 +2924,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2996,10 +3002,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3124,7 +3130,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3536,7 +3542,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3742,7 +3748,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3823,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="AQ14">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3948,7 +3954,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4154,7 +4160,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4644,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>0.43</v>
@@ -4853,7 +4859,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ19">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4978,7 +4984,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5184,7 +5190,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5468,7 +5474,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5802,7 +5808,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5880,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
         <v>1.17</v>
@@ -6008,7 +6014,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6707,7 +6713,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR28">
         <v>0.89</v>
@@ -7038,7 +7044,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7943,7 +7949,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ34">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR34">
         <v>0.6899999999999999</v>
@@ -8068,7 +8074,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8352,7 +8358,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ36">
         <v>2.13</v>
@@ -8480,7 +8486,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8561,7 +8567,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR37">
         <v>2.48</v>
@@ -9098,7 +9104,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9179,7 +9185,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ40">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.52</v>
@@ -9304,7 +9310,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9588,7 +9594,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
         <v>0.5</v>
@@ -9716,7 +9722,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10128,7 +10134,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10540,7 +10546,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10621,7 +10627,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ47">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR47">
         <v>1.24</v>
@@ -10952,7 +10958,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11364,7 +11370,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11445,7 +11451,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR51">
         <v>1.11</v>
@@ -11570,7 +11576,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11776,7 +11782,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11854,7 +11860,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
         <v>2.14</v>
@@ -12600,7 +12606,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12678,7 +12684,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ57">
         <v>2.13</v>
@@ -13012,7 +13018,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13424,7 +13430,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13711,7 +13717,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ62">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -14120,7 +14126,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ64">
         <v>1.25</v>
@@ -14454,7 +14460,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14535,7 +14541,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ66">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR66">
         <v>1.26</v>
@@ -14741,7 +14747,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ67">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR67">
         <v>1.03</v>
@@ -14866,7 +14872,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15562,7 +15568,7 @@
         <v>0.67</v>
       </c>
       <c r="AP71">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ71">
         <v>0.43</v>
@@ -15690,7 +15696,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15974,7 +15980,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ73">
         <v>1.14</v>
@@ -16102,7 +16108,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16180,7 +16186,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16308,7 +16314,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16514,7 +16520,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16926,7 +16932,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17132,7 +17138,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17338,7 +17344,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17831,7 +17837,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ82">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR82">
         <v>1.26</v>
@@ -18243,7 +18249,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ84">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR84">
         <v>0.83</v>
@@ -18368,7 +18374,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18449,7 +18455,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ85">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.49</v>
@@ -18574,7 +18580,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18652,7 +18658,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ86">
         <v>2.13</v>
@@ -18780,7 +18786,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19192,7 +19198,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19270,7 +19276,7 @@
         <v>0.6</v>
       </c>
       <c r="AP89">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ89">
         <v>0.5</v>
@@ -19398,7 +19404,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19604,7 +19610,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19810,7 +19816,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20016,7 +20022,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20094,7 +20100,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20303,7 +20309,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20840,7 +20846,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21252,7 +21258,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21458,7 +21464,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21664,7 +21670,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21870,7 +21876,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22154,7 +22160,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ103">
         <v>1.29</v>
@@ -22488,7 +22494,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22981,7 +22987,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ107">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23106,7 +23112,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23312,7 +23318,7 @@
         <v>143</v>
       </c>
       <c r="P109" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23518,7 +23524,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23599,7 +23605,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AR110">
         <v>1.41</v>
@@ -23724,7 +23730,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24008,7 +24014,7 @@
         <v>1.4</v>
       </c>
       <c r="AP112">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ112">
         <v>1.17</v>
@@ -24217,7 +24223,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR113">
         <v>1.17</v>
@@ -24420,10 +24426,10 @@
         <v>0.17</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AR114">
         <v>1.29</v>
@@ -24832,7 +24838,7 @@
         <v>2</v>
       </c>
       <c r="AP116">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ116">
         <v>2</v>
@@ -25166,7 +25172,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25578,7 +25584,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25990,7 +25996,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26196,7 +26202,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -27638,7 +27644,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27844,7 +27850,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28001,6 +28007,624 @@
       </c>
       <c r="BP131">
         <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7729669</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F132">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s">
+        <v>72</v>
+      </c>
+      <c r="H132" t="s">
+        <v>87</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>2</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>154</v>
+      </c>
+      <c r="P132" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q132">
+        <v>4.5</v>
+      </c>
+      <c r="R132">
+        <v>1.85</v>
+      </c>
+      <c r="S132">
+        <v>2.75</v>
+      </c>
+      <c r="T132">
+        <v>1.55</v>
+      </c>
+      <c r="U132">
+        <v>2.3</v>
+      </c>
+      <c r="V132">
+        <v>3.5</v>
+      </c>
+      <c r="W132">
+        <v>1.25</v>
+      </c>
+      <c r="X132">
+        <v>11</v>
+      </c>
+      <c r="Y132">
+        <v>1.05</v>
+      </c>
+      <c r="Z132">
+        <v>4.6</v>
+      </c>
+      <c r="AA132">
+        <v>3.1</v>
+      </c>
+      <c r="AB132">
+        <v>1.88</v>
+      </c>
+      <c r="AC132">
+        <v>1.11</v>
+      </c>
+      <c r="AD132">
+        <v>6</v>
+      </c>
+      <c r="AE132">
+        <v>1.5</v>
+      </c>
+      <c r="AF132">
+        <v>2.3</v>
+      </c>
+      <c r="AG132">
+        <v>2.62</v>
+      </c>
+      <c r="AH132">
+        <v>1.43</v>
+      </c>
+      <c r="AI132">
+        <v>2.1</v>
+      </c>
+      <c r="AJ132">
+        <v>1.62</v>
+      </c>
+      <c r="AK132">
+        <v>1.67</v>
+      </c>
+      <c r="AL132">
+        <v>1.33</v>
+      </c>
+      <c r="AM132">
+        <v>1.22</v>
+      </c>
+      <c r="AN132">
+        <v>1</v>
+      </c>
+      <c r="AO132">
+        <v>1.71</v>
+      </c>
+      <c r="AP132">
+        <v>1.25</v>
+      </c>
+      <c r="AQ132">
+        <v>1.5</v>
+      </c>
+      <c r="AR132">
+        <v>1.28</v>
+      </c>
+      <c r="AS132">
+        <v>1.36</v>
+      </c>
+      <c r="AT132">
+        <v>2.64</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>7</v>
+      </c>
+      <c r="AW132">
+        <v>6</v>
+      </c>
+      <c r="AX132">
+        <v>10</v>
+      </c>
+      <c r="AY132">
+        <v>10</v>
+      </c>
+      <c r="AZ132">
+        <v>17</v>
+      </c>
+      <c r="BA132">
+        <v>2</v>
+      </c>
+      <c r="BB132">
+        <v>12</v>
+      </c>
+      <c r="BC132">
+        <v>14</v>
+      </c>
+      <c r="BD132">
+        <v>3.24</v>
+      </c>
+      <c r="BE132">
+        <v>6.6</v>
+      </c>
+      <c r="BF132">
+        <v>1.52</v>
+      </c>
+      <c r="BG132">
+        <v>1.25</v>
+      </c>
+      <c r="BH132">
+        <v>3.28</v>
+      </c>
+      <c r="BI132">
+        <v>1.48</v>
+      </c>
+      <c r="BJ132">
+        <v>2.33</v>
+      </c>
+      <c r="BK132">
+        <v>1.85</v>
+      </c>
+      <c r="BL132">
+        <v>1.81</v>
+      </c>
+      <c r="BM132">
+        <v>2.38</v>
+      </c>
+      <c r="BN132">
+        <v>1.46</v>
+      </c>
+      <c r="BO132">
+        <v>3.2</v>
+      </c>
+      <c r="BP132">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7729668</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F133">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s">
+        <v>86</v>
+      </c>
+      <c r="H133" t="s">
+        <v>77</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133" t="s">
+        <v>89</v>
+      </c>
+      <c r="P133" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q133">
+        <v>2.3</v>
+      </c>
+      <c r="R133">
+        <v>1.98</v>
+      </c>
+      <c r="S133">
+        <v>5.5</v>
+      </c>
+      <c r="T133">
+        <v>1.51</v>
+      </c>
+      <c r="U133">
+        <v>2.37</v>
+      </c>
+      <c r="V133">
+        <v>3.4</v>
+      </c>
+      <c r="W133">
+        <v>1.27</v>
+      </c>
+      <c r="X133">
+        <v>9.75</v>
+      </c>
+      <c r="Y133">
+        <v>1.04</v>
+      </c>
+      <c r="Z133">
+        <v>1.77</v>
+      </c>
+      <c r="AA133">
+        <v>3.17</v>
+      </c>
+      <c r="AB133">
+        <v>5.3</v>
+      </c>
+      <c r="AC133">
+        <v>1.09</v>
+      </c>
+      <c r="AD133">
+        <v>6</v>
+      </c>
+      <c r="AE133">
+        <v>1.5</v>
+      </c>
+      <c r="AF133">
+        <v>2.4</v>
+      </c>
+      <c r="AG133">
+        <v>2.3</v>
+      </c>
+      <c r="AH133">
+        <v>1.5</v>
+      </c>
+      <c r="AI133">
+        <v>2.37</v>
+      </c>
+      <c r="AJ133">
+        <v>1.51</v>
+      </c>
+      <c r="AK133">
+        <v>1.15</v>
+      </c>
+      <c r="AL133">
+        <v>1.29</v>
+      </c>
+      <c r="AM133">
+        <v>2.1</v>
+      </c>
+      <c r="AN133">
+        <v>1.83</v>
+      </c>
+      <c r="AO133">
+        <v>0.14</v>
+      </c>
+      <c r="AP133">
+        <v>1.71</v>
+      </c>
+      <c r="AQ133">
+        <v>0.25</v>
+      </c>
+      <c r="AR133">
+        <v>1.09</v>
+      </c>
+      <c r="AS133">
+        <v>1.05</v>
+      </c>
+      <c r="AT133">
+        <v>2.14</v>
+      </c>
+      <c r="AU133">
+        <v>0</v>
+      </c>
+      <c r="AV133">
+        <v>2</v>
+      </c>
+      <c r="AW133">
+        <v>6</v>
+      </c>
+      <c r="AX133">
+        <v>8</v>
+      </c>
+      <c r="AY133">
+        <v>6</v>
+      </c>
+      <c r="AZ133">
+        <v>10</v>
+      </c>
+      <c r="BA133">
+        <v>6</v>
+      </c>
+      <c r="BB133">
+        <v>3</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>1.4</v>
+      </c>
+      <c r="BE133">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF133">
+        <v>3.46</v>
+      </c>
+      <c r="BG133">
+        <v>1.3</v>
+      </c>
+      <c r="BH133">
+        <v>2.97</v>
+      </c>
+      <c r="BI133">
+        <v>1.56</v>
+      </c>
+      <c r="BJ133">
+        <v>2.16</v>
+      </c>
+      <c r="BK133">
+        <v>1.98</v>
+      </c>
+      <c r="BL133">
+        <v>1.7</v>
+      </c>
+      <c r="BM133">
+        <v>2.59</v>
+      </c>
+      <c r="BN133">
+        <v>1.39</v>
+      </c>
+      <c r="BO133">
+        <v>3.58</v>
+      </c>
+      <c r="BP133">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7729670</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F134">
+        <v>15</v>
+      </c>
+      <c r="G134" t="s">
+        <v>78</v>
+      </c>
+      <c r="H134" t="s">
+        <v>76</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" t="s">
+        <v>155</v>
+      </c>
+      <c r="P134" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q134">
+        <v>2.13</v>
+      </c>
+      <c r="R134">
+        <v>2.27</v>
+      </c>
+      <c r="S134">
+        <v>5.2</v>
+      </c>
+      <c r="T134">
+        <v>1.34</v>
+      </c>
+      <c r="U134">
+        <v>2.9</v>
+      </c>
+      <c r="V134">
+        <v>2.6</v>
+      </c>
+      <c r="W134">
+        <v>1.44</v>
+      </c>
+      <c r="X134">
+        <v>6.1</v>
+      </c>
+      <c r="Y134">
+        <v>1.08</v>
+      </c>
+      <c r="Z134">
+        <v>1.99</v>
+      </c>
+      <c r="AA134">
+        <v>3.12</v>
+      </c>
+      <c r="AB134">
+        <v>4.1</v>
+      </c>
+      <c r="AC134">
+        <v>1.02</v>
+      </c>
+      <c r="AD134">
+        <v>10</v>
+      </c>
+      <c r="AE134">
+        <v>1.27</v>
+      </c>
+      <c r="AF134">
+        <v>3.5</v>
+      </c>
+      <c r="AG134">
+        <v>1.91</v>
+      </c>
+      <c r="AH134">
+        <v>1.83</v>
+      </c>
+      <c r="AI134">
+        <v>1.83</v>
+      </c>
+      <c r="AJ134">
+        <v>1.87</v>
+      </c>
+      <c r="AK134">
+        <v>1.16</v>
+      </c>
+      <c r="AL134">
+        <v>1.24</v>
+      </c>
+      <c r="AM134">
+        <v>2.09</v>
+      </c>
+      <c r="AN134">
+        <v>2.43</v>
+      </c>
+      <c r="AO134">
+        <v>1.67</v>
+      </c>
+      <c r="AP134">
+        <v>2.25</v>
+      </c>
+      <c r="AQ134">
+        <v>1.57</v>
+      </c>
+      <c r="AR134">
+        <v>1.8</v>
+      </c>
+      <c r="AS134">
+        <v>1.31</v>
+      </c>
+      <c r="AT134">
+        <v>3.11</v>
+      </c>
+      <c r="AU134">
+        <v>8</v>
+      </c>
+      <c r="AV134">
+        <v>4</v>
+      </c>
+      <c r="AW134">
+        <v>11</v>
+      </c>
+      <c r="AX134">
+        <v>3</v>
+      </c>
+      <c r="AY134">
+        <v>19</v>
+      </c>
+      <c r="AZ134">
+        <v>7</v>
+      </c>
+      <c r="BA134">
+        <v>4</v>
+      </c>
+      <c r="BB134">
+        <v>5</v>
+      </c>
+      <c r="BC134">
+        <v>9</v>
+      </c>
+      <c r="BD134">
+        <v>1.45</v>
+      </c>
+      <c r="BE134">
+        <v>6.85</v>
+      </c>
+      <c r="BF134">
+        <v>3.54</v>
+      </c>
+      <c r="BG134">
+        <v>1.25</v>
+      </c>
+      <c r="BH134">
+        <v>3.28</v>
+      </c>
+      <c r="BI134">
+        <v>1.47</v>
+      </c>
+      <c r="BJ134">
+        <v>2.35</v>
+      </c>
+      <c r="BK134">
+        <v>1.84</v>
+      </c>
+      <c r="BL134">
+        <v>1.82</v>
+      </c>
+      <c r="BM134">
+        <v>2.35</v>
+      </c>
+      <c r="BN134">
+        <v>1.47</v>
+      </c>
+      <c r="BO134">
+        <v>3.2</v>
+      </c>
+      <c r="BP134">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -482,6 +482,12 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['27', '90+1']</t>
+  </si>
+  <si>
+    <t>['27', '90+4']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -1020,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1276,7 +1282,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1482,7 +1488,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2100,7 +2106,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2306,7 +2312,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2384,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ7">
         <v>1.29</v>
@@ -2512,7 +2518,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2799,7 +2805,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ9">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2924,7 +2930,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3130,7 +3136,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3211,7 +3217,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ11">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3542,7 +3548,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3620,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
         <v>2.14</v>
@@ -3748,7 +3754,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3954,7 +3960,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4160,7 +4166,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4984,7 +4990,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5190,7 +5196,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5268,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ21">
         <v>2</v>
@@ -5808,7 +5814,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5889,7 +5895,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.3</v>
@@ -6014,7 +6020,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6916,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7044,7 +7050,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7331,7 +7337,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ31">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR31">
         <v>1.06</v>
@@ -8074,7 +8080,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8486,7 +8492,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9104,7 +9110,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9310,7 +9316,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9722,7 +9728,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10134,7 +10140,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10418,7 +10424,7 @@
         <v>0.33</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
@@ -10546,7 +10552,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10958,7 +10964,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11242,7 +11248,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ50">
         <v>1.14</v>
@@ -11370,7 +11376,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11576,7 +11582,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11657,7 +11663,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11782,7 +11788,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12275,7 +12281,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR55">
         <v>0.74</v>
@@ -12606,7 +12612,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13018,7 +13024,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13302,7 +13308,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ60">
         <v>1.29</v>
@@ -13430,7 +13436,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14460,7 +14466,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14872,7 +14878,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15362,10 +15368,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.68</v>
@@ -15696,7 +15702,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16108,7 +16114,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16314,7 +16320,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16520,7 +16526,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16601,7 +16607,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ76">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR76">
         <v>0.77</v>
@@ -16932,7 +16938,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17138,7 +17144,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17344,7 +17350,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17422,7 +17428,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ80">
         <v>2.13</v>
@@ -18374,7 +18380,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18580,7 +18586,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18786,7 +18792,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19198,7 +19204,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19404,7 +19410,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19610,7 +19616,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19816,7 +19822,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19897,7 +19903,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ92">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR92">
         <v>1.04</v>
@@ -20022,7 +20028,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20306,7 +20312,7 @@
         <v>1.75</v>
       </c>
       <c r="AP94">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ94">
         <v>1.57</v>
@@ -20512,7 +20518,7 @@
         <v>1.6</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ95">
         <v>1.5</v>
@@ -20846,7 +20852,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -20927,7 +20933,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.43</v>
@@ -21258,7 +21264,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21464,7 +21470,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21670,7 +21676,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21876,7 +21882,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22494,7 +22500,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23112,7 +23118,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23524,7 +23530,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23730,7 +23736,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24017,7 +24023,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.95</v>
@@ -24220,7 +24226,7 @@
         <v>1.83</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ113">
         <v>1.5</v>
@@ -24632,7 +24638,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25047,7 +25053,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ117">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR117">
         <v>1.15</v>
@@ -25172,7 +25178,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25584,7 +25590,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25996,7 +26002,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26202,7 +26208,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -27644,7 +27650,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27850,7 +27856,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28468,7 +28474,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -28625,6 +28631,418 @@
       </c>
       <c r="BP134">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7729671</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F135">
+        <v>15</v>
+      </c>
+      <c r="G135" t="s">
+        <v>81</v>
+      </c>
+      <c r="H135" t="s">
+        <v>79</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>2</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>156</v>
+      </c>
+      <c r="P135" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q135">
+        <v>3.01</v>
+      </c>
+      <c r="R135">
+        <v>1.92</v>
+      </c>
+      <c r="S135">
+        <v>4.6</v>
+      </c>
+      <c r="T135">
+        <v>1.59</v>
+      </c>
+      <c r="U135">
+        <v>2.32</v>
+      </c>
+      <c r="V135">
+        <v>3.6</v>
+      </c>
+      <c r="W135">
+        <v>1.25</v>
+      </c>
+      <c r="X135">
+        <v>10</v>
+      </c>
+      <c r="Y135">
+        <v>1.02</v>
+      </c>
+      <c r="Z135">
+        <v>2.1</v>
+      </c>
+      <c r="AA135">
+        <v>2.88</v>
+      </c>
+      <c r="AB135">
+        <v>3.6</v>
+      </c>
+      <c r="AC135">
+        <v>1.11</v>
+      </c>
+      <c r="AD135">
+        <v>5.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.57</v>
+      </c>
+      <c r="AF135">
+        <v>2.25</v>
+      </c>
+      <c r="AG135">
+        <v>2.7</v>
+      </c>
+      <c r="AH135">
+        <v>1.4</v>
+      </c>
+      <c r="AI135">
+        <v>2.25</v>
+      </c>
+      <c r="AJ135">
+        <v>1.57</v>
+      </c>
+      <c r="AK135">
+        <v>1.25</v>
+      </c>
+      <c r="AL135">
+        <v>1.4</v>
+      </c>
+      <c r="AM135">
+        <v>1.7</v>
+      </c>
+      <c r="AN135">
+        <v>1</v>
+      </c>
+      <c r="AO135">
+        <v>1.17</v>
+      </c>
+      <c r="AP135">
+        <v>1.25</v>
+      </c>
+      <c r="AQ135">
+        <v>1</v>
+      </c>
+      <c r="AR135">
+        <v>1.18</v>
+      </c>
+      <c r="AS135">
+        <v>1.03</v>
+      </c>
+      <c r="AT135">
+        <v>2.21</v>
+      </c>
+      <c r="AU135">
+        <v>3</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>6</v>
+      </c>
+      <c r="AX135">
+        <v>7</v>
+      </c>
+      <c r="AY135">
+        <v>9</v>
+      </c>
+      <c r="AZ135">
+        <v>11</v>
+      </c>
+      <c r="BA135">
+        <v>2</v>
+      </c>
+      <c r="BB135">
+        <v>3</v>
+      </c>
+      <c r="BC135">
+        <v>5</v>
+      </c>
+      <c r="BD135">
+        <v>1.49</v>
+      </c>
+      <c r="BE135">
+        <v>6.7</v>
+      </c>
+      <c r="BF135">
+        <v>3.36</v>
+      </c>
+      <c r="BG135">
+        <v>1.32</v>
+      </c>
+      <c r="BH135">
+        <v>2.88</v>
+      </c>
+      <c r="BI135">
+        <v>1.59</v>
+      </c>
+      <c r="BJ135">
+        <v>2.1</v>
+      </c>
+      <c r="BK135">
+        <v>2.04</v>
+      </c>
+      <c r="BL135">
+        <v>1.66</v>
+      </c>
+      <c r="BM135">
+        <v>2.66</v>
+      </c>
+      <c r="BN135">
+        <v>1.37</v>
+      </c>
+      <c r="BO135">
+        <v>3.74</v>
+      </c>
+      <c r="BP135">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7729672</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45711.58333333334</v>
+      </c>
+      <c r="F136">
+        <v>15</v>
+      </c>
+      <c r="G136" t="s">
+        <v>75</v>
+      </c>
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>2</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136" t="s">
+        <v>157</v>
+      </c>
+      <c r="P136" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q136">
+        <v>1.91</v>
+      </c>
+      <c r="R136">
+        <v>2.34</v>
+      </c>
+      <c r="S136">
+        <v>8.07</v>
+      </c>
+      <c r="T136">
+        <v>1.4</v>
+      </c>
+      <c r="U136">
+        <v>2.87</v>
+      </c>
+      <c r="V136">
+        <v>3.02</v>
+      </c>
+      <c r="W136">
+        <v>1.36</v>
+      </c>
+      <c r="X136">
+        <v>6.5</v>
+      </c>
+      <c r="Y136">
+        <v>1.08</v>
+      </c>
+      <c r="Z136">
+        <v>1.47</v>
+      </c>
+      <c r="AA136">
+        <v>3.99</v>
+      </c>
+      <c r="AB136">
+        <v>7.2</v>
+      </c>
+      <c r="AC136">
+        <v>1.03</v>
+      </c>
+      <c r="AD136">
+        <v>9</v>
+      </c>
+      <c r="AE136">
+        <v>1.3</v>
+      </c>
+      <c r="AF136">
+        <v>3.2</v>
+      </c>
+      <c r="AG136">
+        <v>1.95</v>
+      </c>
+      <c r="AH136">
+        <v>1.79</v>
+      </c>
+      <c r="AI136">
+        <v>2.25</v>
+      </c>
+      <c r="AJ136">
+        <v>1.57</v>
+      </c>
+      <c r="AK136">
+        <v>1.07</v>
+      </c>
+      <c r="AL136">
+        <v>1.2</v>
+      </c>
+      <c r="AM136">
+        <v>3</v>
+      </c>
+      <c r="AN136">
+        <v>2.67</v>
+      </c>
+      <c r="AO136">
+        <v>2.17</v>
+      </c>
+      <c r="AP136">
+        <v>2.71</v>
+      </c>
+      <c r="AQ136">
+        <v>1.86</v>
+      </c>
+      <c r="AR136">
+        <v>1.71</v>
+      </c>
+      <c r="AS136">
+        <v>1.19</v>
+      </c>
+      <c r="AT136">
+        <v>2.9</v>
+      </c>
+      <c r="AU136">
+        <v>8</v>
+      </c>
+      <c r="AV136">
+        <v>3</v>
+      </c>
+      <c r="AW136">
+        <v>9</v>
+      </c>
+      <c r="AX136">
+        <v>6</v>
+      </c>
+      <c r="AY136">
+        <v>17</v>
+      </c>
+      <c r="AZ136">
+        <v>9</v>
+      </c>
+      <c r="BA136">
+        <v>7</v>
+      </c>
+      <c r="BB136">
+        <v>4</v>
+      </c>
+      <c r="BC136">
+        <v>11</v>
+      </c>
+      <c r="BD136">
+        <v>1.23</v>
+      </c>
+      <c r="BE136">
+        <v>9.9</v>
+      </c>
+      <c r="BF136">
+        <v>4.9</v>
+      </c>
+      <c r="BG136">
+        <v>1.28</v>
+      </c>
+      <c r="BH136">
+        <v>3.05</v>
+      </c>
+      <c r="BI136">
+        <v>1.53</v>
+      </c>
+      <c r="BJ136">
+        <v>2.21</v>
+      </c>
+      <c r="BK136">
+        <v>1.93</v>
+      </c>
+      <c r="BL136">
+        <v>1.74</v>
+      </c>
+      <c r="BM136">
+        <v>2.52</v>
+      </c>
+      <c r="BN136">
+        <v>1.41</v>
+      </c>
+      <c r="BO136">
+        <v>3.42</v>
+      </c>
+      <c r="BP136">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,6 +490,9 @@
     <t>['27', '90+4']</t>
   </si>
   <si>
+    <t>['72', '83']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -665,6 +668,15 @@
   </si>
   <si>
     <t>['84']</t>
+  </si>
+  <si>
+    <t>['13', '23', '49']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['65', '68']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1282,7 +1294,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1360,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2">
         <v>1.25</v>
@@ -1488,7 +1500,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1978,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -2106,7 +2118,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2312,7 +2324,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2518,7 +2530,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2802,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2930,7 +2942,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3136,7 +3148,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3548,7 +3560,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3629,7 +3641,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ13">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3754,7 +3766,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3960,7 +3972,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4166,7 +4178,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4453,7 +4465,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4659,7 +4671,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ18">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4990,7 +5002,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5196,7 +5208,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5814,7 +5826,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6020,7 +6032,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6304,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ26">
         <v>1.29</v>
@@ -6510,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ27">
         <v>1.29</v>
@@ -6716,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -7050,7 +7062,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7543,7 +7555,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ32">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -7749,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>1.75</v>
@@ -8080,7 +8092,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8161,7 +8173,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ35">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR35">
         <v>2.03</v>
@@ -8492,7 +8504,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8776,7 +8788,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ38">
         <v>1.5</v>
@@ -9110,7 +9122,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9316,7 +9328,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9394,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9728,7 +9740,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10140,7 +10152,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10218,7 +10230,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ45">
         <v>2.13</v>
@@ -10552,7 +10564,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10964,7 +10976,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11042,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11251,7 +11263,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ50">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR50">
         <v>1.6</v>
@@ -11376,7 +11388,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11582,7 +11594,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11788,7 +11800,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11869,7 +11881,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ53">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR53">
         <v>0.97</v>
@@ -12075,7 +12087,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR54">
         <v>1.9</v>
@@ -12278,7 +12290,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
         <v>1.86</v>
@@ -12612,7 +12624,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12899,7 +12911,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ58">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR58">
         <v>0.89</v>
@@ -13024,7 +13036,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13436,7 +13448,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13720,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ62">
         <v>0.25</v>
@@ -14466,7 +14478,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14878,7 +14890,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15577,7 +15589,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ71">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -15702,7 +15714,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15989,7 +16001,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ73">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>1.04</v>
@@ -16114,7 +16126,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16320,7 +16332,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16526,7 +16538,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16810,7 +16822,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ77">
         <v>1.25</v>
@@ -16938,7 +16950,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17019,7 +17031,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ78">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17144,7 +17156,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17350,7 +17362,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17840,7 +17852,7 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ82">
         <v>1.57</v>
@@ -18049,7 +18061,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ83">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR83">
         <v>1.22</v>
@@ -18380,7 +18392,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18586,7 +18598,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18792,7 +18804,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18873,7 +18885,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ87">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR87">
         <v>1.76</v>
@@ -19076,7 +19088,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ88">
         <v>0.43</v>
@@ -19204,7 +19216,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19410,7 +19422,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19616,7 +19628,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19822,7 +19834,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19900,7 +19912,7 @@
         <v>2.25</v>
       </c>
       <c r="AP92">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ92">
         <v>1.86</v>
@@ -20028,7 +20040,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20852,7 +20864,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21264,7 +21276,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21470,7 +21482,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21548,10 +21560,10 @@
         <v>1.8</v>
       </c>
       <c r="AP100">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ100">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -21676,7 +21688,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21882,7 +21894,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -21963,7 +21975,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ102">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR102">
         <v>1.53</v>
@@ -22372,7 +22384,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104">
         <v>0.5</v>
@@ -22500,7 +22512,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22787,7 +22799,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ106">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR106">
         <v>1.49</v>
@@ -23118,7 +23130,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23530,7 +23542,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23736,7 +23748,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -25050,7 +25062,7 @@
         <v>2.4</v>
       </c>
       <c r="AP117">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ117">
         <v>1.86</v>
@@ -25178,7 +25190,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25590,7 +25602,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25874,10 +25886,10 @@
         <v>1.33</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ121">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR121">
         <v>0.9399999999999999</v>
@@ -26002,7 +26014,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26080,10 +26092,10 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ122">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR122">
         <v>1.04</v>
@@ -26208,7 +26220,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26492,7 +26504,7 @@
         <v>2</v>
       </c>
       <c r="AP124">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ124">
         <v>2.13</v>
@@ -26701,7 +26713,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ125">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AR125">
         <v>0.96</v>
@@ -27650,7 +27662,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27856,7 +27868,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28474,7 +28486,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29043,6 +29055,624 @@
       </c>
       <c r="BP136">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7729673</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45714.45833333334</v>
+      </c>
+      <c r="F137">
+        <v>16</v>
+      </c>
+      <c r="G137" t="s">
+        <v>73</v>
+      </c>
+      <c r="H137" t="s">
+        <v>72</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>3</v>
+      </c>
+      <c r="N137">
+        <v>5</v>
+      </c>
+      <c r="O137" t="s">
+        <v>158</v>
+      </c>
+      <c r="P137" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q137">
+        <v>2.8</v>
+      </c>
+      <c r="R137">
+        <v>1.75</v>
+      </c>
+      <c r="S137">
+        <v>6</v>
+      </c>
+      <c r="T137">
+        <v>1.79</v>
+      </c>
+      <c r="U137">
+        <v>1.94</v>
+      </c>
+      <c r="V137">
+        <v>4.5</v>
+      </c>
+      <c r="W137">
+        <v>1.17</v>
+      </c>
+      <c r="X137">
+        <v>12</v>
+      </c>
+      <c r="Y137">
+        <v>1.01</v>
+      </c>
+      <c r="Z137">
+        <v>2.01</v>
+      </c>
+      <c r="AA137">
+        <v>2.69</v>
+      </c>
+      <c r="AB137">
+        <v>5</v>
+      </c>
+      <c r="AC137">
+        <v>1.18</v>
+      </c>
+      <c r="AD137">
+        <v>4.3</v>
+      </c>
+      <c r="AE137">
+        <v>1.85</v>
+      </c>
+      <c r="AF137">
+        <v>1.89</v>
+      </c>
+      <c r="AG137">
+        <v>3.48</v>
+      </c>
+      <c r="AH137">
+        <v>1.26</v>
+      </c>
+      <c r="AI137">
+        <v>2.8</v>
+      </c>
+      <c r="AJ137">
+        <v>1.39</v>
+      </c>
+      <c r="AK137">
+        <v>1.17</v>
+      </c>
+      <c r="AL137">
+        <v>1.38</v>
+      </c>
+      <c r="AM137">
+        <v>1.72</v>
+      </c>
+      <c r="AN137">
+        <v>0.88</v>
+      </c>
+      <c r="AO137">
+        <v>0.43</v>
+      </c>
+      <c r="AP137">
+        <v>0.78</v>
+      </c>
+      <c r="AQ137">
+        <v>0.75</v>
+      </c>
+      <c r="AR137">
+        <v>1.04</v>
+      </c>
+      <c r="AS137">
+        <v>1.14</v>
+      </c>
+      <c r="AT137">
+        <v>2.18</v>
+      </c>
+      <c r="AU137">
+        <v>6</v>
+      </c>
+      <c r="AV137">
+        <v>5</v>
+      </c>
+      <c r="AW137">
+        <v>6</v>
+      </c>
+      <c r="AX137">
+        <v>1</v>
+      </c>
+      <c r="AY137">
+        <v>12</v>
+      </c>
+      <c r="AZ137">
+        <v>6</v>
+      </c>
+      <c r="BA137">
+        <v>2</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>4</v>
+      </c>
+      <c r="BD137">
+        <v>1.54</v>
+      </c>
+      <c r="BE137">
+        <v>8.4</v>
+      </c>
+      <c r="BF137">
+        <v>2.86</v>
+      </c>
+      <c r="BG137">
+        <v>1.28</v>
+      </c>
+      <c r="BH137">
+        <v>3.08</v>
+      </c>
+      <c r="BI137">
+        <v>1.52</v>
+      </c>
+      <c r="BJ137">
+        <v>2.24</v>
+      </c>
+      <c r="BK137">
+        <v>1.92</v>
+      </c>
+      <c r="BL137">
+        <v>1.75</v>
+      </c>
+      <c r="BM137">
+        <v>2.49</v>
+      </c>
+      <c r="BN137">
+        <v>1.42</v>
+      </c>
+      <c r="BO137">
+        <v>3.42</v>
+      </c>
+      <c r="BP137">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7729674</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45714.45833333334</v>
+      </c>
+      <c r="F138">
+        <v>16</v>
+      </c>
+      <c r="G138" t="s">
+        <v>70</v>
+      </c>
+      <c r="H138" t="s">
+        <v>78</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>89</v>
+      </c>
+      <c r="P138" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q138">
+        <v>8</v>
+      </c>
+      <c r="R138">
+        <v>2.3</v>
+      </c>
+      <c r="S138">
+        <v>1.8</v>
+      </c>
+      <c r="T138">
+        <v>1.4</v>
+      </c>
+      <c r="U138">
+        <v>2.7</v>
+      </c>
+      <c r="V138">
+        <v>2.9</v>
+      </c>
+      <c r="W138">
+        <v>1.36</v>
+      </c>
+      <c r="X138">
+        <v>7.75</v>
+      </c>
+      <c r="Y138">
+        <v>1.07</v>
+      </c>
+      <c r="Z138">
+        <v>9.5</v>
+      </c>
+      <c r="AA138">
+        <v>4.3</v>
+      </c>
+      <c r="AB138">
+        <v>1.37</v>
+      </c>
+      <c r="AC138">
+        <v>1.05</v>
+      </c>
+      <c r="AD138">
+        <v>8.5</v>
+      </c>
+      <c r="AE138">
+        <v>1.33</v>
+      </c>
+      <c r="AF138">
+        <v>3.15</v>
+      </c>
+      <c r="AG138">
+        <v>2</v>
+      </c>
+      <c r="AH138">
+        <v>1.75</v>
+      </c>
+      <c r="AI138">
+        <v>2.6</v>
+      </c>
+      <c r="AJ138">
+        <v>1.43</v>
+      </c>
+      <c r="AK138">
+        <v>3.3</v>
+      </c>
+      <c r="AL138">
+        <v>1.17</v>
+      </c>
+      <c r="AM138">
+        <v>1.06</v>
+      </c>
+      <c r="AN138">
+        <v>2</v>
+      </c>
+      <c r="AO138">
+        <v>2.14</v>
+      </c>
+      <c r="AP138">
+        <v>1.75</v>
+      </c>
+      <c r="AQ138">
+        <v>2.25</v>
+      </c>
+      <c r="AR138">
+        <v>1.02</v>
+      </c>
+      <c r="AS138">
+        <v>1.58</v>
+      </c>
+      <c r="AT138">
+        <v>2.6</v>
+      </c>
+      <c r="AU138">
+        <v>3</v>
+      </c>
+      <c r="AV138">
+        <v>2</v>
+      </c>
+      <c r="AW138">
+        <v>4</v>
+      </c>
+      <c r="AX138">
+        <v>7</v>
+      </c>
+      <c r="AY138">
+        <v>7</v>
+      </c>
+      <c r="AZ138">
+        <v>9</v>
+      </c>
+      <c r="BA138">
+        <v>3</v>
+      </c>
+      <c r="BB138">
+        <v>7</v>
+      </c>
+      <c r="BC138">
+        <v>10</v>
+      </c>
+      <c r="BD138">
+        <v>3.62</v>
+      </c>
+      <c r="BE138">
+        <v>8.9</v>
+      </c>
+      <c r="BF138">
+        <v>1.37</v>
+      </c>
+      <c r="BG138">
+        <v>1.27</v>
+      </c>
+      <c r="BH138">
+        <v>3.14</v>
+      </c>
+      <c r="BI138">
+        <v>1.5</v>
+      </c>
+      <c r="BJ138">
+        <v>2.28</v>
+      </c>
+      <c r="BK138">
+        <v>1.88</v>
+      </c>
+      <c r="BL138">
+        <v>1.78</v>
+      </c>
+      <c r="BM138">
+        <v>2.43</v>
+      </c>
+      <c r="BN138">
+        <v>1.44</v>
+      </c>
+      <c r="BO138">
+        <v>3.28</v>
+      </c>
+      <c r="BP138">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7729675</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45714.58333333334</v>
+      </c>
+      <c r="F139">
+        <v>16</v>
+      </c>
+      <c r="G139" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" t="s">
+        <v>74</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>2</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>89</v>
+      </c>
+      <c r="P139" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q139">
+        <v>3.6</v>
+      </c>
+      <c r="R139">
+        <v>1.75</v>
+      </c>
+      <c r="S139">
+        <v>3.85</v>
+      </c>
+      <c r="T139">
+        <v>1.75</v>
+      </c>
+      <c r="U139">
+        <v>1.98</v>
+      </c>
+      <c r="V139">
+        <v>4.33</v>
+      </c>
+      <c r="W139">
+        <v>1.18</v>
+      </c>
+      <c r="X139">
+        <v>12</v>
+      </c>
+      <c r="Y139">
+        <v>1.01</v>
+      </c>
+      <c r="Z139">
+        <v>2.71</v>
+      </c>
+      <c r="AA139">
+        <v>2.66</v>
+      </c>
+      <c r="AB139">
+        <v>3.07</v>
+      </c>
+      <c r="AC139">
+        <v>1.17</v>
+      </c>
+      <c r="AD139">
+        <v>4.6</v>
+      </c>
+      <c r="AE139">
+        <v>1.61</v>
+      </c>
+      <c r="AF139">
+        <v>2.05</v>
+      </c>
+      <c r="AG139">
+        <v>3.27</v>
+      </c>
+      <c r="AH139">
+        <v>1.29</v>
+      </c>
+      <c r="AI139">
+        <v>2.41</v>
+      </c>
+      <c r="AJ139">
+        <v>1.51</v>
+      </c>
+      <c r="AK139">
+        <v>1.36</v>
+      </c>
+      <c r="AL139">
+        <v>1.43</v>
+      </c>
+      <c r="AM139">
+        <v>1.39</v>
+      </c>
+      <c r="AN139">
+        <v>1.29</v>
+      </c>
+      <c r="AO139">
+        <v>1.14</v>
+      </c>
+      <c r="AP139">
+        <v>1.13</v>
+      </c>
+      <c r="AQ139">
+        <v>1.38</v>
+      </c>
+      <c r="AR139">
+        <v>0.97</v>
+      </c>
+      <c r="AS139">
+        <v>0.97</v>
+      </c>
+      <c r="AT139">
+        <v>1.94</v>
+      </c>
+      <c r="AU139">
+        <v>2</v>
+      </c>
+      <c r="AV139">
+        <v>5</v>
+      </c>
+      <c r="AW139">
+        <v>6</v>
+      </c>
+      <c r="AX139">
+        <v>6</v>
+      </c>
+      <c r="AY139">
+        <v>8</v>
+      </c>
+      <c r="AZ139">
+        <v>11</v>
+      </c>
+      <c r="BA139">
+        <v>7</v>
+      </c>
+      <c r="BB139">
+        <v>2</v>
+      </c>
+      <c r="BC139">
+        <v>9</v>
+      </c>
+      <c r="BD139">
+        <v>1.83</v>
+      </c>
+      <c r="BE139">
+        <v>6</v>
+      </c>
+      <c r="BF139">
+        <v>2.47</v>
+      </c>
+      <c r="BG139">
+        <v>1.47</v>
+      </c>
+      <c r="BH139">
+        <v>2.35</v>
+      </c>
+      <c r="BI139">
+        <v>1.86</v>
+      </c>
+      <c r="BJ139">
+        <v>1.8</v>
+      </c>
+      <c r="BK139">
+        <v>2.43</v>
+      </c>
+      <c r="BL139">
+        <v>1.44</v>
+      </c>
+      <c r="BM139">
+        <v>3.34</v>
+      </c>
+      <c r="BN139">
+        <v>1.24</v>
+      </c>
+      <c r="BO139">
+        <v>4.5</v>
+      </c>
+      <c r="BP139">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,12 @@
     <t>['72', '83']</t>
   </si>
   <si>
+    <t>['27', '58']</t>
+  </si>
+  <si>
+    <t>['45+5']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -677,6 +683,12 @@
   </si>
   <si>
     <t>['65', '68']</t>
+  </si>
+  <si>
+    <t>['5', '45+1', '90+1']</t>
+  </si>
+  <si>
+    <t>['84', '90+11']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1294,7 +1306,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1500,7 +1512,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1578,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ3">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1787,7 +1799,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ4">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2118,7 +2130,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2324,7 +2336,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2530,7 +2542,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2608,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2942,7 +2954,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3148,7 +3160,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3560,7 +3572,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3766,7 +3778,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3844,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ14">
         <v>1.57</v>
@@ -3972,7 +3984,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4178,7 +4190,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -5002,7 +5014,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5208,7 +5220,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5289,7 +5301,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR21">
         <v>1.79</v>
@@ -5698,7 +5710,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ23">
         <v>1.25</v>
@@ -5826,7 +5838,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6032,7 +6044,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6110,10 +6122,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
         <v>1.36</v>
@@ -6525,7 +6537,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR27">
         <v>2</v>
@@ -7062,7 +7074,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7758,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ33">
         <v>0.75</v>
@@ -8092,7 +8104,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8504,7 +8516,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8791,7 +8803,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>0.8100000000000001</v>
@@ -8994,7 +9006,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ39">
         <v>1.29</v>
@@ -9122,7 +9134,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9200,7 +9212,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.5</v>
@@ -9328,7 +9340,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9409,7 +9421,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ41">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR41">
         <v>1.57</v>
@@ -9740,7 +9752,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9821,7 +9833,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -10152,7 +10164,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10564,7 +10576,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10642,7 +10654,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ47">
         <v>1.57</v>
@@ -10976,7 +10988,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11388,7 +11400,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11594,7 +11606,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11672,7 +11684,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11800,7 +11812,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12496,7 +12508,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -12624,7 +12636,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13036,7 +13048,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13448,7 +13460,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13529,7 +13541,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR61">
         <v>1.52</v>
@@ -13941,7 +13953,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR63">
         <v>1.51</v>
@@ -14478,7 +14490,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14556,7 +14568,7 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ66">
         <v>1.5</v>
@@ -14890,7 +14902,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14971,7 +14983,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>0.92</v>
@@ -15174,7 +15186,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ69">
         <v>0.43</v>
@@ -15714,7 +15726,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15792,7 +15804,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -16126,7 +16138,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16207,7 +16219,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
         <v>1.35</v>
@@ -16332,7 +16344,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16538,7 +16550,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16950,7 +16962,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17156,7 +17168,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17362,7 +17374,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17649,7 +17661,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.81</v>
@@ -18058,7 +18070,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ83">
         <v>1.38</v>
@@ -18392,7 +18404,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18598,7 +18610,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18804,7 +18816,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18882,7 +18894,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>0.75</v>
@@ -19216,7 +19228,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19422,7 +19434,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19628,7 +19640,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19706,10 +19718,10 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ91">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.61</v>
@@ -19834,7 +19846,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20040,7 +20052,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20533,7 +20545,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR95">
         <v>1.28</v>
@@ -20739,7 +20751,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ96">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR96">
         <v>0.8</v>
@@ -20864,7 +20876,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21276,7 +21288,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21482,7 +21494,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21688,7 +21700,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21894,7 +21906,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22512,7 +22524,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22590,7 +22602,7 @@
         <v>1.83</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ105">
         <v>2.13</v>
@@ -22796,7 +22808,7 @@
         <v>0.4</v>
       </c>
       <c r="AP106">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ106">
         <v>0.75</v>
@@ -23002,7 +23014,7 @@
         <v>0.2</v>
       </c>
       <c r="AP107">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>0.25</v>
@@ -23130,7 +23142,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23211,7 +23223,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ108">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR108">
         <v>0.86</v>
@@ -23417,7 +23429,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ109">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR109">
         <v>1.08</v>
@@ -23542,7 +23554,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23748,7 +23760,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24859,7 +24871,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ116">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR116">
         <v>1.12</v>
@@ -25190,7 +25202,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25474,7 +25486,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.29</v>
@@ -25602,7 +25614,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25680,10 +25692,10 @@
         <v>1.86</v>
       </c>
       <c r="AP120">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ120">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR120">
         <v>1.58</v>
@@ -26014,7 +26026,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26220,7 +26232,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26916,10 +26928,10 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR126">
         <v>1.44</v>
@@ -27125,7 +27137,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ127">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.47</v>
@@ -27662,7 +27674,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27868,7 +27880,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28486,7 +28498,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29104,7 +29116,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29310,7 +29322,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29516,7 +29528,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29673,6 +29685,624 @@
       </c>
       <c r="BP139">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7729676</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45715.45833333334</v>
+      </c>
+      <c r="F140">
+        <v>16</v>
+      </c>
+      <c r="G140" t="s">
+        <v>82</v>
+      </c>
+      <c r="H140" t="s">
+        <v>86</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>2</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>3</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>89</v>
+      </c>
+      <c r="P140" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q140">
+        <v>3.7</v>
+      </c>
+      <c r="R140">
+        <v>1.87</v>
+      </c>
+      <c r="S140">
+        <v>3.3</v>
+      </c>
+      <c r="T140">
+        <v>1.61</v>
+      </c>
+      <c r="U140">
+        <v>2.21</v>
+      </c>
+      <c r="V140">
+        <v>3.65</v>
+      </c>
+      <c r="W140">
+        <v>1.25</v>
+      </c>
+      <c r="X140">
+        <v>9.1</v>
+      </c>
+      <c r="Y140">
+        <v>1.04</v>
+      </c>
+      <c r="Z140">
+        <v>2.93</v>
+      </c>
+      <c r="AA140">
+        <v>2.8</v>
+      </c>
+      <c r="AB140">
+        <v>2.7</v>
+      </c>
+      <c r="AC140">
+        <v>1.12</v>
+      </c>
+      <c r="AD140">
+        <v>5.8</v>
+      </c>
+      <c r="AE140">
+        <v>1.5</v>
+      </c>
+      <c r="AF140">
+        <v>2.25</v>
+      </c>
+      <c r="AG140">
+        <v>2.56</v>
+      </c>
+      <c r="AH140">
+        <v>1.45</v>
+      </c>
+      <c r="AI140">
+        <v>2.1</v>
+      </c>
+      <c r="AJ140">
+        <v>1.66</v>
+      </c>
+      <c r="AK140">
+        <v>1.44</v>
+      </c>
+      <c r="AL140">
+        <v>1.37</v>
+      </c>
+      <c r="AM140">
+        <v>1.37</v>
+      </c>
+      <c r="AN140">
+        <v>1</v>
+      </c>
+      <c r="AO140">
+        <v>1.5</v>
+      </c>
+      <c r="AP140">
+        <v>0.88</v>
+      </c>
+      <c r="AQ140">
+        <v>1.67</v>
+      </c>
+      <c r="AR140">
+        <v>1.52</v>
+      </c>
+      <c r="AS140">
+        <v>1.4</v>
+      </c>
+      <c r="AT140">
+        <v>2.92</v>
+      </c>
+      <c r="AU140">
+        <v>3</v>
+      </c>
+      <c r="AV140">
+        <v>4</v>
+      </c>
+      <c r="AW140">
+        <v>4</v>
+      </c>
+      <c r="AX140">
+        <v>3</v>
+      </c>
+      <c r="AY140">
+        <v>7</v>
+      </c>
+      <c r="AZ140">
+        <v>7</v>
+      </c>
+      <c r="BA140">
+        <v>7</v>
+      </c>
+      <c r="BB140">
+        <v>6</v>
+      </c>
+      <c r="BC140">
+        <v>13</v>
+      </c>
+      <c r="BD140">
+        <v>1.94</v>
+      </c>
+      <c r="BE140">
+        <v>6.2</v>
+      </c>
+      <c r="BF140">
+        <v>2.27</v>
+      </c>
+      <c r="BG140">
+        <v>1.27</v>
+      </c>
+      <c r="BH140">
+        <v>3.14</v>
+      </c>
+      <c r="BI140">
+        <v>1.51</v>
+      </c>
+      <c r="BJ140">
+        <v>2.26</v>
+      </c>
+      <c r="BK140">
+        <v>1.89</v>
+      </c>
+      <c r="BL140">
+        <v>1.77</v>
+      </c>
+      <c r="BM140">
+        <v>2.43</v>
+      </c>
+      <c r="BN140">
+        <v>1.44</v>
+      </c>
+      <c r="BO140">
+        <v>3.34</v>
+      </c>
+      <c r="BP140">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7729677</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45715.45833333334</v>
+      </c>
+      <c r="F141">
+        <v>16</v>
+      </c>
+      <c r="G141" t="s">
+        <v>71</v>
+      </c>
+      <c r="H141" t="s">
+        <v>85</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>2</v>
+      </c>
+      <c r="N141">
+        <v>4</v>
+      </c>
+      <c r="O141" t="s">
+        <v>159</v>
+      </c>
+      <c r="P141" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q141">
+        <v>4.1</v>
+      </c>
+      <c r="R141">
+        <v>1.74</v>
+      </c>
+      <c r="S141">
+        <v>3.55</v>
+      </c>
+      <c r="T141">
+        <v>1.77</v>
+      </c>
+      <c r="U141">
+        <v>1.96</v>
+      </c>
+      <c r="V141">
+        <v>4.33</v>
+      </c>
+      <c r="W141">
+        <v>1.18</v>
+      </c>
+      <c r="X141">
+        <v>11.5</v>
+      </c>
+      <c r="Y141">
+        <v>1.02</v>
+      </c>
+      <c r="Z141">
+        <v>2.92</v>
+      </c>
+      <c r="AA141">
+        <v>2.76</v>
+      </c>
+      <c r="AB141">
+        <v>2.74</v>
+      </c>
+      <c r="AC141">
+        <v>1.18</v>
+      </c>
+      <c r="AD141">
+        <v>4.4</v>
+      </c>
+      <c r="AE141">
+        <v>1.73</v>
+      </c>
+      <c r="AF141">
+        <v>1.91</v>
+      </c>
+      <c r="AG141">
+        <v>2.94</v>
+      </c>
+      <c r="AH141">
+        <v>1.35</v>
+      </c>
+      <c r="AI141">
+        <v>2.46</v>
+      </c>
+      <c r="AJ141">
+        <v>1.5</v>
+      </c>
+      <c r="AK141">
+        <v>1.41</v>
+      </c>
+      <c r="AL141">
+        <v>1.44</v>
+      </c>
+      <c r="AM141">
+        <v>1.33</v>
+      </c>
+      <c r="AN141">
+        <v>0.88</v>
+      </c>
+      <c r="AO141">
+        <v>2</v>
+      </c>
+      <c r="AP141">
+        <v>0.89</v>
+      </c>
+      <c r="AQ141">
+        <v>1.89</v>
+      </c>
+      <c r="AR141">
+        <v>1.43</v>
+      </c>
+      <c r="AS141">
+        <v>1.09</v>
+      </c>
+      <c r="AT141">
+        <v>2.52</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>9</v>
+      </c>
+      <c r="AW141">
+        <v>10</v>
+      </c>
+      <c r="AX141">
+        <v>11</v>
+      </c>
+      <c r="AY141">
+        <v>14</v>
+      </c>
+      <c r="AZ141">
+        <v>20</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
+        <v>9</v>
+      </c>
+      <c r="BC141">
+        <v>14</v>
+      </c>
+      <c r="BD141">
+        <v>2.42</v>
+      </c>
+      <c r="BE141">
+        <v>6.2</v>
+      </c>
+      <c r="BF141">
+        <v>1.84</v>
+      </c>
+      <c r="BG141">
+        <v>1.27</v>
+      </c>
+      <c r="BH141">
+        <v>3.14</v>
+      </c>
+      <c r="BI141">
+        <v>1.52</v>
+      </c>
+      <c r="BJ141">
+        <v>2.24</v>
+      </c>
+      <c r="BK141">
+        <v>1.91</v>
+      </c>
+      <c r="BL141">
+        <v>1.76</v>
+      </c>
+      <c r="BM141">
+        <v>2.46</v>
+      </c>
+      <c r="BN141">
+        <v>1.43</v>
+      </c>
+      <c r="BO141">
+        <v>3.34</v>
+      </c>
+      <c r="BP141">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7729678</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45715.58333333334</v>
+      </c>
+      <c r="F142">
+        <v>16</v>
+      </c>
+      <c r="G142" t="s">
+        <v>76</v>
+      </c>
+      <c r="H142" t="s">
+        <v>81</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>2</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>2</v>
+      </c>
+      <c r="O142" t="s">
+        <v>160</v>
+      </c>
+      <c r="P142" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q142">
+        <v>2.31</v>
+      </c>
+      <c r="R142">
+        <v>2.05</v>
+      </c>
+      <c r="S142">
+        <v>5.6</v>
+      </c>
+      <c r="T142">
+        <v>1.5</v>
+      </c>
+      <c r="U142">
+        <v>2.45</v>
+      </c>
+      <c r="V142">
+        <v>3.2</v>
+      </c>
+      <c r="W142">
+        <v>1.33</v>
+      </c>
+      <c r="X142">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y142">
+        <v>1.06</v>
+      </c>
+      <c r="Z142">
+        <v>1.76</v>
+      </c>
+      <c r="AA142">
+        <v>3.29</v>
+      </c>
+      <c r="AB142">
+        <v>5.09</v>
+      </c>
+      <c r="AC142">
+        <v>1.06</v>
+      </c>
+      <c r="AD142">
+        <v>7.5</v>
+      </c>
+      <c r="AE142">
+        <v>1.42</v>
+      </c>
+      <c r="AF142">
+        <v>2.75</v>
+      </c>
+      <c r="AG142">
+        <v>2.3</v>
+      </c>
+      <c r="AH142">
+        <v>1.57</v>
+      </c>
+      <c r="AI142">
+        <v>2.11</v>
+      </c>
+      <c r="AJ142">
+        <v>1.65</v>
+      </c>
+      <c r="AK142">
+        <v>1.16</v>
+      </c>
+      <c r="AL142">
+        <v>1.29</v>
+      </c>
+      <c r="AM142">
+        <v>1.95</v>
+      </c>
+      <c r="AN142">
+        <v>2.13</v>
+      </c>
+      <c r="AO142">
+        <v>1.29</v>
+      </c>
+      <c r="AP142">
+        <v>2</v>
+      </c>
+      <c r="AQ142">
+        <v>1.25</v>
+      </c>
+      <c r="AR142">
+        <v>1.62</v>
+      </c>
+      <c r="AS142">
+        <v>1.38</v>
+      </c>
+      <c r="AT142">
+        <v>3</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>3</v>
+      </c>
+      <c r="AW142">
+        <v>9</v>
+      </c>
+      <c r="AX142">
+        <v>3</v>
+      </c>
+      <c r="AY142">
+        <v>14</v>
+      </c>
+      <c r="AZ142">
+        <v>6</v>
+      </c>
+      <c r="BA142">
+        <v>4</v>
+      </c>
+      <c r="BB142">
+        <v>2</v>
+      </c>
+      <c r="BC142">
+        <v>6</v>
+      </c>
+      <c r="BD142">
+        <v>1.44</v>
+      </c>
+      <c r="BE142">
+        <v>8.4</v>
+      </c>
+      <c r="BF142">
+        <v>3.28</v>
+      </c>
+      <c r="BG142">
+        <v>1.34</v>
+      </c>
+      <c r="BH142">
+        <v>2.78</v>
+      </c>
+      <c r="BI142">
+        <v>1.65</v>
+      </c>
+      <c r="BJ142">
+        <v>2.05</v>
+      </c>
+      <c r="BK142">
+        <v>2.07</v>
+      </c>
+      <c r="BL142">
+        <v>1.61</v>
+      </c>
+      <c r="BM142">
+        <v>2.78</v>
+      </c>
+      <c r="BN142">
+        <v>1.34</v>
+      </c>
+      <c r="BO142">
+        <v>3.6</v>
+      </c>
+      <c r="BP142">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,15 @@
     <t>['45+5']</t>
   </si>
   <si>
+    <t>['22', '45+2', '80']</t>
+  </si>
+  <si>
+    <t>['9', '36', '40', '82']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -689,6 +698,9 @@
   </si>
   <si>
     <t>['84', '90+11']</t>
+  </si>
+  <si>
+    <t>['45+1', '56', '77']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1318,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1512,7 +1524,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2005,7 +2017,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2130,7 +2142,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2336,7 +2348,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2417,7 +2429,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ7">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2542,7 +2554,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2954,7 +2966,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3160,7 +3172,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3238,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ11">
         <v>1.86</v>
@@ -3444,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3572,7 +3584,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3778,7 +3790,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3984,7 +3996,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4190,7 +4202,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4271,7 +4283,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ16">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4886,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>0.25</v>
@@ -5014,7 +5026,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5095,7 +5107,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR20">
         <v>0.95</v>
@@ -5220,7 +5232,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5838,7 +5850,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6044,7 +6056,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6331,7 +6343,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ26">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -7074,7 +7086,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7152,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30">
         <v>0.43</v>
@@ -7358,7 +7370,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31">
         <v>1.86</v>
@@ -8104,7 +8116,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8391,7 +8403,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ36">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR36">
         <v>1.03</v>
@@ -8516,7 +8528,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8594,7 +8606,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ37">
         <v>1.57</v>
@@ -9009,7 +9021,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ39">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR39">
         <v>1.3</v>
@@ -9134,7 +9146,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9340,7 +9352,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9627,7 +9639,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR42">
         <v>1.45</v>
@@ -9752,7 +9764,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10036,7 +10048,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10164,7 +10176,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10245,7 +10257,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ45">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR45">
         <v>1.27</v>
@@ -10451,7 +10463,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR46">
         <v>0.9399999999999999</v>
@@ -10576,7 +10588,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10860,7 +10872,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48">
         <v>0.43</v>
@@ -10988,7 +11000,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11400,7 +11412,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11606,7 +11618,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11812,7 +11824,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12636,7 +12648,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12717,7 +12729,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ57">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13048,7 +13060,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13335,7 +13347,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
         <v>1.01</v>
@@ -13460,7 +13472,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13538,7 +13550,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>1.67</v>
@@ -13950,7 +13962,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ63">
         <v>1.89</v>
@@ -14365,7 +14377,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR65">
         <v>2.1</v>
@@ -14490,7 +14502,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14902,7 +14914,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14980,7 +14992,7 @@
         <v>1.67</v>
       </c>
       <c r="AP68">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15726,7 +15738,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16138,7 +16150,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16344,7 +16356,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16422,7 +16434,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16550,7 +16562,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16962,7 +16974,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17168,7 +17180,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17246,7 +17258,7 @@
         <v>1.25</v>
       </c>
       <c r="AP79">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17374,7 +17386,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17455,7 +17467,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ80">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18276,7 +18288,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ84">
         <v>0.25</v>
@@ -18404,7 +18416,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18482,7 +18494,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -18610,7 +18622,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18691,7 +18703,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ86">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR86">
         <v>1.96</v>
@@ -18816,7 +18828,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19228,7 +19240,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19309,7 +19321,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR89">
         <v>1.05</v>
@@ -19434,7 +19446,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19515,7 +19527,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
         <v>1.09</v>
@@ -19640,7 +19652,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19846,7 +19858,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20052,7 +20064,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20876,7 +20888,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21288,7 +21300,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21366,7 +21378,7 @@
         <v>0.8</v>
       </c>
       <c r="AP99">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
         <v>1.25</v>
@@ -21494,7 +21506,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21700,7 +21712,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21778,7 +21790,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ101">
         <v>0.43</v>
@@ -21906,7 +21918,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -21984,7 +21996,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>1.38</v>
@@ -22193,7 +22205,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR103">
         <v>2.01</v>
@@ -22399,7 +22411,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR104">
         <v>0.91</v>
@@ -22524,7 +22536,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22605,7 +22617,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ105">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR105">
         <v>1.55</v>
@@ -23142,7 +23154,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23220,7 +23232,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1.67</v>
@@ -23554,7 +23566,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23760,7 +23772,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -25202,7 +25214,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25489,7 +25501,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25614,7 +25626,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -26026,7 +26038,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26232,7 +26244,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26310,10 +26322,10 @@
         <v>0.43</v>
       </c>
       <c r="AP123">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR123">
         <v>1.55</v>
@@ -26519,7 +26531,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ124">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR124">
         <v>1.13</v>
@@ -26722,7 +26734,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125">
         <v>0.75</v>
@@ -27134,7 +27146,7 @@
         <v>1.71</v>
       </c>
       <c r="AP127">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27674,7 +27686,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27880,7 +27892,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28498,7 +28510,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29116,7 +29128,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29322,7 +29334,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29528,7 +29540,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29734,7 +29746,7 @@
         <v>89</v>
       </c>
       <c r="P140" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q140">
         <v>3.7</v>
@@ -29940,7 +29952,7 @@
         <v>159</v>
       </c>
       <c r="P141" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q141">
         <v>4.1</v>
@@ -30146,7 +30158,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30303,6 +30315,624 @@
       </c>
       <c r="BP142">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7729679</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45716.45833333334</v>
+      </c>
+      <c r="F143">
+        <v>16</v>
+      </c>
+      <c r="G143" t="s">
+        <v>79</v>
+      </c>
+      <c r="H143" t="s">
+        <v>84</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>3</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>3</v>
+      </c>
+      <c r="O143" t="s">
+        <v>161</v>
+      </c>
+      <c r="P143" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q143">
+        <v>3.2</v>
+      </c>
+      <c r="R143">
+        <v>1.77</v>
+      </c>
+      <c r="S143">
+        <v>4.4</v>
+      </c>
+      <c r="T143">
+        <v>1.73</v>
+      </c>
+      <c r="U143">
+        <v>2.01</v>
+      </c>
+      <c r="V143">
+        <v>4</v>
+      </c>
+      <c r="W143">
+        <v>1.22</v>
+      </c>
+      <c r="X143">
+        <v>11</v>
+      </c>
+      <c r="Y143">
+        <v>1.02</v>
+      </c>
+      <c r="Z143">
+        <v>2.42</v>
+      </c>
+      <c r="AA143">
+        <v>2.65</v>
+      </c>
+      <c r="AB143">
+        <v>3.59</v>
+      </c>
+      <c r="AC143">
+        <v>1.16</v>
+      </c>
+      <c r="AD143">
+        <v>4.7</v>
+      </c>
+      <c r="AE143">
+        <v>1.61</v>
+      </c>
+      <c r="AF143">
+        <v>2.05</v>
+      </c>
+      <c r="AG143">
+        <v>2.94</v>
+      </c>
+      <c r="AH143">
+        <v>1.35</v>
+      </c>
+      <c r="AI143">
+        <v>2.42</v>
+      </c>
+      <c r="AJ143">
+        <v>1.51</v>
+      </c>
+      <c r="AK143">
+        <v>1.28</v>
+      </c>
+      <c r="AL143">
+        <v>1.41</v>
+      </c>
+      <c r="AM143">
+        <v>1.5</v>
+      </c>
+      <c r="AN143">
+        <v>0.88</v>
+      </c>
+      <c r="AO143">
+        <v>0.5</v>
+      </c>
+      <c r="AP143">
+        <v>1.11</v>
+      </c>
+      <c r="AQ143">
+        <v>0.44</v>
+      </c>
+      <c r="AR143">
+        <v>1.38</v>
+      </c>
+      <c r="AS143">
+        <v>1.15</v>
+      </c>
+      <c r="AT143">
+        <v>2.53</v>
+      </c>
+      <c r="AU143">
+        <v>4</v>
+      </c>
+      <c r="AV143">
+        <v>2</v>
+      </c>
+      <c r="AW143">
+        <v>4</v>
+      </c>
+      <c r="AX143">
+        <v>3</v>
+      </c>
+      <c r="AY143">
+        <v>8</v>
+      </c>
+      <c r="AZ143">
+        <v>5</v>
+      </c>
+      <c r="BA143">
+        <v>4</v>
+      </c>
+      <c r="BB143">
+        <v>6</v>
+      </c>
+      <c r="BC143">
+        <v>10</v>
+      </c>
+      <c r="BD143">
+        <v>1.64</v>
+      </c>
+      <c r="BE143">
+        <v>6.35</v>
+      </c>
+      <c r="BF143">
+        <v>2.85</v>
+      </c>
+      <c r="BG143">
+        <v>1.3</v>
+      </c>
+      <c r="BH143">
+        <v>2.97</v>
+      </c>
+      <c r="BI143">
+        <v>1.64</v>
+      </c>
+      <c r="BJ143">
+        <v>2.24</v>
+      </c>
+      <c r="BK143">
+        <v>2.04</v>
+      </c>
+      <c r="BL143">
+        <v>1.76</v>
+      </c>
+      <c r="BM143">
+        <v>2.59</v>
+      </c>
+      <c r="BN143">
+        <v>1.39</v>
+      </c>
+      <c r="BO143">
+        <v>3.58</v>
+      </c>
+      <c r="BP143">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7729680</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F144">
+        <v>16</v>
+      </c>
+      <c r="G144" t="s">
+        <v>87</v>
+      </c>
+      <c r="H144" t="s">
+        <v>83</v>
+      </c>
+      <c r="I144">
+        <v>3</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144">
+        <v>4</v>
+      </c>
+      <c r="L144">
+        <v>4</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>5</v>
+      </c>
+      <c r="O144" t="s">
+        <v>162</v>
+      </c>
+      <c r="P144" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q144">
+        <v>2.55</v>
+      </c>
+      <c r="R144">
+        <v>1.97</v>
+      </c>
+      <c r="S144">
+        <v>4.8</v>
+      </c>
+      <c r="T144">
+        <v>1.54</v>
+      </c>
+      <c r="U144">
+        <v>2.35</v>
+      </c>
+      <c r="V144">
+        <v>3.3</v>
+      </c>
+      <c r="W144">
+        <v>1.28</v>
+      </c>
+      <c r="X144">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y144">
+        <v>1.05</v>
+      </c>
+      <c r="Z144">
+        <v>1.98</v>
+      </c>
+      <c r="AA144">
+        <v>2.83</v>
+      </c>
+      <c r="AB144">
+        <v>4.7</v>
+      </c>
+      <c r="AC144">
+        <v>1.11</v>
+      </c>
+      <c r="AD144">
+        <v>6</v>
+      </c>
+      <c r="AE144">
+        <v>1.46</v>
+      </c>
+      <c r="AF144">
+        <v>2.6</v>
+      </c>
+      <c r="AG144">
+        <v>2.3</v>
+      </c>
+      <c r="AH144">
+        <v>1.5</v>
+      </c>
+      <c r="AI144">
+        <v>2.06</v>
+      </c>
+      <c r="AJ144">
+        <v>1.68</v>
+      </c>
+      <c r="AK144">
+        <v>1.2</v>
+      </c>
+      <c r="AL144">
+        <v>1.35</v>
+      </c>
+      <c r="AM144">
+        <v>1.72</v>
+      </c>
+      <c r="AN144">
+        <v>1.29</v>
+      </c>
+      <c r="AO144">
+        <v>1.29</v>
+      </c>
+      <c r="AP144">
+        <v>1.5</v>
+      </c>
+      <c r="AQ144">
+        <v>1.13</v>
+      </c>
+      <c r="AR144">
+        <v>1.67</v>
+      </c>
+      <c r="AS144">
+        <v>1.28</v>
+      </c>
+      <c r="AT144">
+        <v>2.95</v>
+      </c>
+      <c r="AU144">
+        <v>8</v>
+      </c>
+      <c r="AV144">
+        <v>6</v>
+      </c>
+      <c r="AW144">
+        <v>6</v>
+      </c>
+      <c r="AX144">
+        <v>11</v>
+      </c>
+      <c r="AY144">
+        <v>14</v>
+      </c>
+      <c r="AZ144">
+        <v>17</v>
+      </c>
+      <c r="BA144">
+        <v>4</v>
+      </c>
+      <c r="BB144">
+        <v>4</v>
+      </c>
+      <c r="BC144">
+        <v>8</v>
+      </c>
+      <c r="BD144">
+        <v>1.57</v>
+      </c>
+      <c r="BE144">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF144">
+        <v>2.78</v>
+      </c>
+      <c r="BG144">
+        <v>1.27</v>
+      </c>
+      <c r="BH144">
+        <v>3.14</v>
+      </c>
+      <c r="BI144">
+        <v>1.5</v>
+      </c>
+      <c r="BJ144">
+        <v>2.28</v>
+      </c>
+      <c r="BK144">
+        <v>1.88</v>
+      </c>
+      <c r="BL144">
+        <v>1.78</v>
+      </c>
+      <c r="BM144">
+        <v>2.43</v>
+      </c>
+      <c r="BN144">
+        <v>1.44</v>
+      </c>
+      <c r="BO144">
+        <v>3.34</v>
+      </c>
+      <c r="BP144">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7729681</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F145">
+        <v>16</v>
+      </c>
+      <c r="G145" t="s">
+        <v>80</v>
+      </c>
+      <c r="H145" t="s">
+        <v>75</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>3</v>
+      </c>
+      <c r="N145">
+        <v>4</v>
+      </c>
+      <c r="O145" t="s">
+        <v>163</v>
+      </c>
+      <c r="P145" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q145">
+        <v>6.6</v>
+      </c>
+      <c r="R145">
+        <v>2.15</v>
+      </c>
+      <c r="S145">
+        <v>2.07</v>
+      </c>
+      <c r="T145">
+        <v>1.46</v>
+      </c>
+      <c r="U145">
+        <v>2.55</v>
+      </c>
+      <c r="V145">
+        <v>3</v>
+      </c>
+      <c r="W145">
+        <v>1.33</v>
+      </c>
+      <c r="X145">
+        <v>8</v>
+      </c>
+      <c r="Y145">
+        <v>1.06</v>
+      </c>
+      <c r="Z145">
+        <v>5.3</v>
+      </c>
+      <c r="AA145">
+        <v>3.52</v>
+      </c>
+      <c r="AB145">
+        <v>1.67</v>
+      </c>
+      <c r="AC145">
+        <v>1.06</v>
+      </c>
+      <c r="AD145">
+        <v>8</v>
+      </c>
+      <c r="AE145">
+        <v>1.39</v>
+      </c>
+      <c r="AF145">
+        <v>2.85</v>
+      </c>
+      <c r="AG145">
+        <v>2.1</v>
+      </c>
+      <c r="AH145">
+        <v>1.6</v>
+      </c>
+      <c r="AI145">
+        <v>2.26</v>
+      </c>
+      <c r="AJ145">
+        <v>1.57</v>
+      </c>
+      <c r="AK145">
+        <v>2.32</v>
+      </c>
+      <c r="AL145">
+        <v>1.22</v>
+      </c>
+      <c r="AM145">
+        <v>1.11</v>
+      </c>
+      <c r="AN145">
+        <v>1.43</v>
+      </c>
+      <c r="AO145">
+        <v>2.13</v>
+      </c>
+      <c r="AP145">
+        <v>1.25</v>
+      </c>
+      <c r="AQ145">
+        <v>2.22</v>
+      </c>
+      <c r="AR145">
+        <v>1.03</v>
+      </c>
+      <c r="AS145">
+        <v>1.41</v>
+      </c>
+      <c r="AT145">
+        <v>2.44</v>
+      </c>
+      <c r="AU145">
+        <v>4</v>
+      </c>
+      <c r="AV145">
+        <v>8</v>
+      </c>
+      <c r="AW145">
+        <v>11</v>
+      </c>
+      <c r="AX145">
+        <v>9</v>
+      </c>
+      <c r="AY145">
+        <v>15</v>
+      </c>
+      <c r="AZ145">
+        <v>17</v>
+      </c>
+      <c r="BA145">
+        <v>8</v>
+      </c>
+      <c r="BB145">
+        <v>1</v>
+      </c>
+      <c r="BC145">
+        <v>9</v>
+      </c>
+      <c r="BD145">
+        <v>3.4</v>
+      </c>
+      <c r="BE145">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF145">
+        <v>1.41</v>
+      </c>
+      <c r="BG145">
+        <v>1.27</v>
+      </c>
+      <c r="BH145">
+        <v>3.14</v>
+      </c>
+      <c r="BI145">
+        <v>1.5</v>
+      </c>
+      <c r="BJ145">
+        <v>2.28</v>
+      </c>
+      <c r="BK145">
+        <v>1.88</v>
+      </c>
+      <c r="BL145">
+        <v>1.78</v>
+      </c>
+      <c r="BM145">
+        <v>2.43</v>
+      </c>
+      <c r="BN145">
+        <v>1.44</v>
+      </c>
+      <c r="BO145">
+        <v>3.34</v>
+      </c>
+      <c r="BP145">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -30887,13 +30887,13 @@
         <v>17</v>
       </c>
       <c r="BA145">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB145">
         <v>1</v>
       </c>
       <c r="BC145">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD145">
         <v>3.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -30887,13 +30887,13 @@
         <v>17</v>
       </c>
       <c r="BA145">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB145">
         <v>1</v>
       </c>
       <c r="BC145">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD145">
         <v>3.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,12 @@
     <t>['79']</t>
   </si>
   <si>
+    <t>['49', '76']</t>
+  </si>
+  <si>
+    <t>['16', '35', '66', '73']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -701,6 +707,9 @@
   </si>
   <si>
     <t>['45+1', '56', '77']</t>
+  </si>
+  <si>
+    <t>['10', '82']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1318,7 +1327,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1524,7 +1533,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2142,7 +2151,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2220,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2348,7 +2357,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2554,7 +2563,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2966,7 +2975,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3172,7 +3181,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3459,7 +3468,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3584,7 +3593,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3790,7 +3799,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3996,7 +4005,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4077,7 +4086,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4202,7 +4211,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4486,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
         <v>1.38</v>
@@ -4692,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5026,7 +5035,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5104,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
         <v>0.44</v>
@@ -5232,7 +5241,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5850,7 +5859,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6056,7 +6065,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6961,7 +6970,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR29">
         <v>0.83</v>
@@ -7086,7 +7095,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7167,7 +7176,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -7576,7 +7585,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>2.25</v>
@@ -7785,7 +7794,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>1.75</v>
@@ -8116,7 +8125,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8400,7 +8409,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ36">
         <v>2.22</v>
@@ -8528,7 +8537,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9146,7 +9155,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9352,7 +9361,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9764,7 +9773,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9842,7 +9851,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
         <v>1.25</v>
@@ -10176,7 +10185,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10588,7 +10597,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10875,7 +10884,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ48">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR48">
         <v>0.85</v>
@@ -11000,7 +11009,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11081,7 +11090,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR49">
         <v>1.04</v>
@@ -11412,7 +11421,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11490,7 +11499,7 @@
         <v>0.67</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -11618,7 +11627,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11824,7 +11833,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11902,7 +11911,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ53">
         <v>2.25</v>
@@ -12111,7 +12120,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR54">
         <v>1.9</v>
@@ -12648,7 +12657,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13060,7 +13069,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13138,7 +13147,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -13472,7 +13481,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14502,7 +14511,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14786,7 +14795,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ67">
         <v>0.25</v>
@@ -14914,7 +14923,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15201,7 +15210,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ69">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR69">
         <v>1.78</v>
@@ -15613,7 +15622,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ71">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -15738,7 +15747,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15819,7 +15828,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR72">
         <v>1.61</v>
@@ -16022,7 +16031,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ73">
         <v>1.38</v>
@@ -16150,7 +16159,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16356,7 +16365,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16437,7 +16446,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR75">
         <v>1.53</v>
@@ -16562,7 +16571,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16974,7 +16983,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17052,7 +17061,7 @@
         <v>2</v>
       </c>
       <c r="AP78">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
         <v>2.25</v>
@@ -17180,7 +17189,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17386,7 +17395,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -18416,7 +18425,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18622,7 +18631,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18828,7 +18837,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -18909,7 +18918,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR87">
         <v>1.76</v>
@@ -19115,7 +19124,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ88">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19240,7 +19249,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19318,7 +19327,7 @@
         <v>0.6</v>
       </c>
       <c r="AP89">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ89">
         <v>0.44</v>
@@ -19446,7 +19455,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19524,7 +19533,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ90">
         <v>1.13</v>
@@ -19652,7 +19661,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19858,7 +19867,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20064,7 +20073,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20145,7 +20154,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR93">
         <v>1.2</v>
@@ -20888,7 +20897,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -20966,7 +20975,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21300,7 +21309,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21506,7 +21515,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21712,7 +21721,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21793,7 +21802,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ101">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR101">
         <v>1.45</v>
@@ -21918,7 +21927,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22536,7 +22545,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22823,7 +22832,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ106">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR106">
         <v>1.49</v>
@@ -23154,7 +23163,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23438,7 +23447,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ109">
         <v>1.25</v>
@@ -23566,7 +23575,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23644,7 +23653,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ110">
         <v>1.57</v>
@@ -23772,7 +23781,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24677,7 +24686,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR115">
         <v>1.73</v>
@@ -24880,7 +24889,7 @@
         <v>2</v>
       </c>
       <c r="AP116">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ116">
         <v>1.89</v>
@@ -25214,7 +25223,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25626,7 +25635,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -26038,7 +26047,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26244,7 +26253,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26737,7 +26746,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR125">
         <v>0.96</v>
@@ -27558,10 +27567,10 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR129">
         <v>1.36</v>
@@ -27686,7 +27695,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27767,7 +27776,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR130">
         <v>1.63</v>
@@ -27892,7 +27901,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -27970,7 +27979,7 @@
         <v>1.14</v>
       </c>
       <c r="AP131">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
         <v>1</v>
@@ -28382,7 +28391,7 @@
         <v>0.14</v>
       </c>
       <c r="AP133">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ133">
         <v>0.25</v>
@@ -28510,7 +28519,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29128,7 +29137,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29209,7 +29218,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR137">
         <v>1.04</v>
@@ -29334,7 +29343,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29540,7 +29549,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29746,7 +29755,7 @@
         <v>89</v>
       </c>
       <c r="P140" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q140">
         <v>3.7</v>
@@ -29952,7 +29961,7 @@
         <v>159</v>
       </c>
       <c r="P141" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q141">
         <v>4.1</v>
@@ -30158,7 +30167,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30570,7 +30579,7 @@
         <v>162</v>
       </c>
       <c r="P144" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q144">
         <v>2.55</v>
@@ -30776,7 +30785,7 @@
         <v>163</v>
       </c>
       <c r="P145" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q145">
         <v>6.6</v>
@@ -30933,6 +30942,624 @@
       </c>
       <c r="BP145">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7729682</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F146">
+        <v>17</v>
+      </c>
+      <c r="G146" t="s">
+        <v>85</v>
+      </c>
+      <c r="H146" t="s">
+        <v>70</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>2</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>3</v>
+      </c>
+      <c r="O146" t="s">
+        <v>164</v>
+      </c>
+      <c r="P146" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q146">
+        <v>2.35</v>
+      </c>
+      <c r="R146">
+        <v>1.95</v>
+      </c>
+      <c r="S146">
+        <v>5.5</v>
+      </c>
+      <c r="T146">
+        <v>1.5</v>
+      </c>
+      <c r="U146">
+        <v>2.4</v>
+      </c>
+      <c r="V146">
+        <v>3.3</v>
+      </c>
+      <c r="W146">
+        <v>1.28</v>
+      </c>
+      <c r="X146">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y146">
+        <v>1.05</v>
+      </c>
+      <c r="Z146">
+        <v>1.88</v>
+      </c>
+      <c r="AA146">
+        <v>3.02</v>
+      </c>
+      <c r="AB146">
+        <v>4.8</v>
+      </c>
+      <c r="AC146">
+        <v>1.1</v>
+      </c>
+      <c r="AD146">
+        <v>6.25</v>
+      </c>
+      <c r="AE146">
+        <v>1.53</v>
+      </c>
+      <c r="AF146">
+        <v>2.25</v>
+      </c>
+      <c r="AG146">
+        <v>2.77</v>
+      </c>
+      <c r="AH146">
+        <v>1.39</v>
+      </c>
+      <c r="AI146">
+        <v>2.1</v>
+      </c>
+      <c r="AJ146">
+        <v>1.6</v>
+      </c>
+      <c r="AK146">
+        <v>1.14</v>
+      </c>
+      <c r="AL146">
+        <v>1.28</v>
+      </c>
+      <c r="AM146">
+        <v>1.91</v>
+      </c>
+      <c r="AN146">
+        <v>1.29</v>
+      </c>
+      <c r="AO146">
+        <v>1</v>
+      </c>
+      <c r="AP146">
+        <v>1.5</v>
+      </c>
+      <c r="AQ146">
+        <v>0.89</v>
+      </c>
+      <c r="AR146">
+        <v>1.16</v>
+      </c>
+      <c r="AS146">
+        <v>0.96</v>
+      </c>
+      <c r="AT146">
+        <v>2.12</v>
+      </c>
+      <c r="AU146">
+        <v>6</v>
+      </c>
+      <c r="AV146">
+        <v>4</v>
+      </c>
+      <c r="AW146">
+        <v>5</v>
+      </c>
+      <c r="AX146">
+        <v>10</v>
+      </c>
+      <c r="AY146">
+        <v>11</v>
+      </c>
+      <c r="AZ146">
+        <v>14</v>
+      </c>
+      <c r="BA146">
+        <v>6</v>
+      </c>
+      <c r="BB146">
+        <v>8</v>
+      </c>
+      <c r="BC146">
+        <v>14</v>
+      </c>
+      <c r="BD146">
+        <v>1.41</v>
+      </c>
+      <c r="BE146">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF146">
+        <v>3.4</v>
+      </c>
+      <c r="BG146">
+        <v>1.25</v>
+      </c>
+      <c r="BH146">
+        <v>3.28</v>
+      </c>
+      <c r="BI146">
+        <v>1.53</v>
+      </c>
+      <c r="BJ146">
+        <v>2.45</v>
+      </c>
+      <c r="BK146">
+        <v>1.92</v>
+      </c>
+      <c r="BL146">
+        <v>1.87</v>
+      </c>
+      <c r="BM146">
+        <v>2.42</v>
+      </c>
+      <c r="BN146">
+        <v>1.54</v>
+      </c>
+      <c r="BO146">
+        <v>3.2</v>
+      </c>
+      <c r="BP146">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7729683</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F147">
+        <v>17</v>
+      </c>
+      <c r="G147" t="s">
+        <v>74</v>
+      </c>
+      <c r="H147" t="s">
+        <v>72</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147" t="s">
+        <v>89</v>
+      </c>
+      <c r="P147" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q147">
+        <v>2.88</v>
+      </c>
+      <c r="R147">
+        <v>1.8</v>
+      </c>
+      <c r="S147">
+        <v>4.5</v>
+      </c>
+      <c r="T147">
+        <v>1.62</v>
+      </c>
+      <c r="U147">
+        <v>2.15</v>
+      </c>
+      <c r="V147">
+        <v>3.9</v>
+      </c>
+      <c r="W147">
+        <v>1.22</v>
+      </c>
+      <c r="X147">
+        <v>11</v>
+      </c>
+      <c r="Y147">
+        <v>1.02</v>
+      </c>
+      <c r="Z147">
+        <v>2.19</v>
+      </c>
+      <c r="AA147">
+        <v>2.76</v>
+      </c>
+      <c r="AB147">
+        <v>3.98</v>
+      </c>
+      <c r="AC147">
+        <v>1.17</v>
+      </c>
+      <c r="AD147">
+        <v>4.75</v>
+      </c>
+      <c r="AE147">
+        <v>1.6</v>
+      </c>
+      <c r="AF147">
+        <v>2.1</v>
+      </c>
+      <c r="AG147">
+        <v>2.89</v>
+      </c>
+      <c r="AH147">
+        <v>1.36</v>
+      </c>
+      <c r="AI147">
+        <v>2.2</v>
+      </c>
+      <c r="AJ147">
+        <v>1.55</v>
+      </c>
+      <c r="AK147">
+        <v>1.2</v>
+      </c>
+      <c r="AL147">
+        <v>1.45</v>
+      </c>
+      <c r="AM147">
+        <v>1.57</v>
+      </c>
+      <c r="AN147">
+        <v>1.38</v>
+      </c>
+      <c r="AO147">
+        <v>0.75</v>
+      </c>
+      <c r="AP147">
+        <v>1.33</v>
+      </c>
+      <c r="AQ147">
+        <v>0.78</v>
+      </c>
+      <c r="AR147">
+        <v>1.32</v>
+      </c>
+      <c r="AS147">
+        <v>1.14</v>
+      </c>
+      <c r="AT147">
+        <v>2.46</v>
+      </c>
+      <c r="AU147">
+        <v>4</v>
+      </c>
+      <c r="AV147">
+        <v>0</v>
+      </c>
+      <c r="AW147">
+        <v>7</v>
+      </c>
+      <c r="AX147">
+        <v>9</v>
+      </c>
+      <c r="AY147">
+        <v>11</v>
+      </c>
+      <c r="AZ147">
+        <v>9</v>
+      </c>
+      <c r="BA147">
+        <v>7</v>
+      </c>
+      <c r="BB147">
+        <v>2</v>
+      </c>
+      <c r="BC147">
+        <v>9</v>
+      </c>
+      <c r="BD147">
+        <v>1.67</v>
+      </c>
+      <c r="BE147">
+        <v>6.35</v>
+      </c>
+      <c r="BF147">
+        <v>2.78</v>
+      </c>
+      <c r="BG147">
+        <v>1.34</v>
+      </c>
+      <c r="BH147">
+        <v>2.78</v>
+      </c>
+      <c r="BI147">
+        <v>1.65</v>
+      </c>
+      <c r="BJ147">
+        <v>2.05</v>
+      </c>
+      <c r="BK147">
+        <v>2.07</v>
+      </c>
+      <c r="BL147">
+        <v>1.61</v>
+      </c>
+      <c r="BM147">
+        <v>2.78</v>
+      </c>
+      <c r="BN147">
+        <v>1.34</v>
+      </c>
+      <c r="BO147">
+        <v>3.6</v>
+      </c>
+      <c r="BP147">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7729684</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F148">
+        <v>17</v>
+      </c>
+      <c r="G148" t="s">
+        <v>86</v>
+      </c>
+      <c r="H148" t="s">
+        <v>73</v>
+      </c>
+      <c r="I148">
+        <v>2</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>3</v>
+      </c>
+      <c r="L148">
+        <v>4</v>
+      </c>
+      <c r="M148">
+        <v>2</v>
+      </c>
+      <c r="N148">
+        <v>6</v>
+      </c>
+      <c r="O148" t="s">
+        <v>165</v>
+      </c>
+      <c r="P148" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q148">
+        <v>2.85</v>
+      </c>
+      <c r="R148">
+        <v>1.8</v>
+      </c>
+      <c r="S148">
+        <v>4.75</v>
+      </c>
+      <c r="T148">
+        <v>1.62</v>
+      </c>
+      <c r="U148">
+        <v>2.15</v>
+      </c>
+      <c r="V148">
+        <v>3.85</v>
+      </c>
+      <c r="W148">
+        <v>1.22</v>
+      </c>
+      <c r="X148">
+        <v>10</v>
+      </c>
+      <c r="Y148">
+        <v>1.03</v>
+      </c>
+      <c r="Z148">
+        <v>2.32</v>
+      </c>
+      <c r="AA148">
+        <v>2.55</v>
+      </c>
+      <c r="AB148">
+        <v>3.85</v>
+      </c>
+      <c r="AC148">
+        <v>1.13</v>
+      </c>
+      <c r="AD148">
+        <v>5.25</v>
+      </c>
+      <c r="AE148">
+        <v>1.62</v>
+      </c>
+      <c r="AF148">
+        <v>2.2</v>
+      </c>
+      <c r="AG148">
+        <v>2.88</v>
+      </c>
+      <c r="AH148">
+        <v>1.38</v>
+      </c>
+      <c r="AI148">
+        <v>2.25</v>
+      </c>
+      <c r="AJ148">
+        <v>1.53</v>
+      </c>
+      <c r="AK148">
+        <v>1.22</v>
+      </c>
+      <c r="AL148">
+        <v>1.36</v>
+      </c>
+      <c r="AM148">
+        <v>1.67</v>
+      </c>
+      <c r="AN148">
+        <v>1.71</v>
+      </c>
+      <c r="AO148">
+        <v>0.43</v>
+      </c>
+      <c r="AP148">
+        <v>1.88</v>
+      </c>
+      <c r="AQ148">
+        <v>0.38</v>
+      </c>
+      <c r="AR148">
+        <v>1.06</v>
+      </c>
+      <c r="AS148">
+        <v>1.02</v>
+      </c>
+      <c r="AT148">
+        <v>2.08</v>
+      </c>
+      <c r="AU148">
+        <v>8</v>
+      </c>
+      <c r="AV148">
+        <v>6</v>
+      </c>
+      <c r="AW148">
+        <v>1</v>
+      </c>
+      <c r="AX148">
+        <v>1</v>
+      </c>
+      <c r="AY148">
+        <v>9</v>
+      </c>
+      <c r="AZ148">
+        <v>7</v>
+      </c>
+      <c r="BA148">
+        <v>3</v>
+      </c>
+      <c r="BB148">
+        <v>4</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>1.57</v>
+      </c>
+      <c r="BE148">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF148">
+        <v>2.78</v>
+      </c>
+      <c r="BG148">
+        <v>1.3</v>
+      </c>
+      <c r="BH148">
+        <v>2.97</v>
+      </c>
+      <c r="BI148">
+        <v>1.56</v>
+      </c>
+      <c r="BJ148">
+        <v>2.16</v>
+      </c>
+      <c r="BK148">
+        <v>1.98</v>
+      </c>
+      <c r="BL148">
+        <v>1.7</v>
+      </c>
+      <c r="BM148">
+        <v>2.59</v>
+      </c>
+      <c r="BN148">
+        <v>1.39</v>
+      </c>
+      <c r="BO148">
+        <v>3.58</v>
+      </c>
+      <c r="BP148">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,9 @@
     <t>['16', '35', '66', '73']</t>
   </si>
   <si>
+    <t>['28', '76']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -710,6 +713,12 @@
   </si>
   <si>
     <t>['10', '82']</t>
+  </si>
+  <si>
+    <t>['53', '66', '90+4']</t>
+  </si>
+  <si>
+    <t>['34', '39']</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1327,7 +1336,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1408,7 +1417,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1533,7 +1542,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2151,7 +2160,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2357,7 +2366,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2563,7 +2572,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2975,7 +2984,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3181,7 +3190,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3465,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12">
         <v>0.89</v>
@@ -3593,7 +3602,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3671,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13">
         <v>2.25</v>
@@ -3799,7 +3808,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3880,7 +3889,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ14">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4005,7 +4014,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4211,7 +4220,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4289,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>2.22</v>
@@ -4910,7 +4919,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5035,7 +5044,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5241,7 +5250,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5734,7 +5743,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ23">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5859,7 +5868,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6065,7 +6074,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6967,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ29">
         <v>0.89</v>
@@ -7095,7 +7104,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7379,7 +7388,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ31">
         <v>1.86</v>
@@ -7997,10 +8006,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR34">
         <v>0.6899999999999999</v>
@@ -8125,7 +8134,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8537,7 +8546,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8618,7 +8627,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ37">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR37">
         <v>2.48</v>
@@ -9155,7 +9164,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9361,7 +9370,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9773,7 +9782,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10185,7 +10194,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10469,7 +10478,7 @@
         <v>0.33</v>
       </c>
       <c r="AP46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ46">
         <v>0.44</v>
@@ -10597,7 +10606,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10678,7 +10687,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ47">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR47">
         <v>1.24</v>
@@ -10881,7 +10890,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ48">
         <v>0.38</v>
@@ -11009,7 +11018,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11421,7 +11430,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11627,7 +11636,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11833,7 +11842,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12657,7 +12666,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12941,7 +12950,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
         <v>2.25</v>
@@ -13069,7 +13078,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13150,7 +13159,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -13353,7 +13362,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ60">
         <v>1.13</v>
@@ -13481,7 +13490,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13768,7 +13777,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ62">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -14180,7 +14189,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14511,7 +14520,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14798,7 +14807,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR67">
         <v>1.03</v>
@@ -14923,7 +14932,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15001,7 +15010,7 @@
         <v>1.67</v>
       </c>
       <c r="AP68">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15747,7 +15756,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16159,7 +16168,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16365,7 +16374,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16571,7 +16580,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16649,7 +16658,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.86</v>
@@ -16858,7 +16867,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR77">
         <v>1.1</v>
@@ -16983,7 +16992,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17189,7 +17198,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17395,7 +17404,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17473,7 +17482,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ80">
         <v>2.22</v>
@@ -17888,7 +17897,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ82">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR82">
         <v>1.26</v>
@@ -18297,10 +18306,10 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ84">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
         <v>0.83</v>
@@ -18425,7 +18434,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18631,7 +18640,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18837,7 +18846,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19249,7 +19258,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19455,7 +19464,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19661,7 +19670,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19867,7 +19876,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20073,7 +20082,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20360,7 +20369,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ94">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20563,7 +20572,7 @@
         <v>1.6</v>
       </c>
       <c r="AP95">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ95">
         <v>1.67</v>
@@ -20769,7 +20778,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>1.89</v>
@@ -20897,7 +20906,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21309,7 +21318,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21390,7 +21399,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21515,7 +21524,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21721,7 +21730,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21927,7 +21936,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22545,7 +22554,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23038,7 +23047,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23163,7 +23172,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23241,7 +23250,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ108">
         <v>1.67</v>
@@ -23575,7 +23584,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23656,7 +23665,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ110">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR110">
         <v>1.41</v>
@@ -23781,7 +23790,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -23862,7 +23871,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ111">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR111">
         <v>1.6</v>
@@ -24271,7 +24280,7 @@
         <v>1.83</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ113">
         <v>1.5</v>
@@ -24480,7 +24489,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR114">
         <v>1.29</v>
@@ -25223,7 +25232,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25301,7 +25310,7 @@
         <v>1.17</v>
       </c>
       <c r="AP118">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -25635,7 +25644,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -26047,7 +26056,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26253,7 +26262,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26743,7 +26752,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ125">
         <v>0.78</v>
@@ -27361,10 +27370,10 @@
         <v>1.43</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR128">
         <v>0.96</v>
@@ -27695,7 +27704,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27901,7 +27910,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28394,7 +28403,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ133">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR133">
         <v>1.09</v>
@@ -28519,7 +28528,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -28600,7 +28609,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR134">
         <v>1.8</v>
@@ -28803,7 +28812,7 @@
         <v>1.17</v>
       </c>
       <c r="AP135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29137,7 +29146,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29343,7 +29352,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29549,7 +29558,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29755,7 +29764,7 @@
         <v>89</v>
       </c>
       <c r="P140" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q140">
         <v>3.7</v>
@@ -29961,7 +29970,7 @@
         <v>159</v>
       </c>
       <c r="P141" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q141">
         <v>4.1</v>
@@ -30167,7 +30176,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30579,7 +30588,7 @@
         <v>162</v>
       </c>
       <c r="P144" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q144">
         <v>2.55</v>
@@ -30785,7 +30794,7 @@
         <v>163</v>
       </c>
       <c r="P145" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q145">
         <v>6.6</v>
@@ -30863,7 +30872,7 @@
         <v>2.13</v>
       </c>
       <c r="AP145">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ145">
         <v>2.22</v>
@@ -31403,7 +31412,7 @@
         <v>165</v>
       </c>
       <c r="P148" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q148">
         <v>2.85</v>
@@ -31560,6 +31569,624 @@
       </c>
       <c r="BP148">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7729685</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45720.66666666666</v>
+      </c>
+      <c r="F149">
+        <v>17</v>
+      </c>
+      <c r="G149" t="s">
+        <v>84</v>
+      </c>
+      <c r="H149" t="s">
+        <v>76</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>3</v>
+      </c>
+      <c r="N149">
+        <v>3</v>
+      </c>
+      <c r="O149" t="s">
+        <v>89</v>
+      </c>
+      <c r="P149" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q149">
+        <v>5.5</v>
+      </c>
+      <c r="R149">
+        <v>2</v>
+      </c>
+      <c r="S149">
+        <v>2.3</v>
+      </c>
+      <c r="T149">
+        <v>1.47</v>
+      </c>
+      <c r="U149">
+        <v>2.4</v>
+      </c>
+      <c r="V149">
+        <v>3.2</v>
+      </c>
+      <c r="W149">
+        <v>1.28</v>
+      </c>
+      <c r="X149">
+        <v>7.8</v>
+      </c>
+      <c r="Y149">
+        <v>1.04</v>
+      </c>
+      <c r="Z149">
+        <v>4.8</v>
+      </c>
+      <c r="AA149">
+        <v>3.13</v>
+      </c>
+      <c r="AB149">
+        <v>1.84</v>
+      </c>
+      <c r="AC149">
+        <v>1.09</v>
+      </c>
+      <c r="AD149">
+        <v>7</v>
+      </c>
+      <c r="AE149">
+        <v>1.4</v>
+      </c>
+      <c r="AF149">
+        <v>2.7</v>
+      </c>
+      <c r="AG149">
+        <v>2.25</v>
+      </c>
+      <c r="AH149">
+        <v>1.53</v>
+      </c>
+      <c r="AI149">
+        <v>2.25</v>
+      </c>
+      <c r="AJ149">
+        <v>1.62</v>
+      </c>
+      <c r="AK149">
+        <v>1.32</v>
+      </c>
+      <c r="AL149">
+        <v>1.27</v>
+      </c>
+      <c r="AM149">
+        <v>1.15</v>
+      </c>
+      <c r="AN149">
+        <v>1.14</v>
+      </c>
+      <c r="AO149">
+        <v>1.57</v>
+      </c>
+      <c r="AP149">
+        <v>1</v>
+      </c>
+      <c r="AQ149">
+        <v>1.75</v>
+      </c>
+      <c r="AR149">
+        <v>0.91</v>
+      </c>
+      <c r="AS149">
+        <v>1.26</v>
+      </c>
+      <c r="AT149">
+        <v>2.17</v>
+      </c>
+      <c r="AU149">
+        <v>0</v>
+      </c>
+      <c r="AV149">
+        <v>6</v>
+      </c>
+      <c r="AW149">
+        <v>5</v>
+      </c>
+      <c r="AX149">
+        <v>14</v>
+      </c>
+      <c r="AY149">
+        <v>5</v>
+      </c>
+      <c r="AZ149">
+        <v>20</v>
+      </c>
+      <c r="BA149">
+        <v>5</v>
+      </c>
+      <c r="BB149">
+        <v>5</v>
+      </c>
+      <c r="BC149">
+        <v>10</v>
+      </c>
+      <c r="BD149">
+        <v>2.91</v>
+      </c>
+      <c r="BE149">
+        <v>7.7</v>
+      </c>
+      <c r="BF149">
+        <v>1.62</v>
+      </c>
+      <c r="BG149">
+        <v>1.33</v>
+      </c>
+      <c r="BH149">
+        <v>3</v>
+      </c>
+      <c r="BI149">
+        <v>1.51</v>
+      </c>
+      <c r="BJ149">
+        <v>2.26</v>
+      </c>
+      <c r="BK149">
+        <v>1.91</v>
+      </c>
+      <c r="BL149">
+        <v>1.8</v>
+      </c>
+      <c r="BM149">
+        <v>2.46</v>
+      </c>
+      <c r="BN149">
+        <v>1.5</v>
+      </c>
+      <c r="BO149">
+        <v>3.2</v>
+      </c>
+      <c r="BP149">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7729686</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45720.66666666666</v>
+      </c>
+      <c r="F150">
+        <v>17</v>
+      </c>
+      <c r="G150" t="s">
+        <v>81</v>
+      </c>
+      <c r="H150" t="s">
+        <v>77</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="K150">
+        <v>3</v>
+      </c>
+      <c r="L150">
+        <v>2</v>
+      </c>
+      <c r="M150">
+        <v>2</v>
+      </c>
+      <c r="N150">
+        <v>4</v>
+      </c>
+      <c r="O150" t="s">
+        <v>166</v>
+      </c>
+      <c r="P150" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q150">
+        <v>2.55</v>
+      </c>
+      <c r="R150">
+        <v>1.91</v>
+      </c>
+      <c r="S150">
+        <v>5.3</v>
+      </c>
+      <c r="T150">
+        <v>1.68</v>
+      </c>
+      <c r="U150">
+        <v>2.02</v>
+      </c>
+      <c r="V150">
+        <v>3.9</v>
+      </c>
+      <c r="W150">
+        <v>1.2</v>
+      </c>
+      <c r="X150">
+        <v>8.5</v>
+      </c>
+      <c r="Y150">
+        <v>1.02</v>
+      </c>
+      <c r="Z150">
+        <v>1.65</v>
+      </c>
+      <c r="AA150">
+        <v>3</v>
+      </c>
+      <c r="AB150">
+        <v>5.5</v>
+      </c>
+      <c r="AC150">
+        <v>1.14</v>
+      </c>
+      <c r="AD150">
+        <v>4.9</v>
+      </c>
+      <c r="AE150">
+        <v>1.66</v>
+      </c>
+      <c r="AF150">
+        <v>2.08</v>
+      </c>
+      <c r="AG150">
+        <v>3.05</v>
+      </c>
+      <c r="AH150">
+        <v>1.36</v>
+      </c>
+      <c r="AI150">
+        <v>2.62</v>
+      </c>
+      <c r="AJ150">
+        <v>1.42</v>
+      </c>
+      <c r="AK150">
+        <v>1.4</v>
+      </c>
+      <c r="AL150">
+        <v>1.36</v>
+      </c>
+      <c r="AM150">
+        <v>2</v>
+      </c>
+      <c r="AN150">
+        <v>1.25</v>
+      </c>
+      <c r="AO150">
+        <v>0.25</v>
+      </c>
+      <c r="AP150">
+        <v>1.22</v>
+      </c>
+      <c r="AQ150">
+        <v>0.33</v>
+      </c>
+      <c r="AR150">
+        <v>1.16</v>
+      </c>
+      <c r="AS150">
+        <v>1.04</v>
+      </c>
+      <c r="AT150">
+        <v>2.2</v>
+      </c>
+      <c r="AU150">
+        <v>7</v>
+      </c>
+      <c r="AV150">
+        <v>3</v>
+      </c>
+      <c r="AW150">
+        <v>4</v>
+      </c>
+      <c r="AX150">
+        <v>3</v>
+      </c>
+      <c r="AY150">
+        <v>11</v>
+      </c>
+      <c r="AZ150">
+        <v>6</v>
+      </c>
+      <c r="BA150">
+        <v>2</v>
+      </c>
+      <c r="BB150">
+        <v>2</v>
+      </c>
+      <c r="BC150">
+        <v>4</v>
+      </c>
+      <c r="BD150">
+        <v>1.5</v>
+      </c>
+      <c r="BE150">
+        <v>7.9</v>
+      </c>
+      <c r="BF150">
+        <v>3.08</v>
+      </c>
+      <c r="BG150">
+        <v>1.49</v>
+      </c>
+      <c r="BH150">
+        <v>2.3</v>
+      </c>
+      <c r="BI150">
+        <v>1.89</v>
+      </c>
+      <c r="BJ150">
+        <v>1.77</v>
+      </c>
+      <c r="BK150">
+        <v>2.49</v>
+      </c>
+      <c r="BL150">
+        <v>1.42</v>
+      </c>
+      <c r="BM150">
+        <v>3.48</v>
+      </c>
+      <c r="BN150">
+        <v>1.22</v>
+      </c>
+      <c r="BO150">
+        <v>4.5</v>
+      </c>
+      <c r="BP150">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7729687</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45720.66666666666</v>
+      </c>
+      <c r="F151">
+        <v>17</v>
+      </c>
+      <c r="G151" t="s">
+        <v>80</v>
+      </c>
+      <c r="H151" t="s">
+        <v>82</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>89</v>
+      </c>
+      <c r="P151" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q151">
+        <v>3.8</v>
+      </c>
+      <c r="R151">
+        <v>1.7</v>
+      </c>
+      <c r="S151">
+        <v>3.5</v>
+      </c>
+      <c r="T151">
+        <v>1.63</v>
+      </c>
+      <c r="U151">
+        <v>2.1</v>
+      </c>
+      <c r="V151">
+        <v>4.05</v>
+      </c>
+      <c r="W151">
+        <v>1.18</v>
+      </c>
+      <c r="X151">
+        <v>12</v>
+      </c>
+      <c r="Y151">
+        <v>1.03</v>
+      </c>
+      <c r="Z151">
+        <v>2.99</v>
+      </c>
+      <c r="AA151">
+        <v>2.68</v>
+      </c>
+      <c r="AB151">
+        <v>2.75</v>
+      </c>
+      <c r="AC151">
+        <v>1.12</v>
+      </c>
+      <c r="AD151">
+        <v>5.2</v>
+      </c>
+      <c r="AE151">
+        <v>1.57</v>
+      </c>
+      <c r="AF151">
+        <v>2.15</v>
+      </c>
+      <c r="AG151">
+        <v>2.99</v>
+      </c>
+      <c r="AH151">
+        <v>1.34</v>
+      </c>
+      <c r="AI151">
+        <v>2.35</v>
+      </c>
+      <c r="AJ151">
+        <v>1.61</v>
+      </c>
+      <c r="AK151">
+        <v>1.46</v>
+      </c>
+      <c r="AL151">
+        <v>1.43</v>
+      </c>
+      <c r="AM151">
+        <v>1.35</v>
+      </c>
+      <c r="AN151">
+        <v>1.25</v>
+      </c>
+      <c r="AO151">
+        <v>1.25</v>
+      </c>
+      <c r="AP151">
+        <v>1.11</v>
+      </c>
+      <c r="AQ151">
+        <v>1.44</v>
+      </c>
+      <c r="AR151">
+        <v>1.09</v>
+      </c>
+      <c r="AS151">
+        <v>1.24</v>
+      </c>
+      <c r="AT151">
+        <v>2.33</v>
+      </c>
+      <c r="AU151">
+        <v>3</v>
+      </c>
+      <c r="AV151">
+        <v>2</v>
+      </c>
+      <c r="AW151">
+        <v>4</v>
+      </c>
+      <c r="AX151">
+        <v>2</v>
+      </c>
+      <c r="AY151">
+        <v>7</v>
+      </c>
+      <c r="AZ151">
+        <v>4</v>
+      </c>
+      <c r="BA151">
+        <v>5</v>
+      </c>
+      <c r="BB151">
+        <v>2</v>
+      </c>
+      <c r="BC151">
+        <v>7</v>
+      </c>
+      <c r="BD151">
+        <v>2.04</v>
+      </c>
+      <c r="BE151">
+        <v>5.9</v>
+      </c>
+      <c r="BF151">
+        <v>2.18</v>
+      </c>
+      <c r="BG151">
+        <v>1.45</v>
+      </c>
+      <c r="BH151">
+        <v>2.41</v>
+      </c>
+      <c r="BI151">
+        <v>1.83</v>
+      </c>
+      <c r="BJ151">
+        <v>1.83</v>
+      </c>
+      <c r="BK151">
+        <v>2.38</v>
+      </c>
+      <c r="BL151">
+        <v>1.46</v>
+      </c>
+      <c r="BM151">
+        <v>3.28</v>
+      </c>
+      <c r="BN151">
+        <v>1.25</v>
+      </c>
+      <c r="BO151">
+        <v>4.33</v>
+      </c>
+      <c r="BP151">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,15 @@
     <t>['28', '76']</t>
   </si>
   <si>
+    <t>['69', '90+8']</t>
+  </si>
+  <si>
+    <t>['46', '90+7']</t>
+  </si>
+  <si>
+    <t>['39', '71']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -719,6 +728,9 @@
   </si>
   <si>
     <t>['34', '39']</t>
+  </si>
+  <si>
+    <t>['53']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1348,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1542,7 +1554,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2160,7 +2172,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2366,7 +2378,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2444,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ7">
         <v>1.13</v>
@@ -2572,7 +2584,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2859,7 +2871,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2984,7 +2996,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3062,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3190,7 +3202,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3271,7 +3283,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ11">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3602,7 +3614,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3808,7 +3820,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4014,7 +4026,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4092,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ15">
         <v>0.38</v>
@@ -4220,7 +4232,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -5044,7 +5056,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5250,7 +5262,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5328,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ21">
         <v>1.89</v>
@@ -5534,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5868,7 +5880,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5949,7 +5961,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR24">
         <v>1.3</v>
@@ -6074,7 +6086,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6773,7 +6785,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>0.89</v>
@@ -7104,7 +7116,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7391,7 +7403,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ31">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR31">
         <v>1.06</v>
@@ -8134,7 +8146,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8212,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ35">
         <v>1.38</v>
@@ -8546,7 +8558,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9164,7 +9176,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9245,7 +9257,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>1.52</v>
@@ -9370,7 +9382,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9782,7 +9794,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10194,7 +10206,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10606,7 +10618,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -11018,7 +11030,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11302,7 +11314,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ50">
         <v>1.38</v>
@@ -11430,7 +11442,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11511,7 +11523,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>1.11</v>
@@ -11636,7 +11648,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11717,7 +11729,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11842,7 +11854,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12126,7 +12138,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ54">
         <v>0.78</v>
@@ -12335,7 +12347,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ55">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR55">
         <v>0.74</v>
@@ -12666,7 +12678,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13078,7 +13090,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13490,7 +13502,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14186,7 +14198,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ64">
         <v>1.44</v>
@@ -14392,7 +14404,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ65">
         <v>0.44</v>
@@ -14520,7 +14532,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14601,7 +14613,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ66">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.26</v>
@@ -14932,7 +14944,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15422,10 +15434,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR70">
         <v>1.68</v>
@@ -15628,7 +15640,7 @@
         <v>0.67</v>
       </c>
       <c r="AP71">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ71">
         <v>0.78</v>
@@ -15756,7 +15768,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16168,7 +16180,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16374,7 +16386,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16580,7 +16592,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16661,7 +16673,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR76">
         <v>0.77</v>
@@ -16992,7 +17004,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17198,7 +17210,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17404,7 +17416,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17688,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ81">
         <v>1.67</v>
@@ -18434,7 +18446,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18515,7 +18527,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
         <v>1.49</v>
@@ -18640,7 +18652,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18718,7 +18730,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ86">
         <v>2.22</v>
@@ -18846,7 +18858,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19258,7 +19270,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19464,7 +19476,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19670,7 +19682,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19876,7 +19888,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19957,7 +19969,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ92">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR92">
         <v>1.04</v>
@@ -20082,7 +20094,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20366,7 +20378,7 @@
         <v>1.75</v>
       </c>
       <c r="AP94">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ94">
         <v>1.75</v>
@@ -20906,7 +20918,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -20987,7 +20999,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR97">
         <v>1.43</v>
@@ -21190,7 +21202,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ98">
         <v>1</v>
@@ -21318,7 +21330,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21524,7 +21536,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21730,7 +21742,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21936,7 +21948,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22220,7 +22232,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103">
         <v>1.13</v>
@@ -22554,7 +22566,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23172,7 +23184,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23584,7 +23596,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23790,7 +23802,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -23868,7 +23880,7 @@
         <v>1.17</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ111">
         <v>1.44</v>
@@ -24074,10 +24086,10 @@
         <v>1.4</v>
       </c>
       <c r="AP112">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR112">
         <v>1.95</v>
@@ -24283,7 +24295,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR113">
         <v>1.17</v>
@@ -24692,7 +24704,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ115">
         <v>0.89</v>
@@ -25107,7 +25119,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ117">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR117">
         <v>1.15</v>
@@ -25232,7 +25244,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25644,7 +25656,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -26056,7 +26068,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26262,7 +26274,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -27704,7 +27716,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27782,7 +27794,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ130">
         <v>0.89</v>
@@ -27910,7 +27922,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28197,7 +28209,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.28</v>
@@ -28528,7 +28540,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -28606,7 +28618,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ134">
         <v>1.75</v>
@@ -28815,7 +28827,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR135">
         <v>1.18</v>
@@ -29018,10 +29030,10 @@
         <v>2.17</v>
       </c>
       <c r="AP136">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ136">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR136">
         <v>1.71</v>
@@ -29146,7 +29158,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29352,7 +29364,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29558,7 +29570,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29764,7 +29776,7 @@
         <v>89</v>
       </c>
       <c r="P140" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q140">
         <v>3.7</v>
@@ -29970,7 +29982,7 @@
         <v>159</v>
       </c>
       <c r="P141" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q141">
         <v>4.1</v>
@@ -30176,7 +30188,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30588,7 +30600,7 @@
         <v>162</v>
       </c>
       <c r="P144" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q144">
         <v>2.55</v>
@@ -30794,7 +30806,7 @@
         <v>163</v>
       </c>
       <c r="P145" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q145">
         <v>6.6</v>
@@ -31412,7 +31424,7 @@
         <v>165</v>
       </c>
       <c r="P148" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q148">
         <v>2.85</v>
@@ -31618,7 +31630,7 @@
         <v>89</v>
       </c>
       <c r="P149" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q149">
         <v>5.5</v>
@@ -31824,7 +31836,7 @@
         <v>166</v>
       </c>
       <c r="P150" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q150">
         <v>2.55</v>
@@ -32187,6 +32199,624 @@
       </c>
       <c r="BP151">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7729689</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45721.66666666666</v>
+      </c>
+      <c r="F152">
+        <v>17</v>
+      </c>
+      <c r="G152" t="s">
+        <v>83</v>
+      </c>
+      <c r="H152" t="s">
+        <v>79</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>2</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>3</v>
+      </c>
+      <c r="O152" t="s">
+        <v>167</v>
+      </c>
+      <c r="P152" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q152">
+        <v>2.95</v>
+      </c>
+      <c r="R152">
+        <v>1.77</v>
+      </c>
+      <c r="S152">
+        <v>4.3</v>
+      </c>
+      <c r="T152">
+        <v>1.57</v>
+      </c>
+      <c r="U152">
+        <v>2.25</v>
+      </c>
+      <c r="V152">
+        <v>3.5</v>
+      </c>
+      <c r="W152">
+        <v>1.25</v>
+      </c>
+      <c r="X152">
+        <v>10</v>
+      </c>
+      <c r="Y152">
+        <v>1.02</v>
+      </c>
+      <c r="Z152">
+        <v>2.27</v>
+      </c>
+      <c r="AA152">
+        <v>2.66</v>
+      </c>
+      <c r="AB152">
+        <v>3.93</v>
+      </c>
+      <c r="AC152">
+        <v>1.04</v>
+      </c>
+      <c r="AD152">
+        <v>5.8</v>
+      </c>
+      <c r="AE152">
+        <v>1.5</v>
+      </c>
+      <c r="AF152">
+        <v>2.3</v>
+      </c>
+      <c r="AG152">
+        <v>2.65</v>
+      </c>
+      <c r="AH152">
+        <v>1.42</v>
+      </c>
+      <c r="AI152">
+        <v>2.16</v>
+      </c>
+      <c r="AJ152">
+        <v>1.68</v>
+      </c>
+      <c r="AK152">
+        <v>1.47</v>
+      </c>
+      <c r="AL152">
+        <v>1.37</v>
+      </c>
+      <c r="AM152">
+        <v>1.58</v>
+      </c>
+      <c r="AN152">
+        <v>1.25</v>
+      </c>
+      <c r="AO152">
+        <v>1</v>
+      </c>
+      <c r="AP152">
+        <v>1.44</v>
+      </c>
+      <c r="AQ152">
+        <v>0.88</v>
+      </c>
+      <c r="AR152">
+        <v>1.59</v>
+      </c>
+      <c r="AS152">
+        <v>1.07</v>
+      </c>
+      <c r="AT152">
+        <v>2.66</v>
+      </c>
+      <c r="AU152">
+        <v>6</v>
+      </c>
+      <c r="AV152">
+        <v>3</v>
+      </c>
+      <c r="AW152">
+        <v>10</v>
+      </c>
+      <c r="AX152">
+        <v>3</v>
+      </c>
+      <c r="AY152">
+        <v>16</v>
+      </c>
+      <c r="AZ152">
+        <v>6</v>
+      </c>
+      <c r="BA152">
+        <v>5</v>
+      </c>
+      <c r="BB152">
+        <v>3</v>
+      </c>
+      <c r="BC152">
+        <v>8</v>
+      </c>
+      <c r="BD152">
+        <v>1.62</v>
+      </c>
+      <c r="BE152">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF152">
+        <v>2.65</v>
+      </c>
+      <c r="BG152">
+        <v>1.27</v>
+      </c>
+      <c r="BH152">
+        <v>3.14</v>
+      </c>
+      <c r="BI152">
+        <v>1.5</v>
+      </c>
+      <c r="BJ152">
+        <v>2.28</v>
+      </c>
+      <c r="BK152">
+        <v>1.88</v>
+      </c>
+      <c r="BL152">
+        <v>1.78</v>
+      </c>
+      <c r="BM152">
+        <v>2.43</v>
+      </c>
+      <c r="BN152">
+        <v>1.44</v>
+      </c>
+      <c r="BO152">
+        <v>3.28</v>
+      </c>
+      <c r="BP152">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7729688</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45721.66666666666</v>
+      </c>
+      <c r="F153">
+        <v>17</v>
+      </c>
+      <c r="G153" t="s">
+        <v>78</v>
+      </c>
+      <c r="H153" t="s">
+        <v>71</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>2</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>2</v>
+      </c>
+      <c r="O153" t="s">
+        <v>168</v>
+      </c>
+      <c r="P153" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q153">
+        <v>1.96</v>
+      </c>
+      <c r="R153">
+        <v>2.2</v>
+      </c>
+      <c r="S153">
+        <v>8</v>
+      </c>
+      <c r="T153">
+        <v>1.4</v>
+      </c>
+      <c r="U153">
+        <v>2.5</v>
+      </c>
+      <c r="V153">
+        <v>3.2</v>
+      </c>
+      <c r="W153">
+        <v>1.33</v>
+      </c>
+      <c r="X153">
+        <v>7.9</v>
+      </c>
+      <c r="Y153">
+        <v>1.05</v>
+      </c>
+      <c r="Z153">
+        <v>1.43</v>
+      </c>
+      <c r="AA153">
+        <v>3.99</v>
+      </c>
+      <c r="AB153">
+        <v>8.4</v>
+      </c>
+      <c r="AC153">
+        <v>1.04</v>
+      </c>
+      <c r="AD153">
+        <v>7.1</v>
+      </c>
+      <c r="AE153">
+        <v>1.39</v>
+      </c>
+      <c r="AF153">
+        <v>2.91</v>
+      </c>
+      <c r="AG153">
+        <v>1.95</v>
+      </c>
+      <c r="AH153">
+        <v>1.79</v>
+      </c>
+      <c r="AI153">
+        <v>2.45</v>
+      </c>
+      <c r="AJ153">
+        <v>1.44</v>
+      </c>
+      <c r="AK153">
+        <v>1.25</v>
+      </c>
+      <c r="AL153">
+        <v>1.19</v>
+      </c>
+      <c r="AM153">
+        <v>2.7</v>
+      </c>
+      <c r="AN153">
+        <v>2.25</v>
+      </c>
+      <c r="AO153">
+        <v>1.86</v>
+      </c>
+      <c r="AP153">
+        <v>2.33</v>
+      </c>
+      <c r="AQ153">
+        <v>1.63</v>
+      </c>
+      <c r="AR153">
+        <v>1.85</v>
+      </c>
+      <c r="AS153">
+        <v>1.17</v>
+      </c>
+      <c r="AT153">
+        <v>3.02</v>
+      </c>
+      <c r="AU153">
+        <v>6</v>
+      </c>
+      <c r="AV153">
+        <v>3</v>
+      </c>
+      <c r="AW153">
+        <v>20</v>
+      </c>
+      <c r="AX153">
+        <v>5</v>
+      </c>
+      <c r="AY153">
+        <v>26</v>
+      </c>
+      <c r="AZ153">
+        <v>8</v>
+      </c>
+      <c r="BA153">
+        <v>5</v>
+      </c>
+      <c r="BB153">
+        <v>2</v>
+      </c>
+      <c r="BC153">
+        <v>7</v>
+      </c>
+      <c r="BD153">
+        <v>1.22</v>
+      </c>
+      <c r="BE153">
+        <v>10.25</v>
+      </c>
+      <c r="BF153">
+        <v>5</v>
+      </c>
+      <c r="BG153">
+        <v>1.25</v>
+      </c>
+      <c r="BH153">
+        <v>3.28</v>
+      </c>
+      <c r="BI153">
+        <v>1.48</v>
+      </c>
+      <c r="BJ153">
+        <v>2.33</v>
+      </c>
+      <c r="BK153">
+        <v>1.85</v>
+      </c>
+      <c r="BL153">
+        <v>1.81</v>
+      </c>
+      <c r="BM153">
+        <v>2.38</v>
+      </c>
+      <c r="BN153">
+        <v>1.46</v>
+      </c>
+      <c r="BO153">
+        <v>3.2</v>
+      </c>
+      <c r="BP153">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7729690</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45721.66666666666</v>
+      </c>
+      <c r="F154">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>75</v>
+      </c>
+      <c r="H154" t="s">
+        <v>87</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>2</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>3</v>
+      </c>
+      <c r="O154" t="s">
+        <v>169</v>
+      </c>
+      <c r="P154" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q154">
+        <v>2.21</v>
+      </c>
+      <c r="R154">
+        <v>2.2</v>
+      </c>
+      <c r="S154">
+        <v>4.6</v>
+      </c>
+      <c r="T154">
+        <v>1.35</v>
+      </c>
+      <c r="U154">
+        <v>2.8</v>
+      </c>
+      <c r="V154">
+        <v>2.85</v>
+      </c>
+      <c r="W154">
+        <v>1.35</v>
+      </c>
+      <c r="X154">
+        <v>7</v>
+      </c>
+      <c r="Y154">
+        <v>1.07</v>
+      </c>
+      <c r="Z154">
+        <v>1.69</v>
+      </c>
+      <c r="AA154">
+        <v>3.45</v>
+      </c>
+      <c r="AB154">
+        <v>5.3</v>
+      </c>
+      <c r="AC154">
+        <v>1.05</v>
+      </c>
+      <c r="AD154">
+        <v>8.9</v>
+      </c>
+      <c r="AE154">
+        <v>1.32</v>
+      </c>
+      <c r="AF154">
+        <v>3.4</v>
+      </c>
+      <c r="AG154">
+        <v>1.98</v>
+      </c>
+      <c r="AH154">
+        <v>1.77</v>
+      </c>
+      <c r="AI154">
+        <v>1.95</v>
+      </c>
+      <c r="AJ154">
+        <v>1.85</v>
+      </c>
+      <c r="AK154">
+        <v>1.17</v>
+      </c>
+      <c r="AL154">
+        <v>1.26</v>
+      </c>
+      <c r="AM154">
+        <v>2.23</v>
+      </c>
+      <c r="AN154">
+        <v>2.71</v>
+      </c>
+      <c r="AO154">
+        <v>1.5</v>
+      </c>
+      <c r="AP154">
+        <v>2.75</v>
+      </c>
+      <c r="AQ154">
+        <v>1.33</v>
+      </c>
+      <c r="AR154">
+        <v>1.75</v>
+      </c>
+      <c r="AS154">
+        <v>1.43</v>
+      </c>
+      <c r="AT154">
+        <v>3.18</v>
+      </c>
+      <c r="AU154">
+        <v>5</v>
+      </c>
+      <c r="AV154">
+        <v>5</v>
+      </c>
+      <c r="AW154">
+        <v>7</v>
+      </c>
+      <c r="AX154">
+        <v>8</v>
+      </c>
+      <c r="AY154">
+        <v>12</v>
+      </c>
+      <c r="AZ154">
+        <v>13</v>
+      </c>
+      <c r="BA154">
+        <v>6</v>
+      </c>
+      <c r="BB154">
+        <v>5</v>
+      </c>
+      <c r="BC154">
+        <v>11</v>
+      </c>
+      <c r="BD154">
+        <v>1.51</v>
+      </c>
+      <c r="BE154">
+        <v>8.5</v>
+      </c>
+      <c r="BF154">
+        <v>2.96</v>
+      </c>
+      <c r="BG154">
+        <v>1.25</v>
+      </c>
+      <c r="BH154">
+        <v>3.28</v>
+      </c>
+      <c r="BI154">
+        <v>1.48</v>
+      </c>
+      <c r="BJ154">
+        <v>2.33</v>
+      </c>
+      <c r="BK154">
+        <v>1.84</v>
+      </c>
+      <c r="BL154">
+        <v>1.82</v>
+      </c>
+      <c r="BM154">
+        <v>2.35</v>
+      </c>
+      <c r="BN154">
+        <v>1.47</v>
+      </c>
+      <c r="BO154">
+        <v>3.2</v>
+      </c>
+      <c r="BP154">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -310,10 +310,10 @@
     <t>['43']</t>
   </si>
   <si>
-    <t>['35', '44', '86', '89']</t>
+    <t>['50', '53', '74']</t>
   </si>
   <si>
-    <t>['50', '53', '74']</t>
+    <t>['35', '44', '86', '89']</t>
   </si>
   <si>
     <t>['67']</t>
@@ -322,19 +322,19 @@
     <t>['90']</t>
   </si>
   <si>
-    <t>['18', '42']</t>
+    <t>['3', '56', '57', '81']</t>
   </si>
   <si>
-    <t>['3', '56', '57', '81']</t>
+    <t>['18', '42']</t>
   </si>
   <si>
     <t>['68']</t>
   </si>
   <si>
-    <t>['73']</t>
+    <t>['54']</t>
   </si>
   <si>
-    <t>['54']</t>
+    <t>['73']</t>
   </si>
   <si>
     <t>['20']</t>
@@ -373,10 +373,10 @@
     <t>['66', '72']</t>
   </si>
   <si>
-    <t>['54', '81']</t>
+    <t>['90+6']</t>
   </si>
   <si>
-    <t>['90+6']</t>
+    <t>['54', '81']</t>
   </si>
   <si>
     <t>['45+3', '50']</t>
@@ -433,10 +433,10 @@
     <t>['75']</t>
   </si>
   <si>
-    <t>['11', '81']</t>
+    <t>['29']</t>
   </si>
   <si>
-    <t>['29']</t>
+    <t>['11', '81']</t>
   </si>
   <si>
     <t>['15', '67']</t>
@@ -517,13 +517,13 @@
     <t>['28', '76']</t>
   </si>
   <si>
-    <t>['69', '90+8']</t>
+    <t>['39', '71']</t>
   </si>
   <si>
     <t>['46', '90+7']</t>
   </si>
   <si>
-    <t>['39', '71']</t>
+    <t>['69', '90+8']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -559,10 +559,10 @@
     <t>['3', '34']</t>
   </si>
   <si>
-    <t>['15', '79', '90+9']</t>
+    <t>['45']</t>
   </si>
   <si>
-    <t>['45']</t>
+    <t>['15', '79', '90+9']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -631,10 +631,10 @@
     <t>['45+11']</t>
   </si>
   <si>
-    <t>['71']</t>
+    <t>['80']</t>
   </si>
   <si>
-    <t>['80']</t>
+    <t>['71']</t>
   </si>
   <si>
     <t>['86']</t>
@@ -667,10 +667,10 @@
     <t>['13', '29', '39']</t>
   </si>
   <si>
-    <t>['40']</t>
+    <t>['23', '51']</t>
   </si>
   <si>
-    <t>['23', '51']</t>
+    <t>['40']</t>
   </si>
   <si>
     <t>['90+12']</t>
@@ -5014,7 +5014,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>7729552</v>
+        <v>7729553</v>
       </c>
       <c r="C20" t="s">
         <v>68</v>
@@ -5029,28 +5029,28 @@
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
         <v>3</v>
       </c>
-      <c r="L20">
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
         <v>4</v>
-      </c>
-      <c r="M20">
-        <v>3</v>
-      </c>
-      <c r="N20">
-        <v>7</v>
       </c>
       <c r="O20" t="s">
         <v>98</v>
@@ -5059,160 +5059,160 @@
         <v>181</v>
       </c>
       <c r="Q20">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="T20">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="V20">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="X20">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
       <c r="Y20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AA20">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AB20">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="AC20">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AD20">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AE20">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
+        <v>3.14</v>
+      </c>
+      <c r="AG20">
         <v>2.1</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
+        <v>1.7</v>
+      </c>
+      <c r="AI20">
+        <v>2.1</v>
+      </c>
+      <c r="AJ20">
+        <v>1.67</v>
+      </c>
+      <c r="AK20">
+        <v>1.06</v>
+      </c>
+      <c r="AL20">
+        <v>1.17</v>
+      </c>
+      <c r="AM20">
+        <v>2.67</v>
+      </c>
+      <c r="AN20">
+        <v>1</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>2.75</v>
+      </c>
+      <c r="AQ20">
+        <v>1.89</v>
+      </c>
+      <c r="AR20">
+        <v>1.79</v>
+      </c>
+      <c r="AS20">
+        <v>1.25</v>
+      </c>
+      <c r="AT20">
+        <v>3.04</v>
+      </c>
+      <c r="AU20">
+        <v>6</v>
+      </c>
+      <c r="AV20">
+        <v>6</v>
+      </c>
+      <c r="AW20">
         <v>3</v>
       </c>
-      <c r="AH20">
-        <v>1.36</v>
-      </c>
-      <c r="AI20">
-        <v>2.5</v>
-      </c>
-      <c r="AJ20">
-        <v>1.5</v>
-      </c>
-      <c r="AK20">
-        <v>1.38</v>
-      </c>
-      <c r="AL20">
-        <v>1.39</v>
-      </c>
-      <c r="AM20">
-        <v>1.29</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>1</v>
-      </c>
-      <c r="AP20">
-        <v>1.33</v>
-      </c>
-      <c r="AQ20">
-        <v>0.44</v>
-      </c>
-      <c r="AR20">
-        <v>0.95</v>
-      </c>
-      <c r="AS20">
-        <v>0.57</v>
-      </c>
-      <c r="AT20">
-        <v>1.52</v>
-      </c>
-      <c r="AU20">
-        <v>11</v>
-      </c>
-      <c r="AV20">
+      <c r="AX20">
         <v>7</v>
       </c>
-      <c r="AW20">
-        <v>1</v>
-      </c>
-      <c r="AX20">
-        <v>3</v>
-      </c>
       <c r="AY20">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC20">
         <v>14</v>
       </c>
       <c r="BD20">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20">
-        <v>1.98</v>
+        <v>5.45</v>
       </c>
       <c r="BG20">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="BH20">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="BI20">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="BJ20">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="BK20">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="BL20">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="BM20">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="BN20">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="BO20">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="BP20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="21" spans="1:68">
@@ -5220,7 +5220,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>7729553</v>
+        <v>7729552</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -5235,28 +5235,28 @@
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
         <v>3</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
       <c r="N21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O21" t="s">
         <v>99</v>
@@ -5265,160 +5265,160 @@
         <v>182</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="R21">
+        <v>1.8</v>
+      </c>
+      <c r="S21">
+        <v>4</v>
+      </c>
+      <c r="T21">
+        <v>1.72</v>
+      </c>
+      <c r="U21">
+        <v>2.02</v>
+      </c>
+      <c r="V21">
+        <v>4.5</v>
+      </c>
+      <c r="W21">
+        <v>1.18</v>
+      </c>
+      <c r="X21">
+        <v>12.5</v>
+      </c>
+      <c r="Y21">
+        <v>1.01</v>
+      </c>
+      <c r="Z21">
+        <v>2.38</v>
+      </c>
+      <c r="AA21">
+        <v>2.63</v>
+      </c>
+      <c r="AB21">
+        <v>3.5</v>
+      </c>
+      <c r="AC21">
+        <v>1.16</v>
+      </c>
+      <c r="AD21">
+        <v>4.8</v>
+      </c>
+      <c r="AE21">
+        <v>1.65</v>
+      </c>
+      <c r="AF21">
         <v>2.1</v>
       </c>
-      <c r="S21">
-        <v>5.5</v>
-      </c>
-      <c r="T21">
+      <c r="AG21">
+        <v>3</v>
+      </c>
+      <c r="AH21">
+        <v>1.36</v>
+      </c>
+      <c r="AI21">
+        <v>2.5</v>
+      </c>
+      <c r="AJ21">
+        <v>1.5</v>
+      </c>
+      <c r="AK21">
+        <v>1.38</v>
+      </c>
+      <c r="AL21">
         <v>1.39</v>
       </c>
-      <c r="U21">
-        <v>2.85</v>
-      </c>
-      <c r="V21">
-        <v>2.7</v>
-      </c>
-      <c r="W21">
-        <v>1.43</v>
-      </c>
-      <c r="X21">
-        <v>6.3</v>
-      </c>
-      <c r="Y21">
-        <v>1.1</v>
-      </c>
-      <c r="Z21">
-        <v>1.65</v>
-      </c>
-      <c r="AA21">
-        <v>3.5</v>
-      </c>
-      <c r="AB21">
-        <v>5.25</v>
-      </c>
-      <c r="AC21">
-        <v>1.02</v>
-      </c>
-      <c r="AD21">
-        <v>7.4</v>
-      </c>
-      <c r="AE21">
-        <v>1.25</v>
-      </c>
-      <c r="AF21">
-        <v>3.14</v>
-      </c>
-      <c r="AG21">
-        <v>2.1</v>
-      </c>
-      <c r="AH21">
-        <v>1.7</v>
-      </c>
-      <c r="AI21">
-        <v>2.1</v>
-      </c>
-      <c r="AJ21">
-        <v>1.67</v>
-      </c>
-      <c r="AK21">
-        <v>1.06</v>
-      </c>
-      <c r="AL21">
-        <v>1.17</v>
-      </c>
       <c r="AM21">
-        <v>2.67</v>
+        <v>1.29</v>
       </c>
       <c r="AN21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>1.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR21">
-        <v>1.79</v>
+        <v>0.95</v>
       </c>
       <c r="AS21">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="AT21">
-        <v>3.04</v>
+        <v>1.52</v>
       </c>
       <c r="AU21">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW21">
+        <v>1</v>
+      </c>
+      <c r="AX21">
         <v>3</v>
       </c>
-      <c r="AX21">
-        <v>7</v>
-      </c>
       <c r="AY21">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC21">
         <v>14</v>
       </c>
       <c r="BD21">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="BE21">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BF21">
-        <v>5.45</v>
+        <v>1.98</v>
       </c>
       <c r="BG21">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="BH21">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="BI21">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="BJ21">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="BK21">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="BL21">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="BM21">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="BN21">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="BO21">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="BP21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="22" spans="1:68">
@@ -6456,7 +6456,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7729560</v>
+        <v>7729559</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -6471,10 +6471,10 @@
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -6501,160 +6501,160 @@
         <v>89</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="R27">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T27">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U27">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="W27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X27">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>4.94</v>
       </c>
       <c r="AA27">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AD27">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="AE27">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AF27">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AG27">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH27">
+        <v>1.61</v>
+      </c>
+      <c r="AI27">
+        <v>2.1</v>
+      </c>
+      <c r="AJ27">
+        <v>1.67</v>
+      </c>
+      <c r="AK27">
+        <v>1.86</v>
+      </c>
+      <c r="AL27">
+        <v>1.24</v>
+      </c>
+      <c r="AM27">
+        <v>1.14</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>1.75</v>
+      </c>
+      <c r="AQ27">
         <v>1.33</v>
       </c>
-      <c r="AI27">
-        <v>2.5</v>
-      </c>
-      <c r="AJ27">
-        <v>1.5</v>
-      </c>
-      <c r="AK27">
-        <v>1.22</v>
-      </c>
-      <c r="AL27">
-        <v>1.29</v>
-      </c>
-      <c r="AM27">
-        <v>1.6</v>
-      </c>
-      <c r="AN27">
-        <v>1</v>
-      </c>
-      <c r="AO27">
-        <v>1</v>
-      </c>
-      <c r="AP27">
-        <v>0.78</v>
-      </c>
-      <c r="AQ27">
-        <v>1.25</v>
-      </c>
       <c r="AR27">
-        <v>2</v>
+        <v>0.89</v>
       </c>
       <c r="AS27">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AT27">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="AU27">
         <v>3</v>
       </c>
       <c r="AV27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AX27">
         <v>8</v>
       </c>
       <c r="AY27">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AZ27">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BA27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BC27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD27">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF27">
-        <v>2.47</v>
+        <v>1.57</v>
       </c>
       <c r="BG27">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BH27">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="BI27">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="BJ27">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BK27">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="BL27">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="BM27">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="BN27">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="BO27">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BP27">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="28" spans="1:68">
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>7729559</v>
+        <v>7729560</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -6677,10 +6677,10 @@
         <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -6707,160 +6707,160 @@
         <v>89</v>
       </c>
       <c r="Q28">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="S28">
+        <v>3.75</v>
+      </c>
+      <c r="T28">
+        <v>1.52</v>
+      </c>
+      <c r="U28">
+        <v>2.39</v>
+      </c>
+      <c r="V28">
+        <v>3.46</v>
+      </c>
+      <c r="W28">
+        <v>1.28</v>
+      </c>
+      <c r="X28">
+        <v>9.5</v>
+      </c>
+      <c r="Y28">
+        <v>1.04</v>
+      </c>
+      <c r="Z28">
+        <v>2.7</v>
+      </c>
+      <c r="AA28">
         <v>2.6</v>
       </c>
-      <c r="T28">
+      <c r="AB28">
+        <v>3</v>
+      </c>
+      <c r="AC28">
+        <v>1.04</v>
+      </c>
+      <c r="AD28">
+        <v>6.45</v>
+      </c>
+      <c r="AE28">
+        <v>1.44</v>
+      </c>
+      <c r="AF28">
+        <v>2.65</v>
+      </c>
+      <c r="AG28">
+        <v>3.25</v>
+      </c>
+      <c r="AH28">
+        <v>1.33</v>
+      </c>
+      <c r="AI28">
+        <v>2.5</v>
+      </c>
+      <c r="AJ28">
         <v>1.5</v>
       </c>
-      <c r="U28">
-        <v>2.5</v>
-      </c>
-      <c r="V28">
-        <v>3.4</v>
-      </c>
-      <c r="W28">
-        <v>1.3</v>
-      </c>
-      <c r="X28">
-        <v>8</v>
-      </c>
-      <c r="Y28">
-        <v>1.06</v>
-      </c>
-      <c r="Z28">
-        <v>4.94</v>
-      </c>
-      <c r="AA28">
-        <v>3.29</v>
-      </c>
-      <c r="AB28">
-        <v>1.68</v>
-      </c>
-      <c r="AC28">
-        <v>1.07</v>
-      </c>
-      <c r="AD28">
-        <v>7.5</v>
-      </c>
-      <c r="AE28">
-        <v>1.39</v>
-      </c>
-      <c r="AF28">
-        <v>2.85</v>
-      </c>
-      <c r="AG28">
-        <v>2.17</v>
-      </c>
-      <c r="AH28">
-        <v>1.61</v>
-      </c>
-      <c r="AI28">
-        <v>2.1</v>
-      </c>
-      <c r="AJ28">
-        <v>1.67</v>
-      </c>
       <c r="AK28">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AM28">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="AS28">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AT28">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="AU28">
         <v>3</v>
       </c>
       <c r="AV28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX28">
         <v>8</v>
       </c>
       <c r="AY28">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AZ28">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC28">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD28">
+        <v>1.82</v>
+      </c>
+      <c r="BE28">
+        <v>7.4</v>
+      </c>
+      <c r="BF28">
+        <v>2.47</v>
+      </c>
+      <c r="BG28">
+        <v>1.46</v>
+      </c>
+      <c r="BH28">
+        <v>2.53</v>
+      </c>
+      <c r="BI28">
+        <v>1.8</v>
+      </c>
+      <c r="BJ28">
+        <v>2</v>
+      </c>
+      <c r="BK28">
+        <v>2.31</v>
+      </c>
+      <c r="BL28">
+        <v>1.54</v>
+      </c>
+      <c r="BM28">
         <v>3.1</v>
       </c>
-      <c r="BE28">
-        <v>7.6</v>
-      </c>
-      <c r="BF28">
-        <v>1.57</v>
-      </c>
-      <c r="BG28">
-        <v>1.36</v>
-      </c>
-      <c r="BH28">
-        <v>2.9</v>
-      </c>
-      <c r="BI28">
-        <v>1.63</v>
-      </c>
-      <c r="BJ28">
-        <v>2.15</v>
-      </c>
-      <c r="BK28">
-        <v>2.04</v>
-      </c>
-      <c r="BL28">
-        <v>1.7</v>
-      </c>
-      <c r="BM28">
-        <v>2.65</v>
-      </c>
       <c r="BN28">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="BO28">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BP28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="29" spans="1:68">
@@ -6868,7 +6868,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>7729561</v>
+        <v>7729562</v>
       </c>
       <c r="C29" t="s">
         <v>68</v>
@@ -6883,82 +6883,82 @@
         <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O29" t="s">
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R29">
         <v>1.91</v>
       </c>
       <c r="S29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="V29">
         <v>3.4</v>
       </c>
       <c r="W29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z29">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA29">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB29">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC29">
         <v>1.1</v>
       </c>
       <c r="AD29">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF29">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AG29">
         <v>2.63</v>
@@ -6967,100 +6967,100 @@
         <v>1.44</v>
       </c>
       <c r="AI29">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AJ29">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AK29">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AM29">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.89</v>
+        <v>0.38</v>
       </c>
       <c r="AR29">
-        <v>0.83</v>
+        <v>1.49</v>
       </c>
       <c r="AS29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AT29">
-        <v>1.91</v>
+        <v>2.59</v>
       </c>
       <c r="AU29">
+        <v>8</v>
+      </c>
+      <c r="AV29">
+        <v>7</v>
+      </c>
+      <c r="AW29">
         <v>4</v>
       </c>
-      <c r="AV29">
-        <v>3</v>
-      </c>
-      <c r="AW29">
-        <v>3</v>
-      </c>
       <c r="AX29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY29">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ29">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BA29">
         <v>3</v>
       </c>
       <c r="BB29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="BC29">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BD29">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="BE29">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="BF29">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="BG29">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="BH29">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="BI29">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BJ29">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="BK29">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="BL29">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BM29">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BN29">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO29">
         <v>0</v>
@@ -7074,7 +7074,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7729562</v>
+        <v>7729561</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
@@ -7089,82 +7089,82 @@
         <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O30" t="s">
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="Q30">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
         <v>1.91</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U30">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
         <v>3.4</v>
       </c>
       <c r="W30">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X30">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z30">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA30">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB30">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC30">
         <v>1.1</v>
       </c>
       <c r="AD30">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE30">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF30">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AG30">
         <v>2.63</v>
@@ -7173,100 +7173,100 @@
         <v>1.44</v>
       </c>
       <c r="AI30">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AJ30">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AL30">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AM30">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1.22</v>
+      </c>
+      <c r="AQ30">
+        <v>0.89</v>
+      </c>
+      <c r="AR30">
+        <v>0.83</v>
+      </c>
+      <c r="AS30">
+        <v>1.08</v>
+      </c>
+      <c r="AT30">
+        <v>1.91</v>
+      </c>
+      <c r="AU30">
+        <v>4</v>
+      </c>
+      <c r="AV30">
         <v>3</v>
       </c>
-      <c r="AO30">
-        <v>1</v>
-      </c>
-      <c r="AP30">
-        <v>1.5</v>
-      </c>
-      <c r="AQ30">
-        <v>0.38</v>
-      </c>
-      <c r="AR30">
-        <v>1.49</v>
-      </c>
-      <c r="AS30">
-        <v>1.1</v>
-      </c>
-      <c r="AT30">
-        <v>2.59</v>
-      </c>
-      <c r="AU30">
-        <v>8</v>
-      </c>
-      <c r="AV30">
-        <v>7</v>
-      </c>
       <c r="AW30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY30">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BA30">
         <v>3</v>
       </c>
       <c r="BB30">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="BC30">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BD30">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="BE30">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="BF30">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG30">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="BH30">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="BI30">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BJ30">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="BK30">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="BL30">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BM30">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BN30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BO30">
         <v>0</v>
@@ -8104,7 +8104,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>7729568</v>
+        <v>7729567</v>
       </c>
       <c r="C35" t="s">
         <v>68</v>
@@ -8119,190 +8119,190 @@
         <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>1</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O35" t="s">
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="Q35">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R35">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S35">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="T35">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W35">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y35">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z35">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB35">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AD35">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AE35">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AF35">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AG35">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH35">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AI35">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ35">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL35">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AM35">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AN35">
         <v>1</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ35">
-        <v>1.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR35">
-        <v>2.03</v>
+        <v>1.03</v>
       </c>
       <c r="AS35">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AT35">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
       <c r="AU35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV35">
         <v>3</v>
       </c>
       <c r="AW35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX35">
+        <v>7</v>
+      </c>
+      <c r="AY35">
+        <v>8</v>
+      </c>
+      <c r="AZ35">
+        <v>11</v>
+      </c>
+      <c r="BA35">
+        <v>5</v>
+      </c>
+      <c r="BB35">
         <v>4</v>
       </c>
-      <c r="AY35">
-        <v>15</v>
-      </c>
-      <c r="AZ35">
-        <v>12</v>
-      </c>
-      <c r="BA35">
-        <v>1</v>
-      </c>
-      <c r="BB35">
-        <v>3</v>
-      </c>
       <c r="BC35">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BD35">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="BE35">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF35">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
       <c r="BG35">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="BH35">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="BI35">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="BJ35">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="BK35">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="BL35">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BM35">
-        <v>3.28</v>
+        <v>2.69</v>
       </c>
       <c r="BN35">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="BO35">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="BP35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="36" spans="1:68">
@@ -8310,7 +8310,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>7729567</v>
+        <v>7729568</v>
       </c>
       <c r="C36" t="s">
         <v>68</v>
@@ -8325,190 +8325,190 @@
         <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36" t="s">
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="Q36">
+        <v>3.1</v>
+      </c>
+      <c r="R36">
+        <v>1.83</v>
+      </c>
+      <c r="S36">
         <v>4</v>
       </c>
-      <c r="R36">
-        <v>1.91</v>
-      </c>
-      <c r="S36">
-        <v>2.88</v>
-      </c>
       <c r="T36">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W36">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X36">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA36">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC36">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AD36">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AE36">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AF36">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG36">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH36">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI36">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ36">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AK36">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AM36">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AN36">
         <v>1</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ36">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="AR36">
-        <v>1.03</v>
+        <v>2.03</v>
       </c>
       <c r="AS36">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AT36">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="AU36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV36">
         <v>3</v>
       </c>
       <c r="AW36">
+        <v>6</v>
+      </c>
+      <c r="AX36">
         <v>4</v>
       </c>
-      <c r="AX36">
-        <v>7</v>
-      </c>
       <c r="AY36">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB36">
+        <v>3</v>
+      </c>
+      <c r="BC36">
         <v>4</v>
       </c>
-      <c r="BC36">
-        <v>9</v>
-      </c>
       <c r="BD36">
-        <v>2.72</v>
+        <v>1.88</v>
       </c>
       <c r="BE36">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF36">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="BG36">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="BH36">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="BI36">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="BJ36">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="BK36">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="BL36">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BM36">
-        <v>2.69</v>
+        <v>3.28</v>
       </c>
       <c r="BN36">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="BO36">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="BP36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="37" spans="1:68">
@@ -8722,7 +8722,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>7729571</v>
+        <v>7729570</v>
       </c>
       <c r="C38" t="s">
         <v>68</v>
@@ -8737,73 +8737,73 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="s">
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="Q38">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="T38">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U38">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="W38">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X38">
-        <v>11.75</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z38">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="AA38">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AB38">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AC38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AD38">
         <v>7</v>
@@ -8815,112 +8815,112 @@
         <v>2.4</v>
       </c>
       <c r="AG38">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI38">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AK38">
-        <v>2.29</v>
+        <v>1.19</v>
       </c>
       <c r="AL38">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AM38">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="AN38">
         <v>0.5</v>
       </c>
       <c r="AO38">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.75</v>
+        <v>0.89</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AS38">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT38">
-        <v>2.19</v>
+        <v>2.72</v>
       </c>
       <c r="AU38">
         <v>2</v>
       </c>
       <c r="AV38">
+        <v>4</v>
+      </c>
+      <c r="AW38">
+        <v>7</v>
+      </c>
+      <c r="AX38">
         <v>5</v>
       </c>
-      <c r="AW38">
-        <v>0</v>
-      </c>
-      <c r="AX38">
-        <v>8</v>
-      </c>
       <c r="AY38">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AZ38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BC38">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BD38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="BF38">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BG38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BH38">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BI38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BJ38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BK38">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BL38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BM38">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BN38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BO38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BP38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="39" spans="1:68">
@@ -8928,7 +8928,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7729570</v>
+        <v>7729571</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -8943,73 +8943,73 @@
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="s">
         <v>89</v>
       </c>
       <c r="P39" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="R39">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S39">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="T39">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="V39">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="W39">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>11.75</v>
       </c>
       <c r="Y39">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z39">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="AA39">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AB39">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD39">
         <v>7</v>
@@ -9021,112 +9021,112 @@
         <v>2.4</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH39">
+        <v>1.4</v>
+      </c>
+      <c r="AI39">
+        <v>2.88</v>
+      </c>
+      <c r="AJ39">
         <v>1.36</v>
       </c>
-      <c r="AI39">
-        <v>2.5</v>
-      </c>
-      <c r="AJ39">
-        <v>1.5</v>
-      </c>
       <c r="AK39">
-        <v>1.19</v>
+        <v>2.29</v>
       </c>
       <c r="AL39">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AM39">
-        <v>1.73</v>
+        <v>1.08</v>
       </c>
       <c r="AN39">
         <v>0.5</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AP39">
-        <v>0.89</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AR39">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS39">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT39">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="AU39">
         <v>2</v>
       </c>
       <c r="AV39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AX39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY39">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AZ39">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC39">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD39">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BE39">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="BF39">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BG39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BH39">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BI39">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BJ39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BK39">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BL39">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BM39">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BN39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BO39">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:68">
@@ -9340,7 +9340,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7729573</v>
+        <v>7729574</v>
       </c>
       <c r="C41" t="s">
         <v>68</v>
@@ -9355,190 +9355,190 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41">
         <v>1</v>
       </c>
       <c r="O41" t="s">
+        <v>108</v>
+      </c>
+      <c r="P41" t="s">
         <v>89</v>
       </c>
-      <c r="P41" t="s">
-        <v>189</v>
-      </c>
       <c r="Q41">
+        <v>4.5</v>
+      </c>
+      <c r="R41">
+        <v>1.67</v>
+      </c>
+      <c r="S41">
         <v>3.4</v>
-      </c>
-      <c r="R41">
-        <v>1.83</v>
-      </c>
-      <c r="S41">
-        <v>3.75</v>
       </c>
       <c r="T41">
         <v>1.62</v>
       </c>
       <c r="U41">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V41">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W41">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X41">
-        <v>12.5</v>
+        <v>10.75</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z41">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA41">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB41">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AC41">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AD41">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE41">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF41">
         <v>2.25</v>
       </c>
       <c r="AG41">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AH41">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI41">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AJ41">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AK41">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AL41">
         <v>1.36</v>
       </c>
       <c r="AM41">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.78</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>1.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR41">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AS41">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AT41">
-        <v>3.01</v>
+        <v>2.59</v>
       </c>
       <c r="AU41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX41">
+        <v>6</v>
+      </c>
+      <c r="AY41">
+        <v>15</v>
+      </c>
+      <c r="AZ41">
+        <v>14</v>
+      </c>
+      <c r="BA41">
         <v>5</v>
-      </c>
-      <c r="AY41">
-        <v>7</v>
-      </c>
-      <c r="AZ41">
-        <v>11</v>
-      </c>
-      <c r="BA41">
-        <v>3</v>
       </c>
       <c r="BB41">
         <v>5</v>
       </c>
       <c r="BC41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD41">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BE41">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="BF41">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="BG41">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BH41">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="BI41">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="BJ41">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BK41">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="BL41">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="BM41">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="BN41">
         <v>1.44</v>
       </c>
       <c r="BO41">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="BP41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="42" spans="1:68">
@@ -9546,7 +9546,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>7729574</v>
+        <v>7729573</v>
       </c>
       <c r="C42" t="s">
         <v>68</v>
@@ -9561,190 +9561,190 @@
         <v>5</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="Q42">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="S42">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T42">
         <v>1.62</v>
       </c>
       <c r="U42">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V42">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="W42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X42">
-        <v>10.75</v>
+        <v>12.5</v>
       </c>
       <c r="Y42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z42">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA42">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB42">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AC42">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD42">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE42">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF42">
         <v>2.25</v>
       </c>
       <c r="AG42">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH42">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI42">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AJ42">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AK42">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AL42">
         <v>1.36</v>
       </c>
       <c r="AM42">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AN42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO42">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AQ42">
-        <v>0.44</v>
+        <v>1.89</v>
       </c>
       <c r="AR42">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS42">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AT42">
-        <v>2.59</v>
+        <v>3.01</v>
       </c>
       <c r="AU42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV42">
+        <v>3</v>
+      </c>
+      <c r="AW42">
+        <v>3</v>
+      </c>
+      <c r="AX42">
         <v>5</v>
       </c>
-      <c r="AW42">
+      <c r="AY42">
         <v>7</v>
       </c>
-      <c r="AX42">
-        <v>6</v>
-      </c>
-      <c r="AY42">
-        <v>15</v>
-      </c>
       <c r="AZ42">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB42">
         <v>5</v>
       </c>
       <c r="BC42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD42">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BE42">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="BF42">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="BG42">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BH42">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="BI42">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="BJ42">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BK42">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="BL42">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BM42">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="BN42">
         <v>1.44</v>
       </c>
       <c r="BO42">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="BP42">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="43" spans="1:68">
@@ -10206,7 +10206,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10782,7 +10782,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7729581</v>
+        <v>7729582</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -10797,88 +10797,88 @@
         <v>6</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="Q48">
+        <v>2.6</v>
+      </c>
+      <c r="R48">
+        <v>1.83</v>
+      </c>
+      <c r="S48">
+        <v>5.5</v>
+      </c>
+      <c r="T48">
+        <v>1.62</v>
+      </c>
+      <c r="U48">
+        <v>2.2</v>
+      </c>
+      <c r="V48">
         <v>4</v>
       </c>
-      <c r="R48">
-        <v>1.73</v>
-      </c>
-      <c r="S48">
-        <v>3.5</v>
-      </c>
-      <c r="T48">
-        <v>1.65</v>
-      </c>
-      <c r="U48">
-        <v>2.1</v>
-      </c>
-      <c r="V48">
-        <v>3.95</v>
-      </c>
       <c r="W48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X48">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AA48">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB48">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="AC48">
         <v>1.13</v>
       </c>
       <c r="AD48">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AE48">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF48">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG48">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH48">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI48">
         <v>2.5</v>
@@ -10887,100 +10887,100 @@
         <v>1.5</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AL48">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AM48">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AN48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO48">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AQ48">
-        <v>0.38</v>
+        <v>0.89</v>
       </c>
       <c r="AR48">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="AS48">
-        <v>1.32</v>
+        <v>0.9</v>
       </c>
       <c r="AT48">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AU48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW48">
         <v>3</v>
       </c>
       <c r="AX48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY48">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AZ48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA48">
         <v>6</v>
       </c>
       <c r="BB48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD48">
-        <v>2.27</v>
+        <v>1.5</v>
       </c>
       <c r="BE48">
-        <v>6.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF48">
-        <v>1.88</v>
+        <v>3.04</v>
       </c>
       <c r="BG48">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="BH48">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="BI48">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="BJ48">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="BK48">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="BL48">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BM48">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="BN48">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO48">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP48">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="49" spans="1:68">
@@ -10988,7 +10988,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>7729582</v>
+        <v>7729581</v>
       </c>
       <c r="C49" t="s">
         <v>68</v>
@@ -11003,88 +11003,88 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>89</v>
+      </c>
+      <c r="P49" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q49">
         <v>4</v>
       </c>
-      <c r="O49" t="s">
-        <v>112</v>
-      </c>
-      <c r="P49" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q49">
+      <c r="R49">
+        <v>1.73</v>
+      </c>
+      <c r="S49">
+        <v>3.5</v>
+      </c>
+      <c r="T49">
+        <v>1.65</v>
+      </c>
+      <c r="U49">
+        <v>2.1</v>
+      </c>
+      <c r="V49">
+        <v>3.95</v>
+      </c>
+      <c r="W49">
+        <v>1.2</v>
+      </c>
+      <c r="X49">
+        <v>12</v>
+      </c>
+      <c r="Y49">
+        <v>1.01</v>
+      </c>
+      <c r="Z49">
+        <v>3</v>
+      </c>
+      <c r="AA49">
         <v>2.6</v>
       </c>
-      <c r="R49">
-        <v>1.83</v>
-      </c>
-      <c r="S49">
-        <v>5.5</v>
-      </c>
-      <c r="T49">
-        <v>1.62</v>
-      </c>
-      <c r="U49">
-        <v>2.2</v>
-      </c>
-      <c r="V49">
-        <v>4</v>
-      </c>
-      <c r="W49">
-        <v>1.22</v>
-      </c>
-      <c r="X49">
-        <v>9</v>
-      </c>
-      <c r="Y49">
-        <v>1.04</v>
-      </c>
-      <c r="Z49">
-        <v>1.83</v>
-      </c>
-      <c r="AA49">
-        <v>2.88</v>
-      </c>
       <c r="AB49">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="AC49">
         <v>1.13</v>
       </c>
       <c r="AD49">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AE49">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF49">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG49">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="AH49">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI49">
         <v>2.5</v>
@@ -11093,100 +11093,100 @@
         <v>1.5</v>
       </c>
       <c r="AK49">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AL49">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AM49">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="AN49">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49">
-        <v>0.89</v>
+        <v>0.38</v>
       </c>
       <c r="AR49">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="AS49">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="AT49">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AU49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW49">
         <v>3</v>
       </c>
       <c r="AX49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY49">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ49">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA49">
         <v>6</v>
       </c>
       <c r="BB49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC49">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD49">
+        <v>2.27</v>
+      </c>
+      <c r="BE49">
+        <v>6.85</v>
+      </c>
+      <c r="BF49">
+        <v>1.88</v>
+      </c>
+      <c r="BG49">
         <v>1.5</v>
       </c>
-      <c r="BE49">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF49">
-        <v>3.04</v>
-      </c>
-      <c r="BG49">
-        <v>1.35</v>
-      </c>
       <c r="BH49">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="BI49">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="BJ49">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="BK49">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="BL49">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BM49">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BN49">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO49">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP49">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="50" spans="1:68">
@@ -13048,7 +13048,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>7729592</v>
+        <v>7729593</v>
       </c>
       <c r="C59" t="s">
         <v>68</v>
@@ -13063,190 +13063,190 @@
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O59" t="s">
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="Q59">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R59">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="S59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T59">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="U59">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V59">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="W59">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X59">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y59">
         <v>1.04</v>
       </c>
       <c r="Z59">
+        <v>2.3</v>
+      </c>
+      <c r="AA59">
+        <v>2.7</v>
+      </c>
+      <c r="AB59">
         <v>3.4</v>
       </c>
-      <c r="AA59">
-        <v>3</v>
-      </c>
-      <c r="AB59">
-        <v>2</v>
-      </c>
       <c r="AC59">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AD59">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE59">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF59">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AG59">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH59">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AI59">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AJ59">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AK59">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AL59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AM59">
-        <v>1.26</v>
+        <v>1.82</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO59">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ59">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AR59">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AS59">
         <v>1.34</v>
       </c>
       <c r="AT59">
+        <v>2.35</v>
+      </c>
+      <c r="AU59">
+        <v>8</v>
+      </c>
+      <c r="AV59">
+        <v>6</v>
+      </c>
+      <c r="AW59">
+        <v>9</v>
+      </c>
+      <c r="AX59">
+        <v>2</v>
+      </c>
+      <c r="AY59">
+        <v>24</v>
+      </c>
+      <c r="AZ59">
+        <v>8</v>
+      </c>
+      <c r="BA59">
+        <v>8</v>
+      </c>
+      <c r="BB59">
+        <v>1</v>
+      </c>
+      <c r="BC59">
+        <v>9</v>
+      </c>
+      <c r="BD59">
+        <v>1.57</v>
+      </c>
+      <c r="BE59">
+        <v>6.4</v>
+      </c>
+      <c r="BF59">
+        <v>3.08</v>
+      </c>
+      <c r="BG59">
+        <v>1.44</v>
+      </c>
+      <c r="BH59">
+        <v>2.67</v>
+      </c>
+      <c r="BI59">
+        <v>1.75</v>
+      </c>
+      <c r="BJ59">
+        <v>2.01</v>
+      </c>
+      <c r="BK59">
+        <v>2.22</v>
+      </c>
+      <c r="BL59">
+        <v>1.61</v>
+      </c>
+      <c r="BM59">
         <v>2.92</v>
       </c>
-      <c r="AU59">
-        <v>4</v>
-      </c>
-      <c r="AV59">
-        <v>5</v>
-      </c>
-      <c r="AW59">
-        <v>2</v>
-      </c>
-      <c r="AX59">
-        <v>4</v>
-      </c>
-      <c r="AY59">
-        <v>7</v>
-      </c>
-      <c r="AZ59">
-        <v>9</v>
-      </c>
-      <c r="BA59">
-        <v>5</v>
-      </c>
-      <c r="BB59">
-        <v>2</v>
-      </c>
-      <c r="BC59">
-        <v>7</v>
-      </c>
-      <c r="BD59">
-        <v>2.42</v>
-      </c>
-      <c r="BE59">
-        <v>6.1</v>
-      </c>
-      <c r="BF59">
-        <v>1.85</v>
-      </c>
-      <c r="BG59">
-        <v>1.32</v>
-      </c>
-      <c r="BH59">
-        <v>2.88</v>
-      </c>
-      <c r="BI59">
-        <v>1.68</v>
-      </c>
-      <c r="BJ59">
-        <v>2.14</v>
-      </c>
-      <c r="BK59">
-        <v>2.11</v>
-      </c>
-      <c r="BL59">
-        <v>1.71</v>
-      </c>
-      <c r="BM59">
-        <v>2.66</v>
-      </c>
       <c r="BN59">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BO59">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="BP59">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="60" spans="1:68">
@@ -13254,7 +13254,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>7729593</v>
+        <v>7729592</v>
       </c>
       <c r="C60" t="s">
         <v>68</v>
@@ -13269,190 +13269,190 @@
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O60" t="s">
         <v>120</v>
       </c>
       <c r="P60" t="s">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="Q60">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R60">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T60">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V60">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="W60">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X60">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y60">
         <v>1.04</v>
       </c>
       <c r="Z60">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA60">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB60">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AC60">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AD60">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE60">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF60">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AG60">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH60">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI60">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AJ60">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AK60">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AL60">
+        <v>1.31</v>
+      </c>
+      <c r="AM60">
+        <v>1.26</v>
+      </c>
+      <c r="AN60">
+        <v>1</v>
+      </c>
+      <c r="AO60">
+        <v>2</v>
+      </c>
+      <c r="AP60">
         <v>1.33</v>
       </c>
-      <c r="AM60">
-        <v>1.82</v>
-      </c>
-      <c r="AN60">
-        <v>1.33</v>
-      </c>
-      <c r="AO60">
-        <v>1.33</v>
-      </c>
-      <c r="AP60">
-        <v>1.22</v>
-      </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AR60">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AS60">
         <v>1.34</v>
       </c>
       <c r="AT60">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AU60">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW60">
+        <v>2</v>
+      </c>
+      <c r="AX60">
+        <v>4</v>
+      </c>
+      <c r="AY60">
+        <v>7</v>
+      </c>
+      <c r="AZ60">
         <v>9</v>
       </c>
-      <c r="AX60">
-        <v>2</v>
-      </c>
-      <c r="AY60">
-        <v>24</v>
-      </c>
-      <c r="AZ60">
-        <v>8</v>
-      </c>
       <c r="BA60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD60">
-        <v>1.57</v>
+        <v>2.42</v>
       </c>
       <c r="BE60">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="BF60">
-        <v>3.08</v>
+        <v>1.85</v>
       </c>
       <c r="BG60">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="BH60">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="BI60">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="BJ60">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="BK60">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BL60">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BM60">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="BN60">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BO60">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="BP60">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="61" spans="1:68">
@@ -13499,7 +13499,7 @@
         <v>2</v>
       </c>
       <c r="O61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P61" t="s">
         <v>198</v>
@@ -17168,7 +17168,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>7729611</v>
+        <v>7729612</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -17183,10 +17183,10 @@
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -17198,172 +17198,172 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="P79" t="s">
         <v>205</v>
       </c>
       <c r="Q79">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S79">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T79">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="U79">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V79">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="W79">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X79">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="Y79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA79">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB79">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AD79">
+        <v>7.5</v>
+      </c>
+      <c r="AE79">
+        <v>1.36</v>
+      </c>
+      <c r="AF79">
+        <v>2.88</v>
+      </c>
+      <c r="AG79">
+        <v>2.63</v>
+      </c>
+      <c r="AH79">
+        <v>1.44</v>
+      </c>
+      <c r="AI79">
+        <v>2.2</v>
+      </c>
+      <c r="AJ79">
+        <v>1.62</v>
+      </c>
+      <c r="AK79">
+        <v>1.72</v>
+      </c>
+      <c r="AL79">
+        <v>1.31</v>
+      </c>
+      <c r="AM79">
+        <v>1.2</v>
+      </c>
+      <c r="AN79">
+        <v>1.25</v>
+      </c>
+      <c r="AO79">
+        <v>1.75</v>
+      </c>
+      <c r="AP79">
+        <v>1.22</v>
+      </c>
+      <c r="AQ79">
+        <v>2.22</v>
+      </c>
+      <c r="AR79">
+        <v>1.3</v>
+      </c>
+      <c r="AS79">
+        <v>1.38</v>
+      </c>
+      <c r="AT79">
+        <v>2.68</v>
+      </c>
+      <c r="AU79">
+        <v>5</v>
+      </c>
+      <c r="AV79">
         <v>7</v>
       </c>
-      <c r="AE79">
-        <v>1.5</v>
-      </c>
-      <c r="AF79">
-        <v>2.4</v>
-      </c>
-      <c r="AG79">
-        <v>2.2</v>
-      </c>
-      <c r="AH79">
-        <v>1.65</v>
-      </c>
-      <c r="AI79">
-        <v>2.25</v>
-      </c>
-      <c r="AJ79">
-        <v>1.57</v>
-      </c>
-      <c r="AK79">
-        <v>1.13</v>
-      </c>
-      <c r="AL79">
-        <v>1.28</v>
-      </c>
-      <c r="AM79">
-        <v>1.91</v>
-      </c>
-      <c r="AN79">
-        <v>2.33</v>
-      </c>
-      <c r="AO79">
-        <v>1.25</v>
-      </c>
-      <c r="AP79">
-        <v>1.5</v>
-      </c>
-      <c r="AQ79">
-        <v>1</v>
-      </c>
-      <c r="AR79">
-        <v>1.49</v>
-      </c>
-      <c r="AS79">
-        <v>0.87</v>
-      </c>
-      <c r="AT79">
-        <v>2.36</v>
-      </c>
-      <c r="AU79">
+      <c r="AW79">
+        <v>5</v>
+      </c>
+      <c r="AX79">
         <v>6</v>
       </c>
-      <c r="AV79">
-        <v>3</v>
-      </c>
-      <c r="AW79">
-        <v>8</v>
-      </c>
-      <c r="AX79">
-        <v>4</v>
-      </c>
       <c r="AY79">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ79">
+        <v>13</v>
+      </c>
+      <c r="BA79">
+        <v>2</v>
+      </c>
+      <c r="BB79">
+        <v>5</v>
+      </c>
+      <c r="BC79">
         <v>7</v>
       </c>
-      <c r="BA79">
-        <v>12</v>
-      </c>
-      <c r="BB79">
-        <v>0</v>
-      </c>
-      <c r="BC79">
-        <v>12</v>
-      </c>
       <c r="BD79">
-        <v>1.37</v>
+        <v>2.71</v>
       </c>
       <c r="BE79">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="BF79">
-        <v>4.26</v>
+        <v>1.69</v>
       </c>
       <c r="BG79">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BH79">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BI79">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BJ79">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="BK79">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="BL79">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="BM79">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BN79">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BO79">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP79">
         <v>1.29</v>
@@ -17374,7 +17374,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>7729612</v>
+        <v>7729611</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -17389,10 +17389,10 @@
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H80" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -17404,172 +17404,172 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80">
         <v>1</v>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O80" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="P80" t="s">
         <v>206</v>
       </c>
       <c r="Q80">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R80">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S80">
+        <v>5.5</v>
+      </c>
+      <c r="T80">
+        <v>1.56</v>
+      </c>
+      <c r="U80">
+        <v>2.31</v>
+      </c>
+      <c r="V80">
+        <v>3.4</v>
+      </c>
+      <c r="W80">
+        <v>1.29</v>
+      </c>
+      <c r="X80">
+        <v>8.9</v>
+      </c>
+      <c r="Y80">
+        <v>1.05</v>
+      </c>
+      <c r="Z80">
+        <v>1.65</v>
+      </c>
+      <c r="AA80">
+        <v>3.4</v>
+      </c>
+      <c r="AB80">
+        <v>5.25</v>
+      </c>
+      <c r="AC80">
+        <v>1.07</v>
+      </c>
+      <c r="AD80">
+        <v>7</v>
+      </c>
+      <c r="AE80">
+        <v>1.5</v>
+      </c>
+      <c r="AF80">
+        <v>2.4</v>
+      </c>
+      <c r="AG80">
+        <v>2.2</v>
+      </c>
+      <c r="AH80">
+        <v>1.65</v>
+      </c>
+      <c r="AI80">
+        <v>2.25</v>
+      </c>
+      <c r="AJ80">
+        <v>1.57</v>
+      </c>
+      <c r="AK80">
+        <v>1.13</v>
+      </c>
+      <c r="AL80">
+        <v>1.28</v>
+      </c>
+      <c r="AM80">
+        <v>1.91</v>
+      </c>
+      <c r="AN80">
+        <v>2.33</v>
+      </c>
+      <c r="AO80">
+        <v>1.25</v>
+      </c>
+      <c r="AP80">
+        <v>1.5</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.49</v>
+      </c>
+      <c r="AS80">
+        <v>0.87</v>
+      </c>
+      <c r="AT80">
+        <v>2.36</v>
+      </c>
+      <c r="AU80">
+        <v>6</v>
+      </c>
+      <c r="AV80">
         <v>3</v>
       </c>
-      <c r="T80">
-        <v>1.52</v>
-      </c>
-      <c r="U80">
-        <v>2.4</v>
-      </c>
-      <c r="V80">
-        <v>3.27</v>
-      </c>
-      <c r="W80">
-        <v>1.32</v>
-      </c>
-      <c r="X80">
-        <v>7.7</v>
-      </c>
-      <c r="Y80">
-        <v>1.06</v>
-      </c>
-      <c r="Z80">
-        <v>3.5</v>
-      </c>
-      <c r="AA80">
+      <c r="AW80">
+        <v>8</v>
+      </c>
+      <c r="AX80">
+        <v>4</v>
+      </c>
+      <c r="AY80">
+        <v>14</v>
+      </c>
+      <c r="AZ80">
+        <v>7</v>
+      </c>
+      <c r="BA80">
+        <v>12</v>
+      </c>
+      <c r="BB80">
+        <v>0</v>
+      </c>
+      <c r="BC80">
+        <v>12</v>
+      </c>
+      <c r="BD80">
+        <v>1.37</v>
+      </c>
+      <c r="BE80">
+        <v>8</v>
+      </c>
+      <c r="BF80">
+        <v>4.26</v>
+      </c>
+      <c r="BG80">
+        <v>1.38</v>
+      </c>
+      <c r="BH80">
         <v>2.8</v>
       </c>
-      <c r="AB80">
-        <v>2.2</v>
-      </c>
-      <c r="AC80">
-        <v>1.06</v>
-      </c>
-      <c r="AD80">
-        <v>7.5</v>
-      </c>
-      <c r="AE80">
-        <v>1.36</v>
-      </c>
-      <c r="AF80">
-        <v>2.88</v>
-      </c>
-      <c r="AG80">
-        <v>2.63</v>
-      </c>
-      <c r="AH80">
+      <c r="BI80">
+        <v>1.65</v>
+      </c>
+      <c r="BJ80">
+        <v>2.22</v>
+      </c>
+      <c r="BK80">
+        <v>2.07</v>
+      </c>
+      <c r="BL80">
+        <v>1.74</v>
+      </c>
+      <c r="BM80">
+        <v>2.6</v>
+      </c>
+      <c r="BN80">
         <v>1.44</v>
       </c>
-      <c r="AI80">
-        <v>2.2</v>
-      </c>
-      <c r="AJ80">
-        <v>1.62</v>
-      </c>
-      <c r="AK80">
-        <v>1.72</v>
-      </c>
-      <c r="AL80">
-        <v>1.31</v>
-      </c>
-      <c r="AM80">
-        <v>1.2</v>
-      </c>
-      <c r="AN80">
-        <v>1.25</v>
-      </c>
-      <c r="AO80">
-        <v>1.75</v>
-      </c>
-      <c r="AP80">
-        <v>1.22</v>
-      </c>
-      <c r="AQ80">
-        <v>2.22</v>
-      </c>
-      <c r="AR80">
-        <v>1.3</v>
-      </c>
-      <c r="AS80">
-        <v>1.38</v>
-      </c>
-      <c r="AT80">
-        <v>2.68</v>
-      </c>
-      <c r="AU80">
-        <v>5</v>
-      </c>
-      <c r="AV80">
-        <v>7</v>
-      </c>
-      <c r="AW80">
-        <v>5</v>
-      </c>
-      <c r="AX80">
-        <v>6</v>
-      </c>
-      <c r="AY80">
-        <v>10</v>
-      </c>
-      <c r="AZ80">
-        <v>13</v>
-      </c>
-      <c r="BA80">
-        <v>2</v>
-      </c>
-      <c r="BB80">
-        <v>5</v>
-      </c>
-      <c r="BC80">
-        <v>7</v>
-      </c>
-      <c r="BD80">
-        <v>2.71</v>
-      </c>
-      <c r="BE80">
-        <v>7.7</v>
-      </c>
-      <c r="BF80">
-        <v>1.69</v>
-      </c>
-      <c r="BG80">
-        <v>1.36</v>
-      </c>
-      <c r="BH80">
-        <v>2.9</v>
-      </c>
-      <c r="BI80">
-        <v>1.64</v>
-      </c>
-      <c r="BJ80">
-        <v>2.23</v>
-      </c>
-      <c r="BK80">
-        <v>2.03</v>
-      </c>
-      <c r="BL80">
-        <v>1.77</v>
-      </c>
-      <c r="BM80">
-        <v>2.5</v>
-      </c>
-      <c r="BN80">
-        <v>1.48</v>
-      </c>
       <c r="BO80">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP80">
         <v>1.29</v>
@@ -20464,7 +20464,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>7729628</v>
+        <v>7729627</v>
       </c>
       <c r="C95" t="s">
         <v>68</v>
@@ -20479,160 +20479,160 @@
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I95">
         <v>0</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95">
         <v>1</v>
       </c>
       <c r="N95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O95" t="s">
+        <v>89</v>
+      </c>
+      <c r="P95" t="s">
         <v>136</v>
       </c>
-      <c r="P95" t="s">
-        <v>97</v>
-      </c>
       <c r="Q95">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S95">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T95">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="U95">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V95">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="W95">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X95">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y95">
         <v>1.03</v>
       </c>
       <c r="Z95">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA95">
+        <v>3.25</v>
+      </c>
+      <c r="AB95">
+        <v>2.3</v>
+      </c>
+      <c r="AC95">
+        <v>1.15</v>
+      </c>
+      <c r="AD95">
+        <v>5</v>
+      </c>
+      <c r="AE95">
+        <v>1.61</v>
+      </c>
+      <c r="AF95">
+        <v>2.15</v>
+      </c>
+      <c r="AG95">
         <v>2.75</v>
       </c>
-      <c r="AB95">
-        <v>2.75</v>
-      </c>
-      <c r="AC95">
-        <v>1.1</v>
-      </c>
-      <c r="AD95">
-        <v>6.5</v>
-      </c>
-      <c r="AE95">
-        <v>1.5</v>
-      </c>
-      <c r="AF95">
-        <v>2.55</v>
-      </c>
-      <c r="AG95">
-        <v>2.7</v>
-      </c>
       <c r="AH95">
+        <v>1.4</v>
+      </c>
+      <c r="AI95">
+        <v>2.63</v>
+      </c>
+      <c r="AJ95">
         <v>1.44</v>
       </c>
-      <c r="AI95">
-        <v>2.15</v>
-      </c>
-      <c r="AJ95">
-        <v>1.67</v>
-      </c>
       <c r="AK95">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL95">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AM95">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AN95">
         <v>1</v>
       </c>
       <c r="AO95">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AP95">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AR95">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="AS95">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="AT95">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="AU95">
+        <v>2</v>
+      </c>
+      <c r="AV95">
         <v>3</v>
       </c>
-      <c r="AV95">
-        <v>6</v>
-      </c>
       <c r="AW95">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ95">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA95">
         <v>5</v>
       </c>
       <c r="BB95">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC95">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD95">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="BE95">
         <v>6.1</v>
       </c>
       <c r="BF95">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG95">
         <v>1.31</v>
@@ -20670,7 +20670,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>7729627</v>
+        <v>7729628</v>
       </c>
       <c r="C96" t="s">
         <v>68</v>
@@ -20685,160 +20685,160 @@
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I96">
         <v>0</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96">
         <v>1</v>
       </c>
       <c r="N96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="P96" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="Q96">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R96">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S96">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T96">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="U96">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="W96">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X96">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y96">
         <v>1.03</v>
       </c>
       <c r="Z96">
+        <v>2.88</v>
+      </c>
+      <c r="AA96">
+        <v>2.75</v>
+      </c>
+      <c r="AB96">
+        <v>2.75</v>
+      </c>
+      <c r="AC96">
+        <v>1.1</v>
+      </c>
+      <c r="AD96">
+        <v>6.5</v>
+      </c>
+      <c r="AE96">
+        <v>1.5</v>
+      </c>
+      <c r="AF96">
+        <v>2.55</v>
+      </c>
+      <c r="AG96">
         <v>2.7</v>
       </c>
-      <c r="AA96">
-        <v>3.25</v>
-      </c>
-      <c r="AB96">
-        <v>2.3</v>
-      </c>
-      <c r="AC96">
-        <v>1.15</v>
-      </c>
-      <c r="AD96">
-        <v>5</v>
-      </c>
-      <c r="AE96">
-        <v>1.61</v>
-      </c>
-      <c r="AF96">
+      <c r="AH96">
+        <v>1.44</v>
+      </c>
+      <c r="AI96">
         <v>2.15</v>
       </c>
-      <c r="AG96">
-        <v>2.75</v>
-      </c>
-      <c r="AH96">
+      <c r="AJ96">
+        <v>1.67</v>
+      </c>
+      <c r="AK96">
+        <v>1.44</v>
+      </c>
+      <c r="AL96">
         <v>1.4</v>
       </c>
-      <c r="AI96">
-        <v>2.63</v>
-      </c>
-      <c r="AJ96">
-        <v>1.44</v>
-      </c>
-      <c r="AK96">
-        <v>1.49</v>
-      </c>
-      <c r="AL96">
-        <v>1.43</v>
-      </c>
       <c r="AM96">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AN96">
         <v>1</v>
       </c>
       <c r="AO96">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ96">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AR96">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="AS96">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="AT96">
-        <v>1.85</v>
+        <v>2.79</v>
       </c>
       <c r="AU96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV96">
+        <v>6</v>
+      </c>
+      <c r="AW96">
+        <v>0</v>
+      </c>
+      <c r="AX96">
+        <v>6</v>
+      </c>
+      <c r="AY96">
         <v>3</v>
       </c>
-      <c r="AW96">
-        <v>3</v>
-      </c>
-      <c r="AX96">
-        <v>5</v>
-      </c>
-      <c r="AY96">
-        <v>5</v>
-      </c>
       <c r="AZ96">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA96">
         <v>5</v>
       </c>
       <c r="BB96">
+        <v>5</v>
+      </c>
+      <c r="BC96">
         <v>10</v>
       </c>
-      <c r="BC96">
-        <v>15</v>
-      </c>
       <c r="BD96">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="BE96">
         <v>6.1</v>
       </c>
       <c r="BF96">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG96">
         <v>1.31</v>
@@ -21700,7 +21700,7 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>7729633</v>
+        <v>7729634</v>
       </c>
       <c r="C101" t="s">
         <v>68</v>
@@ -21715,10 +21715,10 @@
         <v>12</v>
       </c>
       <c r="G101" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H101" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -21730,10 +21730,10 @@
         <v>2</v>
       </c>
       <c r="L101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N101">
         <v>3</v>
@@ -21745,160 +21745,160 @@
         <v>217</v>
       </c>
       <c r="Q101">
+        <v>2.35</v>
+      </c>
+      <c r="R101">
+        <v>2.05</v>
+      </c>
+      <c r="S101">
+        <v>5</v>
+      </c>
+      <c r="T101">
+        <v>1.44</v>
+      </c>
+      <c r="U101">
+        <v>2.55</v>
+      </c>
+      <c r="V101">
+        <v>3</v>
+      </c>
+      <c r="W101">
+        <v>1.33</v>
+      </c>
+      <c r="X101">
+        <v>8.25</v>
+      </c>
+      <c r="Y101">
+        <v>1.06</v>
+      </c>
+      <c r="Z101">
+        <v>1.72</v>
+      </c>
+      <c r="AA101">
+        <v>3.41</v>
+      </c>
+      <c r="AB101">
+        <v>5.1</v>
+      </c>
+      <c r="AC101">
+        <v>1.07</v>
+      </c>
+      <c r="AD101">
+        <v>7.5</v>
+      </c>
+      <c r="AE101">
+        <v>1.38</v>
+      </c>
+      <c r="AF101">
+        <v>2.8</v>
+      </c>
+      <c r="AG101">
+        <v>2.1</v>
+      </c>
+      <c r="AH101">
+        <v>1.61</v>
+      </c>
+      <c r="AI101">
+        <v>2.05</v>
+      </c>
+      <c r="AJ101">
+        <v>1.66</v>
+      </c>
+      <c r="AK101">
+        <v>1.18</v>
+      </c>
+      <c r="AL101">
+        <v>1.29</v>
+      </c>
+      <c r="AM101">
+        <v>2.05</v>
+      </c>
+      <c r="AN101">
+        <v>1.6</v>
+      </c>
+      <c r="AO101">
+        <v>1</v>
+      </c>
+      <c r="AP101">
+        <v>1.5</v>
+      </c>
+      <c r="AQ101">
+        <v>1.38</v>
+      </c>
+      <c r="AR101">
+        <v>1.53</v>
+      </c>
+      <c r="AS101">
+        <v>0.85</v>
+      </c>
+      <c r="AT101">
+        <v>2.38</v>
+      </c>
+      <c r="AU101">
         <v>4</v>
       </c>
-      <c r="R101">
-        <v>1.75</v>
-      </c>
-      <c r="S101">
-        <v>3.3</v>
-      </c>
-      <c r="T101">
-        <v>1.71</v>
-      </c>
-      <c r="U101">
-        <v>2</v>
-      </c>
-      <c r="V101">
-        <v>4.5</v>
-      </c>
-      <c r="W101">
-        <v>1.17</v>
-      </c>
-      <c r="X101">
-        <v>14.5</v>
-      </c>
-      <c r="Y101">
-        <v>1.02</v>
-      </c>
-      <c r="Z101">
-        <v>3.29</v>
-      </c>
-      <c r="AA101">
-        <v>2.64</v>
-      </c>
-      <c r="AB101">
+      <c r="AV101">
+        <v>5</v>
+      </c>
+      <c r="AW101">
+        <v>11</v>
+      </c>
+      <c r="AX101">
+        <v>3</v>
+      </c>
+      <c r="AY101">
+        <v>15</v>
+      </c>
+      <c r="AZ101">
+        <v>8</v>
+      </c>
+      <c r="BA101">
+        <v>7</v>
+      </c>
+      <c r="BB101">
+        <v>1</v>
+      </c>
+      <c r="BC101">
+        <v>8</v>
+      </c>
+      <c r="BD101">
+        <v>1.33</v>
+      </c>
+      <c r="BE101">
+        <v>9</v>
+      </c>
+      <c r="BF101">
+        <v>3.92</v>
+      </c>
+      <c r="BG101">
+        <v>1.31</v>
+      </c>
+      <c r="BH101">
+        <v>2.92</v>
+      </c>
+      <c r="BI101">
+        <v>1.57</v>
+      </c>
+      <c r="BJ101">
+        <v>2.14</v>
+      </c>
+      <c r="BK101">
+        <v>2</v>
+      </c>
+      <c r="BL101">
+        <v>1.69</v>
+      </c>
+      <c r="BM101">
         <v>2.59</v>
       </c>
-      <c r="AC101">
-        <v>1.17</v>
-      </c>
-      <c r="AD101">
-        <v>4.75</v>
-      </c>
-      <c r="AE101">
-        <v>1.83</v>
-      </c>
-      <c r="AF101">
-        <v>1.91</v>
-      </c>
-      <c r="AG101">
-        <v>3.21</v>
-      </c>
-      <c r="AH101">
-        <v>1.3</v>
-      </c>
-      <c r="AI101">
-        <v>2.55</v>
-      </c>
-      <c r="AJ101">
-        <v>1.44</v>
-      </c>
-      <c r="AK101">
-        <v>1.5</v>
-      </c>
-      <c r="AL101">
-        <v>1.41</v>
-      </c>
-      <c r="AM101">
-        <v>1.33</v>
-      </c>
-      <c r="AN101">
-        <v>0.17</v>
-      </c>
-      <c r="AO101">
-        <v>0.4</v>
-      </c>
-      <c r="AP101">
-        <v>1.11</v>
-      </c>
-      <c r="AQ101">
-        <v>0.38</v>
-      </c>
-      <c r="AR101">
-        <v>1.45</v>
-      </c>
-      <c r="AS101">
-        <v>1.13</v>
-      </c>
-      <c r="AT101">
-        <v>2.58</v>
-      </c>
-      <c r="AU101">
-        <v>5</v>
-      </c>
-      <c r="AV101">
-        <v>2</v>
-      </c>
-      <c r="AW101">
-        <v>8</v>
-      </c>
-      <c r="AX101">
-        <v>0</v>
-      </c>
-      <c r="AY101">
-        <v>13</v>
-      </c>
-      <c r="AZ101">
-        <v>2</v>
-      </c>
-      <c r="BA101">
-        <v>9</v>
-      </c>
-      <c r="BB101">
-        <v>3</v>
-      </c>
-      <c r="BC101">
-        <v>12</v>
-      </c>
-      <c r="BD101">
-        <v>2.15</v>
-      </c>
-      <c r="BE101">
-        <v>6.7</v>
-      </c>
-      <c r="BF101">
-        <v>1.92</v>
-      </c>
-      <c r="BG101">
-        <v>1.26</v>
-      </c>
-      <c r="BH101">
-        <v>3.4</v>
-      </c>
-      <c r="BI101">
-        <v>1.52</v>
-      </c>
-      <c r="BJ101">
-        <v>2.32</v>
-      </c>
-      <c r="BK101">
-        <v>1.92</v>
-      </c>
-      <c r="BL101">
-        <v>1.75</v>
-      </c>
-      <c r="BM101">
-        <v>2.6</v>
-      </c>
       <c r="BN101">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BO101">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BP101">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="102" spans="1:68">
@@ -21906,7 +21906,7 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>7729634</v>
+        <v>7729633</v>
       </c>
       <c r="C102" t="s">
         <v>68</v>
@@ -21921,10 +21921,10 @@
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -21936,10 +21936,10 @@
         <v>2</v>
       </c>
       <c r="L102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N102">
         <v>3</v>
@@ -21951,160 +21951,160 @@
         <v>218</v>
       </c>
       <c r="Q102">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="R102">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="S102">
+        <v>3.3</v>
+      </c>
+      <c r="T102">
+        <v>1.71</v>
+      </c>
+      <c r="U102">
+        <v>2</v>
+      </c>
+      <c r="V102">
+        <v>4.5</v>
+      </c>
+      <c r="W102">
+        <v>1.17</v>
+      </c>
+      <c r="X102">
+        <v>14.5</v>
+      </c>
+      <c r="Y102">
+        <v>1.02</v>
+      </c>
+      <c r="Z102">
+        <v>3.29</v>
+      </c>
+      <c r="AA102">
+        <v>2.64</v>
+      </c>
+      <c r="AB102">
+        <v>2.59</v>
+      </c>
+      <c r="AC102">
+        <v>1.17</v>
+      </c>
+      <c r="AD102">
+        <v>4.75</v>
+      </c>
+      <c r="AE102">
+        <v>1.83</v>
+      </c>
+      <c r="AF102">
+        <v>1.91</v>
+      </c>
+      <c r="AG102">
+        <v>3.21</v>
+      </c>
+      <c r="AH102">
+        <v>1.3</v>
+      </c>
+      <c r="AI102">
+        <v>2.55</v>
+      </c>
+      <c r="AJ102">
+        <v>1.44</v>
+      </c>
+      <c r="AK102">
+        <v>1.5</v>
+      </c>
+      <c r="AL102">
+        <v>1.41</v>
+      </c>
+      <c r="AM102">
+        <v>1.33</v>
+      </c>
+      <c r="AN102">
+        <v>0.17</v>
+      </c>
+      <c r="AO102">
+        <v>0.4</v>
+      </c>
+      <c r="AP102">
+        <v>1.11</v>
+      </c>
+      <c r="AQ102">
+        <v>0.38</v>
+      </c>
+      <c r="AR102">
+        <v>1.45</v>
+      </c>
+      <c r="AS102">
+        <v>1.13</v>
+      </c>
+      <c r="AT102">
+        <v>2.58</v>
+      </c>
+      <c r="AU102">
         <v>5</v>
       </c>
-      <c r="T102">
-        <v>1.44</v>
-      </c>
-      <c r="U102">
-        <v>2.55</v>
-      </c>
-      <c r="V102">
+      <c r="AV102">
+        <v>2</v>
+      </c>
+      <c r="AW102">
+        <v>8</v>
+      </c>
+      <c r="AX102">
+        <v>0</v>
+      </c>
+      <c r="AY102">
+        <v>13</v>
+      </c>
+      <c r="AZ102">
+        <v>2</v>
+      </c>
+      <c r="BA102">
+        <v>9</v>
+      </c>
+      <c r="BB102">
         <v>3</v>
       </c>
-      <c r="W102">
-        <v>1.33</v>
-      </c>
-      <c r="X102">
-        <v>8.25</v>
-      </c>
-      <c r="Y102">
-        <v>1.06</v>
-      </c>
-      <c r="Z102">
-        <v>1.72</v>
-      </c>
-      <c r="AA102">
-        <v>3.41</v>
-      </c>
-      <c r="AB102">
-        <v>5.1</v>
-      </c>
-      <c r="AC102">
-        <v>1.07</v>
-      </c>
-      <c r="AD102">
-        <v>7.5</v>
-      </c>
-      <c r="AE102">
-        <v>1.38</v>
-      </c>
-      <c r="AF102">
-        <v>2.8</v>
-      </c>
-      <c r="AG102">
-        <v>2.1</v>
-      </c>
-      <c r="AH102">
-        <v>1.61</v>
-      </c>
-      <c r="AI102">
-        <v>2.05</v>
-      </c>
-      <c r="AJ102">
-        <v>1.66</v>
-      </c>
-      <c r="AK102">
-        <v>1.18</v>
-      </c>
-      <c r="AL102">
-        <v>1.29</v>
-      </c>
-      <c r="AM102">
-        <v>2.05</v>
-      </c>
-      <c r="AN102">
-        <v>1.6</v>
-      </c>
-      <c r="AO102">
-        <v>1</v>
-      </c>
-      <c r="AP102">
-        <v>1.5</v>
-      </c>
-      <c r="AQ102">
-        <v>1.38</v>
-      </c>
-      <c r="AR102">
-        <v>1.53</v>
-      </c>
-      <c r="AS102">
-        <v>0.85</v>
-      </c>
-      <c r="AT102">
-        <v>2.38</v>
-      </c>
-      <c r="AU102">
-        <v>4</v>
-      </c>
-      <c r="AV102">
-        <v>5</v>
-      </c>
-      <c r="AW102">
-        <v>11</v>
-      </c>
-      <c r="AX102">
-        <v>3</v>
-      </c>
-      <c r="AY102">
-        <v>15</v>
-      </c>
-      <c r="AZ102">
-        <v>8</v>
-      </c>
-      <c r="BA102">
-        <v>7</v>
-      </c>
-      <c r="BB102">
-        <v>1</v>
-      </c>
       <c r="BC102">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD102">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="BE102">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="BF102">
-        <v>3.92</v>
+        <v>1.92</v>
       </c>
       <c r="BG102">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="BH102">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="BI102">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BJ102">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="BK102">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BL102">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="BM102">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="BN102">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BO102">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BP102">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="103" spans="1:68">
@@ -22318,7 +22318,7 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>7729637</v>
+        <v>7729636</v>
       </c>
       <c r="C104" t="s">
         <v>68</v>
@@ -22333,10 +22333,10 @@
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -22348,145 +22348,145 @@
         <v>0</v>
       </c>
       <c r="L104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104">
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="P104" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="Q104">
-        <v>3.78</v>
+        <v>4.75</v>
       </c>
       <c r="R104">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="S104">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="T104">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="U104">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="V104">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="W104">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X104">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y104">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Z104">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="AA104">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="AB104">
-        <v>2.61</v>
+        <v>2.07</v>
       </c>
       <c r="AC104">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AD104">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AE104">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AF104">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="AG104">
-        <v>2.89</v>
+        <v>1.98</v>
       </c>
       <c r="AH104">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AI104">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AJ104">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AK104">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AL104">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AM104">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO104">
-        <v>0.5</v>
+        <v>1.83</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>0.88</v>
       </c>
       <c r="AQ104">
-        <v>0.44</v>
+        <v>2.22</v>
       </c>
       <c r="AR104">
-        <v>0.91</v>
+        <v>1.55</v>
       </c>
       <c r="AS104">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AT104">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AU104">
+        <v>8</v>
+      </c>
+      <c r="AV104">
+        <v>6</v>
+      </c>
+      <c r="AW104">
         <v>5</v>
       </c>
-      <c r="AV104">
-        <v>3</v>
-      </c>
-      <c r="AW104">
-        <v>2</v>
-      </c>
       <c r="AX104">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY104">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AZ104">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA104">
         <v>4</v>
       </c>
       <c r="BB104">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC104">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD104">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="BE104">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF104">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="BG104">
         <v>1.34</v>
@@ -22498,10 +22498,10 @@
         <v>1.71</v>
       </c>
       <c r="BJ104">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BK104">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BL104">
         <v>1.68</v>
@@ -22524,7 +22524,7 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>7729636</v>
+        <v>7729637</v>
       </c>
       <c r="C105" t="s">
         <v>68</v>
@@ -22539,10 +22539,10 @@
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H105" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -22554,145 +22554,145 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105">
         <v>1</v>
       </c>
       <c r="O105" t="s">
+        <v>130</v>
+      </c>
+      <c r="P105" t="s">
         <v>89</v>
       </c>
-      <c r="P105" t="s">
-        <v>219</v>
-      </c>
       <c r="Q105">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
       <c r="R105">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="S105">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="T105">
+        <v>1.63</v>
+      </c>
+      <c r="U105">
+        <v>2.19</v>
+      </c>
+      <c r="V105">
+        <v>4</v>
+      </c>
+      <c r="W105">
+        <v>1.22</v>
+      </c>
+      <c r="X105">
+        <v>11.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.02</v>
+      </c>
+      <c r="Z105">
+        <v>3</v>
+      </c>
+      <c r="AA105">
+        <v>2.82</v>
+      </c>
+      <c r="AB105">
+        <v>2.61</v>
+      </c>
+      <c r="AC105">
+        <v>1.08</v>
+      </c>
+      <c r="AD105">
+        <v>5.5</v>
+      </c>
+      <c r="AE105">
+        <v>1.57</v>
+      </c>
+      <c r="AF105">
+        <v>2.15</v>
+      </c>
+      <c r="AG105">
+        <v>2.89</v>
+      </c>
+      <c r="AH105">
+        <v>1.36</v>
+      </c>
+      <c r="AI105">
+        <v>2.21</v>
+      </c>
+      <c r="AJ105">
+        <v>1.56</v>
+      </c>
+      <c r="AK105">
         <v>1.44</v>
       </c>
-      <c r="U105">
-        <v>2.63</v>
-      </c>
-      <c r="V105">
-        <v>3.25</v>
-      </c>
-      <c r="W105">
-        <v>1.33</v>
-      </c>
-      <c r="X105">
-        <v>7.5</v>
-      </c>
-      <c r="Y105">
-        <v>1.07</v>
-      </c>
-      <c r="Z105">
-        <v>3.57</v>
-      </c>
-      <c r="AA105">
-        <v>3.25</v>
-      </c>
-      <c r="AB105">
-        <v>2.07</v>
-      </c>
-      <c r="AC105">
-        <v>1</v>
-      </c>
-      <c r="AD105">
-        <v>9</v>
-      </c>
-      <c r="AE105">
-        <v>1.27</v>
-      </c>
-      <c r="AF105">
-        <v>3.14</v>
-      </c>
-      <c r="AG105">
-        <v>1.98</v>
-      </c>
-      <c r="AH105">
-        <v>1.77</v>
-      </c>
-      <c r="AI105">
-        <v>2</v>
-      </c>
-      <c r="AJ105">
-        <v>1.73</v>
-      </c>
-      <c r="AK105">
-        <v>2.35</v>
-      </c>
       <c r="AL105">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AM105">
+        <v>1.35</v>
+      </c>
+      <c r="AN105">
+        <v>1.6</v>
+      </c>
+      <c r="AO105">
+        <v>0.5</v>
+      </c>
+      <c r="AP105">
+        <v>1.75</v>
+      </c>
+      <c r="AQ105">
+        <v>0.44</v>
+      </c>
+      <c r="AR105">
+        <v>0.91</v>
+      </c>
+      <c r="AS105">
         <v>1.12</v>
       </c>
-      <c r="AN105">
-        <v>1.4</v>
-      </c>
-      <c r="AO105">
-        <v>1.83</v>
-      </c>
-      <c r="AP105">
-        <v>0.88</v>
-      </c>
-      <c r="AQ105">
-        <v>2.22</v>
-      </c>
-      <c r="AR105">
-        <v>1.55</v>
-      </c>
-      <c r="AS105">
-        <v>1.33</v>
-      </c>
       <c r="AT105">
-        <v>2.88</v>
+        <v>2.03</v>
       </c>
       <c r="AU105">
+        <v>5</v>
+      </c>
+      <c r="AV105">
+        <v>3</v>
+      </c>
+      <c r="AW105">
+        <v>2</v>
+      </c>
+      <c r="AX105">
+        <v>5</v>
+      </c>
+      <c r="AY105">
+        <v>7</v>
+      </c>
+      <c r="AZ105">
         <v>8</v>
-      </c>
-      <c r="AV105">
-        <v>6</v>
-      </c>
-      <c r="AW105">
-        <v>5</v>
-      </c>
-      <c r="AX105">
-        <v>9</v>
-      </c>
-      <c r="AY105">
-        <v>13</v>
-      </c>
-      <c r="AZ105">
-        <v>15</v>
       </c>
       <c r="BA105">
         <v>4</v>
       </c>
       <c r="BB105">
+        <v>5</v>
+      </c>
+      <c r="BC105">
         <v>9</v>
       </c>
-      <c r="BC105">
-        <v>13</v>
-      </c>
       <c r="BD105">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="BE105">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="BF105">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="BG105">
         <v>1.34</v>
@@ -22704,10 +22704,10 @@
         <v>1.71</v>
       </c>
       <c r="BJ105">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="BK105">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BL105">
         <v>1.68</v>
@@ -23181,7 +23181,7 @@
         <v>3</v>
       </c>
       <c r="O108" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P108" t="s">
         <v>220</v>
@@ -23554,7 +23554,7 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>7729642</v>
+        <v>7729643</v>
       </c>
       <c r="C110" t="s">
         <v>68</v>
@@ -23569,10 +23569,10 @@
         <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -23596,160 +23596,160 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q110">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R110">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S110">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="T110">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="U110">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="V110">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="W110">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="X110">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="Y110">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z110">
-        <v>5.1</v>
+        <v>2.82</v>
       </c>
       <c r="AA110">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AB110">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="AC110">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AD110">
-        <v>7.5</v>
+        <v>5.88</v>
       </c>
       <c r="AE110">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AF110">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="AH110">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AI110">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AJ110">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AM110">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AN110">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO110">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ110">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AR110">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AS110">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT110">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AU110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV110">
         <v>3</v>
       </c>
       <c r="AW110">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY110">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ110">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA110">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BB110">
         <v>3</v>
       </c>
       <c r="BC110">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD110">
-        <v>3.28</v>
+        <v>2.06</v>
       </c>
       <c r="BE110">
-        <v>8.4</v>
+        <v>6.05</v>
       </c>
       <c r="BF110">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="BG110">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BH110">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="BI110">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="BJ110">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="BK110">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="BL110">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="BM110">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BN110">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO110">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="BP110">
         <v>1.2</v>
@@ -23760,7 +23760,7 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>7729643</v>
+        <v>7729642</v>
       </c>
       <c r="C111" t="s">
         <v>68</v>
@@ -23775,10 +23775,10 @@
         <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H111" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -23802,160 +23802,160 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q111">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R111">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="S111">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="T111">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="U111">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="V111">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="W111">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X111">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="Y111">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z111">
-        <v>2.82</v>
+        <v>5.1</v>
       </c>
       <c r="AA111">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AB111">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC111">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AD111">
-        <v>5.88</v>
+        <v>7.5</v>
       </c>
       <c r="AE111">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AF111">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG111">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="AH111">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AI111">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AJ111">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL111">
+        <v>1.29</v>
+      </c>
+      <c r="AM111">
+        <v>1.18</v>
+      </c>
+      <c r="AN111">
+        <v>1.67</v>
+      </c>
+      <c r="AO111">
+        <v>1.4</v>
+      </c>
+      <c r="AP111">
+        <v>1.33</v>
+      </c>
+      <c r="AQ111">
+        <v>1.75</v>
+      </c>
+      <c r="AR111">
         <v>1.41</v>
       </c>
-      <c r="AM111">
-        <v>1.38</v>
-      </c>
-      <c r="AN111">
-        <v>1.5</v>
-      </c>
-      <c r="AO111">
-        <v>1.17</v>
-      </c>
-      <c r="AP111">
-        <v>1.44</v>
-      </c>
-      <c r="AQ111">
-        <v>1.44</v>
-      </c>
-      <c r="AR111">
-        <v>1.6</v>
-      </c>
       <c r="AS111">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AU111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV111">
         <v>3</v>
       </c>
       <c r="AW111">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY111">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ111">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA111">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB111">
         <v>3</v>
       </c>
       <c r="BC111">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BD111">
-        <v>2.06</v>
+        <v>3.28</v>
       </c>
       <c r="BE111">
-        <v>6.05</v>
+        <v>8.4</v>
       </c>
       <c r="BF111">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="BG111">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BH111">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="BI111">
+        <v>1.58</v>
+      </c>
+      <c r="BJ111">
+        <v>2.12</v>
+      </c>
+      <c r="BK111">
+        <v>2.01</v>
+      </c>
+      <c r="BL111">
         <v>1.68</v>
       </c>
-      <c r="BJ111">
-        <v>2.01</v>
-      </c>
-      <c r="BK111">
-        <v>2.14</v>
-      </c>
-      <c r="BL111">
-        <v>1.57</v>
-      </c>
       <c r="BM111">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BN111">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="BO111">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="BP111">
         <v>1.2</v>
@@ -24584,7 +24584,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7729648</v>
+        <v>7729647</v>
       </c>
       <c r="C115" t="s">
         <v>68</v>
@@ -24599,190 +24599,190 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H115" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M115">
         <v>0</v>
       </c>
       <c r="N115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="P115" t="s">
         <v>89</v>
       </c>
       <c r="Q115">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="R115">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="S115">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="T115">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="U115">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="V115">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="W115">
+        <v>1.22</v>
+      </c>
+      <c r="X115">
+        <v>9</v>
+      </c>
+      <c r="Y115">
+        <v>1.04</v>
+      </c>
+      <c r="Z115">
+        <v>2.28</v>
+      </c>
+      <c r="AA115">
+        <v>2.86</v>
+      </c>
+      <c r="AB115">
+        <v>3.55</v>
+      </c>
+      <c r="AC115">
+        <v>1.13</v>
+      </c>
+      <c r="AD115">
+        <v>5.4</v>
+      </c>
+      <c r="AE115">
+        <v>1.57</v>
+      </c>
+      <c r="AF115">
+        <v>2.15</v>
+      </c>
+      <c r="AG115">
+        <v>2.89</v>
+      </c>
+      <c r="AH115">
+        <v>1.36</v>
+      </c>
+      <c r="AI115">
+        <v>2.38</v>
+      </c>
+      <c r="AJ115">
+        <v>1.53</v>
+      </c>
+      <c r="AK115">
+        <v>1.27</v>
+      </c>
+      <c r="AL115">
         <v>1.39</v>
       </c>
-      <c r="X115">
+      <c r="AM115">
+        <v>1.62</v>
+      </c>
+      <c r="AN115">
+        <v>2</v>
+      </c>
+      <c r="AO115">
+        <v>2</v>
+      </c>
+      <c r="AP115">
+        <v>1.88</v>
+      </c>
+      <c r="AQ115">
+        <v>1.89</v>
+      </c>
+      <c r="AR115">
+        <v>1.12</v>
+      </c>
+      <c r="AS115">
+        <v>1.05</v>
+      </c>
+      <c r="AT115">
+        <v>2.17</v>
+      </c>
+      <c r="AU115">
+        <v>3</v>
+      </c>
+      <c r="AV115">
+        <v>2</v>
+      </c>
+      <c r="AW115">
+        <v>3</v>
+      </c>
+      <c r="AX115">
         <v>7</v>
       </c>
-      <c r="Y115">
-        <v>1.08</v>
-      </c>
-      <c r="Z115">
-        <v>1.29</v>
-      </c>
-      <c r="AA115">
-        <v>4.8</v>
-      </c>
-      <c r="AB115">
-        <v>11</v>
-      </c>
-      <c r="AC115">
-        <v>1.04</v>
-      </c>
-      <c r="AD115">
+      <c r="AY115">
+        <v>6</v>
+      </c>
+      <c r="AZ115">
         <v>9</v>
       </c>
-      <c r="AE115">
-        <v>1.3</v>
-      </c>
-      <c r="AF115">
-        <v>3.35</v>
-      </c>
-      <c r="AG115">
-        <v>1.87</v>
-      </c>
-      <c r="AH115">
-        <v>1.87</v>
-      </c>
-      <c r="AI115">
-        <v>2.6</v>
-      </c>
-      <c r="AJ115">
-        <v>1.43</v>
-      </c>
-      <c r="AK115">
-        <v>1.05</v>
-      </c>
-      <c r="AL115">
-        <v>1.15</v>
-      </c>
-      <c r="AM115">
-        <v>3.6</v>
-      </c>
-      <c r="AN115">
-        <v>2.6</v>
-      </c>
-      <c r="AO115">
-        <v>1.17</v>
-      </c>
-      <c r="AP115">
-        <v>2.75</v>
-      </c>
-      <c r="AQ115">
-        <v>0.89</v>
-      </c>
-      <c r="AR115">
-        <v>1.73</v>
-      </c>
-      <c r="AS115">
-        <v>1.01</v>
-      </c>
-      <c r="AT115">
-        <v>2.74</v>
-      </c>
-      <c r="AU115">
+      <c r="BA115">
         <v>5</v>
-      </c>
-      <c r="AV115">
-        <v>2</v>
-      </c>
-      <c r="AW115">
-        <v>8</v>
-      </c>
-      <c r="AX115">
-        <v>4</v>
-      </c>
-      <c r="AY115">
-        <v>13</v>
-      </c>
-      <c r="AZ115">
-        <v>6</v>
-      </c>
-      <c r="BA115">
-        <v>7</v>
       </c>
       <c r="BB115">
         <v>8</v>
       </c>
       <c r="BC115">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD115">
+        <v>1.6</v>
+      </c>
+      <c r="BE115">
+        <v>6.6</v>
+      </c>
+      <c r="BF115">
+        <v>2.93</v>
+      </c>
+      <c r="BG115">
         <v>1.23</v>
       </c>
-      <c r="BE115">
-        <v>12.25</v>
-      </c>
-      <c r="BF115">
-        <v>4.5</v>
-      </c>
-      <c r="BG115">
-        <v>1.27</v>
-      </c>
       <c r="BH115">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="BI115">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BJ115">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="BK115">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="BL115">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="BM115">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="BN115">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO115">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="BP115">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="116" spans="1:68">
@@ -24790,7 +24790,7 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>7729647</v>
+        <v>7729648</v>
       </c>
       <c r="C116" t="s">
         <v>68</v>
@@ -24805,190 +24805,190 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H116" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M116">
         <v>0</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O116" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="P116" t="s">
         <v>89</v>
       </c>
       <c r="Q116">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="R116">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="S116">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="T116">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="U116">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="V116">
+        <v>2.75</v>
+      </c>
+      <c r="W116">
+        <v>1.39</v>
+      </c>
+      <c r="X116">
+        <v>7</v>
+      </c>
+      <c r="Y116">
+        <v>1.08</v>
+      </c>
+      <c r="Z116">
+        <v>1.29</v>
+      </c>
+      <c r="AA116">
+        <v>4.8</v>
+      </c>
+      <c r="AB116">
+        <v>11</v>
+      </c>
+      <c r="AC116">
+        <v>1.04</v>
+      </c>
+      <c r="AD116">
+        <v>9</v>
+      </c>
+      <c r="AE116">
+        <v>1.3</v>
+      </c>
+      <c r="AF116">
+        <v>3.35</v>
+      </c>
+      <c r="AG116">
+        <v>1.87</v>
+      </c>
+      <c r="AH116">
+        <v>1.87</v>
+      </c>
+      <c r="AI116">
+        <v>2.6</v>
+      </c>
+      <c r="AJ116">
+        <v>1.43</v>
+      </c>
+      <c r="AK116">
+        <v>1.05</v>
+      </c>
+      <c r="AL116">
+        <v>1.15</v>
+      </c>
+      <c r="AM116">
+        <v>3.6</v>
+      </c>
+      <c r="AN116">
+        <v>2.6</v>
+      </c>
+      <c r="AO116">
+        <v>1.17</v>
+      </c>
+      <c r="AP116">
+        <v>2.75</v>
+      </c>
+      <c r="AQ116">
+        <v>0.89</v>
+      </c>
+      <c r="AR116">
+        <v>1.73</v>
+      </c>
+      <c r="AS116">
+        <v>1.01</v>
+      </c>
+      <c r="AT116">
+        <v>2.74</v>
+      </c>
+      <c r="AU116">
+        <v>5</v>
+      </c>
+      <c r="AV116">
+        <v>2</v>
+      </c>
+      <c r="AW116">
+        <v>8</v>
+      </c>
+      <c r="AX116">
         <v>4</v>
       </c>
-      <c r="W116">
-        <v>1.22</v>
-      </c>
-      <c r="X116">
-        <v>9</v>
-      </c>
-      <c r="Y116">
-        <v>1.04</v>
-      </c>
-      <c r="Z116">
-        <v>2.28</v>
-      </c>
-      <c r="AA116">
-        <v>2.86</v>
-      </c>
-      <c r="AB116">
-        <v>3.55</v>
-      </c>
-      <c r="AC116">
-        <v>1.13</v>
-      </c>
-      <c r="AD116">
-        <v>5.4</v>
-      </c>
-      <c r="AE116">
-        <v>1.57</v>
-      </c>
-      <c r="AF116">
-        <v>2.15</v>
-      </c>
-      <c r="AG116">
-        <v>2.89</v>
-      </c>
-      <c r="AH116">
-        <v>1.36</v>
-      </c>
-      <c r="AI116">
-        <v>2.38</v>
-      </c>
-      <c r="AJ116">
-        <v>1.53</v>
-      </c>
-      <c r="AK116">
-        <v>1.27</v>
-      </c>
-      <c r="AL116">
-        <v>1.39</v>
-      </c>
-      <c r="AM116">
-        <v>1.62</v>
-      </c>
-      <c r="AN116">
-        <v>2</v>
-      </c>
-      <c r="AO116">
-        <v>2</v>
-      </c>
-      <c r="AP116">
-        <v>1.88</v>
-      </c>
-      <c r="AQ116">
-        <v>1.89</v>
-      </c>
-      <c r="AR116">
-        <v>1.12</v>
-      </c>
-      <c r="AS116">
-        <v>1.05</v>
-      </c>
-      <c r="AT116">
-        <v>2.17</v>
-      </c>
-      <c r="AU116">
-        <v>3</v>
-      </c>
-      <c r="AV116">
-        <v>2</v>
-      </c>
-      <c r="AW116">
-        <v>3</v>
-      </c>
-      <c r="AX116">
+      <c r="AY116">
+        <v>13</v>
+      </c>
+      <c r="AZ116">
+        <v>6</v>
+      </c>
+      <c r="BA116">
         <v>7</v>
-      </c>
-      <c r="AY116">
-        <v>6</v>
-      </c>
-      <c r="AZ116">
-        <v>9</v>
-      </c>
-      <c r="BA116">
-        <v>5</v>
       </c>
       <c r="BB116">
         <v>8</v>
       </c>
       <c r="BC116">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD116">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="BE116">
-        <v>6.6</v>
+        <v>12.25</v>
       </c>
       <c r="BF116">
-        <v>2.93</v>
+        <v>4.5</v>
       </c>
       <c r="BG116">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BH116">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="BI116">
+        <v>1.51</v>
+      </c>
+      <c r="BJ116">
+        <v>2.26</v>
+      </c>
+      <c r="BK116">
+        <v>1.88</v>
+      </c>
+      <c r="BL116">
+        <v>1.78</v>
+      </c>
+      <c r="BM116">
+        <v>2.43</v>
+      </c>
+      <c r="BN116">
         <v>1.44</v>
       </c>
-      <c r="BJ116">
-        <v>2.43</v>
-      </c>
-      <c r="BK116">
-        <v>1.79</v>
-      </c>
-      <c r="BL116">
-        <v>1.87</v>
-      </c>
-      <c r="BM116">
-        <v>2.28</v>
-      </c>
-      <c r="BN116">
-        <v>1.5</v>
-      </c>
       <c r="BO116">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="BP116">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="117" spans="1:68">
@@ -25408,7 +25408,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7729651</v>
+        <v>7729652</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -25423,190 +25423,190 @@
         <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I119">
         <v>0</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119">
         <v>1</v>
       </c>
       <c r="M119">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O119" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="P119" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="Q119">
+        <v>2.95</v>
+      </c>
+      <c r="R119">
+        <v>1.88</v>
+      </c>
+      <c r="S119">
+        <v>4</v>
+      </c>
+      <c r="T119">
+        <v>1.55</v>
+      </c>
+      <c r="U119">
+        <v>2.25</v>
+      </c>
+      <c r="V119">
+        <v>3.6</v>
+      </c>
+      <c r="W119">
+        <v>1.25</v>
+      </c>
+      <c r="X119">
+        <v>10.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
+        <v>2.3</v>
+      </c>
+      <c r="AA119">
+        <v>2.65</v>
+      </c>
+      <c r="AB119">
+        <v>3.88</v>
+      </c>
+      <c r="AC119">
+        <v>1.12</v>
+      </c>
+      <c r="AD119">
+        <v>5.8</v>
+      </c>
+      <c r="AE119">
+        <v>1.48</v>
+      </c>
+      <c r="AF119">
+        <v>2.37</v>
+      </c>
+      <c r="AG119">
+        <v>2.69</v>
+      </c>
+      <c r="AH119">
+        <v>1.41</v>
+      </c>
+      <c r="AI119">
         <v>2.15</v>
       </c>
-      <c r="R119">
-        <v>2.2</v>
-      </c>
-      <c r="S119">
-        <v>5.25</v>
-      </c>
-      <c r="T119">
-        <v>1.37</v>
-      </c>
-      <c r="U119">
-        <v>2.8</v>
-      </c>
-      <c r="V119">
-        <v>2.7</v>
-      </c>
-      <c r="W119">
-        <v>1.41</v>
-      </c>
-      <c r="X119">
-        <v>6.75</v>
-      </c>
-      <c r="Y119">
-        <v>1.09</v>
-      </c>
-      <c r="Z119">
-        <v>1.73</v>
-      </c>
-      <c r="AA119">
-        <v>3.38</v>
-      </c>
-      <c r="AB119">
-        <v>5.1</v>
-      </c>
-      <c r="AC119">
-        <v>1.05</v>
-      </c>
-      <c r="AD119">
-        <v>8.5</v>
-      </c>
-      <c r="AE119">
+      <c r="AJ119">
+        <v>1.61</v>
+      </c>
+      <c r="AK119">
         <v>1.3</v>
       </c>
-      <c r="AF119">
-        <v>3.35</v>
-      </c>
-      <c r="AG119">
-        <v>1.92</v>
-      </c>
-      <c r="AH119">
-        <v>1.82</v>
-      </c>
-      <c r="AI119">
-        <v>1.9</v>
-      </c>
-      <c r="AJ119">
-        <v>1.78</v>
-      </c>
-      <c r="AK119">
-        <v>1.15</v>
-      </c>
       <c r="AL119">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AM119">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AN119">
-        <v>2.29</v>
+        <v>1.17</v>
       </c>
       <c r="AO119">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="AQ119">
-        <v>1.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR119">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AS119">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AT119">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AU119">
         <v>4</v>
       </c>
       <c r="AV119">
+        <v>6</v>
+      </c>
+      <c r="AW119">
+        <v>3</v>
+      </c>
+      <c r="AX119">
         <v>4</v>
       </c>
-      <c r="AW119">
-        <v>8</v>
-      </c>
-      <c r="AX119">
-        <v>9</v>
-      </c>
       <c r="AY119">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ119">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA119">
         <v>6</v>
       </c>
       <c r="BB119">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC119">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD119">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="BE119">
-        <v>8.9</v>
+        <v>6.25</v>
       </c>
       <c r="BF119">
-        <v>3.44</v>
+        <v>2.35</v>
       </c>
       <c r="BG119">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BH119">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="BI119">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BJ119">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="BK119">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BL119">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BM119">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="BN119">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO119">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="BP119">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="120" spans="1:68">
@@ -25614,7 +25614,7 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>7729652</v>
+        <v>7729651</v>
       </c>
       <c r="C120" t="s">
         <v>68</v>
@@ -25629,190 +25629,190 @@
         <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H120" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I120">
         <v>0</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120">
         <v>1</v>
       </c>
       <c r="M120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N120">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O120" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="Q120">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="R120">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="T120">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="U120">
+        <v>2.8</v>
+      </c>
+      <c r="V120">
+        <v>2.7</v>
+      </c>
+      <c r="W120">
+        <v>1.41</v>
+      </c>
+      <c r="X120">
+        <v>6.75</v>
+      </c>
+      <c r="Y120">
+        <v>1.09</v>
+      </c>
+      <c r="Z120">
+        <v>1.73</v>
+      </c>
+      <c r="AA120">
+        <v>3.38</v>
+      </c>
+      <c r="AB120">
+        <v>5.1</v>
+      </c>
+      <c r="AC120">
+        <v>1.05</v>
+      </c>
+      <c r="AD120">
+        <v>8.5</v>
+      </c>
+      <c r="AE120">
+        <v>1.3</v>
+      </c>
+      <c r="AF120">
+        <v>3.35</v>
+      </c>
+      <c r="AG120">
+        <v>1.92</v>
+      </c>
+      <c r="AH120">
+        <v>1.82</v>
+      </c>
+      <c r="AI120">
+        <v>1.9</v>
+      </c>
+      <c r="AJ120">
+        <v>1.78</v>
+      </c>
+      <c r="AK120">
+        <v>1.15</v>
+      </c>
+      <c r="AL120">
+        <v>1.24</v>
+      </c>
+      <c r="AM120">
         <v>2.25</v>
       </c>
-      <c r="V120">
-        <v>3.6</v>
-      </c>
-      <c r="W120">
-        <v>1.25</v>
-      </c>
-      <c r="X120">
-        <v>10.5</v>
-      </c>
-      <c r="Y120">
-        <v>1.04</v>
-      </c>
-      <c r="Z120">
-        <v>2.3</v>
-      </c>
-      <c r="AA120">
-        <v>2.65</v>
-      </c>
-      <c r="AB120">
-        <v>3.88</v>
-      </c>
-      <c r="AC120">
-        <v>1.12</v>
-      </c>
-      <c r="AD120">
-        <v>5.8</v>
-      </c>
-      <c r="AE120">
-        <v>1.48</v>
-      </c>
-      <c r="AF120">
-        <v>2.37</v>
-      </c>
-      <c r="AG120">
-        <v>2.69</v>
-      </c>
-      <c r="AH120">
-        <v>1.41</v>
-      </c>
-      <c r="AI120">
-        <v>2.15</v>
-      </c>
-      <c r="AJ120">
-        <v>1.61</v>
-      </c>
-      <c r="AK120">
-        <v>1.3</v>
-      </c>
-      <c r="AL120">
-        <v>1.36</v>
-      </c>
-      <c r="AM120">
-        <v>1.6</v>
-      </c>
       <c r="AN120">
-        <v>1.17</v>
+        <v>2.29</v>
       </c>
       <c r="AO120">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
-        <v>1.89</v>
+        <v>1.13</v>
       </c>
       <c r="AR120">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AS120">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AT120">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AU120">
         <v>4</v>
       </c>
       <c r="AV120">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW120">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX120">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY120">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ120">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA120">
         <v>6</v>
       </c>
       <c r="BB120">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC120">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD120">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="BE120">
-        <v>6.25</v>
+        <v>8.9</v>
       </c>
       <c r="BF120">
+        <v>3.44</v>
+      </c>
+      <c r="BG120">
+        <v>1.24</v>
+      </c>
+      <c r="BH120">
+        <v>3.34</v>
+      </c>
+      <c r="BI120">
+        <v>1.47</v>
+      </c>
+      <c r="BJ120">
         <v>2.35</v>
       </c>
-      <c r="BG120">
-        <v>1.28</v>
-      </c>
-      <c r="BH120">
-        <v>3.08</v>
-      </c>
-      <c r="BI120">
-        <v>1.52</v>
-      </c>
-      <c r="BJ120">
-        <v>2.24</v>
-      </c>
       <c r="BK120">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="BL120">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="BM120">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="BN120">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO120">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="BP120">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="121" spans="1:68">
@@ -26438,7 +26438,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7729661</v>
+        <v>7729660</v>
       </c>
       <c r="C124" t="s">
         <v>68</v>
@@ -26453,190 +26453,190 @@
         <v>14</v>
       </c>
       <c r="G124" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I124">
         <v>0</v>
       </c>
       <c r="J124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124">
         <v>1</v>
       </c>
       <c r="O124" t="s">
+        <v>130</v>
+      </c>
+      <c r="P124" t="s">
         <v>89</v>
       </c>
-      <c r="P124" t="s">
-        <v>96</v>
-      </c>
       <c r="Q124">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="R124">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="S124">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="T124">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="U124">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="V124">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="W124">
+        <v>1.2</v>
+      </c>
+      <c r="X124">
+        <v>13</v>
+      </c>
+      <c r="Y124">
+        <v>1.02</v>
+      </c>
+      <c r="Z124">
+        <v>2.37</v>
+      </c>
+      <c r="AA124">
+        <v>2.62</v>
+      </c>
+      <c r="AB124">
+        <v>3.75</v>
+      </c>
+      <c r="AC124">
+        <v>1.16</v>
+      </c>
+      <c r="AD124">
+        <v>4.76</v>
+      </c>
+      <c r="AE124">
+        <v>1.67</v>
+      </c>
+      <c r="AF124">
+        <v>2</v>
+      </c>
+      <c r="AG124">
+        <v>3.15</v>
+      </c>
+      <c r="AH124">
+        <v>1.31</v>
+      </c>
+      <c r="AI124">
+        <v>2.5</v>
+      </c>
+      <c r="AJ124">
+        <v>1.46</v>
+      </c>
+      <c r="AK124">
         <v>1.28</v>
       </c>
-      <c r="X124">
-        <v>9.5</v>
-      </c>
-      <c r="Y124">
-        <v>1.05</v>
-      </c>
-      <c r="Z124">
-        <v>5.1</v>
-      </c>
-      <c r="AA124">
-        <v>3.41</v>
-      </c>
-      <c r="AB124">
-        <v>1.72</v>
-      </c>
-      <c r="AC124">
-        <v>1.04</v>
-      </c>
-      <c r="AD124">
-        <v>6.95</v>
-      </c>
-      <c r="AE124">
-        <v>1.46</v>
-      </c>
-      <c r="AF124">
-        <v>2.6</v>
-      </c>
-      <c r="AG124">
-        <v>2.3</v>
-      </c>
-      <c r="AH124">
-        <v>1.5</v>
-      </c>
-      <c r="AI124">
-        <v>2.3</v>
-      </c>
-      <c r="AJ124">
+      <c r="AL124">
+        <v>1.43</v>
+      </c>
+      <c r="AM124">
         <v>1.55</v>
       </c>
-      <c r="AK124">
-        <v>2.1</v>
-      </c>
-      <c r="AL124">
-        <v>1.29</v>
-      </c>
-      <c r="AM124">
-        <v>1.16</v>
-      </c>
       <c r="AN124">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO124">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AP124">
+        <v>1.11</v>
+      </c>
+      <c r="AQ124">
         <v>0.78</v>
       </c>
-      <c r="AQ124">
-        <v>2.22</v>
-      </c>
       <c r="AR124">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="AS124">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AT124">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="AU124">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV124">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX124">
+        <v>3</v>
+      </c>
+      <c r="AY124">
+        <v>13</v>
+      </c>
+      <c r="AZ124">
         <v>7</v>
       </c>
-      <c r="AY124">
-        <v>2</v>
-      </c>
-      <c r="AZ124">
-        <v>12</v>
-      </c>
       <c r="BA124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB124">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC124">
+        <v>3</v>
+      </c>
+      <c r="BD124">
+        <v>1.73</v>
+      </c>
+      <c r="BE124">
         <v>8</v>
       </c>
-      <c r="BD124">
-        <v>3.42</v>
-      </c>
-      <c r="BE124">
-        <v>8.6</v>
-      </c>
       <c r="BF124">
-        <v>1.41</v>
+        <v>2.42</v>
       </c>
       <c r="BG124">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BH124">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="BI124">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BJ124">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="BK124">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="BL124">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BM124">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="BN124">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BO124">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="BP124">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="125" spans="1:68">
@@ -26644,7 +26644,7 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>7729660</v>
+        <v>7729661</v>
       </c>
       <c r="C125" t="s">
         <v>68</v>
@@ -26659,190 +26659,190 @@
         <v>14</v>
       </c>
       <c r="G125" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I125">
         <v>0</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N125">
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="P125" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="Q125">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="R125">
+        <v>1.98</v>
+      </c>
+      <c r="S125">
+        <v>2.3</v>
+      </c>
+      <c r="T125">
+        <v>1.5</v>
+      </c>
+      <c r="U125">
+        <v>2.4</v>
+      </c>
+      <c r="V125">
+        <v>3.4</v>
+      </c>
+      <c r="W125">
+        <v>1.28</v>
+      </c>
+      <c r="X125">
+        <v>9.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.05</v>
+      </c>
+      <c r="Z125">
+        <v>5.1</v>
+      </c>
+      <c r="AA125">
+        <v>3.41</v>
+      </c>
+      <c r="AB125">
+        <v>1.72</v>
+      </c>
+      <c r="AC125">
+        <v>1.04</v>
+      </c>
+      <c r="AD125">
+        <v>6.95</v>
+      </c>
+      <c r="AE125">
+        <v>1.46</v>
+      </c>
+      <c r="AF125">
+        <v>2.6</v>
+      </c>
+      <c r="AG125">
+        <v>2.3</v>
+      </c>
+      <c r="AH125">
+        <v>1.5</v>
+      </c>
+      <c r="AI125">
+        <v>2.3</v>
+      </c>
+      <c r="AJ125">
+        <v>1.55</v>
+      </c>
+      <c r="AK125">
+        <v>2.1</v>
+      </c>
+      <c r="AL125">
+        <v>1.29</v>
+      </c>
+      <c r="AM125">
+        <v>1.16</v>
+      </c>
+      <c r="AN125">
+        <v>1</v>
+      </c>
+      <c r="AO125">
+        <v>2</v>
+      </c>
+      <c r="AP125">
+        <v>0.78</v>
+      </c>
+      <c r="AQ125">
+        <v>2.22</v>
+      </c>
+      <c r="AR125">
+        <v>1.13</v>
+      </c>
+      <c r="AS125">
+        <v>1.4</v>
+      </c>
+      <c r="AT125">
+        <v>2.53</v>
+      </c>
+      <c r="AU125">
+        <v>0</v>
+      </c>
+      <c r="AV125">
+        <v>5</v>
+      </c>
+      <c r="AW125">
+        <v>2</v>
+      </c>
+      <c r="AX125">
+        <v>7</v>
+      </c>
+      <c r="AY125">
+        <v>2</v>
+      </c>
+      <c r="AZ125">
+        <v>12</v>
+      </c>
+      <c r="BA125">
+        <v>2</v>
+      </c>
+      <c r="BB125">
+        <v>6</v>
+      </c>
+      <c r="BC125">
+        <v>8</v>
+      </c>
+      <c r="BD125">
+        <v>3.42</v>
+      </c>
+      <c r="BE125">
+        <v>8.6</v>
+      </c>
+      <c r="BF125">
+        <v>1.41</v>
+      </c>
+      <c r="BG125">
+        <v>1.28</v>
+      </c>
+      <c r="BH125">
+        <v>3.08</v>
+      </c>
+      <c r="BI125">
+        <v>1.53</v>
+      </c>
+      <c r="BJ125">
+        <v>2.21</v>
+      </c>
+      <c r="BK125">
+        <v>1.92</v>
+      </c>
+      <c r="BL125">
         <v>1.75</v>
       </c>
-      <c r="S125">
-        <v>4.33</v>
-      </c>
-      <c r="T125">
-        <v>1.68</v>
-      </c>
-      <c r="U125">
-        <v>2.05</v>
-      </c>
-      <c r="V125">
-        <v>4.2</v>
-      </c>
-      <c r="W125">
-        <v>1.2</v>
-      </c>
-      <c r="X125">
-        <v>13</v>
-      </c>
-      <c r="Y125">
-        <v>1.02</v>
-      </c>
-      <c r="Z125">
-        <v>2.37</v>
-      </c>
-      <c r="AA125">
-        <v>2.62</v>
-      </c>
-      <c r="AB125">
-        <v>3.75</v>
-      </c>
-      <c r="AC125">
-        <v>1.16</v>
-      </c>
-      <c r="AD125">
-        <v>4.76</v>
-      </c>
-      <c r="AE125">
-        <v>1.67</v>
-      </c>
-      <c r="AF125">
-        <v>2</v>
-      </c>
-      <c r="AG125">
-        <v>3.15</v>
-      </c>
-      <c r="AH125">
-        <v>1.31</v>
-      </c>
-      <c r="AI125">
-        <v>2.5</v>
-      </c>
-      <c r="AJ125">
-        <v>1.46</v>
-      </c>
-      <c r="AK125">
-        <v>1.28</v>
-      </c>
-      <c r="AL125">
-        <v>1.43</v>
-      </c>
-      <c r="AM125">
-        <v>1.55</v>
-      </c>
-      <c r="AN125">
-        <v>1.17</v>
-      </c>
-      <c r="AO125">
-        <v>0.5</v>
-      </c>
-      <c r="AP125">
-        <v>1.11</v>
-      </c>
-      <c r="AQ125">
-        <v>0.78</v>
-      </c>
-      <c r="AR125">
-        <v>0.96</v>
-      </c>
-      <c r="AS125">
-        <v>1.21</v>
-      </c>
-      <c r="AT125">
-        <v>2.17</v>
-      </c>
-      <c r="AU125">
-        <v>6</v>
-      </c>
-      <c r="AV125">
-        <v>2</v>
-      </c>
-      <c r="AW125">
-        <v>4</v>
-      </c>
-      <c r="AX125">
-        <v>3</v>
-      </c>
-      <c r="AY125">
-        <v>13</v>
-      </c>
-      <c r="AZ125">
-        <v>7</v>
-      </c>
-      <c r="BA125">
-        <v>1</v>
-      </c>
-      <c r="BB125">
-        <v>2</v>
-      </c>
-      <c r="BC125">
-        <v>3</v>
-      </c>
-      <c r="BD125">
-        <v>1.73</v>
-      </c>
-      <c r="BE125">
-        <v>8</v>
-      </c>
-      <c r="BF125">
-        <v>2.42</v>
-      </c>
-      <c r="BG125">
-        <v>1.32</v>
-      </c>
-      <c r="BH125">
-        <v>2.88</v>
-      </c>
-      <c r="BI125">
-        <v>1.6</v>
-      </c>
-      <c r="BJ125">
-        <v>2.08</v>
-      </c>
-      <c r="BK125">
-        <v>2.05</v>
-      </c>
-      <c r="BL125">
-        <v>1.65</v>
-      </c>
       <c r="BM125">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="BN125">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO125">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="BP125">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="126" spans="1:68">
@@ -27095,7 +27095,7 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P127" t="s">
         <v>89</v>
@@ -32206,7 +32206,7 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>7729689</v>
+        <v>7729690</v>
       </c>
       <c r="C152" t="s">
         <v>68</v>
@@ -32221,19 +32221,19 @@
         <v>17</v>
       </c>
       <c r="G152" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H152" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152">
         <v>2</v>
@@ -32248,163 +32248,163 @@
         <v>167</v>
       </c>
       <c r="P152" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="Q152">
-        <v>2.95</v>
+        <v>2.21</v>
       </c>
       <c r="R152">
+        <v>2.2</v>
+      </c>
+      <c r="S152">
+        <v>4.6</v>
+      </c>
+      <c r="T152">
+        <v>1.35</v>
+      </c>
+      <c r="U152">
+        <v>2.8</v>
+      </c>
+      <c r="V152">
+        <v>2.85</v>
+      </c>
+      <c r="W152">
+        <v>1.35</v>
+      </c>
+      <c r="X152">
+        <v>7</v>
+      </c>
+      <c r="Y152">
+        <v>1.07</v>
+      </c>
+      <c r="Z152">
+        <v>1.69</v>
+      </c>
+      <c r="AA152">
+        <v>3.45</v>
+      </c>
+      <c r="AB152">
+        <v>5.3</v>
+      </c>
+      <c r="AC152">
+        <v>1.05</v>
+      </c>
+      <c r="AD152">
+        <v>8.9</v>
+      </c>
+      <c r="AE152">
+        <v>1.32</v>
+      </c>
+      <c r="AF152">
+        <v>3.4</v>
+      </c>
+      <c r="AG152">
+        <v>1.98</v>
+      </c>
+      <c r="AH152">
         <v>1.77</v>
       </c>
-      <c r="S152">
-        <v>4.3</v>
-      </c>
-      <c r="T152">
-        <v>1.57</v>
-      </c>
-      <c r="U152">
-        <v>2.25</v>
-      </c>
-      <c r="V152">
-        <v>3.5</v>
-      </c>
-      <c r="W152">
+      <c r="AI152">
+        <v>1.95</v>
+      </c>
+      <c r="AJ152">
+        <v>1.85</v>
+      </c>
+      <c r="AK152">
+        <v>1.17</v>
+      </c>
+      <c r="AL152">
+        <v>1.26</v>
+      </c>
+      <c r="AM152">
+        <v>2.23</v>
+      </c>
+      <c r="AN152">
+        <v>2.71</v>
+      </c>
+      <c r="AO152">
+        <v>1.5</v>
+      </c>
+      <c r="AP152">
+        <v>2.75</v>
+      </c>
+      <c r="AQ152">
+        <v>1.33</v>
+      </c>
+      <c r="AR152">
+        <v>1.75</v>
+      </c>
+      <c r="AS152">
+        <v>1.43</v>
+      </c>
+      <c r="AT152">
+        <v>3.18</v>
+      </c>
+      <c r="AU152">
+        <v>5</v>
+      </c>
+      <c r="AV152">
+        <v>5</v>
+      </c>
+      <c r="AW152">
+        <v>7</v>
+      </c>
+      <c r="AX152">
+        <v>8</v>
+      </c>
+      <c r="AY152">
+        <v>12</v>
+      </c>
+      <c r="AZ152">
+        <v>13</v>
+      </c>
+      <c r="BA152">
+        <v>6</v>
+      </c>
+      <c r="BB152">
+        <v>5</v>
+      </c>
+      <c r="BC152">
+        <v>11</v>
+      </c>
+      <c r="BD152">
+        <v>1.51</v>
+      </c>
+      <c r="BE152">
+        <v>8.5</v>
+      </c>
+      <c r="BF152">
+        <v>2.96</v>
+      </c>
+      <c r="BG152">
         <v>1.25</v>
       </c>
-      <c r="X152">
-        <v>10</v>
-      </c>
-      <c r="Y152">
-        <v>1.02</v>
-      </c>
-      <c r="Z152">
-        <v>2.27</v>
-      </c>
-      <c r="AA152">
-        <v>2.66</v>
-      </c>
-      <c r="AB152">
-        <v>3.93</v>
-      </c>
-      <c r="AC152">
-        <v>1.04</v>
-      </c>
-      <c r="AD152">
-        <v>5.8</v>
-      </c>
-      <c r="AE152">
-        <v>1.5</v>
-      </c>
-      <c r="AF152">
-        <v>2.3</v>
-      </c>
-      <c r="AG152">
-        <v>2.65</v>
-      </c>
-      <c r="AH152">
-        <v>1.42</v>
-      </c>
-      <c r="AI152">
-        <v>2.16</v>
-      </c>
-      <c r="AJ152">
-        <v>1.68</v>
-      </c>
-      <c r="AK152">
+      <c r="BH152">
+        <v>3.28</v>
+      </c>
+      <c r="BI152">
+        <v>1.48</v>
+      </c>
+      <c r="BJ152">
+        <v>2.33</v>
+      </c>
+      <c r="BK152">
+        <v>1.84</v>
+      </c>
+      <c r="BL152">
+        <v>1.82</v>
+      </c>
+      <c r="BM152">
+        <v>2.35</v>
+      </c>
+      <c r="BN152">
         <v>1.47</v>
       </c>
-      <c r="AL152">
-        <v>1.37</v>
-      </c>
-      <c r="AM152">
-        <v>1.58</v>
-      </c>
-      <c r="AN152">
-        <v>1.25</v>
-      </c>
-      <c r="AO152">
-        <v>1</v>
-      </c>
-      <c r="AP152">
-        <v>1.44</v>
-      </c>
-      <c r="AQ152">
-        <v>0.88</v>
-      </c>
-      <c r="AR152">
-        <v>1.59</v>
-      </c>
-      <c r="AS152">
-        <v>1.07</v>
-      </c>
-      <c r="AT152">
-        <v>2.66</v>
-      </c>
-      <c r="AU152">
-        <v>6</v>
-      </c>
-      <c r="AV152">
-        <v>3</v>
-      </c>
-      <c r="AW152">
-        <v>10</v>
-      </c>
-      <c r="AX152">
-        <v>3</v>
-      </c>
-      <c r="AY152">
-        <v>16</v>
-      </c>
-      <c r="AZ152">
-        <v>6</v>
-      </c>
-      <c r="BA152">
-        <v>5</v>
-      </c>
-      <c r="BB152">
-        <v>3</v>
-      </c>
-      <c r="BC152">
-        <v>8</v>
-      </c>
-      <c r="BD152">
-        <v>1.62</v>
-      </c>
-      <c r="BE152">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF152">
-        <v>2.65</v>
-      </c>
-      <c r="BG152">
-        <v>1.27</v>
-      </c>
-      <c r="BH152">
-        <v>3.14</v>
-      </c>
-      <c r="BI152">
-        <v>1.5</v>
-      </c>
-      <c r="BJ152">
-        <v>2.28</v>
-      </c>
-      <c r="BK152">
-        <v>1.88</v>
-      </c>
-      <c r="BL152">
-        <v>1.78</v>
-      </c>
-      <c r="BM152">
-        <v>2.43</v>
-      </c>
-      <c r="BN152">
-        <v>1.44</v>
-      </c>
       <c r="BO152">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="BP152">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="153" spans="1:68">
@@ -32618,7 +32618,7 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>7729690</v>
+        <v>7729689</v>
       </c>
       <c r="C154" t="s">
         <v>68</v>
@@ -32633,19 +32633,19 @@
         <v>17</v>
       </c>
       <c r="G154" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H154" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154">
         <v>0</v>
       </c>
       <c r="K154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154">
         <v>2</v>
@@ -32660,163 +32660,163 @@
         <v>169</v>
       </c>
       <c r="P154" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="Q154">
-        <v>2.21</v>
+        <v>2.95</v>
       </c>
       <c r="R154">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="S154">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="T154">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="U154">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V154">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="W154">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X154">
+        <v>10</v>
+      </c>
+      <c r="Y154">
+        <v>1.02</v>
+      </c>
+      <c r="Z154">
+        <v>2.27</v>
+      </c>
+      <c r="AA154">
+        <v>2.66</v>
+      </c>
+      <c r="AB154">
+        <v>3.93</v>
+      </c>
+      <c r="AC154">
+        <v>1.04</v>
+      </c>
+      <c r="AD154">
+        <v>5.8</v>
+      </c>
+      <c r="AE154">
+        <v>1.5</v>
+      </c>
+      <c r="AF154">
+        <v>2.3</v>
+      </c>
+      <c r="AG154">
+        <v>2.65</v>
+      </c>
+      <c r="AH154">
+        <v>1.42</v>
+      </c>
+      <c r="AI154">
+        <v>2.16</v>
+      </c>
+      <c r="AJ154">
+        <v>1.68</v>
+      </c>
+      <c r="AK154">
+        <v>1.47</v>
+      </c>
+      <c r="AL154">
+        <v>1.37</v>
+      </c>
+      <c r="AM154">
+        <v>1.58</v>
+      </c>
+      <c r="AN154">
+        <v>1.25</v>
+      </c>
+      <c r="AO154">
+        <v>1</v>
+      </c>
+      <c r="AP154">
+        <v>1.44</v>
+      </c>
+      <c r="AQ154">
+        <v>0.88</v>
+      </c>
+      <c r="AR154">
+        <v>1.59</v>
+      </c>
+      <c r="AS154">
+        <v>1.07</v>
+      </c>
+      <c r="AT154">
+        <v>2.66</v>
+      </c>
+      <c r="AU154">
+        <v>6</v>
+      </c>
+      <c r="AV154">
+        <v>3</v>
+      </c>
+      <c r="AW154">
+        <v>10</v>
+      </c>
+      <c r="AX154">
+        <v>3</v>
+      </c>
+      <c r="AY154">
+        <v>16</v>
+      </c>
+      <c r="AZ154">
+        <v>6</v>
+      </c>
+      <c r="BA154">
+        <v>5</v>
+      </c>
+      <c r="BB154">
+        <v>2</v>
+      </c>
+      <c r="BC154">
         <v>7</v>
       </c>
-      <c r="Y154">
-        <v>1.07</v>
-      </c>
-      <c r="Z154">
-        <v>1.69</v>
-      </c>
-      <c r="AA154">
-        <v>3.45</v>
-      </c>
-      <c r="AB154">
-        <v>5.3</v>
-      </c>
-      <c r="AC154">
-        <v>1.05</v>
-      </c>
-      <c r="AD154">
-        <v>8.9</v>
-      </c>
-      <c r="AE154">
-        <v>1.32</v>
-      </c>
-      <c r="AF154">
-        <v>3.4</v>
-      </c>
-      <c r="AG154">
-        <v>1.98</v>
-      </c>
-      <c r="AH154">
-        <v>1.77</v>
-      </c>
-      <c r="AI154">
-        <v>1.95</v>
-      </c>
-      <c r="AJ154">
-        <v>1.85</v>
-      </c>
-      <c r="AK154">
-        <v>1.17</v>
-      </c>
-      <c r="AL154">
-        <v>1.26</v>
-      </c>
-      <c r="AM154">
-        <v>2.23</v>
-      </c>
-      <c r="AN154">
-        <v>2.71</v>
-      </c>
-      <c r="AO154">
+      <c r="BD154">
+        <v>1.62</v>
+      </c>
+      <c r="BE154">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF154">
+        <v>2.65</v>
+      </c>
+      <c r="BG154">
+        <v>1.27</v>
+      </c>
+      <c r="BH154">
+        <v>3.14</v>
+      </c>
+      <c r="BI154">
         <v>1.5</v>
       </c>
-      <c r="AP154">
-        <v>2.75</v>
-      </c>
-      <c r="AQ154">
-        <v>1.33</v>
-      </c>
-      <c r="AR154">
-        <v>1.75</v>
-      </c>
-      <c r="AS154">
-        <v>1.43</v>
-      </c>
-      <c r="AT154">
-        <v>3.18</v>
-      </c>
-      <c r="AU154">
-        <v>5</v>
-      </c>
-      <c r="AV154">
-        <v>5</v>
-      </c>
-      <c r="AW154">
-        <v>7</v>
-      </c>
-      <c r="AX154">
-        <v>8</v>
-      </c>
-      <c r="AY154">
-        <v>12</v>
-      </c>
-      <c r="AZ154">
-        <v>13</v>
-      </c>
-      <c r="BA154">
-        <v>6</v>
-      </c>
-      <c r="BB154">
-        <v>5</v>
-      </c>
-      <c r="BC154">
-        <v>11</v>
-      </c>
-      <c r="BD154">
-        <v>1.51</v>
-      </c>
-      <c r="BE154">
-        <v>8.5</v>
-      </c>
-      <c r="BF154">
-        <v>2.96</v>
-      </c>
-      <c r="BG154">
+      <c r="BJ154">
+        <v>2.28</v>
+      </c>
+      <c r="BK154">
+        <v>1.88</v>
+      </c>
+      <c r="BL154">
+        <v>1.78</v>
+      </c>
+      <c r="BM154">
+        <v>2.43</v>
+      </c>
+      <c r="BN154">
+        <v>1.44</v>
+      </c>
+      <c r="BO154">
+        <v>3.28</v>
+      </c>
+      <c r="BP154">
         <v>1.25</v>
-      </c>
-      <c r="BH154">
-        <v>3.28</v>
-      </c>
-      <c r="BI154">
-        <v>1.48</v>
-      </c>
-      <c r="BJ154">
-        <v>2.33</v>
-      </c>
-      <c r="BK154">
-        <v>1.84</v>
-      </c>
-      <c r="BL154">
-        <v>1.82</v>
-      </c>
-      <c r="BM154">
-        <v>2.35</v>
-      </c>
-      <c r="BN154">
-        <v>1.47</v>
-      </c>
-      <c r="BO154">
-        <v>3.2</v>
-      </c>
-      <c r="BP154">
-        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,15 @@
     <t>['46', '90+7']</t>
   </si>
   <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['61', '68']</t>
+  </si>
+  <si>
+    <t>['66', '80']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -731,6 +740,9 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['27', '30']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1348,7 +1360,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1426,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ2">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1554,7 +1566,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1838,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4">
         <v>1.25</v>
@@ -2044,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>0.44</v>
@@ -2172,7 +2184,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2253,7 +2265,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2378,7 +2390,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2459,7 +2471,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ7">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2584,7 +2596,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2996,7 +3008,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3408,7 +3420,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3614,7 +3626,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3820,7 +3832,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4026,7 +4038,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4232,7 +4244,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -5056,7 +5068,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5262,7 +5274,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5549,7 +5561,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5674,7 +5686,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>3.5</v>
@@ -5752,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23">
         <v>0.88</v>
@@ -5961,7 +5973,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ24">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6086,7 +6098,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6373,7 +6385,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ26">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6576,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27">
         <v>1.33</v>
@@ -6782,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1.25</v>
@@ -7116,7 +7128,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -8146,7 +8158,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8558,7 +8570,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8845,7 +8857,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.3</v>
@@ -9048,7 +9060,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ39">
         <v>1.67</v>
@@ -9176,7 +9188,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9382,7 +9394,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9460,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.89</v>
@@ -9666,7 +9678,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
         <v>0.44</v>
@@ -9794,7 +9806,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10081,7 +10093,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -10206,7 +10218,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10618,7 +10630,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -11030,7 +11042,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11442,7 +11454,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11648,7 +11660,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -12060,7 +12072,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12344,7 +12356,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ55">
         <v>1.63</v>
@@ -12553,7 +12565,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12678,7 +12690,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12756,7 +12768,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ57">
         <v>2.22</v>
@@ -13090,7 +13102,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13171,7 +13183,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -13377,7 +13389,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.01</v>
@@ -13502,7 +13514,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13786,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>0.33</v>
@@ -14201,7 +14213,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ64">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14532,7 +14544,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14944,7 +14956,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15768,7 +15780,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16180,7 +16192,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16258,7 +16270,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
         <v>1.89</v>
@@ -16386,7 +16398,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16592,7 +16604,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16879,7 +16891,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR77">
         <v>1.1</v>
@@ -17004,7 +17016,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17210,7 +17222,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17291,7 +17303,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17416,7 +17428,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17906,7 +17918,7 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
         <v>1.75</v>
@@ -18446,7 +18458,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18652,7 +18664,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18858,7 +18870,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19142,7 +19154,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88">
         <v>0.38</v>
@@ -19270,7 +19282,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19476,7 +19488,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19557,7 +19569,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ90">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.09</v>
@@ -19682,7 +19694,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19888,7 +19900,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -20094,7 +20106,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20172,7 +20184,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ93">
         <v>0.89</v>
@@ -20918,7 +20930,7 @@
         <v>137</v>
       </c>
       <c r="P97" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21205,7 +21217,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR98">
         <v>1.73</v>
@@ -21330,7 +21342,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21411,7 +21423,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21536,7 +21548,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21614,7 +21626,7 @@
         <v>1.8</v>
       </c>
       <c r="AP100">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>2.25</v>
@@ -21742,7 +21754,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21948,7 +21960,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22235,7 +22247,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ103">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>2.01</v>
@@ -22438,7 +22450,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ104">
         <v>0.44</v>
@@ -22566,7 +22578,7 @@
         <v>89</v>
       </c>
       <c r="P105" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23184,7 +23196,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23596,7 +23608,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -23802,7 +23814,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -23883,7 +23895,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ111">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR111">
         <v>1.6</v>
@@ -24498,7 +24510,7 @@
         <v>0.17</v>
       </c>
       <c r="AP114">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ114">
         <v>0.33</v>
@@ -25116,7 +25128,7 @@
         <v>2.4</v>
       </c>
       <c r="AP117">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ117">
         <v>1.63</v>
@@ -25244,7 +25256,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25325,7 +25337,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR118">
         <v>0.78</v>
@@ -25531,7 +25543,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25656,7 +25668,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -25940,7 +25952,7 @@
         <v>1.33</v>
       </c>
       <c r="AP121">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ121">
         <v>1.38</v>
@@ -26068,7 +26080,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26274,7 +26286,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -26764,7 +26776,7 @@
         <v>2</v>
       </c>
       <c r="AP125">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ125">
         <v>2.22</v>
@@ -27591,7 +27603,7 @@
         <v>1</v>
       </c>
       <c r="AQ129">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR129">
         <v>0.96</v>
@@ -27716,7 +27728,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27922,7 +27934,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28003,7 +28015,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28412,7 +28424,7 @@
         <v>1.71</v>
       </c>
       <c r="AP133">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ133">
         <v>1.33</v>
@@ -28540,7 +28552,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29158,7 +29170,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29236,7 +29248,7 @@
         <v>0.43</v>
       </c>
       <c r="AP137">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
         <v>0.78</v>
@@ -29364,7 +29376,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29442,7 +29454,7 @@
         <v>2.14</v>
       </c>
       <c r="AP138">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ138">
         <v>2.25</v>
@@ -29570,7 +29582,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29776,7 +29788,7 @@
         <v>159</v>
       </c>
       <c r="P140" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q140">
         <v>4.1</v>
@@ -29982,7 +29994,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q141">
         <v>3.7</v>
@@ -30188,7 +30200,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30600,7 +30612,7 @@
         <v>162</v>
       </c>
       <c r="P144" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q144">
         <v>2.55</v>
@@ -30681,7 +30693,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR144">
         <v>1.67</v>
@@ -30806,7 +30818,7 @@
         <v>163</v>
       </c>
       <c r="P145" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q145">
         <v>6.6</v>
@@ -31424,7 +31436,7 @@
         <v>165</v>
       </c>
       <c r="P148" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q148">
         <v>2.85</v>
@@ -31630,7 +31642,7 @@
         <v>89</v>
       </c>
       <c r="P149" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q149">
         <v>5.5</v>
@@ -31836,7 +31848,7 @@
         <v>166</v>
       </c>
       <c r="P150" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q150">
         <v>2.55</v>
@@ -32123,7 +32135,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ151">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR151">
         <v>1.09</v>
@@ -32454,7 +32466,7 @@
         <v>168</v>
       </c>
       <c r="P153" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q153">
         <v>2.21</v>
@@ -32817,6 +32829,624 @@
       </c>
       <c r="BP154">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7847611</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45727.6875</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155" t="s">
+        <v>70</v>
+      </c>
+      <c r="H155" t="s">
+        <v>83</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155" t="s">
+        <v>170</v>
+      </c>
+      <c r="P155" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q155">
+        <v>4.31</v>
+      </c>
+      <c r="R155">
+        <v>1.9</v>
+      </c>
+      <c r="S155">
+        <v>3.21</v>
+      </c>
+      <c r="T155">
+        <v>1.61</v>
+      </c>
+      <c r="U155">
+        <v>2.28</v>
+      </c>
+      <c r="V155">
+        <v>3.65</v>
+      </c>
+      <c r="W155">
+        <v>1.22</v>
+      </c>
+      <c r="X155">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y155">
+        <v>1</v>
+      </c>
+      <c r="Z155">
+        <v>3.5</v>
+      </c>
+      <c r="AA155">
+        <v>2.69</v>
+      </c>
+      <c r="AB155">
+        <v>2.43</v>
+      </c>
+      <c r="AC155">
+        <v>1.1</v>
+      </c>
+      <c r="AD155">
+        <v>5.05</v>
+      </c>
+      <c r="AE155">
+        <v>1.5</v>
+      </c>
+      <c r="AF155">
+        <v>2.3</v>
+      </c>
+      <c r="AG155">
+        <v>2.6</v>
+      </c>
+      <c r="AH155">
+        <v>1.44</v>
+      </c>
+      <c r="AI155">
+        <v>2.14</v>
+      </c>
+      <c r="AJ155">
+        <v>1.6</v>
+      </c>
+      <c r="AK155">
+        <v>1.5</v>
+      </c>
+      <c r="AL155">
+        <v>1.41</v>
+      </c>
+      <c r="AM155">
+        <v>1.26</v>
+      </c>
+      <c r="AN155">
+        <v>1.29</v>
+      </c>
+      <c r="AO155">
+        <v>1.29</v>
+      </c>
+      <c r="AP155">
+        <v>1.22</v>
+      </c>
+      <c r="AQ155">
+        <v>1.39</v>
+      </c>
+      <c r="AR155">
+        <v>1.02</v>
+      </c>
+      <c r="AS155">
+        <v>1.49</v>
+      </c>
+      <c r="AT155">
+        <v>2.51</v>
+      </c>
+      <c r="AU155">
+        <v>4</v>
+      </c>
+      <c r="AV155">
+        <v>4</v>
+      </c>
+      <c r="AW155">
+        <v>8</v>
+      </c>
+      <c r="AX155">
+        <v>6</v>
+      </c>
+      <c r="AY155">
+        <v>12</v>
+      </c>
+      <c r="AZ155">
+        <v>10</v>
+      </c>
+      <c r="BA155">
+        <v>5</v>
+      </c>
+      <c r="BB155">
+        <v>4</v>
+      </c>
+      <c r="BC155">
+        <v>9</v>
+      </c>
+      <c r="BD155">
+        <v>2.07</v>
+      </c>
+      <c r="BE155">
+        <v>6.15</v>
+      </c>
+      <c r="BF155">
+        <v>2.12</v>
+      </c>
+      <c r="BG155">
+        <v>1.28</v>
+      </c>
+      <c r="BH155">
+        <v>3.08</v>
+      </c>
+      <c r="BI155">
+        <v>1.52</v>
+      </c>
+      <c r="BJ155">
+        <v>2.24</v>
+      </c>
+      <c r="BK155">
+        <v>1.92</v>
+      </c>
+      <c r="BL155">
+        <v>1.75</v>
+      </c>
+      <c r="BM155">
+        <v>2.49</v>
+      </c>
+      <c r="BN155">
+        <v>1.42</v>
+      </c>
+      <c r="BO155">
+        <v>3.42</v>
+      </c>
+      <c r="BP155">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7847615</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45727.6875</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156" t="s">
+        <v>73</v>
+      </c>
+      <c r="H156" t="s">
+        <v>82</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>2</v>
+      </c>
+      <c r="O156" t="s">
+        <v>171</v>
+      </c>
+      <c r="P156" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q156">
+        <v>3.51</v>
+      </c>
+      <c r="R156">
+        <v>1.83</v>
+      </c>
+      <c r="S156">
+        <v>4.15</v>
+      </c>
+      <c r="T156">
+        <v>1.67</v>
+      </c>
+      <c r="U156">
+        <v>2.17</v>
+      </c>
+      <c r="V156">
+        <v>4</v>
+      </c>
+      <c r="W156">
+        <v>1.19</v>
+      </c>
+      <c r="X156">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y156">
+        <v>1.02</v>
+      </c>
+      <c r="Z156">
+        <v>2.62</v>
+      </c>
+      <c r="AA156">
+        <v>2.69</v>
+      </c>
+      <c r="AB156">
+        <v>3.21</v>
+      </c>
+      <c r="AC156">
+        <v>1.09</v>
+      </c>
+      <c r="AD156">
+        <v>5.3</v>
+      </c>
+      <c r="AE156">
+        <v>1.63</v>
+      </c>
+      <c r="AF156">
+        <v>2.15</v>
+      </c>
+      <c r="AG156">
+        <v>2.81</v>
+      </c>
+      <c r="AH156">
+        <v>1.33</v>
+      </c>
+      <c r="AI156">
+        <v>2.28</v>
+      </c>
+      <c r="AJ156">
+        <v>1.53</v>
+      </c>
+      <c r="AK156">
+        <v>1.33</v>
+      </c>
+      <c r="AL156">
+        <v>1.36</v>
+      </c>
+      <c r="AM156">
+        <v>1.47</v>
+      </c>
+      <c r="AN156">
+        <v>0.59</v>
+      </c>
+      <c r="AO156">
+        <v>1.18</v>
+      </c>
+      <c r="AP156">
+        <v>0.72</v>
+      </c>
+      <c r="AQ156">
+        <v>1.11</v>
+      </c>
+      <c r="AR156">
+        <v>1.1</v>
+      </c>
+      <c r="AS156">
+        <v>1.32</v>
+      </c>
+      <c r="AT156">
+        <v>2.42</v>
+      </c>
+      <c r="AU156">
+        <v>6</v>
+      </c>
+      <c r="AV156">
+        <v>7</v>
+      </c>
+      <c r="AW156">
+        <v>7</v>
+      </c>
+      <c r="AX156">
+        <v>6</v>
+      </c>
+      <c r="AY156">
+        <v>13</v>
+      </c>
+      <c r="AZ156">
+        <v>13</v>
+      </c>
+      <c r="BA156">
+        <v>4</v>
+      </c>
+      <c r="BB156">
+        <v>7</v>
+      </c>
+      <c r="BC156">
+        <v>11</v>
+      </c>
+      <c r="BD156">
+        <v>1.79</v>
+      </c>
+      <c r="BE156">
+        <v>7.7</v>
+      </c>
+      <c r="BF156">
+        <v>2.33</v>
+      </c>
+      <c r="BG156">
+        <v>1.38</v>
+      </c>
+      <c r="BH156">
+        <v>2.62</v>
+      </c>
+      <c r="BI156">
+        <v>1.71</v>
+      </c>
+      <c r="BJ156">
+        <v>1.97</v>
+      </c>
+      <c r="BK156">
+        <v>2.17</v>
+      </c>
+      <c r="BL156">
+        <v>1.55</v>
+      </c>
+      <c r="BM156">
+        <v>2.92</v>
+      </c>
+      <c r="BN156">
+        <v>1.31</v>
+      </c>
+      <c r="BO156">
+        <v>3.6</v>
+      </c>
+      <c r="BP156">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7847616</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45727.6875</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157" t="s">
+        <v>72</v>
+      </c>
+      <c r="H157" t="s">
+        <v>79</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>2</v>
+      </c>
+      <c r="O157" t="s">
+        <v>172</v>
+      </c>
+      <c r="P157" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q157">
+        <v>3.87</v>
+      </c>
+      <c r="R157">
+        <v>1.83</v>
+      </c>
+      <c r="S157">
+        <v>3.74</v>
+      </c>
+      <c r="T157">
+        <v>1.66</v>
+      </c>
+      <c r="U157">
+        <v>2.17</v>
+      </c>
+      <c r="V157">
+        <v>4</v>
+      </c>
+      <c r="W157">
+        <v>1.19</v>
+      </c>
+      <c r="X157">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y157">
+        <v>1.02</v>
+      </c>
+      <c r="Z157">
+        <v>3.07</v>
+      </c>
+      <c r="AA157">
+        <v>2.69</v>
+      </c>
+      <c r="AB157">
+        <v>2.68</v>
+      </c>
+      <c r="AC157">
+        <v>1.12</v>
+      </c>
+      <c r="AD157">
+        <v>5.25</v>
+      </c>
+      <c r="AE157">
+        <v>1.63</v>
+      </c>
+      <c r="AF157">
+        <v>2.15</v>
+      </c>
+      <c r="AG157">
+        <v>2.9</v>
+      </c>
+      <c r="AH157">
+        <v>1.36</v>
+      </c>
+      <c r="AI157">
+        <v>2.25</v>
+      </c>
+      <c r="AJ157">
+        <v>1.57</v>
+      </c>
+      <c r="AK157">
+        <v>1.4</v>
+      </c>
+      <c r="AL157">
+        <v>1.37</v>
+      </c>
+      <c r="AM157">
+        <v>1.38</v>
+      </c>
+      <c r="AN157">
+        <v>1</v>
+      </c>
+      <c r="AO157">
+        <v>1.06</v>
+      </c>
+      <c r="AP157">
+        <v>1.11</v>
+      </c>
+      <c r="AQ157">
+        <v>1</v>
+      </c>
+      <c r="AR157">
+        <v>1.17</v>
+      </c>
+      <c r="AS157">
+        <v>1.08</v>
+      </c>
+      <c r="AT157">
+        <v>2.25</v>
+      </c>
+      <c r="AU157">
+        <v>3</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>6</v>
+      </c>
+      <c r="AX157">
+        <v>2</v>
+      </c>
+      <c r="AY157">
+        <v>9</v>
+      </c>
+      <c r="AZ157">
+        <v>6</v>
+      </c>
+      <c r="BA157">
+        <v>11</v>
+      </c>
+      <c r="BB157">
+        <v>3</v>
+      </c>
+      <c r="BC157">
+        <v>14</v>
+      </c>
+      <c r="BD157">
+        <v>2.32</v>
+      </c>
+      <c r="BE157">
+        <v>6</v>
+      </c>
+      <c r="BF157">
+        <v>1.92</v>
+      </c>
+      <c r="BG157">
+        <v>1.38</v>
+      </c>
+      <c r="BH157">
+        <v>2.62</v>
+      </c>
+      <c r="BI157">
+        <v>1.71</v>
+      </c>
+      <c r="BJ157">
+        <v>1.97</v>
+      </c>
+      <c r="BK157">
+        <v>2.17</v>
+      </c>
+      <c r="BL157">
+        <v>1.55</v>
+      </c>
+      <c r="BM157">
+        <v>2.92</v>
+      </c>
+      <c r="BN157">
+        <v>1.31</v>
+      </c>
+      <c r="BO157">
+        <v>3.85</v>
+      </c>
+      <c r="BP157">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>['70', '89']</t>
+  </si>
+  <si>
+    <t>['69', '90+2']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -1110,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1366,7 +1369,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1572,7 +1575,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -2190,7 +2193,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2271,7 +2274,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2396,7 +2399,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2602,7 +2605,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2886,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ9">
         <v>0.88</v>
@@ -3014,7 +3017,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -3220,7 +3223,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3632,7 +3635,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3838,7 +3841,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -3919,7 +3922,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ14">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4044,7 +4047,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4250,7 +4253,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4328,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16">
         <v>2.22</v>
@@ -5074,7 +5077,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5280,7 +5283,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5567,7 +5570,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ22">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5898,7 +5901,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -6104,7 +6107,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6388,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -7134,7 +7137,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7215,7 +7218,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -8036,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ34">
         <v>0.6</v>
@@ -8370,7 +8373,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8576,7 +8579,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -9194,7 +9197,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9606,7 +9609,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9812,7 +9815,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10099,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -10224,7 +10227,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10302,7 +10305,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ45">
         <v>2.22</v>
@@ -10636,7 +10639,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10923,7 +10926,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ48">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR48">
         <v>0.85</v>
@@ -11048,7 +11051,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11126,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49">
         <v>0.89</v>
@@ -11460,7 +11463,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q51">
         <v>2.38</v>
@@ -11666,7 +11669,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11872,7 +11875,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12571,7 +12574,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12774,7 +12777,7 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ57">
         <v>2.25</v>
@@ -12902,7 +12905,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13108,7 +13111,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13520,7 +13523,7 @@
         <v>105</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14550,7 +14553,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14962,7 +14965,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15249,7 +15252,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ69">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR69">
         <v>1.78</v>
@@ -15786,7 +15789,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -16198,7 +16201,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16404,7 +16407,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16610,7 +16613,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16688,7 +16691,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ76">
         <v>1.63</v>
@@ -16894,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ77">
         <v>1.3</v>
@@ -17022,7 +17025,7 @@
         <v>127</v>
       </c>
       <c r="P78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>6</v>
@@ -17228,7 +17231,7 @@
         <v>128</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>2.3</v>
@@ -17309,7 +17312,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR79">
         <v>1.49</v>
@@ -17434,7 +17437,7 @@
         <v>89</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -18464,7 +18467,7 @@
         <v>89</v>
       </c>
       <c r="P85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18670,7 +18673,7 @@
         <v>131</v>
       </c>
       <c r="P86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18876,7 +18879,7 @@
         <v>132</v>
       </c>
       <c r="P87" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.05</v>
@@ -19163,7 +19166,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ88">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19288,7 +19291,7 @@
         <v>133</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -19494,7 +19497,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19700,7 +19703,7 @@
         <v>134</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19906,7 +19909,7 @@
         <v>90</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>3.25</v>
@@ -19984,7 +19987,7 @@
         <v>2.25</v>
       </c>
       <c r="AP92">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ92">
         <v>1.63</v>
@@ -20112,7 +20115,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>3.25</v>
@@ -20602,7 +20605,7 @@
         <v>1.8</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ95">
         <v>1.7</v>
@@ -21017,7 +21020,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ97">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR97">
         <v>1.73</v>
@@ -21142,7 +21145,7 @@
         <v>137</v>
       </c>
       <c r="P98" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21348,7 +21351,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q99">
         <v>2.65</v>
@@ -21554,7 +21557,7 @@
         <v>138</v>
       </c>
       <c r="P100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q100">
         <v>6.5</v>
@@ -21760,7 +21763,7 @@
         <v>139</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21841,7 +21844,7 @@
         <v>1</v>
       </c>
       <c r="AQ101">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR101">
         <v>1.45</v>
@@ -21966,7 +21969,7 @@
         <v>140</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>2.35</v>
@@ -22378,7 +22381,7 @@
         <v>89</v>
       </c>
       <c r="P104" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q104">
         <v>4.75</v>
@@ -23202,7 +23205,7 @@
         <v>120</v>
       </c>
       <c r="P108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q108">
         <v>4.33</v>
@@ -23614,7 +23617,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q110">
         <v>3.6</v>
@@ -23820,7 +23823,7 @@
         <v>89</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>5</v>
@@ -25262,7 +25265,7 @@
         <v>147</v>
       </c>
       <c r="P118" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25340,10 +25343,10 @@
         <v>1.17</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ118">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR118">
         <v>0.78</v>
@@ -25674,7 +25677,7 @@
         <v>148</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q120">
         <v>2.95</v>
@@ -26086,7 +26089,7 @@
         <v>89</v>
       </c>
       <c r="P122" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>6.25</v>
@@ -26164,7 +26167,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ122">
         <v>2.25</v>
@@ -26292,7 +26295,7 @@
         <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q123">
         <v>2.15</v>
@@ -27400,7 +27403,7 @@
         <v>1.43</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27609,7 +27612,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR129">
         <v>1.36</v>
@@ -27734,7 +27737,7 @@
         <v>152</v>
       </c>
       <c r="P130" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q130">
         <v>2.88</v>
@@ -27940,7 +27943,7 @@
         <v>153</v>
       </c>
       <c r="P131" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q131">
         <v>2.85</v>
@@ -28021,7 +28024,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28558,7 +28561,7 @@
         <v>155</v>
       </c>
       <c r="P134" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q134">
         <v>2.13</v>
@@ -29176,7 +29179,7 @@
         <v>158</v>
       </c>
       <c r="P137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q137">
         <v>2.8</v>
@@ -29382,7 +29385,7 @@
         <v>89</v>
       </c>
       <c r="P138" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q138">
         <v>8</v>
@@ -29588,7 +29591,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29666,7 +29669,7 @@
         <v>1.14</v>
       </c>
       <c r="AP139">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ139">
         <v>1.38</v>
@@ -29794,7 +29797,7 @@
         <v>89</v>
       </c>
       <c r="P140" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q140">
         <v>3.7</v>
@@ -30000,7 +30003,7 @@
         <v>159</v>
       </c>
       <c r="P141" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q141">
         <v>4.1</v>
@@ -30206,7 +30209,7 @@
         <v>160</v>
       </c>
       <c r="P142" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q142">
         <v>2.31</v>
@@ -30618,7 +30621,7 @@
         <v>162</v>
       </c>
       <c r="P144" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q144">
         <v>6.6</v>
@@ -30824,7 +30827,7 @@
         <v>163</v>
       </c>
       <c r="P145" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q145">
         <v>2.55</v>
@@ -31442,7 +31445,7 @@
         <v>165</v>
       </c>
       <c r="P148" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q148">
         <v>2.85</v>
@@ -31523,7 +31526,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ148">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR148">
         <v>1.06</v>
@@ -31648,7 +31651,7 @@
         <v>89</v>
       </c>
       <c r="P149" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q149">
         <v>5.5</v>
@@ -31726,7 +31729,7 @@
         <v>1.57</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ149">
         <v>1.75</v>
@@ -31854,7 +31857,7 @@
         <v>166</v>
       </c>
       <c r="P150" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q150">
         <v>2.55</v>
@@ -32266,7 +32269,7 @@
         <v>167</v>
       </c>
       <c r="P152" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q152">
         <v>2.21</v>
@@ -32884,7 +32887,7 @@
         <v>170</v>
       </c>
       <c r="P155" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q155">
         <v>4.31</v>
@@ -33168,7 +33171,7 @@
         <v>1.18</v>
       </c>
       <c r="AP156">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="AQ156">
         <v>1.11</v>
@@ -33502,7 +33505,7 @@
         <v>173</v>
       </c>
       <c r="P158" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q158">
         <v>4.51</v>
@@ -33914,7 +33917,7 @@
         <v>89</v>
       </c>
       <c r="P160" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q160">
         <v>4.28</v>
@@ -34120,7 +34123,7 @@
         <v>89</v>
       </c>
       <c r="P161" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q161">
         <v>3.1</v>
@@ -34201,7 +34204,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ161">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AR161">
         <v>1.28</v>
@@ -34277,6 +34280,418 @@
       </c>
       <c r="BP161">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7847672</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45757.45833333334</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162" t="s">
+        <v>84</v>
+      </c>
+      <c r="H162" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162" t="s">
+        <v>174</v>
+      </c>
+      <c r="P162" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q162">
+        <v>4.6</v>
+      </c>
+      <c r="R162">
+        <v>1.75</v>
+      </c>
+      <c r="S162">
+        <v>3.1</v>
+      </c>
+      <c r="T162">
+        <v>1.65</v>
+      </c>
+      <c r="U162">
+        <v>1.95</v>
+      </c>
+      <c r="V162">
+        <v>4.5</v>
+      </c>
+      <c r="W162">
+        <v>1.17</v>
+      </c>
+      <c r="X162">
+        <v>12</v>
+      </c>
+      <c r="Y162">
+        <v>1</v>
+      </c>
+      <c r="Z162">
+        <v>3.93</v>
+      </c>
+      <c r="AA162">
+        <v>2.73</v>
+      </c>
+      <c r="AB162">
+        <v>2.15</v>
+      </c>
+      <c r="AC162">
+        <v>1.18</v>
+      </c>
+      <c r="AD162">
+        <v>4.7</v>
+      </c>
+      <c r="AE162">
+        <v>1.7</v>
+      </c>
+      <c r="AF162">
+        <v>2</v>
+      </c>
+      <c r="AG162">
+        <v>3.3</v>
+      </c>
+      <c r="AH162">
+        <v>1.28</v>
+      </c>
+      <c r="AI162">
+        <v>2.5</v>
+      </c>
+      <c r="AJ162">
+        <v>1.48</v>
+      </c>
+      <c r="AK162">
+        <v>1.49</v>
+      </c>
+      <c r="AL162">
+        <v>1.36</v>
+      </c>
+      <c r="AM162">
+        <v>1.24</v>
+      </c>
+      <c r="AN162">
+        <v>0.71</v>
+      </c>
+      <c r="AO162">
+        <v>0.72</v>
+      </c>
+      <c r="AP162">
+        <v>0.83</v>
+      </c>
+      <c r="AQ162">
+        <v>0.68</v>
+      </c>
+      <c r="AR162">
+        <v>1</v>
+      </c>
+      <c r="AS162">
+        <v>1.12</v>
+      </c>
+      <c r="AT162">
+        <v>2.12</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>1</v>
+      </c>
+      <c r="AX162">
+        <v>5</v>
+      </c>
+      <c r="AY162">
+        <v>5</v>
+      </c>
+      <c r="AZ162">
+        <v>8</v>
+      </c>
+      <c r="BA162">
+        <v>3</v>
+      </c>
+      <c r="BB162">
+        <v>4</v>
+      </c>
+      <c r="BC162">
+        <v>7</v>
+      </c>
+      <c r="BD162">
+        <v>2.1</v>
+      </c>
+      <c r="BE162">
+        <v>6.05</v>
+      </c>
+      <c r="BF162">
+        <v>2.11</v>
+      </c>
+      <c r="BG162">
+        <v>1.42</v>
+      </c>
+      <c r="BH162">
+        <v>2.77</v>
+      </c>
+      <c r="BI162">
+        <v>1.7</v>
+      </c>
+      <c r="BJ162">
+        <v>2.13</v>
+      </c>
+      <c r="BK162">
+        <v>2.48</v>
+      </c>
+      <c r="BL162">
+        <v>1.65</v>
+      </c>
+      <c r="BM162">
+        <v>2.8</v>
+      </c>
+      <c r="BN162">
+        <v>1.38</v>
+      </c>
+      <c r="BO162">
+        <v>3.6</v>
+      </c>
+      <c r="BP162">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7847673</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45757.58333333334</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163" t="s">
+        <v>77</v>
+      </c>
+      <c r="H163" t="s">
+        <v>80</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
+        <v>89</v>
+      </c>
+      <c r="P163" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q163">
+        <v>3.95</v>
+      </c>
+      <c r="R163">
+        <v>1.59</v>
+      </c>
+      <c r="S163">
+        <v>4.33</v>
+      </c>
+      <c r="T163">
+        <v>1.96</v>
+      </c>
+      <c r="U163">
+        <v>1.85</v>
+      </c>
+      <c r="V163">
+        <v>5.2</v>
+      </c>
+      <c r="W163">
+        <v>1.11</v>
+      </c>
+      <c r="X163">
+        <v>10</v>
+      </c>
+      <c r="Y163">
+        <v>1</v>
+      </c>
+      <c r="Z163">
+        <v>2.96</v>
+      </c>
+      <c r="AA163">
+        <v>2.6</v>
+      </c>
+      <c r="AB163">
+        <v>2.95</v>
+      </c>
+      <c r="AC163">
+        <v>1.22</v>
+      </c>
+      <c r="AD163">
+        <v>3.8</v>
+      </c>
+      <c r="AE163">
+        <v>1.98</v>
+      </c>
+      <c r="AF163">
+        <v>1.79</v>
+      </c>
+      <c r="AG163">
+        <v>4</v>
+      </c>
+      <c r="AH163">
+        <v>1.2</v>
+      </c>
+      <c r="AI163">
+        <v>2.8</v>
+      </c>
+      <c r="AJ163">
+        <v>1.4</v>
+      </c>
+      <c r="AK163">
+        <v>1.3</v>
+      </c>
+      <c r="AL163">
+        <v>1.4</v>
+      </c>
+      <c r="AM163">
+        <v>1.36</v>
+      </c>
+      <c r="AN163">
+        <v>0.83</v>
+      </c>
+      <c r="AO163">
+        <v>1</v>
+      </c>
+      <c r="AP163">
+        <v>0.84</v>
+      </c>
+      <c r="AQ163">
+        <v>1</v>
+      </c>
+      <c r="AR163">
+        <v>0.99</v>
+      </c>
+      <c r="AS163">
+        <v>1.08</v>
+      </c>
+      <c r="AT163">
+        <v>2.07</v>
+      </c>
+      <c r="AU163">
+        <v>0</v>
+      </c>
+      <c r="AV163">
+        <v>2</v>
+      </c>
+      <c r="AW163">
+        <v>8</v>
+      </c>
+      <c r="AX163">
+        <v>3</v>
+      </c>
+      <c r="AY163">
+        <v>8</v>
+      </c>
+      <c r="AZ163">
+        <v>5</v>
+      </c>
+      <c r="BA163">
+        <v>3</v>
+      </c>
+      <c r="BB163">
+        <v>1</v>
+      </c>
+      <c r="BC163">
+        <v>4</v>
+      </c>
+      <c r="BD163">
+        <v>2.1</v>
+      </c>
+      <c r="BE163">
+        <v>6.8</v>
+      </c>
+      <c r="BF163">
+        <v>2.12</v>
+      </c>
+      <c r="BG163">
+        <v>1.56</v>
+      </c>
+      <c r="BH163">
+        <v>2.33</v>
+      </c>
+      <c r="BI163">
+        <v>1.95</v>
+      </c>
+      <c r="BJ163">
+        <v>1.79</v>
+      </c>
+      <c r="BK163">
+        <v>3.05</v>
+      </c>
+      <c r="BL163">
+        <v>1.42</v>
+      </c>
+      <c r="BM163">
+        <v>3.48</v>
+      </c>
+      <c r="BN163">
+        <v>1.25</v>
+      </c>
+      <c r="BO163">
+        <v>4.7</v>
+      </c>
+      <c r="BP163">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
